--- a/Database/MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D.xlsx
+++ b/Database/MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1182">
   <si>
     <t>MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D</t>
   </si>
@@ -3549,6 +3549,18 @@
   </si>
   <si>
     <t>Pembayaran tunjangan kinerja bulan Agustus tahun 2025 untuk 3 Pegawai</t>
+  </si>
+  <si>
+    <t>2025-08-04</t>
+  </si>
+  <si>
+    <t>'00332T</t>
+  </si>
+  <si>
+    <t>'259991310355508</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja barang berupa Honor Pengelola Keuangan Bulan Juli 2025 untuk 8 Pegawai sesuai Sk No B.1/BRPBATPP/KU.110/I/2025 tanggal 2 Januari 2025</t>
   </si>
 </sst>
 </file>
@@ -3891,7 +3903,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:L1148"/>
+  <dimension ref="A1:L1154"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -47446,6 +47458,234 @@
       </c>
       <c r="L1148">
         <v>16723413</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:12">
+      <c r="A1149">
+        <v>1146</v>
+      </c>
+      <c r="B1149">
+        <v>403829</v>
+      </c>
+      <c r="C1149" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1149" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E1149" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F1149" t="s">
+        <v>1180</v>
+      </c>
+      <c r="G1149" t="s">
+        <v>1181</v>
+      </c>
+      <c r="H1149" t="s">
+        <v>154</v>
+      </c>
+      <c r="I1149" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1149">
+        <v>1</v>
+      </c>
+      <c r="K1149">
+        <v>2550000</v>
+      </c>
+      <c r="L1149">
+        <v>2550000</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:12">
+      <c r="A1150">
+        <v>1147</v>
+      </c>
+      <c r="B1150">
+        <v>403829</v>
+      </c>
+      <c r="C1150" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1150" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E1150" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F1150" t="s">
+        <v>1180</v>
+      </c>
+      <c r="G1150" t="s">
+        <v>1181</v>
+      </c>
+      <c r="H1150" t="s">
+        <v>155</v>
+      </c>
+      <c r="I1150" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1150">
+        <v>1</v>
+      </c>
+      <c r="K1150">
+        <v>2480000</v>
+      </c>
+      <c r="L1150">
+        <v>2480000</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:12">
+      <c r="A1151">
+        <v>1148</v>
+      </c>
+      <c r="B1151">
+        <v>403829</v>
+      </c>
+      <c r="C1151" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1151" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E1151" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F1151" t="s">
+        <v>1180</v>
+      </c>
+      <c r="G1151" t="s">
+        <v>1181</v>
+      </c>
+      <c r="H1151" t="s">
+        <v>156</v>
+      </c>
+      <c r="I1151" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1151">
+        <v>1</v>
+      </c>
+      <c r="K1151">
+        <v>1230000</v>
+      </c>
+      <c r="L1151">
+        <v>1230000</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:12">
+      <c r="A1152">
+        <v>1149</v>
+      </c>
+      <c r="B1152">
+        <v>403829</v>
+      </c>
+      <c r="C1152" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1152" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E1152" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F1152" t="s">
+        <v>1180</v>
+      </c>
+      <c r="G1152" t="s">
+        <v>1181</v>
+      </c>
+      <c r="H1152" t="s">
+        <v>157</v>
+      </c>
+      <c r="I1152" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1152">
+        <v>1</v>
+      </c>
+      <c r="K1152">
+        <v>1070000</v>
+      </c>
+      <c r="L1152">
+        <v>1070000</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:12">
+      <c r="A1153">
+        <v>1150</v>
+      </c>
+      <c r="B1153">
+        <v>403829</v>
+      </c>
+      <c r="C1153" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1153" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E1153" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F1153" t="s">
+        <v>1180</v>
+      </c>
+      <c r="G1153" t="s">
+        <v>1181</v>
+      </c>
+      <c r="H1153" t="s">
+        <v>158</v>
+      </c>
+      <c r="I1153" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1153">
+        <v>1</v>
+      </c>
+      <c r="K1153">
+        <v>2400000</v>
+      </c>
+      <c r="L1153">
+        <v>2400000</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:12">
+      <c r="A1154">
+        <v>1151</v>
+      </c>
+      <c r="B1154">
+        <v>403829</v>
+      </c>
+      <c r="C1154" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1154" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E1154" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F1154" t="s">
+        <v>1180</v>
+      </c>
+      <c r="G1154" t="s">
+        <v>1181</v>
+      </c>
+      <c r="H1154" t="s">
+        <v>159</v>
+      </c>
+      <c r="I1154" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1154">
+        <v>1</v>
+      </c>
+      <c r="K1154">
+        <v>180000</v>
+      </c>
+      <c r="L1154">
+        <v>180000</v>
       </c>
     </row>
   </sheetData>

--- a/Database/MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D.xlsx
+++ b/Database/MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1189">
   <si>
     <t>MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D</t>
   </si>
@@ -3561,6 +3561,27 @@
   </si>
   <si>
     <t>Pembayaran Belanja barang berupa Honor Pengelola Keuangan Bulan Juli 2025 untuk 8 Pegawai sesuai Sk No B.1/BRPBATPP/KU.110/I/2025 tanggal 2 Januari 2025</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
+    <t>'00333T</t>
+  </si>
+  <si>
+    <t>'259991320204825</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang berupa Tagihan PDAM Bulan Juli 2025 Idpel No.1249-1046 An LEMB PERIKANAN DARAT</t>
+  </si>
+  <si>
+    <t>'00334T</t>
+  </si>
+  <si>
+    <t>'259991310397303</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang termin ke 7 Sesuai SPK No.2/BRPBATPP/PPK/PL.400/I/2025 Tanggal 2 Januari 2025 dan BAPP B.442 /BRPBATPP/PPK/PL.400/VII/2025 31 Juli 2025</t>
   </si>
 </sst>
 </file>
@@ -3903,7 +3924,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:L1154"/>
+  <dimension ref="A1:L1156"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -47686,6 +47707,82 @@
       </c>
       <c r="L1154">
         <v>180000</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:12">
+      <c r="A1155">
+        <v>1152</v>
+      </c>
+      <c r="B1155">
+        <v>403829</v>
+      </c>
+      <c r="C1155" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1155" t="s">
+        <v>1182</v>
+      </c>
+      <c r="E1155" t="s">
+        <v>1183</v>
+      </c>
+      <c r="F1155" t="s">
+        <v>1184</v>
+      </c>
+      <c r="G1155" t="s">
+        <v>1185</v>
+      </c>
+      <c r="H1155" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1155" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1155">
+        <v>1</v>
+      </c>
+      <c r="K1155">
+        <v>647800</v>
+      </c>
+      <c r="L1155">
+        <v>647800</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:12">
+      <c r="A1156">
+        <v>1153</v>
+      </c>
+      <c r="B1156">
+        <v>403829</v>
+      </c>
+      <c r="C1156" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1156" t="s">
+        <v>1182</v>
+      </c>
+      <c r="E1156" t="s">
+        <v>1186</v>
+      </c>
+      <c r="F1156" t="s">
+        <v>1187</v>
+      </c>
+      <c r="G1156" t="s">
+        <v>1188</v>
+      </c>
+      <c r="H1156" t="s">
+        <v>203</v>
+      </c>
+      <c r="I1156" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1156">
+        <v>1</v>
+      </c>
+      <c r="K1156">
+        <v>184486500</v>
+      </c>
+      <c r="L1156">
+        <v>184486500</v>
       </c>
     </row>
   </sheetData>

--- a/Database/MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D.xlsx
+++ b/Database/MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1249">
   <si>
     <t>MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D</t>
   </si>
@@ -3582,6 +3582,186 @@
   </si>
   <si>
     <t>Pembayaran Belanja Barang termin ke 7 Sesuai SPK No.2/BRPBATPP/PPK/PL.400/I/2025 Tanggal 2 Januari 2025 dan BAPP B.442 /BRPBATPP/PPK/PL.400/VII/2025 31 Juli 2025</t>
+  </si>
+  <si>
+    <t>2025-08-15</t>
+  </si>
+  <si>
+    <t>'00341T</t>
+  </si>
+  <si>
+    <t>'259991320221348</t>
+  </si>
+  <si>
+    <t>Pembayaran belanja barang berupa tagihan listrik bulan Agustus 2025 untuk 10 invoice</t>
+  </si>
+  <si>
+    <t>'00342T</t>
+  </si>
+  <si>
+    <t>'259991310426308</t>
+  </si>
+  <si>
+    <t>Pembayaran belanja barang berupa tagihan telepon bulan Agustus 2025 untuk 12 invoice</t>
+  </si>
+  <si>
+    <t>2025-08-13</t>
+  </si>
+  <si>
+    <t>'00344T</t>
+  </si>
+  <si>
+    <t>'259991320224231</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang berupa Tagihan Internet Bulan Juli 2025 Idpel no.GO18A106  An Balai Riset Perikanan Budidaya Air Tawar dan Penyuluhan Perikanan</t>
+  </si>
+  <si>
+    <t>2025-08-12</t>
+  </si>
+  <si>
+    <t>'00345T</t>
+  </si>
+  <si>
+    <t>'259991310439898</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Juli 2025 untuk 50 Pegawai</t>
+  </si>
+  <si>
+    <t>'00346T</t>
+  </si>
+  <si>
+    <t>'259991330140597</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Juli 2025 untuk 62 Pegawai</t>
+  </si>
+  <si>
+    <t>'00347T</t>
+  </si>
+  <si>
+    <t>'259991310439899</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Juli 2025 untuk 34 Pegawai</t>
+  </si>
+  <si>
+    <t>'00348T</t>
+  </si>
+  <si>
+    <t>'259991330140598</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Juli 2025 untuk 22 Pegawai</t>
+  </si>
+  <si>
+    <t>'00349T</t>
+  </si>
+  <si>
+    <t>'259991310439896</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Juli 2025 untuk 36 Pegawai</t>
+  </si>
+  <si>
+    <t>'00350T</t>
+  </si>
+  <si>
+    <t>'259991310439897</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Juli 2025 untuk 133 Pegawai</t>
+  </si>
+  <si>
+    <t>'00351T</t>
+  </si>
+  <si>
+    <t>'259991330140596</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan juli 2025 untuk 172 Pegawai</t>
+  </si>
+  <si>
+    <t>'00352T</t>
+  </si>
+  <si>
+    <t>'259991305093125</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Juli 2025 untuk 4 Pegawai</t>
+  </si>
+  <si>
+    <t>'00353T</t>
+  </si>
+  <si>
+    <t>'259991310447652</t>
+  </si>
+  <si>
+    <t>'00355T</t>
+  </si>
+  <si>
+    <t>'259991310466419</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa kekurangan Gaji Bulan Juli 2025 untuk 2 pegawai/5 jiwa</t>
+  </si>
+  <si>
+    <t>'00356T</t>
+  </si>
+  <si>
+    <t>'259991330149878</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa kekurangan Gaji Bulan Juli 2025 untuk 3 Pegawai/7 Jiwa</t>
+  </si>
+  <si>
+    <t>2025-08-19</t>
+  </si>
+  <si>
+    <t>'00357T</t>
+  </si>
+  <si>
+    <t>'259991310471404</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan JULI tahun 2025 untuk 134 Pegawai</t>
+  </si>
+  <si>
+    <t>'00359T</t>
+  </si>
+  <si>
+    <t>'259991310471405</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Juli tahun 2025 untuk 50 Pegawai</t>
+  </si>
+  <si>
+    <t>'00360T</t>
+  </si>
+  <si>
+    <t>'259991330150984</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Juli tahun 2025 untuk 63 Pegawai</t>
+  </si>
+  <si>
+    <t>'00361T</t>
+  </si>
+  <si>
+    <t>'259991310471406</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Juli tahun 2025 untuk 35 Pegawai</t>
+  </si>
+  <si>
+    <t>'00362T</t>
+  </si>
+  <si>
+    <t>'259991330150985</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Juli tahun 2025 untuk 23 Pegawai</t>
   </si>
 </sst>
 </file>
@@ -3924,7 +4104,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:L1156"/>
+  <dimension ref="A1:L1205"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -47783,6 +47963,1868 @@
       </c>
       <c r="L1156">
         <v>184486500</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:12">
+      <c r="A1157">
+        <v>1154</v>
+      </c>
+      <c r="B1157">
+        <v>403829</v>
+      </c>
+      <c r="C1157" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1157" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E1157" t="s">
+        <v>1190</v>
+      </c>
+      <c r="F1157" t="s">
+        <v>1191</v>
+      </c>
+      <c r="G1157" t="s">
+        <v>1192</v>
+      </c>
+      <c r="H1157" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1157" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1157">
+        <v>1</v>
+      </c>
+      <c r="K1157">
+        <v>41758847</v>
+      </c>
+      <c r="L1157">
+        <v>41758847</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:12">
+      <c r="A1158">
+        <v>1155</v>
+      </c>
+      <c r="B1158">
+        <v>403829</v>
+      </c>
+      <c r="C1158" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1158" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E1158" t="s">
+        <v>1193</v>
+      </c>
+      <c r="F1158" t="s">
+        <v>1194</v>
+      </c>
+      <c r="G1158" t="s">
+        <v>1195</v>
+      </c>
+      <c r="H1158" t="s">
+        <v>83</v>
+      </c>
+      <c r="I1158" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1158">
+        <v>1</v>
+      </c>
+      <c r="K1158">
+        <v>263514</v>
+      </c>
+      <c r="L1158">
+        <v>263514</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:12">
+      <c r="A1159">
+        <v>1156</v>
+      </c>
+      <c r="B1159">
+        <v>403829</v>
+      </c>
+      <c r="C1159" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1159" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E1159" t="s">
+        <v>1193</v>
+      </c>
+      <c r="F1159" t="s">
+        <v>1194</v>
+      </c>
+      <c r="G1159" t="s">
+        <v>1195</v>
+      </c>
+      <c r="H1159" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1159" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1159">
+        <v>1</v>
+      </c>
+      <c r="K1159">
+        <v>2580750</v>
+      </c>
+      <c r="L1159">
+        <v>2580750</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:12">
+      <c r="A1160">
+        <v>1157</v>
+      </c>
+      <c r="B1160">
+        <v>403829</v>
+      </c>
+      <c r="C1160" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1160" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E1160" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F1160" t="s">
+        <v>1198</v>
+      </c>
+      <c r="G1160" t="s">
+        <v>1199</v>
+      </c>
+      <c r="H1160" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1160" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1160">
+        <v>1</v>
+      </c>
+      <c r="K1160">
+        <v>6670000</v>
+      </c>
+      <c r="L1160">
+        <v>6670000</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:12">
+      <c r="A1161">
+        <v>1158</v>
+      </c>
+      <c r="B1161">
+        <v>403829</v>
+      </c>
+      <c r="C1161" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1161" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E1161" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F1161" t="s">
+        <v>1202</v>
+      </c>
+      <c r="G1161" t="s">
+        <v>1203</v>
+      </c>
+      <c r="H1161" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1161" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1161">
+        <v>1</v>
+      </c>
+      <c r="K1161">
+        <v>7665000</v>
+      </c>
+      <c r="L1161">
+        <v>7665000</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:12">
+      <c r="A1162">
+        <v>1159</v>
+      </c>
+      <c r="B1162">
+        <v>403829</v>
+      </c>
+      <c r="C1162" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1162" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E1162" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F1162" t="s">
+        <v>1202</v>
+      </c>
+      <c r="G1162" t="s">
+        <v>1203</v>
+      </c>
+      <c r="H1162" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1162" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1162">
+        <v>1</v>
+      </c>
+      <c r="K1162">
+        <v>32967000</v>
+      </c>
+      <c r="L1162">
+        <v>32967000</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:12">
+      <c r="A1163">
+        <v>1160</v>
+      </c>
+      <c r="B1163">
+        <v>403829</v>
+      </c>
+      <c r="C1163" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1163" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E1163" t="s">
+        <v>1204</v>
+      </c>
+      <c r="F1163" t="s">
+        <v>1205</v>
+      </c>
+      <c r="G1163" t="s">
+        <v>1206</v>
+      </c>
+      <c r="H1163" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1163" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1163">
+        <v>1</v>
+      </c>
+      <c r="K1163">
+        <v>1610000</v>
+      </c>
+      <c r="L1163">
+        <v>1610000</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:12">
+      <c r="A1164">
+        <v>1161</v>
+      </c>
+      <c r="B1164">
+        <v>403829</v>
+      </c>
+      <c r="C1164" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1164" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E1164" t="s">
+        <v>1204</v>
+      </c>
+      <c r="F1164" t="s">
+        <v>1205</v>
+      </c>
+      <c r="G1164" t="s">
+        <v>1206</v>
+      </c>
+      <c r="H1164" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1164" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1164">
+        <v>1</v>
+      </c>
+      <c r="K1164">
+        <v>50320000</v>
+      </c>
+      <c r="L1164">
+        <v>50320000</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:12">
+      <c r="A1165">
+        <v>1162</v>
+      </c>
+      <c r="B1165">
+        <v>403829</v>
+      </c>
+      <c r="C1165" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1165" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E1165" t="s">
+        <v>1207</v>
+      </c>
+      <c r="F1165" t="s">
+        <v>1208</v>
+      </c>
+      <c r="G1165" t="s">
+        <v>1209</v>
+      </c>
+      <c r="H1165" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1165" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1165">
+        <v>1</v>
+      </c>
+      <c r="K1165">
+        <v>2415000</v>
+      </c>
+      <c r="L1165">
+        <v>2415000</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:12">
+      <c r="A1166">
+        <v>1163</v>
+      </c>
+      <c r="B1166">
+        <v>403829</v>
+      </c>
+      <c r="C1166" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1166" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E1166" t="s">
+        <v>1207</v>
+      </c>
+      <c r="F1166" t="s">
+        <v>1208</v>
+      </c>
+      <c r="G1166" t="s">
+        <v>1209</v>
+      </c>
+      <c r="H1166" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1166" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1166">
+        <v>1</v>
+      </c>
+      <c r="K1166">
+        <v>25493000</v>
+      </c>
+      <c r="L1166">
+        <v>25493000</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:12">
+      <c r="A1167">
+        <v>1164</v>
+      </c>
+      <c r="B1167">
+        <v>403829</v>
+      </c>
+      <c r="C1167" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1167" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E1167" t="s">
+        <v>1210</v>
+      </c>
+      <c r="F1167" t="s">
+        <v>1211</v>
+      </c>
+      <c r="G1167" t="s">
+        <v>1212</v>
+      </c>
+      <c r="H1167" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1167" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1167">
+        <v>1</v>
+      </c>
+      <c r="K1167">
+        <v>1610000</v>
+      </c>
+      <c r="L1167">
+        <v>1610000</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:12">
+      <c r="A1168">
+        <v>1165</v>
+      </c>
+      <c r="B1168">
+        <v>403829</v>
+      </c>
+      <c r="C1168" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1168" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E1168" t="s">
+        <v>1210</v>
+      </c>
+      <c r="F1168" t="s">
+        <v>1211</v>
+      </c>
+      <c r="G1168" t="s">
+        <v>1212</v>
+      </c>
+      <c r="H1168" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1168" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1168">
+        <v>1</v>
+      </c>
+      <c r="K1168">
+        <v>16798000</v>
+      </c>
+      <c r="L1168">
+        <v>16798000</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:12">
+      <c r="A1169">
+        <v>1166</v>
+      </c>
+      <c r="B1169">
+        <v>403829</v>
+      </c>
+      <c r="C1169" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1169" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E1169" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F1169" t="s">
+        <v>1214</v>
+      </c>
+      <c r="G1169" t="s">
+        <v>1215</v>
+      </c>
+      <c r="H1169" t="s">
+        <v>241</v>
+      </c>
+      <c r="I1169" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1169">
+        <v>1</v>
+      </c>
+      <c r="K1169">
+        <v>1610000</v>
+      </c>
+      <c r="L1169">
+        <v>1610000</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:12">
+      <c r="A1170">
+        <v>1167</v>
+      </c>
+      <c r="B1170">
+        <v>403829</v>
+      </c>
+      <c r="C1170" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1170" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E1170" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F1170" t="s">
+        <v>1214</v>
+      </c>
+      <c r="G1170" t="s">
+        <v>1215</v>
+      </c>
+      <c r="H1170" t="s">
+        <v>149</v>
+      </c>
+      <c r="I1170" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1170">
+        <v>1</v>
+      </c>
+      <c r="K1170">
+        <v>24642000</v>
+      </c>
+      <c r="L1170">
+        <v>24642000</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:12">
+      <c r="A1171">
+        <v>1168</v>
+      </c>
+      <c r="B1171">
+        <v>403829</v>
+      </c>
+      <c r="C1171" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1171" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E1171" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F1171" t="s">
+        <v>1214</v>
+      </c>
+      <c r="G1171" t="s">
+        <v>1215</v>
+      </c>
+      <c r="H1171" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1171" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1171">
+        <v>1</v>
+      </c>
+      <c r="K1171">
+        <v>3321000</v>
+      </c>
+      <c r="L1171">
+        <v>3321000</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:12">
+      <c r="A1172">
+        <v>1169</v>
+      </c>
+      <c r="B1172">
+        <v>403829</v>
+      </c>
+      <c r="C1172" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1172" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E1172" t="s">
+        <v>1216</v>
+      </c>
+      <c r="F1172" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G1172" t="s">
+        <v>1218</v>
+      </c>
+      <c r="H1172" t="s">
+        <v>266</v>
+      </c>
+      <c r="I1172" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1172">
+        <v>1</v>
+      </c>
+      <c r="K1172">
+        <v>11515000</v>
+      </c>
+      <c r="L1172">
+        <v>11515000</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:12">
+      <c r="A1173">
+        <v>1170</v>
+      </c>
+      <c r="B1173">
+        <v>403829</v>
+      </c>
+      <c r="C1173" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1173" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E1173" t="s">
+        <v>1216</v>
+      </c>
+      <c r="F1173" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G1173" t="s">
+        <v>1218</v>
+      </c>
+      <c r="H1173" t="s">
+        <v>267</v>
+      </c>
+      <c r="I1173" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1173">
+        <v>1</v>
+      </c>
+      <c r="K1173">
+        <v>74962000</v>
+      </c>
+      <c r="L1173">
+        <v>74962000</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:12">
+      <c r="A1174">
+        <v>1171</v>
+      </c>
+      <c r="B1174">
+        <v>403829</v>
+      </c>
+      <c r="C1174" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1174" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E1174" t="s">
+        <v>1216</v>
+      </c>
+      <c r="F1174" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G1174" t="s">
+        <v>1218</v>
+      </c>
+      <c r="H1174" t="s">
+        <v>268</v>
+      </c>
+      <c r="I1174" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1174">
+        <v>1</v>
+      </c>
+      <c r="K1174">
+        <v>25256000</v>
+      </c>
+      <c r="L1174">
+        <v>25256000</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:12">
+      <c r="A1175">
+        <v>1172</v>
+      </c>
+      <c r="B1175">
+        <v>403829</v>
+      </c>
+      <c r="C1175" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1175" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E1175" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F1175" t="s">
+        <v>1220</v>
+      </c>
+      <c r="G1175" t="s">
+        <v>1221</v>
+      </c>
+      <c r="H1175" t="s">
+        <v>266</v>
+      </c>
+      <c r="I1175" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1175">
+        <v>1</v>
+      </c>
+      <c r="K1175">
+        <v>12040000</v>
+      </c>
+      <c r="L1175">
+        <v>12040000</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:12">
+      <c r="A1176">
+        <v>1173</v>
+      </c>
+      <c r="B1176">
+        <v>403829</v>
+      </c>
+      <c r="C1176" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1176" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E1176" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F1176" t="s">
+        <v>1220</v>
+      </c>
+      <c r="G1176" t="s">
+        <v>1221</v>
+      </c>
+      <c r="H1176" t="s">
+        <v>267</v>
+      </c>
+      <c r="I1176" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1176">
+        <v>1</v>
+      </c>
+      <c r="K1176">
+        <v>109076000</v>
+      </c>
+      <c r="L1176">
+        <v>109076000</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:12">
+      <c r="A1177">
+        <v>1174</v>
+      </c>
+      <c r="B1177">
+        <v>403829</v>
+      </c>
+      <c r="C1177" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1177" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E1177" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F1177" t="s">
+        <v>1220</v>
+      </c>
+      <c r="G1177" t="s">
+        <v>1221</v>
+      </c>
+      <c r="H1177" t="s">
+        <v>268</v>
+      </c>
+      <c r="I1177" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1177">
+        <v>1</v>
+      </c>
+      <c r="K1177">
+        <v>24272000</v>
+      </c>
+      <c r="L1177">
+        <v>24272000</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:12">
+      <c r="A1178">
+        <v>1175</v>
+      </c>
+      <c r="B1178">
+        <v>403829</v>
+      </c>
+      <c r="C1178" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1178" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E1178" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F1178" t="s">
+        <v>1223</v>
+      </c>
+      <c r="G1178" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H1178" t="s">
+        <v>149</v>
+      </c>
+      <c r="I1178" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1178">
+        <v>1</v>
+      </c>
+      <c r="K1178">
+        <v>2331000</v>
+      </c>
+      <c r="L1178">
+        <v>2331000</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:12">
+      <c r="A1179">
+        <v>1176</v>
+      </c>
+      <c r="B1179">
+        <v>403829</v>
+      </c>
+      <c r="C1179" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1179" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E1179" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F1179" t="s">
+        <v>1223</v>
+      </c>
+      <c r="G1179" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H1179" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1179" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1179">
+        <v>1</v>
+      </c>
+      <c r="K1179">
+        <v>861000</v>
+      </c>
+      <c r="L1179">
+        <v>861000</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:12">
+      <c r="A1180">
+        <v>1177</v>
+      </c>
+      <c r="B1180">
+        <v>403829</v>
+      </c>
+      <c r="C1180" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1180" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E1180" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F1180" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G1180" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1180" t="s">
+        <v>173</v>
+      </c>
+      <c r="I1180" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1180">
+        <v>1</v>
+      </c>
+      <c r="K1180">
+        <v>2017000</v>
+      </c>
+      <c r="L1180">
+        <v>2017000</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:12">
+      <c r="A1181">
+        <v>1178</v>
+      </c>
+      <c r="B1181">
+        <v>403829</v>
+      </c>
+      <c r="C1181" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1181" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E1181" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F1181" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G1181" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1181" t="s">
+        <v>174</v>
+      </c>
+      <c r="I1181" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1181">
+        <v>1</v>
+      </c>
+      <c r="K1181">
+        <v>222500</v>
+      </c>
+      <c r="L1181">
+        <v>222500</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:12">
+      <c r="A1182">
+        <v>1179</v>
+      </c>
+      <c r="B1182">
+        <v>403829</v>
+      </c>
+      <c r="C1182" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1182" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E1182" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F1182" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G1182" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1182" t="s">
+        <v>175</v>
+      </c>
+      <c r="I1182" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1182">
+        <v>1</v>
+      </c>
+      <c r="K1182">
+        <v>4279000</v>
+      </c>
+      <c r="L1182">
+        <v>4279000</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:12">
+      <c r="A1183">
+        <v>1180</v>
+      </c>
+      <c r="B1183">
+        <v>403829</v>
+      </c>
+      <c r="C1183" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1183" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E1183" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F1183" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G1183" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1183" t="s">
+        <v>176</v>
+      </c>
+      <c r="I1183" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1183">
+        <v>1</v>
+      </c>
+      <c r="K1183">
+        <v>25625000</v>
+      </c>
+      <c r="L1183">
+        <v>25625000</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:12">
+      <c r="A1184">
+        <v>1181</v>
+      </c>
+      <c r="B1184">
+        <v>403829</v>
+      </c>
+      <c r="C1184" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1184" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E1184" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F1184" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G1184" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1184" t="s">
+        <v>1040</v>
+      </c>
+      <c r="I1184" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1184">
+        <v>1</v>
+      </c>
+      <c r="K1184">
+        <v>9115000</v>
+      </c>
+      <c r="L1184">
+        <v>9115000</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:12">
+      <c r="A1185">
+        <v>1182</v>
+      </c>
+      <c r="B1185">
+        <v>403829</v>
+      </c>
+      <c r="C1185" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1185" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E1185" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F1185" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G1185" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1185" t="s">
+        <v>177</v>
+      </c>
+      <c r="I1185" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1185">
+        <v>1</v>
+      </c>
+      <c r="K1185">
+        <v>41321696</v>
+      </c>
+      <c r="L1185">
+        <v>41321696</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:12">
+      <c r="A1186">
+        <v>1183</v>
+      </c>
+      <c r="B1186">
+        <v>403829</v>
+      </c>
+      <c r="C1186" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1186" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E1186" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F1186" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G1186" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1186" t="s">
+        <v>178</v>
+      </c>
+      <c r="I1186" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1186">
+        <v>1</v>
+      </c>
+      <c r="K1186">
+        <v>9468528</v>
+      </c>
+      <c r="L1186">
+        <v>9468528</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:12">
+      <c r="A1187">
+        <v>1184</v>
+      </c>
+      <c r="B1187">
+        <v>403829</v>
+      </c>
+      <c r="C1187" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1187" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E1187" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F1187" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G1187" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1187" t="s">
+        <v>179</v>
+      </c>
+      <c r="I1187" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1187">
+        <v>1</v>
+      </c>
+      <c r="K1187">
+        <v>13729784</v>
+      </c>
+      <c r="L1187">
+        <v>13729784</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:12">
+      <c r="A1188">
+        <v>1185</v>
+      </c>
+      <c r="B1188">
+        <v>403829</v>
+      </c>
+      <c r="C1188" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1188" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E1188" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F1188" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G1188" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1188" t="s">
+        <v>180</v>
+      </c>
+      <c r="I1188" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1188">
+        <v>1</v>
+      </c>
+      <c r="K1188">
+        <v>4629928</v>
+      </c>
+      <c r="L1188">
+        <v>4629928</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:12">
+      <c r="A1189">
+        <v>1186</v>
+      </c>
+      <c r="B1189">
+        <v>403829</v>
+      </c>
+      <c r="C1189" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1189" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E1189" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F1189" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G1189" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1189" t="s">
+        <v>181</v>
+      </c>
+      <c r="I1189" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1189">
+        <v>1</v>
+      </c>
+      <c r="K1189">
+        <v>750000</v>
+      </c>
+      <c r="L1189">
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:12">
+      <c r="A1190">
+        <v>1187</v>
+      </c>
+      <c r="B1190">
+        <v>403829</v>
+      </c>
+      <c r="C1190" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1190" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E1190" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F1190" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G1190" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1190" t="s">
+        <v>185</v>
+      </c>
+      <c r="I1190" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1190">
+        <v>1</v>
+      </c>
+      <c r="K1190">
+        <v>4845000</v>
+      </c>
+      <c r="L1190">
+        <v>4845000</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:12">
+      <c r="A1191">
+        <v>1188</v>
+      </c>
+      <c r="B1191">
+        <v>403829</v>
+      </c>
+      <c r="C1191" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1191" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E1191" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F1191" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G1191" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1191" t="s">
+        <v>186</v>
+      </c>
+      <c r="I1191" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1191">
+        <v>1</v>
+      </c>
+      <c r="K1191">
+        <v>1225000</v>
+      </c>
+      <c r="L1191">
+        <v>1225000</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:12">
+      <c r="A1192">
+        <v>1189</v>
+      </c>
+      <c r="B1192">
+        <v>403829</v>
+      </c>
+      <c r="C1192" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1192" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E1192" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F1192" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G1192" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1192" t="s">
+        <v>187</v>
+      </c>
+      <c r="I1192" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1192">
+        <v>1</v>
+      </c>
+      <c r="K1192">
+        <v>233875</v>
+      </c>
+      <c r="L1192">
+        <v>233875</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:12">
+      <c r="A1193">
+        <v>1190</v>
+      </c>
+      <c r="B1193">
+        <v>403829</v>
+      </c>
+      <c r="C1193" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1193" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E1193" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F1193" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G1193" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1193" t="s">
+        <v>189</v>
+      </c>
+      <c r="I1193" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1193">
+        <v>1</v>
+      </c>
+      <c r="K1193">
+        <v>385700</v>
+      </c>
+      <c r="L1193">
+        <v>385700</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:12">
+      <c r="A1194">
+        <v>1191</v>
+      </c>
+      <c r="B1194">
+        <v>403829</v>
+      </c>
+      <c r="C1194" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1194" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E1194" t="s">
+        <v>1227</v>
+      </c>
+      <c r="F1194" t="s">
+        <v>1228</v>
+      </c>
+      <c r="G1194" t="s">
+        <v>1229</v>
+      </c>
+      <c r="H1194" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1194" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1194">
+        <v>1</v>
+      </c>
+      <c r="K1194">
+        <v>461900</v>
+      </c>
+      <c r="L1194">
+        <v>461900</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:12">
+      <c r="A1195">
+        <v>1192</v>
+      </c>
+      <c r="B1195">
+        <v>403829</v>
+      </c>
+      <c r="C1195" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1195" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E1195" t="s">
+        <v>1227</v>
+      </c>
+      <c r="F1195" t="s">
+        <v>1228</v>
+      </c>
+      <c r="G1195" t="s">
+        <v>1229</v>
+      </c>
+      <c r="H1195" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1195" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1195">
+        <v>1</v>
+      </c>
+      <c r="K1195">
+        <v>4</v>
+      </c>
+      <c r="L1195">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:12">
+      <c r="A1196">
+        <v>1193</v>
+      </c>
+      <c r="B1196">
+        <v>403829</v>
+      </c>
+      <c r="C1196" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1196" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E1196" t="s">
+        <v>1227</v>
+      </c>
+      <c r="F1196" t="s">
+        <v>1228</v>
+      </c>
+      <c r="G1196" t="s">
+        <v>1229</v>
+      </c>
+      <c r="H1196" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1196" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1196">
+        <v>1</v>
+      </c>
+      <c r="K1196">
+        <v>23810</v>
+      </c>
+      <c r="L1196">
+        <v>23810</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:12">
+      <c r="A1197">
+        <v>1194</v>
+      </c>
+      <c r="B1197">
+        <v>403829</v>
+      </c>
+      <c r="C1197" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1197" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E1197" t="s">
+        <v>1227</v>
+      </c>
+      <c r="F1197" t="s">
+        <v>1228</v>
+      </c>
+      <c r="G1197" t="s">
+        <v>1229</v>
+      </c>
+      <c r="H1197" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1197" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1197">
+        <v>1</v>
+      </c>
+      <c r="K1197">
+        <v>9524</v>
+      </c>
+      <c r="L1197">
+        <v>9524</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:12">
+      <c r="A1198">
+        <v>1195</v>
+      </c>
+      <c r="B1198">
+        <v>403829</v>
+      </c>
+      <c r="C1198" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1198" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E1198" t="s">
+        <v>1230</v>
+      </c>
+      <c r="F1198" t="s">
+        <v>1231</v>
+      </c>
+      <c r="G1198" t="s">
+        <v>1232</v>
+      </c>
+      <c r="H1198" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1198" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1198">
+        <v>1</v>
+      </c>
+      <c r="K1198">
+        <v>685700</v>
+      </c>
+      <c r="L1198">
+        <v>685700</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:12">
+      <c r="A1199">
+        <v>1196</v>
+      </c>
+      <c r="B1199">
+        <v>403829</v>
+      </c>
+      <c r="C1199" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1199" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E1199" t="s">
+        <v>1230</v>
+      </c>
+      <c r="F1199" t="s">
+        <v>1231</v>
+      </c>
+      <c r="G1199" t="s">
+        <v>1232</v>
+      </c>
+      <c r="H1199" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1199" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1199">
+        <v>1</v>
+      </c>
+      <c r="K1199">
+        <v>68570</v>
+      </c>
+      <c r="L1199">
+        <v>68570</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:12">
+      <c r="A1200">
+        <v>1197</v>
+      </c>
+      <c r="B1200">
+        <v>403829</v>
+      </c>
+      <c r="C1200" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1200" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E1200" t="s">
+        <v>1230</v>
+      </c>
+      <c r="F1200" t="s">
+        <v>1231</v>
+      </c>
+      <c r="G1200" t="s">
+        <v>1232</v>
+      </c>
+      <c r="H1200" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1200" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1200">
+        <v>1</v>
+      </c>
+      <c r="K1200">
+        <v>4762</v>
+      </c>
+      <c r="L1200">
+        <v>4762</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:12">
+      <c r="A1201">
+        <v>1198</v>
+      </c>
+      <c r="B1201">
+        <v>403829</v>
+      </c>
+      <c r="C1201" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1201" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E1201" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F1201" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G1201" t="s">
+        <v>1236</v>
+      </c>
+      <c r="H1201" t="s">
+        <v>272</v>
+      </c>
+      <c r="I1201" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1201">
+        <v>1</v>
+      </c>
+      <c r="K1201">
+        <v>878387055</v>
+      </c>
+      <c r="L1201">
+        <v>878387055</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:12">
+      <c r="A1202">
+        <v>1199</v>
+      </c>
+      <c r="B1202">
+        <v>403829</v>
+      </c>
+      <c r="C1202" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1202" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E1202" t="s">
+        <v>1237</v>
+      </c>
+      <c r="F1202" t="s">
+        <v>1238</v>
+      </c>
+      <c r="G1202" t="s">
+        <v>1239</v>
+      </c>
+      <c r="H1202" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1202" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1202">
+        <v>1</v>
+      </c>
+      <c r="K1202">
+        <v>218758166</v>
+      </c>
+      <c r="L1202">
+        <v>218758166</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:12">
+      <c r="A1203">
+        <v>1200</v>
+      </c>
+      <c r="B1203">
+        <v>403829</v>
+      </c>
+      <c r="C1203" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1203" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E1203" t="s">
+        <v>1240</v>
+      </c>
+      <c r="F1203" t="s">
+        <v>1241</v>
+      </c>
+      <c r="G1203" t="s">
+        <v>1242</v>
+      </c>
+      <c r="H1203" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1203" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1203">
+        <v>1</v>
+      </c>
+      <c r="K1203">
+        <v>286896591</v>
+      </c>
+      <c r="L1203">
+        <v>286896591</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:12">
+      <c r="A1204">
+        <v>1201</v>
+      </c>
+      <c r="B1204">
+        <v>403829</v>
+      </c>
+      <c r="C1204" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1204" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E1204" t="s">
+        <v>1243</v>
+      </c>
+      <c r="F1204" t="s">
+        <v>1244</v>
+      </c>
+      <c r="G1204" t="s">
+        <v>1245</v>
+      </c>
+      <c r="H1204" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1204" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1204">
+        <v>1</v>
+      </c>
+      <c r="K1204">
+        <v>157239652</v>
+      </c>
+      <c r="L1204">
+        <v>157239652</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:12">
+      <c r="A1205">
+        <v>1202</v>
+      </c>
+      <c r="B1205">
+        <v>403829</v>
+      </c>
+      <c r="C1205" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1205" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E1205" t="s">
+        <v>1246</v>
+      </c>
+      <c r="F1205" t="s">
+        <v>1247</v>
+      </c>
+      <c r="G1205" t="s">
+        <v>1248</v>
+      </c>
+      <c r="H1205" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1205" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1205">
+        <v>1</v>
+      </c>
+      <c r="K1205">
+        <v>102124944</v>
+      </c>
+      <c r="L1205">
+        <v>102124944</v>
       </c>
     </row>
   </sheetData>

--- a/Database/MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D.xlsx
+++ b/Database/MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1353">
   <si>
     <t>MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D</t>
   </si>
@@ -3584,6 +3584,63 @@
     <t>Pembayaran Belanja Barang termin ke 7 Sesuai SPK No.2/BRPBATPP/PPK/PL.400/I/2025 Tanggal 2 Januari 2025 dan BAPP B.442 /BRPBATPP/PPK/PL.400/VII/2025 31 Juli 2025</t>
   </si>
   <si>
+    <t>2025-09-01</t>
+  </si>
+  <si>
+    <t>'00335T</t>
+  </si>
+  <si>
+    <t>'259991530041993</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan September 2025 untuk 50 Pegawai/125 Jiwa</t>
+  </si>
+  <si>
+    <t>'00336T</t>
+  </si>
+  <si>
+    <t>'259991531008985</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan September 2025  untuk 63 Pegawai/181 jiwa</t>
+  </si>
+  <si>
+    <t>'00337T</t>
+  </si>
+  <si>
+    <t>'259991530041994</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan September 2025 untuk 35 Pegawai/101 Jiwa</t>
+  </si>
+  <si>
+    <t>'00338T</t>
+  </si>
+  <si>
+    <t>'259991531008986</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan September 2025 untuk 23 Pegawai/52 jiwa</t>
+  </si>
+  <si>
+    <t>'00339T</t>
+  </si>
+  <si>
+    <t>'259991531008984</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan September 2025 untuk 170 Pegawai /532 Jiwa</t>
+  </si>
+  <si>
+    <t>'00340T</t>
+  </si>
+  <si>
+    <t>'259991530041992</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan September 2025 untuk 131 Pegawai/384 Jiwa</t>
+  </si>
+  <si>
     <t>2025-08-15</t>
   </si>
   <si>
@@ -3605,6 +3662,15 @@
     <t>Pembayaran belanja barang berupa tagihan telepon bulan Agustus 2025 untuk 12 invoice</t>
   </si>
   <si>
+    <t>'00343T</t>
+  </si>
+  <si>
+    <t>'259991525018157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pembayaran Belanja Pegawai berupa Gaji Induk bulan September 2025 untuk 4 Pegawai/16 Jiwa </t>
+  </si>
+  <si>
     <t>2025-08-13</t>
   </si>
   <si>
@@ -3698,6 +3764,15 @@
     <t>'259991310447652</t>
   </si>
   <si>
+    <t>'00354T</t>
+  </si>
+  <si>
+    <t>'259991530041991</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan September 2025 untuk 37 Pegawai/103 Jiwa</t>
+  </si>
+  <si>
     <t>'00355T</t>
   </si>
   <si>
@@ -3762,6 +3837,243 @@
   </si>
   <si>
     <t>Pembayaran tunjangan kinerja bulan Juli tahun 2025 untuk 23 Pegawai</t>
+  </si>
+  <si>
+    <t>2025-08-21</t>
+  </si>
+  <si>
+    <t>'00363T</t>
+  </si>
+  <si>
+    <t>'259991310489796</t>
+  </si>
+  <si>
+    <t>'00364T</t>
+  </si>
+  <si>
+    <t>'259991530053253</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Agustus Tahun 2025 untuk 16 Pegawai.sesuai SK No. B.4/BRPBATPP/KP.340/I/2025 Tanggal 2 Januari 2025</t>
+  </si>
+  <si>
+    <t>2025-08-22</t>
+  </si>
+  <si>
+    <t>'00367T</t>
+  </si>
+  <si>
+    <t>'259991330160684</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Juli tahun 2025 untuk 173 Pegawai</t>
+  </si>
+  <si>
+    <t>'00368T</t>
+  </si>
+  <si>
+    <t>'259991310518118</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan September tahun 2025 untuk 37 Pegawai</t>
+  </si>
+  <si>
+    <t>'00369T</t>
+  </si>
+  <si>
+    <t>'259991305107153</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan September tahun 2025 untuk 4 Pegawai</t>
+  </si>
+  <si>
+    <t>'00370T</t>
+  </si>
+  <si>
+    <t>'259991310536551</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang Sesuai SPD No. 0038-0047/BRPBATPP/KP.440/VIII/2025  Tanggal 18 Juni 2025 s.d 09 Agustus 2025</t>
+  </si>
+  <si>
+    <t>2025-09-03</t>
+  </si>
+  <si>
+    <t>'00371T</t>
+  </si>
+  <si>
+    <t>'259991310546276</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja barang berupa Honor Pengelola Keuangan Bulan Agustus 2025 untuk 8 Pegawai sesuai Sk NoB.1/BRPBATPP/KU.110/I/2025 tanggal 2 Januari 202</t>
+  </si>
+  <si>
+    <t>'00372T</t>
+  </si>
+  <si>
+    <t>'259991310566063</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Agustus Tahun 2025 untuk 103 Pegawai Sesuai Sk No 9 Tahun2025 Tanggal 6 Januari 2025</t>
+  </si>
+  <si>
+    <t>'403829.023.521111.03212WA.2378EBA.A000000001.00000.2.0252.2.000000.000000.994.002.DA.000288</t>
+  </si>
+  <si>
+    <t>'403829.023.521111.03212WA.2378EBA.A000000001.00000.2.0252.2.000000.000000.994.002.DA.000289</t>
+  </si>
+  <si>
+    <t>'403829.023.521111.03212WA.2378EBA.A000000001.00000.2.0252.2.000000.000000.994.002.DA.000290</t>
+  </si>
+  <si>
+    <t>'00373T</t>
+  </si>
+  <si>
+    <t>'259991330186965</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Agustus Tahun 2025 untuk 91 Pegawai Sesuai Sk No 9 Tahun 2025 Tanggal 6 Januari 2025</t>
+  </si>
+  <si>
+    <t>2025-09-04</t>
+  </si>
+  <si>
+    <t>'00374T</t>
+  </si>
+  <si>
+    <t>'259991310562990</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang termin ke 8 Sesuai SPK No.2/BRPBATPP/PPK/PL.400/I/2025 Tanggal 2 Januari 2025 dan BAPP No.B.537/BRPBATPP/PPK/PL.400/VIII/2025 Tanggal 31 Agustus 2025</t>
+  </si>
+  <si>
+    <t>2025-09-08</t>
+  </si>
+  <si>
+    <t>'00375T</t>
+  </si>
+  <si>
+    <t>'259991320309399</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang sesuai Kwitansi No. 03/PHRA/KW/VIII/2025 Tanggal 28 Agustus 2025 kegiatan Biaya Pemeliharaan gedung laboratorium Kantor Depok</t>
+  </si>
+  <si>
+    <t>'00376T</t>
+  </si>
+  <si>
+    <t>'259991310573379</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang sesuai SPD No. 0039-0048/BRPBATPP/KP.440/VII/2025 Tanggal 18 Juni 2025 sd 17 agustus 2025</t>
+  </si>
+  <si>
+    <t>'00384T</t>
+  </si>
+  <si>
+    <t>'259991310590456</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Agustus 2025 untuk 50 Pegawai</t>
+  </si>
+  <si>
+    <t>'00385T</t>
+  </si>
+  <si>
+    <t>'259991330196056</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Agustus 2025 untuk 62 Pegawai</t>
+  </si>
+  <si>
+    <t>'00386T</t>
+  </si>
+  <si>
+    <t>'259991310591106</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Agustus 2025 untuk 34 Pegawai</t>
+  </si>
+  <si>
+    <t>'00387T</t>
+  </si>
+  <si>
+    <t>'259991330196057</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Agustus 2025 untuk 22 Pegawai</t>
+  </si>
+  <si>
+    <t>'00388T</t>
+  </si>
+  <si>
+    <t>'259991310592673</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Agustus 2025 untuk 35 Pegawai</t>
+  </si>
+  <si>
+    <t>'00389T</t>
+  </si>
+  <si>
+    <t>'259991310592674</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Agustus 2025 untuk 131 Pegawai</t>
+  </si>
+  <si>
+    <t>'00390T</t>
+  </si>
+  <si>
+    <t>'259991305125224</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Agustus 2025 untuk 5 Pegawai</t>
+  </si>
+  <si>
+    <t>2025-09-10</t>
+  </si>
+  <si>
+    <t>'00391T</t>
+  </si>
+  <si>
+    <t>'259991320319155</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang berupa Tagihan PDAM Bulan Agustus 2025 Idpel No. 1249-1046 An Lemb Perikanan Darat</t>
+  </si>
+  <si>
+    <t>'00393T</t>
+  </si>
+  <si>
+    <t>'259991320326689</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang berupa Tagihan Internet Bulan Agustus 2025 idpel No.GO18A106 An Balai Riset Perikanan Budidaya Air Tawar dan Penyuluhan Perikanan</t>
+  </si>
+  <si>
+    <t>2025-09-09</t>
+  </si>
+  <si>
+    <t>'00394T</t>
+  </si>
+  <si>
+    <t>'259991330199770</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Agustus 2025 untuk 169 Pegawai</t>
+  </si>
+  <si>
+    <t>'00395T</t>
+  </si>
+  <si>
+    <t>'259991310605586</t>
+  </si>
+  <si>
+    <t>'403829.023.521111.03212WA.2378EBA.A000000001.00000.2.0252.2.000000.000000.994.002.DA.000291</t>
+  </si>
+  <si>
+    <t>'403829.023.523121.03212WA.2378EBA.A000000001.00000.2.0252.2.000000.000000.994.002.DC.000176</t>
   </si>
 </sst>
 </file>
@@ -4104,7 +4416,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:L1205"/>
+  <dimension ref="A1:L1329"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -47988,7 +48300,7 @@
         <v>1192</v>
       </c>
       <c r="H1157" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="I1157" t="s">
         <v>19</v>
@@ -47997,10 +48309,10 @@
         <v>1</v>
       </c>
       <c r="K1157">
-        <v>41758847</v>
+        <v>158344800</v>
       </c>
       <c r="L1157">
-        <v>41758847</v>
+        <v>158344800</v>
       </c>
     </row>
     <row r="1158" spans="1:12">
@@ -48017,16 +48329,16 @@
         <v>1189</v>
       </c>
       <c r="E1158" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="F1158" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
       <c r="G1158" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="H1158" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="I1158" t="s">
         <v>19</v>
@@ -48035,10 +48347,10 @@
         <v>1</v>
       </c>
       <c r="K1158">
-        <v>263514</v>
+        <v>3214</v>
       </c>
       <c r="L1158">
-        <v>263514</v>
+        <v>3214</v>
       </c>
     </row>
     <row r="1159" spans="1:12">
@@ -48055,16 +48367,16 @@
         <v>1189</v>
       </c>
       <c r="E1159" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="F1159" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
       <c r="G1159" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="H1159" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="I1159" t="s">
         <v>19</v>
@@ -48073,10 +48385,10 @@
         <v>1</v>
       </c>
       <c r="K1159">
-        <v>2580750</v>
+        <v>9154120</v>
       </c>
       <c r="L1159">
-        <v>2580750</v>
+        <v>9154120</v>
       </c>
     </row>
     <row r="1160" spans="1:12">
@@ -48090,19 +48402,19 @@
         <v>13</v>
       </c>
       <c r="D1160" t="s">
-        <v>1196</v>
+        <v>1189</v>
       </c>
       <c r="E1160" t="s">
-        <v>1197</v>
+        <v>1190</v>
       </c>
       <c r="F1160" t="s">
-        <v>1198</v>
+        <v>1191</v>
       </c>
       <c r="G1160" t="s">
-        <v>1199</v>
+        <v>1192</v>
       </c>
       <c r="H1160" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="I1160" t="s">
         <v>19</v>
@@ -48111,10 +48423,10 @@
         <v>1</v>
       </c>
       <c r="K1160">
-        <v>6670000</v>
+        <v>2901696</v>
       </c>
       <c r="L1160">
-        <v>6670000</v>
+        <v>2901696</v>
       </c>
     </row>
     <row r="1161" spans="1:12">
@@ -48128,19 +48440,19 @@
         <v>13</v>
       </c>
       <c r="D1161" t="s">
-        <v>1200</v>
+        <v>1189</v>
       </c>
       <c r="E1161" t="s">
-        <v>1201</v>
+        <v>1190</v>
       </c>
       <c r="F1161" t="s">
-        <v>1202</v>
+        <v>1191</v>
       </c>
       <c r="G1161" t="s">
-        <v>1203</v>
+        <v>1192</v>
       </c>
       <c r="H1161" t="s">
-        <v>233</v>
+        <v>52</v>
       </c>
       <c r="I1161" t="s">
         <v>19</v>
@@ -48149,10 +48461,10 @@
         <v>1</v>
       </c>
       <c r="K1161">
-        <v>7665000</v>
+        <v>25200000</v>
       </c>
       <c r="L1161">
-        <v>7665000</v>
+        <v>25200000</v>
       </c>
     </row>
     <row r="1162" spans="1:12">
@@ -48166,19 +48478,19 @@
         <v>13</v>
       </c>
       <c r="D1162" t="s">
-        <v>1200</v>
+        <v>1189</v>
       </c>
       <c r="E1162" t="s">
-        <v>1201</v>
+        <v>1190</v>
       </c>
       <c r="F1162" t="s">
-        <v>1202</v>
+        <v>1191</v>
       </c>
       <c r="G1162" t="s">
-        <v>1203</v>
+        <v>1192</v>
       </c>
       <c r="H1162" t="s">
-        <v>234</v>
+        <v>53</v>
       </c>
       <c r="I1162" t="s">
         <v>19</v>
@@ -48187,10 +48499,10 @@
         <v>1</v>
       </c>
       <c r="K1162">
-        <v>32967000</v>
+        <v>9052500</v>
       </c>
       <c r="L1162">
-        <v>32967000</v>
+        <v>9052500</v>
       </c>
     </row>
     <row r="1163" spans="1:12">
@@ -48204,19 +48516,19 @@
         <v>13</v>
       </c>
       <c r="D1163" t="s">
-        <v>1200</v>
+        <v>1189</v>
       </c>
       <c r="E1163" t="s">
-        <v>1204</v>
+        <v>1193</v>
       </c>
       <c r="F1163" t="s">
-        <v>1205</v>
+        <v>1194</v>
       </c>
       <c r="G1163" t="s">
-        <v>1206</v>
+        <v>1195</v>
       </c>
       <c r="H1163" t="s">
-        <v>233</v>
+        <v>48</v>
       </c>
       <c r="I1163" t="s">
         <v>19</v>
@@ -48225,10 +48537,10 @@
         <v>1</v>
       </c>
       <c r="K1163">
-        <v>1610000</v>
+        <v>207286000</v>
       </c>
       <c r="L1163">
-        <v>1610000</v>
+        <v>207286000</v>
       </c>
     </row>
     <row r="1164" spans="1:12">
@@ -48242,19 +48554,19 @@
         <v>13</v>
       </c>
       <c r="D1164" t="s">
-        <v>1200</v>
+        <v>1189</v>
       </c>
       <c r="E1164" t="s">
-        <v>1204</v>
+        <v>1193</v>
       </c>
       <c r="F1164" t="s">
-        <v>1205</v>
+        <v>1194</v>
       </c>
       <c r="G1164" t="s">
-        <v>1206</v>
+        <v>1195</v>
       </c>
       <c r="H1164" t="s">
-        <v>234</v>
+        <v>49</v>
       </c>
       <c r="I1164" t="s">
         <v>19</v>
@@ -48263,10 +48575,10 @@
         <v>1</v>
       </c>
       <c r="K1164">
-        <v>50320000</v>
+        <v>3012</v>
       </c>
       <c r="L1164">
-        <v>50320000</v>
+        <v>3012</v>
       </c>
     </row>
     <row r="1165" spans="1:12">
@@ -48280,19 +48592,19 @@
         <v>13</v>
       </c>
       <c r="D1165" t="s">
-        <v>1200</v>
+        <v>1189</v>
       </c>
       <c r="E1165" t="s">
-        <v>1207</v>
+        <v>1193</v>
       </c>
       <c r="F1165" t="s">
-        <v>1208</v>
+        <v>1194</v>
       </c>
       <c r="G1165" t="s">
-        <v>1209</v>
+        <v>1195</v>
       </c>
       <c r="H1165" t="s">
-        <v>233</v>
+        <v>50</v>
       </c>
       <c r="I1165" t="s">
         <v>19</v>
@@ -48301,10 +48613,10 @@
         <v>1</v>
       </c>
       <c r="K1165">
-        <v>2415000</v>
+        <v>15155680</v>
       </c>
       <c r="L1165">
-        <v>2415000</v>
+        <v>15155680</v>
       </c>
     </row>
     <row r="1166" spans="1:12">
@@ -48318,19 +48630,19 @@
         <v>13</v>
       </c>
       <c r="D1166" t="s">
-        <v>1200</v>
+        <v>1189</v>
       </c>
       <c r="E1166" t="s">
-        <v>1207</v>
+        <v>1193</v>
       </c>
       <c r="F1166" t="s">
-        <v>1208</v>
+        <v>1194</v>
       </c>
       <c r="G1166" t="s">
-        <v>1209</v>
+        <v>1195</v>
       </c>
       <c r="H1166" t="s">
-        <v>234</v>
+        <v>51</v>
       </c>
       <c r="I1166" t="s">
         <v>19</v>
@@ -48339,10 +48651,10 @@
         <v>1</v>
       </c>
       <c r="K1166">
-        <v>25493000</v>
+        <v>4722688</v>
       </c>
       <c r="L1166">
-        <v>25493000</v>
+        <v>4722688</v>
       </c>
     </row>
     <row r="1167" spans="1:12">
@@ -48356,19 +48668,19 @@
         <v>13</v>
       </c>
       <c r="D1167" t="s">
-        <v>1200</v>
+        <v>1189</v>
       </c>
       <c r="E1167" t="s">
-        <v>1210</v>
+        <v>1193</v>
       </c>
       <c r="F1167" t="s">
-        <v>1211</v>
+        <v>1194</v>
       </c>
       <c r="G1167" t="s">
-        <v>1212</v>
+        <v>1195</v>
       </c>
       <c r="H1167" t="s">
-        <v>233</v>
+        <v>52</v>
       </c>
       <c r="I1167" t="s">
         <v>19</v>
@@ -48377,10 +48689,10 @@
         <v>1</v>
       </c>
       <c r="K1167">
-        <v>1610000</v>
+        <v>33660000</v>
       </c>
       <c r="L1167">
-        <v>1610000</v>
+        <v>33660000</v>
       </c>
     </row>
     <row r="1168" spans="1:12">
@@ -48394,19 +48706,19 @@
         <v>13</v>
       </c>
       <c r="D1168" t="s">
-        <v>1200</v>
+        <v>1189</v>
       </c>
       <c r="E1168" t="s">
-        <v>1210</v>
+        <v>1193</v>
       </c>
       <c r="F1168" t="s">
-        <v>1211</v>
+        <v>1194</v>
       </c>
       <c r="G1168" t="s">
-        <v>1212</v>
+        <v>1195</v>
       </c>
       <c r="H1168" t="s">
-        <v>234</v>
+        <v>53</v>
       </c>
       <c r="I1168" t="s">
         <v>19</v>
@@ -48415,10 +48727,10 @@
         <v>1</v>
       </c>
       <c r="K1168">
-        <v>16798000</v>
+        <v>13108020</v>
       </c>
       <c r="L1168">
-        <v>16798000</v>
+        <v>13108020</v>
       </c>
     </row>
     <row r="1169" spans="1:12">
@@ -48432,19 +48744,19 @@
         <v>13</v>
       </c>
       <c r="D1169" t="s">
-        <v>1200</v>
+        <v>1189</v>
       </c>
       <c r="E1169" t="s">
-        <v>1213</v>
+        <v>1196</v>
       </c>
       <c r="F1169" t="s">
-        <v>1214</v>
+        <v>1197</v>
       </c>
       <c r="G1169" t="s">
-        <v>1215</v>
+        <v>1198</v>
       </c>
       <c r="H1169" t="s">
-        <v>241</v>
+        <v>48</v>
       </c>
       <c r="I1169" t="s">
         <v>19</v>
@@ -48453,10 +48765,10 @@
         <v>1</v>
       </c>
       <c r="K1169">
-        <v>1610000</v>
+        <v>111091600</v>
       </c>
       <c r="L1169">
-        <v>1610000</v>
+        <v>111091600</v>
       </c>
     </row>
     <row r="1170" spans="1:12">
@@ -48470,19 +48782,19 @@
         <v>13</v>
       </c>
       <c r="D1170" t="s">
-        <v>1200</v>
+        <v>1189</v>
       </c>
       <c r="E1170" t="s">
-        <v>1213</v>
+        <v>1196</v>
       </c>
       <c r="F1170" t="s">
-        <v>1214</v>
+        <v>1197</v>
       </c>
       <c r="G1170" t="s">
-        <v>1215</v>
+        <v>1198</v>
       </c>
       <c r="H1170" t="s">
-        <v>149</v>
+        <v>49</v>
       </c>
       <c r="I1170" t="s">
         <v>19</v>
@@ -48491,10 +48803,10 @@
         <v>1</v>
       </c>
       <c r="K1170">
-        <v>24642000</v>
+        <v>2345</v>
       </c>
       <c r="L1170">
-        <v>24642000</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="1171" spans="1:12">
@@ -48508,19 +48820,19 @@
         <v>13</v>
       </c>
       <c r="D1171" t="s">
-        <v>1200</v>
+        <v>1189</v>
       </c>
       <c r="E1171" t="s">
-        <v>1213</v>
+        <v>1196</v>
       </c>
       <c r="F1171" t="s">
-        <v>1214</v>
+        <v>1197</v>
       </c>
       <c r="G1171" t="s">
-        <v>1215</v>
+        <v>1198</v>
       </c>
       <c r="H1171" t="s">
-        <v>242</v>
+        <v>50</v>
       </c>
       <c r="I1171" t="s">
         <v>19</v>
@@ -48529,10 +48841,10 @@
         <v>1</v>
       </c>
       <c r="K1171">
-        <v>3321000</v>
+        <v>8580760</v>
       </c>
       <c r="L1171">
-        <v>3321000</v>
+        <v>8580760</v>
       </c>
     </row>
     <row r="1172" spans="1:12">
@@ -48546,19 +48858,19 @@
         <v>13</v>
       </c>
       <c r="D1172" t="s">
-        <v>1200</v>
+        <v>1189</v>
       </c>
       <c r="E1172" t="s">
-        <v>1216</v>
+        <v>1196</v>
       </c>
       <c r="F1172" t="s">
-        <v>1217</v>
+        <v>1197</v>
       </c>
       <c r="G1172" t="s">
-        <v>1218</v>
+        <v>1198</v>
       </c>
       <c r="H1172" t="s">
-        <v>266</v>
+        <v>51</v>
       </c>
       <c r="I1172" t="s">
         <v>19</v>
@@ -48567,10 +48879,10 @@
         <v>1</v>
       </c>
       <c r="K1172">
-        <v>11515000</v>
+        <v>2478120</v>
       </c>
       <c r="L1172">
-        <v>11515000</v>
+        <v>2478120</v>
       </c>
     </row>
     <row r="1173" spans="1:12">
@@ -48584,19 +48896,19 @@
         <v>13</v>
       </c>
       <c r="D1173" t="s">
-        <v>1200</v>
+        <v>1189</v>
       </c>
       <c r="E1173" t="s">
-        <v>1216</v>
+        <v>1196</v>
       </c>
       <c r="F1173" t="s">
-        <v>1217</v>
+        <v>1197</v>
       </c>
       <c r="G1173" t="s">
-        <v>1218</v>
+        <v>1198</v>
       </c>
       <c r="H1173" t="s">
-        <v>267</v>
+        <v>52</v>
       </c>
       <c r="I1173" t="s">
         <v>19</v>
@@ -48605,10 +48917,10 @@
         <v>1</v>
       </c>
       <c r="K1173">
-        <v>74962000</v>
+        <v>18360000</v>
       </c>
       <c r="L1173">
-        <v>74962000</v>
+        <v>18360000</v>
       </c>
     </row>
     <row r="1174" spans="1:12">
@@ -48622,19 +48934,19 @@
         <v>13</v>
       </c>
       <c r="D1174" t="s">
-        <v>1200</v>
+        <v>1189</v>
       </c>
       <c r="E1174" t="s">
-        <v>1216</v>
+        <v>1196</v>
       </c>
       <c r="F1174" t="s">
-        <v>1217</v>
+        <v>1197</v>
       </c>
       <c r="G1174" t="s">
-        <v>1218</v>
+        <v>1198</v>
       </c>
       <c r="H1174" t="s">
-        <v>268</v>
+        <v>53</v>
       </c>
       <c r="I1174" t="s">
         <v>19</v>
@@ -48643,10 +48955,10 @@
         <v>1</v>
       </c>
       <c r="K1174">
-        <v>25256000</v>
+        <v>7314420</v>
       </c>
       <c r="L1174">
-        <v>25256000</v>
+        <v>7314420</v>
       </c>
     </row>
     <row r="1175" spans="1:12">
@@ -48660,19 +48972,19 @@
         <v>13</v>
       </c>
       <c r="D1175" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E1175" t="s">
+        <v>1199</v>
+      </c>
+      <c r="F1175" t="s">
         <v>1200</v>
       </c>
-      <c r="E1175" t="s">
-        <v>1219</v>
-      </c>
-      <c r="F1175" t="s">
-        <v>1220</v>
-      </c>
       <c r="G1175" t="s">
-        <v>1221</v>
+        <v>1201</v>
       </c>
       <c r="H1175" t="s">
-        <v>266</v>
+        <v>48</v>
       </c>
       <c r="I1175" t="s">
         <v>19</v>
@@ -48681,10 +48993,10 @@
         <v>1</v>
       </c>
       <c r="K1175">
-        <v>12040000</v>
+        <v>72648400</v>
       </c>
       <c r="L1175">
-        <v>12040000</v>
+        <v>72648400</v>
       </c>
     </row>
     <row r="1176" spans="1:12">
@@ -48698,19 +49010,19 @@
         <v>13</v>
       </c>
       <c r="D1176" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E1176" t="s">
+        <v>1199</v>
+      </c>
+      <c r="F1176" t="s">
         <v>1200</v>
       </c>
-      <c r="E1176" t="s">
-        <v>1219</v>
-      </c>
-      <c r="F1176" t="s">
-        <v>1220</v>
-      </c>
       <c r="G1176" t="s">
-        <v>1221</v>
+        <v>1201</v>
       </c>
       <c r="H1176" t="s">
-        <v>267</v>
+        <v>49</v>
       </c>
       <c r="I1176" t="s">
         <v>19</v>
@@ -48719,10 +49031,10 @@
         <v>1</v>
       </c>
       <c r="K1176">
-        <v>109076000</v>
+        <v>1467</v>
       </c>
       <c r="L1176">
-        <v>109076000</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="1177" spans="1:12">
@@ -48736,19 +49048,19 @@
         <v>13</v>
       </c>
       <c r="D1177" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E1177" t="s">
+        <v>1199</v>
+      </c>
+      <c r="F1177" t="s">
         <v>1200</v>
       </c>
-      <c r="E1177" t="s">
-        <v>1219</v>
-      </c>
-      <c r="F1177" t="s">
-        <v>1220</v>
-      </c>
       <c r="G1177" t="s">
-        <v>1221</v>
+        <v>1201</v>
       </c>
       <c r="H1177" t="s">
-        <v>268</v>
+        <v>50</v>
       </c>
       <c r="I1177" t="s">
         <v>19</v>
@@ -48757,10 +49069,10 @@
         <v>1</v>
       </c>
       <c r="K1177">
-        <v>24272000</v>
+        <v>4416080</v>
       </c>
       <c r="L1177">
-        <v>24272000</v>
+        <v>4416080</v>
       </c>
     </row>
     <row r="1178" spans="1:12">
@@ -48774,19 +49086,19 @@
         <v>13</v>
       </c>
       <c r="D1178" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E1178" t="s">
+        <v>1199</v>
+      </c>
+      <c r="F1178" t="s">
         <v>1200</v>
       </c>
-      <c r="E1178" t="s">
-        <v>1222</v>
-      </c>
-      <c r="F1178" t="s">
-        <v>1223</v>
-      </c>
       <c r="G1178" t="s">
-        <v>1224</v>
+        <v>1201</v>
       </c>
       <c r="H1178" t="s">
-        <v>149</v>
+        <v>51</v>
       </c>
       <c r="I1178" t="s">
         <v>19</v>
@@ -48795,10 +49107,10 @@
         <v>1</v>
       </c>
       <c r="K1178">
-        <v>2331000</v>
+        <v>940392</v>
       </c>
       <c r="L1178">
-        <v>2331000</v>
+        <v>940392</v>
       </c>
     </row>
     <row r="1179" spans="1:12">
@@ -48812,19 +49124,19 @@
         <v>13</v>
       </c>
       <c r="D1179" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E1179" t="s">
+        <v>1199</v>
+      </c>
+      <c r="F1179" t="s">
         <v>1200</v>
       </c>
-      <c r="E1179" t="s">
-        <v>1222</v>
-      </c>
-      <c r="F1179" t="s">
-        <v>1223</v>
-      </c>
       <c r="G1179" t="s">
-        <v>1224</v>
+        <v>1201</v>
       </c>
       <c r="H1179" t="s">
-        <v>242</v>
+        <v>52</v>
       </c>
       <c r="I1179" t="s">
         <v>19</v>
@@ -48833,10 +49145,10 @@
         <v>1</v>
       </c>
       <c r="K1179">
-        <v>861000</v>
+        <v>11520000</v>
       </c>
       <c r="L1179">
-        <v>861000</v>
+        <v>11520000</v>
       </c>
     </row>
     <row r="1180" spans="1:12">
@@ -48850,19 +49162,19 @@
         <v>13</v>
       </c>
       <c r="D1180" t="s">
-        <v>1196</v>
+        <v>1189</v>
       </c>
       <c r="E1180" t="s">
-        <v>1225</v>
+        <v>1199</v>
       </c>
       <c r="F1180" t="s">
-        <v>1226</v>
+        <v>1200</v>
       </c>
       <c r="G1180" t="s">
-        <v>171</v>
+        <v>1201</v>
       </c>
       <c r="H1180" t="s">
-        <v>173</v>
+        <v>53</v>
       </c>
       <c r="I1180" t="s">
         <v>19</v>
@@ -48871,10 +49183,10 @@
         <v>1</v>
       </c>
       <c r="K1180">
-        <v>2017000</v>
+        <v>3765840</v>
       </c>
       <c r="L1180">
-        <v>2017000</v>
+        <v>3765840</v>
       </c>
     </row>
     <row r="1181" spans="1:12">
@@ -48888,19 +49200,19 @@
         <v>13</v>
       </c>
       <c r="D1181" t="s">
-        <v>1196</v>
+        <v>1189</v>
       </c>
       <c r="E1181" t="s">
-        <v>1225</v>
+        <v>1202</v>
       </c>
       <c r="F1181" t="s">
-        <v>1226</v>
+        <v>1203</v>
       </c>
       <c r="G1181" t="s">
-        <v>171</v>
+        <v>1204</v>
       </c>
       <c r="H1181" t="s">
-        <v>174</v>
+        <v>31</v>
       </c>
       <c r="I1181" t="s">
         <v>19</v>
@@ -48909,10 +49221,10 @@
         <v>1</v>
       </c>
       <c r="K1181">
-        <v>222500</v>
+        <v>665320100</v>
       </c>
       <c r="L1181">
-        <v>222500</v>
+        <v>665320100</v>
       </c>
     </row>
     <row r="1182" spans="1:12">
@@ -48926,19 +49238,19 @@
         <v>13</v>
       </c>
       <c r="D1182" t="s">
-        <v>1196</v>
+        <v>1189</v>
       </c>
       <c r="E1182" t="s">
-        <v>1225</v>
+        <v>1202</v>
       </c>
       <c r="F1182" t="s">
-        <v>1226</v>
+        <v>1203</v>
       </c>
       <c r="G1182" t="s">
-        <v>171</v>
+        <v>1204</v>
       </c>
       <c r="H1182" t="s">
-        <v>175</v>
+        <v>32</v>
       </c>
       <c r="I1182" t="s">
         <v>19</v>
@@ -48947,10 +49259,10 @@
         <v>1</v>
       </c>
       <c r="K1182">
-        <v>4279000</v>
+        <v>8999</v>
       </c>
       <c r="L1182">
-        <v>4279000</v>
+        <v>8999</v>
       </c>
     </row>
     <row r="1183" spans="1:12">
@@ -48964,19 +49276,19 @@
         <v>13</v>
       </c>
       <c r="D1183" t="s">
-        <v>1196</v>
+        <v>1189</v>
       </c>
       <c r="E1183" t="s">
-        <v>1225</v>
+        <v>1202</v>
       </c>
       <c r="F1183" t="s">
-        <v>1226</v>
+        <v>1203</v>
       </c>
       <c r="G1183" t="s">
-        <v>171</v>
+        <v>1204</v>
       </c>
       <c r="H1183" t="s">
-        <v>176</v>
+        <v>33</v>
       </c>
       <c r="I1183" t="s">
         <v>19</v>
@@ -48985,10 +49297,10 @@
         <v>1</v>
       </c>
       <c r="K1183">
-        <v>25625000</v>
+        <v>53769830</v>
       </c>
       <c r="L1183">
-        <v>25625000</v>
+        <v>53769830</v>
       </c>
     </row>
     <row r="1184" spans="1:12">
@@ -49002,19 +49314,19 @@
         <v>13</v>
       </c>
       <c r="D1184" t="s">
-        <v>1196</v>
+        <v>1189</v>
       </c>
       <c r="E1184" t="s">
-        <v>1225</v>
+        <v>1202</v>
       </c>
       <c r="F1184" t="s">
-        <v>1226</v>
+        <v>1203</v>
       </c>
       <c r="G1184" t="s">
-        <v>171</v>
+        <v>1204</v>
       </c>
       <c r="H1184" t="s">
-        <v>1040</v>
+        <v>34</v>
       </c>
       <c r="I1184" t="s">
         <v>19</v>
@@ -49023,10 +49335,10 @@
         <v>1</v>
       </c>
       <c r="K1184">
-        <v>9115000</v>
+        <v>17648898</v>
       </c>
       <c r="L1184">
-        <v>9115000</v>
+        <v>17648898</v>
       </c>
     </row>
     <row r="1185" spans="1:12">
@@ -49040,19 +49352,19 @@
         <v>13</v>
       </c>
       <c r="D1185" t="s">
-        <v>1196</v>
+        <v>1189</v>
       </c>
       <c r="E1185" t="s">
-        <v>1225</v>
+        <v>1202</v>
       </c>
       <c r="F1185" t="s">
-        <v>1226</v>
+        <v>1203</v>
       </c>
       <c r="G1185" t="s">
-        <v>171</v>
+        <v>1204</v>
       </c>
       <c r="H1185" t="s">
-        <v>177</v>
+        <v>35</v>
       </c>
       <c r="I1185" t="s">
         <v>19</v>
@@ -49061,10 +49373,10 @@
         <v>1</v>
       </c>
       <c r="K1185">
-        <v>41321696</v>
+        <v>146340000</v>
       </c>
       <c r="L1185">
-        <v>41321696</v>
+        <v>146340000</v>
       </c>
     </row>
     <row r="1186" spans="1:12">
@@ -49078,19 +49390,19 @@
         <v>13</v>
       </c>
       <c r="D1186" t="s">
-        <v>1196</v>
+        <v>1189</v>
       </c>
       <c r="E1186" t="s">
-        <v>1225</v>
+        <v>1202</v>
       </c>
       <c r="F1186" t="s">
-        <v>1226</v>
+        <v>1203</v>
       </c>
       <c r="G1186" t="s">
-        <v>171</v>
+        <v>1204</v>
       </c>
       <c r="H1186" t="s">
-        <v>178</v>
+        <v>36</v>
       </c>
       <c r="I1186" t="s">
         <v>19</v>
@@ -49099,10 +49411,10 @@
         <v>1</v>
       </c>
       <c r="K1186">
-        <v>9468528</v>
+        <v>1490999</v>
       </c>
       <c r="L1186">
-        <v>9468528</v>
+        <v>1490999</v>
       </c>
     </row>
     <row r="1187" spans="1:12">
@@ -49116,19 +49428,19 @@
         <v>13</v>
       </c>
       <c r="D1187" t="s">
-        <v>1196</v>
+        <v>1189</v>
       </c>
       <c r="E1187" t="s">
-        <v>1225</v>
+        <v>1202</v>
       </c>
       <c r="F1187" t="s">
-        <v>1226</v>
+        <v>1203</v>
       </c>
       <c r="G1187" t="s">
-        <v>171</v>
+        <v>1204</v>
       </c>
       <c r="H1187" t="s">
-        <v>179</v>
+        <v>37</v>
       </c>
       <c r="I1187" t="s">
         <v>19</v>
@@ -49137,10 +49449,10 @@
         <v>1</v>
       </c>
       <c r="K1187">
-        <v>13729784</v>
+        <v>38527440</v>
       </c>
       <c r="L1187">
-        <v>13729784</v>
+        <v>38527440</v>
       </c>
     </row>
     <row r="1188" spans="1:12">
@@ -49154,19 +49466,19 @@
         <v>13</v>
       </c>
       <c r="D1188" t="s">
-        <v>1196</v>
+        <v>1189</v>
       </c>
       <c r="E1188" t="s">
-        <v>1225</v>
+        <v>1205</v>
       </c>
       <c r="F1188" t="s">
-        <v>1226</v>
+        <v>1206</v>
       </c>
       <c r="G1188" t="s">
-        <v>171</v>
+        <v>1207</v>
       </c>
       <c r="H1188" t="s">
-        <v>180</v>
+        <v>31</v>
       </c>
       <c r="I1188" t="s">
         <v>19</v>
@@ -49175,10 +49487,10 @@
         <v>1</v>
       </c>
       <c r="K1188">
-        <v>4629928</v>
+        <v>525613900</v>
       </c>
       <c r="L1188">
-        <v>4629928</v>
+        <v>525613900</v>
       </c>
     </row>
     <row r="1189" spans="1:12">
@@ -49192,19 +49504,19 @@
         <v>13</v>
       </c>
       <c r="D1189" t="s">
-        <v>1196</v>
+        <v>1189</v>
       </c>
       <c r="E1189" t="s">
-        <v>1225</v>
+        <v>1205</v>
       </c>
       <c r="F1189" t="s">
-        <v>1226</v>
+        <v>1206</v>
       </c>
       <c r="G1189" t="s">
-        <v>171</v>
+        <v>1207</v>
       </c>
       <c r="H1189" t="s">
-        <v>181</v>
+        <v>32</v>
       </c>
       <c r="I1189" t="s">
         <v>19</v>
@@ -49213,10 +49525,10 @@
         <v>1</v>
       </c>
       <c r="K1189">
-        <v>750000</v>
+        <v>6732</v>
       </c>
       <c r="L1189">
-        <v>750000</v>
+        <v>6732</v>
       </c>
     </row>
     <row r="1190" spans="1:12">
@@ -49230,19 +49542,19 @@
         <v>13</v>
       </c>
       <c r="D1190" t="s">
-        <v>1196</v>
+        <v>1189</v>
       </c>
       <c r="E1190" t="s">
-        <v>1225</v>
+        <v>1205</v>
       </c>
       <c r="F1190" t="s">
-        <v>1226</v>
+        <v>1206</v>
       </c>
       <c r="G1190" t="s">
-        <v>171</v>
+        <v>1207</v>
       </c>
       <c r="H1190" t="s">
-        <v>185</v>
+        <v>33</v>
       </c>
       <c r="I1190" t="s">
         <v>19</v>
@@ -49251,10 +49563,10 @@
         <v>1</v>
       </c>
       <c r="K1190">
-        <v>4845000</v>
+        <v>40371110</v>
       </c>
       <c r="L1190">
-        <v>4845000</v>
+        <v>40371110</v>
       </c>
     </row>
     <row r="1191" spans="1:12">
@@ -49268,19 +49580,19 @@
         <v>13</v>
       </c>
       <c r="D1191" t="s">
-        <v>1196</v>
+        <v>1189</v>
       </c>
       <c r="E1191" t="s">
-        <v>1225</v>
+        <v>1205</v>
       </c>
       <c r="F1191" t="s">
-        <v>1226</v>
+        <v>1206</v>
       </c>
       <c r="G1191" t="s">
-        <v>171</v>
+        <v>1207</v>
       </c>
       <c r="H1191" t="s">
-        <v>186</v>
+        <v>34</v>
       </c>
       <c r="I1191" t="s">
         <v>19</v>
@@ -49289,10 +49601,10 @@
         <v>1</v>
       </c>
       <c r="K1191">
-        <v>1225000</v>
+        <v>11964300</v>
       </c>
       <c r="L1191">
-        <v>1225000</v>
+        <v>11964300</v>
       </c>
     </row>
     <row r="1192" spans="1:12">
@@ -49306,19 +49618,19 @@
         <v>13</v>
       </c>
       <c r="D1192" t="s">
-        <v>1196</v>
+        <v>1189</v>
       </c>
       <c r="E1192" t="s">
-        <v>1225</v>
+        <v>1205</v>
       </c>
       <c r="F1192" t="s">
-        <v>1226</v>
+        <v>1206</v>
       </c>
       <c r="G1192" t="s">
-        <v>171</v>
+        <v>1207</v>
       </c>
       <c r="H1192" t="s">
-        <v>187</v>
+        <v>35</v>
       </c>
       <c r="I1192" t="s">
         <v>19</v>
@@ -49327,10 +49639,10 @@
         <v>1</v>
       </c>
       <c r="K1192">
-        <v>233875</v>
+        <v>109680000</v>
       </c>
       <c r="L1192">
-        <v>233875</v>
+        <v>109680000</v>
       </c>
     </row>
     <row r="1193" spans="1:12">
@@ -49344,19 +49656,19 @@
         <v>13</v>
       </c>
       <c r="D1193" t="s">
-        <v>1196</v>
+        <v>1189</v>
       </c>
       <c r="E1193" t="s">
-        <v>1225</v>
+        <v>1205</v>
       </c>
       <c r="F1193" t="s">
-        <v>1226</v>
+        <v>1206</v>
       </c>
       <c r="G1193" t="s">
-        <v>171</v>
+        <v>1207</v>
       </c>
       <c r="H1193" t="s">
-        <v>189</v>
+        <v>36</v>
       </c>
       <c r="I1193" t="s">
         <v>19</v>
@@ -49365,10 +49677,10 @@
         <v>1</v>
       </c>
       <c r="K1193">
-        <v>385700</v>
+        <v>1852199</v>
       </c>
       <c r="L1193">
-        <v>385700</v>
+        <v>1852199</v>
       </c>
     </row>
     <row r="1194" spans="1:12">
@@ -49385,16 +49697,16 @@
         <v>1189</v>
       </c>
       <c r="E1194" t="s">
-        <v>1227</v>
+        <v>1205</v>
       </c>
       <c r="F1194" t="s">
-        <v>1228</v>
+        <v>1206</v>
       </c>
       <c r="G1194" t="s">
-        <v>1229</v>
+        <v>1207</v>
       </c>
       <c r="H1194" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I1194" t="s">
         <v>19</v>
@@ -49403,10 +49715,10 @@
         <v>1</v>
       </c>
       <c r="K1194">
-        <v>461900</v>
+        <v>27809280</v>
       </c>
       <c r="L1194">
-        <v>461900</v>
+        <v>27809280</v>
       </c>
     </row>
     <row r="1195" spans="1:12">
@@ -49423,16 +49735,16 @@
         <v>1189</v>
       </c>
       <c r="E1195" t="s">
-        <v>1227</v>
+        <v>1205</v>
       </c>
       <c r="F1195" t="s">
-        <v>1228</v>
+        <v>1206</v>
       </c>
       <c r="G1195" t="s">
-        <v>1229</v>
+        <v>1207</v>
       </c>
       <c r="H1195" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I1195" t="s">
         <v>19</v>
@@ -49441,10 +49753,10 @@
         <v>1</v>
       </c>
       <c r="K1195">
-        <v>4</v>
+        <v>185000</v>
       </c>
       <c r="L1195">
-        <v>4</v>
+        <v>185000</v>
       </c>
     </row>
     <row r="1196" spans="1:12">
@@ -49458,19 +49770,19 @@
         <v>13</v>
       </c>
       <c r="D1196" t="s">
-        <v>1189</v>
+        <v>1208</v>
       </c>
       <c r="E1196" t="s">
-        <v>1227</v>
+        <v>1209</v>
       </c>
       <c r="F1196" t="s">
-        <v>1228</v>
+        <v>1210</v>
       </c>
       <c r="G1196" t="s">
-        <v>1229</v>
+        <v>1211</v>
       </c>
       <c r="H1196" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="I1196" t="s">
         <v>19</v>
@@ -49479,10 +49791,10 @@
         <v>1</v>
       </c>
       <c r="K1196">
-        <v>23810</v>
+        <v>41758847</v>
       </c>
       <c r="L1196">
-        <v>23810</v>
+        <v>41758847</v>
       </c>
     </row>
     <row r="1197" spans="1:12">
@@ -49496,19 +49808,19 @@
         <v>13</v>
       </c>
       <c r="D1197" t="s">
-        <v>1189</v>
+        <v>1208</v>
       </c>
       <c r="E1197" t="s">
-        <v>1227</v>
+        <v>1212</v>
       </c>
       <c r="F1197" t="s">
-        <v>1228</v>
+        <v>1213</v>
       </c>
       <c r="G1197" t="s">
-        <v>1229</v>
+        <v>1214</v>
       </c>
       <c r="H1197" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="I1197" t="s">
         <v>19</v>
@@ -49517,10 +49829,10 @@
         <v>1</v>
       </c>
       <c r="K1197">
-        <v>9524</v>
+        <v>263514</v>
       </c>
       <c r="L1197">
-        <v>9524</v>
+        <v>263514</v>
       </c>
     </row>
     <row r="1198" spans="1:12">
@@ -49534,19 +49846,19 @@
         <v>13</v>
       </c>
       <c r="D1198" t="s">
-        <v>1189</v>
+        <v>1208</v>
       </c>
       <c r="E1198" t="s">
-        <v>1230</v>
+        <v>1212</v>
       </c>
       <c r="F1198" t="s">
-        <v>1231</v>
+        <v>1213</v>
       </c>
       <c r="G1198" t="s">
-        <v>1232</v>
+        <v>1214</v>
       </c>
       <c r="H1198" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="I1198" t="s">
         <v>19</v>
@@ -49555,10 +49867,10 @@
         <v>1</v>
       </c>
       <c r="K1198">
-        <v>685700</v>
+        <v>2580750</v>
       </c>
       <c r="L1198">
-        <v>685700</v>
+        <v>2580750</v>
       </c>
     </row>
     <row r="1199" spans="1:12">
@@ -49575,16 +49887,16 @@
         <v>1189</v>
       </c>
       <c r="E1199" t="s">
-        <v>1230</v>
+        <v>1215</v>
       </c>
       <c r="F1199" t="s">
-        <v>1231</v>
+        <v>1216</v>
       </c>
       <c r="G1199" t="s">
-        <v>1232</v>
+        <v>1217</v>
       </c>
       <c r="H1199" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="I1199" t="s">
         <v>19</v>
@@ -49593,10 +49905,10 @@
         <v>1</v>
       </c>
       <c r="K1199">
-        <v>68570</v>
+        <v>16200700</v>
       </c>
       <c r="L1199">
-        <v>68570</v>
+        <v>16200700</v>
       </c>
     </row>
     <row r="1200" spans="1:12">
@@ -49613,16 +49925,16 @@
         <v>1189</v>
       </c>
       <c r="E1200" t="s">
-        <v>1230</v>
+        <v>1215</v>
       </c>
       <c r="F1200" t="s">
-        <v>1231</v>
+        <v>1216</v>
       </c>
       <c r="G1200" t="s">
-        <v>1232</v>
+        <v>1217</v>
       </c>
       <c r="H1200" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="I1200" t="s">
         <v>19</v>
@@ -49631,10 +49943,10 @@
         <v>1</v>
       </c>
       <c r="K1200">
-        <v>4762</v>
+        <v>121</v>
       </c>
       <c r="L1200">
-        <v>4762</v>
+        <v>121</v>
       </c>
     </row>
     <row r="1201" spans="1:12">
@@ -49648,19 +49960,19 @@
         <v>13</v>
       </c>
       <c r="D1201" t="s">
-        <v>1233</v>
+        <v>1189</v>
       </c>
       <c r="E1201" t="s">
-        <v>1234</v>
+        <v>1215</v>
       </c>
       <c r="F1201" t="s">
-        <v>1235</v>
+        <v>1216</v>
       </c>
       <c r="G1201" t="s">
-        <v>1236</v>
+        <v>1217</v>
       </c>
       <c r="H1201" t="s">
-        <v>272</v>
+        <v>21</v>
       </c>
       <c r="I1201" t="s">
         <v>19</v>
@@ -49669,10 +49981,10 @@
         <v>1</v>
       </c>
       <c r="K1201">
-        <v>878387055</v>
+        <v>1620070</v>
       </c>
       <c r="L1201">
-        <v>878387055</v>
+        <v>1620070</v>
       </c>
     </row>
     <row r="1202" spans="1:12">
@@ -49686,19 +49998,19 @@
         <v>13</v>
       </c>
       <c r="D1202" t="s">
-        <v>1233</v>
+        <v>1189</v>
       </c>
       <c r="E1202" t="s">
-        <v>1237</v>
+        <v>1215</v>
       </c>
       <c r="F1202" t="s">
-        <v>1238</v>
+        <v>1216</v>
       </c>
       <c r="G1202" t="s">
-        <v>1239</v>
+        <v>1217</v>
       </c>
       <c r="H1202" t="s">
-        <v>276</v>
+        <v>22</v>
       </c>
       <c r="I1202" t="s">
         <v>19</v>
@@ -49707,10 +50019,10 @@
         <v>1</v>
       </c>
       <c r="K1202">
-        <v>218758166</v>
+        <v>648028</v>
       </c>
       <c r="L1202">
-        <v>218758166</v>
+        <v>648028</v>
       </c>
     </row>
     <row r="1203" spans="1:12">
@@ -49724,19 +50036,19 @@
         <v>13</v>
       </c>
       <c r="D1203" t="s">
-        <v>1233</v>
+        <v>1189</v>
       </c>
       <c r="E1203" t="s">
-        <v>1240</v>
+        <v>1215</v>
       </c>
       <c r="F1203" t="s">
-        <v>1241</v>
+        <v>1216</v>
       </c>
       <c r="G1203" t="s">
-        <v>1242</v>
+        <v>1217</v>
       </c>
       <c r="H1203" t="s">
-        <v>276</v>
+        <v>23</v>
       </c>
       <c r="I1203" t="s">
         <v>19</v>
@@ -49745,10 +50057,10 @@
         <v>1</v>
       </c>
       <c r="K1203">
-        <v>286896591</v>
+        <v>540000</v>
       </c>
       <c r="L1203">
-        <v>286896591</v>
+        <v>540000</v>
       </c>
     </row>
     <row r="1204" spans="1:12">
@@ -49762,19 +50074,19 @@
         <v>13</v>
       </c>
       <c r="D1204" t="s">
-        <v>1233</v>
+        <v>1189</v>
       </c>
       <c r="E1204" t="s">
-        <v>1243</v>
+        <v>1215</v>
       </c>
       <c r="F1204" t="s">
-        <v>1244</v>
+        <v>1216</v>
       </c>
       <c r="G1204" t="s">
-        <v>1245</v>
+        <v>1217</v>
       </c>
       <c r="H1204" t="s">
-        <v>276</v>
+        <v>24</v>
       </c>
       <c r="I1204" t="s">
         <v>19</v>
@@ -49783,10 +50095,10 @@
         <v>1</v>
       </c>
       <c r="K1204">
-        <v>157239652</v>
+        <v>1100000</v>
       </c>
       <c r="L1204">
-        <v>157239652</v>
+        <v>1100000</v>
       </c>
     </row>
     <row r="1205" spans="1:12">
@@ -49800,31 +50112,4743 @@
         <v>13</v>
       </c>
       <c r="D1205" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E1205" t="s">
+        <v>1215</v>
+      </c>
+      <c r="F1205" t="s">
+        <v>1216</v>
+      </c>
+      <c r="G1205" t="s">
+        <v>1217</v>
+      </c>
+      <c r="H1205" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1205" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1205">
+        <v>1</v>
+      </c>
+      <c r="K1205">
+        <v>1158720</v>
+      </c>
+      <c r="L1205">
+        <v>1158720</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:12">
+      <c r="A1206">
+        <v>1203</v>
+      </c>
+      <c r="B1206">
+        <v>403829</v>
+      </c>
+      <c r="C1206" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1206" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E1206" t="s">
+        <v>1215</v>
+      </c>
+      <c r="F1206" t="s">
+        <v>1216</v>
+      </c>
+      <c r="G1206" t="s">
+        <v>1217</v>
+      </c>
+      <c r="H1206" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1206" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1206">
+        <v>1</v>
+      </c>
+      <c r="K1206">
+        <v>375000</v>
+      </c>
+      <c r="L1206">
+        <v>375000</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:12">
+      <c r="A1207">
+        <v>1204</v>
+      </c>
+      <c r="B1207">
+        <v>403829</v>
+      </c>
+      <c r="C1207" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1207" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E1207" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F1207" t="s">
+        <v>1220</v>
+      </c>
+      <c r="G1207" t="s">
+        <v>1221</v>
+      </c>
+      <c r="H1207" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1207" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1207">
+        <v>1</v>
+      </c>
+      <c r="K1207">
+        <v>6670000</v>
+      </c>
+      <c r="L1207">
+        <v>6670000</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:12">
+      <c r="A1208">
+        <v>1205</v>
+      </c>
+      <c r="B1208">
+        <v>403829</v>
+      </c>
+      <c r="C1208" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1208" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E1208" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F1208" t="s">
+        <v>1224</v>
+      </c>
+      <c r="G1208" t="s">
+        <v>1225</v>
+      </c>
+      <c r="H1208" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1208" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1208">
+        <v>1</v>
+      </c>
+      <c r="K1208">
+        <v>7665000</v>
+      </c>
+      <c r="L1208">
+        <v>7665000</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:12">
+      <c r="A1209">
+        <v>1206</v>
+      </c>
+      <c r="B1209">
+        <v>403829</v>
+      </c>
+      <c r="C1209" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1209" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E1209" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F1209" t="s">
+        <v>1224</v>
+      </c>
+      <c r="G1209" t="s">
+        <v>1225</v>
+      </c>
+      <c r="H1209" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1209" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1209">
+        <v>1</v>
+      </c>
+      <c r="K1209">
+        <v>32967000</v>
+      </c>
+      <c r="L1209">
+        <v>32967000</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:12">
+      <c r="A1210">
+        <v>1207</v>
+      </c>
+      <c r="B1210">
+        <v>403829</v>
+      </c>
+      <c r="C1210" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1210" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E1210" t="s">
+        <v>1226</v>
+      </c>
+      <c r="F1210" t="s">
+        <v>1227</v>
+      </c>
+      <c r="G1210" t="s">
+        <v>1228</v>
+      </c>
+      <c r="H1210" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1210" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1210">
+        <v>1</v>
+      </c>
+      <c r="K1210">
+        <v>1610000</v>
+      </c>
+      <c r="L1210">
+        <v>1610000</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:12">
+      <c r="A1211">
+        <v>1208</v>
+      </c>
+      <c r="B1211">
+        <v>403829</v>
+      </c>
+      <c r="C1211" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1211" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E1211" t="s">
+        <v>1226</v>
+      </c>
+      <c r="F1211" t="s">
+        <v>1227</v>
+      </c>
+      <c r="G1211" t="s">
+        <v>1228</v>
+      </c>
+      <c r="H1211" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1211" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1211">
+        <v>1</v>
+      </c>
+      <c r="K1211">
+        <v>50320000</v>
+      </c>
+      <c r="L1211">
+        <v>50320000</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:12">
+      <c r="A1212">
+        <v>1209</v>
+      </c>
+      <c r="B1212">
+        <v>403829</v>
+      </c>
+      <c r="C1212" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1212" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E1212" t="s">
+        <v>1229</v>
+      </c>
+      <c r="F1212" t="s">
+        <v>1230</v>
+      </c>
+      <c r="G1212" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H1212" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1212" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1212">
+        <v>1</v>
+      </c>
+      <c r="K1212">
+        <v>2415000</v>
+      </c>
+      <c r="L1212">
+        <v>2415000</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:12">
+      <c r="A1213">
+        <v>1210</v>
+      </c>
+      <c r="B1213">
+        <v>403829</v>
+      </c>
+      <c r="C1213" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1213" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E1213" t="s">
+        <v>1229</v>
+      </c>
+      <c r="F1213" t="s">
+        <v>1230</v>
+      </c>
+      <c r="G1213" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H1213" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1213" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1213">
+        <v>1</v>
+      </c>
+      <c r="K1213">
+        <v>25493000</v>
+      </c>
+      <c r="L1213">
+        <v>25493000</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:12">
+      <c r="A1214">
+        <v>1211</v>
+      </c>
+      <c r="B1214">
+        <v>403829</v>
+      </c>
+      <c r="C1214" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1214" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E1214" t="s">
+        <v>1232</v>
+      </c>
+      <c r="F1214" t="s">
         <v>1233</v>
       </c>
-      <c r="E1205" t="s">
+      <c r="G1214" t="s">
+        <v>1234</v>
+      </c>
+      <c r="H1214" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1214" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1214">
+        <v>1</v>
+      </c>
+      <c r="K1214">
+        <v>1610000</v>
+      </c>
+      <c r="L1214">
+        <v>1610000</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:12">
+      <c r="A1215">
+        <v>1212</v>
+      </c>
+      <c r="B1215">
+        <v>403829</v>
+      </c>
+      <c r="C1215" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1215" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E1215" t="s">
+        <v>1232</v>
+      </c>
+      <c r="F1215" t="s">
+        <v>1233</v>
+      </c>
+      <c r="G1215" t="s">
+        <v>1234</v>
+      </c>
+      <c r="H1215" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1215" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1215">
+        <v>1</v>
+      </c>
+      <c r="K1215">
+        <v>16798000</v>
+      </c>
+      <c r="L1215">
+        <v>16798000</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:12">
+      <c r="A1216">
+        <v>1213</v>
+      </c>
+      <c r="B1216">
+        <v>403829</v>
+      </c>
+      <c r="C1216" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1216" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E1216" t="s">
+        <v>1235</v>
+      </c>
+      <c r="F1216" t="s">
+        <v>1236</v>
+      </c>
+      <c r="G1216" t="s">
+        <v>1237</v>
+      </c>
+      <c r="H1216" t="s">
+        <v>241</v>
+      </c>
+      <c r="I1216" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1216">
+        <v>1</v>
+      </c>
+      <c r="K1216">
+        <v>1610000</v>
+      </c>
+      <c r="L1216">
+        <v>1610000</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:12">
+      <c r="A1217">
+        <v>1214</v>
+      </c>
+      <c r="B1217">
+        <v>403829</v>
+      </c>
+      <c r="C1217" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1217" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E1217" t="s">
+        <v>1235</v>
+      </c>
+      <c r="F1217" t="s">
+        <v>1236</v>
+      </c>
+      <c r="G1217" t="s">
+        <v>1237</v>
+      </c>
+      <c r="H1217" t="s">
+        <v>149</v>
+      </c>
+      <c r="I1217" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1217">
+        <v>1</v>
+      </c>
+      <c r="K1217">
+        <v>24642000</v>
+      </c>
+      <c r="L1217">
+        <v>24642000</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:12">
+      <c r="A1218">
+        <v>1215</v>
+      </c>
+      <c r="B1218">
+        <v>403829</v>
+      </c>
+      <c r="C1218" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1218" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E1218" t="s">
+        <v>1235</v>
+      </c>
+      <c r="F1218" t="s">
+        <v>1236</v>
+      </c>
+      <c r="G1218" t="s">
+        <v>1237</v>
+      </c>
+      <c r="H1218" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1218" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1218">
+        <v>1</v>
+      </c>
+      <c r="K1218">
+        <v>3321000</v>
+      </c>
+      <c r="L1218">
+        <v>3321000</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:12">
+      <c r="A1219">
+        <v>1216</v>
+      </c>
+      <c r="B1219">
+        <v>403829</v>
+      </c>
+      <c r="C1219" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1219" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E1219" t="s">
+        <v>1238</v>
+      </c>
+      <c r="F1219" t="s">
+        <v>1239</v>
+      </c>
+      <c r="G1219" t="s">
+        <v>1240</v>
+      </c>
+      <c r="H1219" t="s">
+        <v>266</v>
+      </c>
+      <c r="I1219" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1219">
+        <v>1</v>
+      </c>
+      <c r="K1219">
+        <v>11515000</v>
+      </c>
+      <c r="L1219">
+        <v>11515000</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:12">
+      <c r="A1220">
+        <v>1217</v>
+      </c>
+      <c r="B1220">
+        <v>403829</v>
+      </c>
+      <c r="C1220" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1220" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E1220" t="s">
+        <v>1238</v>
+      </c>
+      <c r="F1220" t="s">
+        <v>1239</v>
+      </c>
+      <c r="G1220" t="s">
+        <v>1240</v>
+      </c>
+      <c r="H1220" t="s">
+        <v>267</v>
+      </c>
+      <c r="I1220" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1220">
+        <v>1</v>
+      </c>
+      <c r="K1220">
+        <v>74962000</v>
+      </c>
+      <c r="L1220">
+        <v>74962000</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:12">
+      <c r="A1221">
+        <v>1218</v>
+      </c>
+      <c r="B1221">
+        <v>403829</v>
+      </c>
+      <c r="C1221" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1221" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E1221" t="s">
+        <v>1238</v>
+      </c>
+      <c r="F1221" t="s">
+        <v>1239</v>
+      </c>
+      <c r="G1221" t="s">
+        <v>1240</v>
+      </c>
+      <c r="H1221" t="s">
+        <v>268</v>
+      </c>
+      <c r="I1221" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1221">
+        <v>1</v>
+      </c>
+      <c r="K1221">
+        <v>25256000</v>
+      </c>
+      <c r="L1221">
+        <v>25256000</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:12">
+      <c r="A1222">
+        <v>1219</v>
+      </c>
+      <c r="B1222">
+        <v>403829</v>
+      </c>
+      <c r="C1222" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1222" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E1222" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F1222" t="s">
+        <v>1242</v>
+      </c>
+      <c r="G1222" t="s">
+        <v>1243</v>
+      </c>
+      <c r="H1222" t="s">
+        <v>266</v>
+      </c>
+      <c r="I1222" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1222">
+        <v>1</v>
+      </c>
+      <c r="K1222">
+        <v>12040000</v>
+      </c>
+      <c r="L1222">
+        <v>12040000</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:12">
+      <c r="A1223">
+        <v>1220</v>
+      </c>
+      <c r="B1223">
+        <v>403829</v>
+      </c>
+      <c r="C1223" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1223" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E1223" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F1223" t="s">
+        <v>1242</v>
+      </c>
+      <c r="G1223" t="s">
+        <v>1243</v>
+      </c>
+      <c r="H1223" t="s">
+        <v>267</v>
+      </c>
+      <c r="I1223" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1223">
+        <v>1</v>
+      </c>
+      <c r="K1223">
+        <v>109076000</v>
+      </c>
+      <c r="L1223">
+        <v>109076000</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:12">
+      <c r="A1224">
+        <v>1221</v>
+      </c>
+      <c r="B1224">
+        <v>403829</v>
+      </c>
+      <c r="C1224" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1224" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E1224" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F1224" t="s">
+        <v>1242</v>
+      </c>
+      <c r="G1224" t="s">
+        <v>1243</v>
+      </c>
+      <c r="H1224" t="s">
+        <v>268</v>
+      </c>
+      <c r="I1224" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1224">
+        <v>1</v>
+      </c>
+      <c r="K1224">
+        <v>24272000</v>
+      </c>
+      <c r="L1224">
+        <v>24272000</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:12">
+      <c r="A1225">
+        <v>1222</v>
+      </c>
+      <c r="B1225">
+        <v>403829</v>
+      </c>
+      <c r="C1225" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1225" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E1225" t="s">
+        <v>1244</v>
+      </c>
+      <c r="F1225" t="s">
+        <v>1245</v>
+      </c>
+      <c r="G1225" t="s">
         <v>1246</v>
       </c>
-      <c r="F1205" t="s">
+      <c r="H1225" t="s">
+        <v>149</v>
+      </c>
+      <c r="I1225" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1225">
+        <v>1</v>
+      </c>
+      <c r="K1225">
+        <v>2331000</v>
+      </c>
+      <c r="L1225">
+        <v>2331000</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:12">
+      <c r="A1226">
+        <v>1223</v>
+      </c>
+      <c r="B1226">
+        <v>403829</v>
+      </c>
+      <c r="C1226" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1226" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E1226" t="s">
+        <v>1244</v>
+      </c>
+      <c r="F1226" t="s">
+        <v>1245</v>
+      </c>
+      <c r="G1226" t="s">
+        <v>1246</v>
+      </c>
+      <c r="H1226" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1226" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1226">
+        <v>1</v>
+      </c>
+      <c r="K1226">
+        <v>861000</v>
+      </c>
+      <c r="L1226">
+        <v>861000</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:12">
+      <c r="A1227">
+        <v>1224</v>
+      </c>
+      <c r="B1227">
+        <v>403829</v>
+      </c>
+      <c r="C1227" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1227" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E1227" t="s">
         <v>1247</v>
       </c>
-      <c r="G1205" t="s">
+      <c r="F1227" t="s">
         <v>1248</v>
       </c>
-      <c r="H1205" t="s">
+      <c r="G1227" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1227" t="s">
+        <v>173</v>
+      </c>
+      <c r="I1227" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1227">
+        <v>1</v>
+      </c>
+      <c r="K1227">
+        <v>2017000</v>
+      </c>
+      <c r="L1227">
+        <v>2017000</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:12">
+      <c r="A1228">
+        <v>1225</v>
+      </c>
+      <c r="B1228">
+        <v>403829</v>
+      </c>
+      <c r="C1228" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1228" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E1228" t="s">
+        <v>1247</v>
+      </c>
+      <c r="F1228" t="s">
+        <v>1248</v>
+      </c>
+      <c r="G1228" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1228" t="s">
+        <v>174</v>
+      </c>
+      <c r="I1228" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1228">
+        <v>1</v>
+      </c>
+      <c r="K1228">
+        <v>222500</v>
+      </c>
+      <c r="L1228">
+        <v>222500</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:12">
+      <c r="A1229">
+        <v>1226</v>
+      </c>
+      <c r="B1229">
+        <v>403829</v>
+      </c>
+      <c r="C1229" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1229" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E1229" t="s">
+        <v>1247</v>
+      </c>
+      <c r="F1229" t="s">
+        <v>1248</v>
+      </c>
+      <c r="G1229" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1229" t="s">
+        <v>175</v>
+      </c>
+      <c r="I1229" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1229">
+        <v>1</v>
+      </c>
+      <c r="K1229">
+        <v>4279000</v>
+      </c>
+      <c r="L1229">
+        <v>4279000</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:12">
+      <c r="A1230">
+        <v>1227</v>
+      </c>
+      <c r="B1230">
+        <v>403829</v>
+      </c>
+      <c r="C1230" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1230" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E1230" t="s">
+        <v>1247</v>
+      </c>
+      <c r="F1230" t="s">
+        <v>1248</v>
+      </c>
+      <c r="G1230" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1230" t="s">
+        <v>176</v>
+      </c>
+      <c r="I1230" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1230">
+        <v>1</v>
+      </c>
+      <c r="K1230">
+        <v>25625000</v>
+      </c>
+      <c r="L1230">
+        <v>25625000</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:12">
+      <c r="A1231">
+        <v>1228</v>
+      </c>
+      <c r="B1231">
+        <v>403829</v>
+      </c>
+      <c r="C1231" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1231" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E1231" t="s">
+        <v>1247</v>
+      </c>
+      <c r="F1231" t="s">
+        <v>1248</v>
+      </c>
+      <c r="G1231" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1231" t="s">
+        <v>1040</v>
+      </c>
+      <c r="I1231" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1231">
+        <v>1</v>
+      </c>
+      <c r="K1231">
+        <v>9115000</v>
+      </c>
+      <c r="L1231">
+        <v>9115000</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:12">
+      <c r="A1232">
+        <v>1229</v>
+      </c>
+      <c r="B1232">
+        <v>403829</v>
+      </c>
+      <c r="C1232" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1232" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E1232" t="s">
+        <v>1247</v>
+      </c>
+      <c r="F1232" t="s">
+        <v>1248</v>
+      </c>
+      <c r="G1232" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1232" t="s">
+        <v>177</v>
+      </c>
+      <c r="I1232" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1232">
+        <v>1</v>
+      </c>
+      <c r="K1232">
+        <v>41321696</v>
+      </c>
+      <c r="L1232">
+        <v>41321696</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:12">
+      <c r="A1233">
+        <v>1230</v>
+      </c>
+      <c r="B1233">
+        <v>403829</v>
+      </c>
+      <c r="C1233" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1233" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E1233" t="s">
+        <v>1247</v>
+      </c>
+      <c r="F1233" t="s">
+        <v>1248</v>
+      </c>
+      <c r="G1233" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1233" t="s">
+        <v>178</v>
+      </c>
+      <c r="I1233" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1233">
+        <v>1</v>
+      </c>
+      <c r="K1233">
+        <v>9468528</v>
+      </c>
+      <c r="L1233">
+        <v>9468528</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:12">
+      <c r="A1234">
+        <v>1231</v>
+      </c>
+      <c r="B1234">
+        <v>403829</v>
+      </c>
+      <c r="C1234" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1234" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E1234" t="s">
+        <v>1247</v>
+      </c>
+      <c r="F1234" t="s">
+        <v>1248</v>
+      </c>
+      <c r="G1234" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1234" t="s">
+        <v>179</v>
+      </c>
+      <c r="I1234" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1234">
+        <v>1</v>
+      </c>
+      <c r="K1234">
+        <v>13729784</v>
+      </c>
+      <c r="L1234">
+        <v>13729784</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:12">
+      <c r="A1235">
+        <v>1232</v>
+      </c>
+      <c r="B1235">
+        <v>403829</v>
+      </c>
+      <c r="C1235" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1235" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E1235" t="s">
+        <v>1247</v>
+      </c>
+      <c r="F1235" t="s">
+        <v>1248</v>
+      </c>
+      <c r="G1235" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1235" t="s">
+        <v>180</v>
+      </c>
+      <c r="I1235" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1235">
+        <v>1</v>
+      </c>
+      <c r="K1235">
+        <v>4629928</v>
+      </c>
+      <c r="L1235">
+        <v>4629928</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:12">
+      <c r="A1236">
+        <v>1233</v>
+      </c>
+      <c r="B1236">
+        <v>403829</v>
+      </c>
+      <c r="C1236" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1236" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E1236" t="s">
+        <v>1247</v>
+      </c>
+      <c r="F1236" t="s">
+        <v>1248</v>
+      </c>
+      <c r="G1236" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1236" t="s">
+        <v>181</v>
+      </c>
+      <c r="I1236" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1236">
+        <v>1</v>
+      </c>
+      <c r="K1236">
+        <v>750000</v>
+      </c>
+      <c r="L1236">
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:12">
+      <c r="A1237">
+        <v>1234</v>
+      </c>
+      <c r="B1237">
+        <v>403829</v>
+      </c>
+      <c r="C1237" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1237" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E1237" t="s">
+        <v>1247</v>
+      </c>
+      <c r="F1237" t="s">
+        <v>1248</v>
+      </c>
+      <c r="G1237" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1237" t="s">
+        <v>185</v>
+      </c>
+      <c r="I1237" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1237">
+        <v>1</v>
+      </c>
+      <c r="K1237">
+        <v>4845000</v>
+      </c>
+      <c r="L1237">
+        <v>4845000</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:12">
+      <c r="A1238">
+        <v>1235</v>
+      </c>
+      <c r="B1238">
+        <v>403829</v>
+      </c>
+      <c r="C1238" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1238" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E1238" t="s">
+        <v>1247</v>
+      </c>
+      <c r="F1238" t="s">
+        <v>1248</v>
+      </c>
+      <c r="G1238" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1238" t="s">
+        <v>186</v>
+      </c>
+      <c r="I1238" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1238">
+        <v>1</v>
+      </c>
+      <c r="K1238">
+        <v>1225000</v>
+      </c>
+      <c r="L1238">
+        <v>1225000</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:12">
+      <c r="A1239">
+        <v>1236</v>
+      </c>
+      <c r="B1239">
+        <v>403829</v>
+      </c>
+      <c r="C1239" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1239" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E1239" t="s">
+        <v>1247</v>
+      </c>
+      <c r="F1239" t="s">
+        <v>1248</v>
+      </c>
+      <c r="G1239" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1239" t="s">
+        <v>187</v>
+      </c>
+      <c r="I1239" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1239">
+        <v>1</v>
+      </c>
+      <c r="K1239">
+        <v>233875</v>
+      </c>
+      <c r="L1239">
+        <v>233875</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:12">
+      <c r="A1240">
+        <v>1237</v>
+      </c>
+      <c r="B1240">
+        <v>403829</v>
+      </c>
+      <c r="C1240" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1240" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E1240" t="s">
+        <v>1247</v>
+      </c>
+      <c r="F1240" t="s">
+        <v>1248</v>
+      </c>
+      <c r="G1240" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1240" t="s">
+        <v>189</v>
+      </c>
+      <c r="I1240" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1240">
+        <v>1</v>
+      </c>
+      <c r="K1240">
+        <v>385700</v>
+      </c>
+      <c r="L1240">
+        <v>385700</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:12">
+      <c r="A1241">
+        <v>1238</v>
+      </c>
+      <c r="B1241">
+        <v>403829</v>
+      </c>
+      <c r="C1241" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1241" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E1241" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F1241" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G1241" t="s">
+        <v>1251</v>
+      </c>
+      <c r="H1241" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1241" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1241">
+        <v>1</v>
+      </c>
+      <c r="K1241">
+        <v>148480900</v>
+      </c>
+      <c r="L1241">
+        <v>148480900</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:12">
+      <c r="A1242">
+        <v>1239</v>
+      </c>
+      <c r="B1242">
+        <v>403829</v>
+      </c>
+      <c r="C1242" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1242" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E1242" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F1242" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G1242" t="s">
+        <v>1251</v>
+      </c>
+      <c r="H1242" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1242" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1242">
+        <v>1</v>
+      </c>
+      <c r="K1242">
+        <v>1704</v>
+      </c>
+      <c r="L1242">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:12">
+      <c r="A1243">
+        <v>1240</v>
+      </c>
+      <c r="B1243">
+        <v>403829</v>
+      </c>
+      <c r="C1243" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1243" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E1243" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F1243" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G1243" t="s">
+        <v>1251</v>
+      </c>
+      <c r="H1243" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1243" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1243">
+        <v>1</v>
+      </c>
+      <c r="K1243">
+        <v>10913750</v>
+      </c>
+      <c r="L1243">
+        <v>10913750</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:12">
+      <c r="A1244">
+        <v>1241</v>
+      </c>
+      <c r="B1244">
+        <v>403829</v>
+      </c>
+      <c r="C1244" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1244" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E1244" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F1244" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G1244" t="s">
+        <v>1251</v>
+      </c>
+      <c r="H1244" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1244" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1244">
+        <v>1</v>
+      </c>
+      <c r="K1244">
+        <v>3150736</v>
+      </c>
+      <c r="L1244">
+        <v>3150736</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:12">
+      <c r="A1245">
+        <v>1242</v>
+      </c>
+      <c r="B1245">
+        <v>403829</v>
+      </c>
+      <c r="C1245" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1245" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E1245" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F1245" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G1245" t="s">
+        <v>1251</v>
+      </c>
+      <c r="H1245" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1245" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1245">
+        <v>1</v>
+      </c>
+      <c r="K1245">
+        <v>1260000</v>
+      </c>
+      <c r="L1245">
+        <v>1260000</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:12">
+      <c r="A1246">
+        <v>1243</v>
+      </c>
+      <c r="B1246">
+        <v>403829</v>
+      </c>
+      <c r="C1246" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1246" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E1246" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F1246" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G1246" t="s">
+        <v>1251</v>
+      </c>
+      <c r="H1246" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1246" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1246">
+        <v>1</v>
+      </c>
+      <c r="K1246">
+        <v>9834000</v>
+      </c>
+      <c r="L1246">
+        <v>9834000</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:12">
+      <c r="A1247">
+        <v>1244</v>
+      </c>
+      <c r="B1247">
+        <v>403829</v>
+      </c>
+      <c r="C1247" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1247" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E1247" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F1247" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G1247" t="s">
+        <v>1251</v>
+      </c>
+      <c r="H1247" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1247" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1247">
+        <v>1</v>
+      </c>
+      <c r="K1247">
+        <v>197170</v>
+      </c>
+      <c r="L1247">
+        <v>197170</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:12">
+      <c r="A1248">
+        <v>1245</v>
+      </c>
+      <c r="B1248">
+        <v>403829</v>
+      </c>
+      <c r="C1248" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1248" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E1248" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F1248" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G1248" t="s">
+        <v>1251</v>
+      </c>
+      <c r="H1248" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1248" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1248">
+        <v>1</v>
+      </c>
+      <c r="K1248">
+        <v>7459260</v>
+      </c>
+      <c r="L1248">
+        <v>7459260</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:12">
+      <c r="A1249">
+        <v>1246</v>
+      </c>
+      <c r="B1249">
+        <v>403829</v>
+      </c>
+      <c r="C1249" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1249" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E1249" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F1249" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G1249" t="s">
+        <v>1251</v>
+      </c>
+      <c r="H1249" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1249" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1249">
+        <v>1</v>
+      </c>
+      <c r="K1249">
+        <v>3880000</v>
+      </c>
+      <c r="L1249">
+        <v>3880000</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:12">
+      <c r="A1250">
+        <v>1247</v>
+      </c>
+      <c r="B1250">
+        <v>403829</v>
+      </c>
+      <c r="C1250" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1250" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1250" t="s">
+        <v>1252</v>
+      </c>
+      <c r="F1250" t="s">
+        <v>1253</v>
+      </c>
+      <c r="G1250" t="s">
+        <v>1254</v>
+      </c>
+      <c r="H1250" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1250" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1250">
+        <v>1</v>
+      </c>
+      <c r="K1250">
+        <v>461900</v>
+      </c>
+      <c r="L1250">
+        <v>461900</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:12">
+      <c r="A1251">
+        <v>1248</v>
+      </c>
+      <c r="B1251">
+        <v>403829</v>
+      </c>
+      <c r="C1251" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1251" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1251" t="s">
+        <v>1252</v>
+      </c>
+      <c r="F1251" t="s">
+        <v>1253</v>
+      </c>
+      <c r="G1251" t="s">
+        <v>1254</v>
+      </c>
+      <c r="H1251" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1251" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1251">
+        <v>1</v>
+      </c>
+      <c r="K1251">
+        <v>4</v>
+      </c>
+      <c r="L1251">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:12">
+      <c r="A1252">
+        <v>1249</v>
+      </c>
+      <c r="B1252">
+        <v>403829</v>
+      </c>
+      <c r="C1252" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1252" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1252" t="s">
+        <v>1252</v>
+      </c>
+      <c r="F1252" t="s">
+        <v>1253</v>
+      </c>
+      <c r="G1252" t="s">
+        <v>1254</v>
+      </c>
+      <c r="H1252" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1252" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1252">
+        <v>1</v>
+      </c>
+      <c r="K1252">
+        <v>23810</v>
+      </c>
+      <c r="L1252">
+        <v>23810</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:12">
+      <c r="A1253">
+        <v>1250</v>
+      </c>
+      <c r="B1253">
+        <v>403829</v>
+      </c>
+      <c r="C1253" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1253" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1253" t="s">
+        <v>1252</v>
+      </c>
+      <c r="F1253" t="s">
+        <v>1253</v>
+      </c>
+      <c r="G1253" t="s">
+        <v>1254</v>
+      </c>
+      <c r="H1253" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1253" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1253">
+        <v>1</v>
+      </c>
+      <c r="K1253">
+        <v>9524</v>
+      </c>
+      <c r="L1253">
+        <v>9524</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:12">
+      <c r="A1254">
+        <v>1251</v>
+      </c>
+      <c r="B1254">
+        <v>403829</v>
+      </c>
+      <c r="C1254" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1254" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1254" t="s">
+        <v>1255</v>
+      </c>
+      <c r="F1254" t="s">
+        <v>1256</v>
+      </c>
+      <c r="G1254" t="s">
+        <v>1257</v>
+      </c>
+      <c r="H1254" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1254" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1254">
+        <v>1</v>
+      </c>
+      <c r="K1254">
+        <v>685700</v>
+      </c>
+      <c r="L1254">
+        <v>685700</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:12">
+      <c r="A1255">
+        <v>1252</v>
+      </c>
+      <c r="B1255">
+        <v>403829</v>
+      </c>
+      <c r="C1255" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1255" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1255" t="s">
+        <v>1255</v>
+      </c>
+      <c r="F1255" t="s">
+        <v>1256</v>
+      </c>
+      <c r="G1255" t="s">
+        <v>1257</v>
+      </c>
+      <c r="H1255" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1255" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1255">
+        <v>1</v>
+      </c>
+      <c r="K1255">
+        <v>68570</v>
+      </c>
+      <c r="L1255">
+        <v>68570</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:12">
+      <c r="A1256">
+        <v>1253</v>
+      </c>
+      <c r="B1256">
+        <v>403829</v>
+      </c>
+      <c r="C1256" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1256" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E1256" t="s">
+        <v>1255</v>
+      </c>
+      <c r="F1256" t="s">
+        <v>1256</v>
+      </c>
+      <c r="G1256" t="s">
+        <v>1257</v>
+      </c>
+      <c r="H1256" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1256" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1256">
+        <v>1</v>
+      </c>
+      <c r="K1256">
+        <v>4762</v>
+      </c>
+      <c r="L1256">
+        <v>4762</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:12">
+      <c r="A1257">
+        <v>1254</v>
+      </c>
+      <c r="B1257">
+        <v>403829</v>
+      </c>
+      <c r="C1257" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1257" t="s">
+        <v>1258</v>
+      </c>
+      <c r="E1257" t="s">
+        <v>1259</v>
+      </c>
+      <c r="F1257" t="s">
+        <v>1260</v>
+      </c>
+      <c r="G1257" t="s">
+        <v>1261</v>
+      </c>
+      <c r="H1257" t="s">
+        <v>272</v>
+      </c>
+      <c r="I1257" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1257">
+        <v>1</v>
+      </c>
+      <c r="K1257">
+        <v>878387055</v>
+      </c>
+      <c r="L1257">
+        <v>878387055</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:12">
+      <c r="A1258">
+        <v>1255</v>
+      </c>
+      <c r="B1258">
+        <v>403829</v>
+      </c>
+      <c r="C1258" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1258" t="s">
+        <v>1258</v>
+      </c>
+      <c r="E1258" t="s">
+        <v>1262</v>
+      </c>
+      <c r="F1258" t="s">
+        <v>1263</v>
+      </c>
+      <c r="G1258" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H1258" t="s">
         <v>276</v>
       </c>
-      <c r="I1205" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1205">
-        <v>1</v>
-      </c>
-      <c r="K1205">
+      <c r="I1258" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1258">
+        <v>1</v>
+      </c>
+      <c r="K1258">
+        <v>218758166</v>
+      </c>
+      <c r="L1258">
+        <v>218758166</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:12">
+      <c r="A1259">
+        <v>1256</v>
+      </c>
+      <c r="B1259">
+        <v>403829</v>
+      </c>
+      <c r="C1259" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1259" t="s">
+        <v>1258</v>
+      </c>
+      <c r="E1259" t="s">
+        <v>1265</v>
+      </c>
+      <c r="F1259" t="s">
+        <v>1266</v>
+      </c>
+      <c r="G1259" t="s">
+        <v>1267</v>
+      </c>
+      <c r="H1259" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1259" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1259">
+        <v>1</v>
+      </c>
+      <c r="K1259">
+        <v>286896591</v>
+      </c>
+      <c r="L1259">
+        <v>286896591</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:12">
+      <c r="A1260">
+        <v>1257</v>
+      </c>
+      <c r="B1260">
+        <v>403829</v>
+      </c>
+      <c r="C1260" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1260" t="s">
+        <v>1258</v>
+      </c>
+      <c r="E1260" t="s">
+        <v>1268</v>
+      </c>
+      <c r="F1260" t="s">
+        <v>1269</v>
+      </c>
+      <c r="G1260" t="s">
+        <v>1270</v>
+      </c>
+      <c r="H1260" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1260" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1260">
+        <v>1</v>
+      </c>
+      <c r="K1260">
+        <v>157239652</v>
+      </c>
+      <c r="L1260">
+        <v>157239652</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:12">
+      <c r="A1261">
+        <v>1258</v>
+      </c>
+      <c r="B1261">
+        <v>403829</v>
+      </c>
+      <c r="C1261" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1261" t="s">
+        <v>1258</v>
+      </c>
+      <c r="E1261" t="s">
+        <v>1271</v>
+      </c>
+      <c r="F1261" t="s">
+        <v>1272</v>
+      </c>
+      <c r="G1261" t="s">
+        <v>1273</v>
+      </c>
+      <c r="H1261" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1261" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1261">
+        <v>1</v>
+      </c>
+      <c r="K1261">
         <v>102124944</v>
       </c>
-      <c r="L1205">
+      <c r="L1261">
         <v>102124944</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:12">
+      <c r="A1262">
+        <v>1259</v>
+      </c>
+      <c r="B1262">
+        <v>403829</v>
+      </c>
+      <c r="C1262" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1262" t="s">
+        <v>1274</v>
+      </c>
+      <c r="E1262" t="s">
+        <v>1275</v>
+      </c>
+      <c r="F1262" t="s">
+        <v>1276</v>
+      </c>
+      <c r="G1262" t="s">
+        <v>206</v>
+      </c>
+      <c r="H1262" t="s">
+        <v>173</v>
+      </c>
+      <c r="I1262" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1262">
+        <v>1</v>
+      </c>
+      <c r="K1262">
+        <v>60000</v>
+      </c>
+      <c r="L1262">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:12">
+      <c r="A1263">
+        <v>1260</v>
+      </c>
+      <c r="B1263">
+        <v>403829</v>
+      </c>
+      <c r="C1263" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1263" t="s">
+        <v>1274</v>
+      </c>
+      <c r="E1263" t="s">
+        <v>1275</v>
+      </c>
+      <c r="F1263" t="s">
+        <v>1276</v>
+      </c>
+      <c r="G1263" t="s">
+        <v>206</v>
+      </c>
+      <c r="H1263" t="s">
+        <v>207</v>
+      </c>
+      <c r="I1263" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1263">
+        <v>1</v>
+      </c>
+      <c r="K1263">
+        <v>532800</v>
+      </c>
+      <c r="L1263">
+        <v>532800</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:12">
+      <c r="A1264">
+        <v>1261</v>
+      </c>
+      <c r="B1264">
+        <v>403829</v>
+      </c>
+      <c r="C1264" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1264" t="s">
+        <v>1274</v>
+      </c>
+      <c r="E1264" t="s">
+        <v>1275</v>
+      </c>
+      <c r="F1264" t="s">
+        <v>1276</v>
+      </c>
+      <c r="G1264" t="s">
+        <v>206</v>
+      </c>
+      <c r="H1264" t="s">
+        <v>186</v>
+      </c>
+      <c r="I1264" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1264">
+        <v>1</v>
+      </c>
+      <c r="K1264">
+        <v>3512800</v>
+      </c>
+      <c r="L1264">
+        <v>3512800</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:12">
+      <c r="A1265">
+        <v>1262</v>
+      </c>
+      <c r="B1265">
+        <v>403829</v>
+      </c>
+      <c r="C1265" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1265" t="s">
+        <v>1274</v>
+      </c>
+      <c r="E1265" t="s">
+        <v>1275</v>
+      </c>
+      <c r="F1265" t="s">
+        <v>1276</v>
+      </c>
+      <c r="G1265" t="s">
+        <v>206</v>
+      </c>
+      <c r="H1265" t="s">
+        <v>189</v>
+      </c>
+      <c r="I1265" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1265">
+        <v>1</v>
+      </c>
+      <c r="K1265">
+        <v>1963000</v>
+      </c>
+      <c r="L1265">
+        <v>1963000</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:12">
+      <c r="A1266">
+        <v>1263</v>
+      </c>
+      <c r="B1266">
+        <v>403829</v>
+      </c>
+      <c r="C1266" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1266" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E1266" t="s">
+        <v>1277</v>
+      </c>
+      <c r="F1266" t="s">
+        <v>1278</v>
+      </c>
+      <c r="G1266" t="s">
+        <v>1279</v>
+      </c>
+      <c r="H1266" t="s">
+        <v>111</v>
+      </c>
+      <c r="I1266" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1266">
+        <v>1</v>
+      </c>
+      <c r="K1266">
+        <v>63500000</v>
+      </c>
+      <c r="L1266">
+        <v>63500000</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:12">
+      <c r="A1267">
+        <v>1264</v>
+      </c>
+      <c r="B1267">
+        <v>403829</v>
+      </c>
+      <c r="C1267" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1267" t="s">
+        <v>1280</v>
+      </c>
+      <c r="E1267" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F1267" t="s">
+        <v>1282</v>
+      </c>
+      <c r="G1267" t="s">
+        <v>1283</v>
+      </c>
+      <c r="H1267" t="s">
+        <v>272</v>
+      </c>
+      <c r="I1267" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1267">
+        <v>1</v>
+      </c>
+      <c r="K1267">
+        <v>1094536726</v>
+      </c>
+      <c r="L1267">
+        <v>1094536726</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:12">
+      <c r="A1268">
+        <v>1265</v>
+      </c>
+      <c r="B1268">
+        <v>403829</v>
+      </c>
+      <c r="C1268" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1268" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E1268" t="s">
+        <v>1284</v>
+      </c>
+      <c r="F1268" t="s">
+        <v>1285</v>
+      </c>
+      <c r="G1268" t="s">
+        <v>1286</v>
+      </c>
+      <c r="H1268" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1268" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1268">
+        <v>1</v>
+      </c>
+      <c r="K1268">
+        <v>161822342</v>
+      </c>
+      <c r="L1268">
+        <v>161822342</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:12">
+      <c r="A1269">
+        <v>1266</v>
+      </c>
+      <c r="B1269">
+        <v>403829</v>
+      </c>
+      <c r="C1269" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1269" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E1269" t="s">
+        <v>1287</v>
+      </c>
+      <c r="F1269" t="s">
+        <v>1288</v>
+      </c>
+      <c r="G1269" t="s">
+        <v>1289</v>
+      </c>
+      <c r="H1269" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1269" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1269">
+        <v>1</v>
+      </c>
+      <c r="K1269">
+        <v>20764662</v>
+      </c>
+      <c r="L1269">
+        <v>20764662</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:12">
+      <c r="A1270">
+        <v>1267</v>
+      </c>
+      <c r="B1270">
+        <v>403829</v>
+      </c>
+      <c r="C1270" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1270" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E1270" t="s">
+        <v>1290</v>
+      </c>
+      <c r="F1270" t="s">
+        <v>1291</v>
+      </c>
+      <c r="G1270" t="s">
+        <v>1292</v>
+      </c>
+      <c r="H1270" t="s">
+        <v>797</v>
+      </c>
+      <c r="I1270" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1270">
+        <v>1</v>
+      </c>
+      <c r="K1270">
+        <v>2330000</v>
+      </c>
+      <c r="L1270">
+        <v>2330000</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:12">
+      <c r="A1271">
+        <v>1268</v>
+      </c>
+      <c r="B1271">
+        <v>403829</v>
+      </c>
+      <c r="C1271" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1271" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E1271" t="s">
+        <v>1294</v>
+      </c>
+      <c r="F1271" t="s">
+        <v>1295</v>
+      </c>
+      <c r="G1271" t="s">
+        <v>1296</v>
+      </c>
+      <c r="H1271" t="s">
+        <v>154</v>
+      </c>
+      <c r="I1271" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1271">
+        <v>1</v>
+      </c>
+      <c r="K1271">
+        <v>2550000</v>
+      </c>
+      <c r="L1271">
+        <v>2550000</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:12">
+      <c r="A1272">
+        <v>1269</v>
+      </c>
+      <c r="B1272">
+        <v>403829</v>
+      </c>
+      <c r="C1272" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1272" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E1272" t="s">
+        <v>1294</v>
+      </c>
+      <c r="F1272" t="s">
+        <v>1295</v>
+      </c>
+      <c r="G1272" t="s">
+        <v>1296</v>
+      </c>
+      <c r="H1272" t="s">
+        <v>155</v>
+      </c>
+      <c r="I1272" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1272">
+        <v>1</v>
+      </c>
+      <c r="K1272">
+        <v>2480000</v>
+      </c>
+      <c r="L1272">
+        <v>2480000</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:12">
+      <c r="A1273">
+        <v>1270</v>
+      </c>
+      <c r="B1273">
+        <v>403829</v>
+      </c>
+      <c r="C1273" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1273" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E1273" t="s">
+        <v>1294</v>
+      </c>
+      <c r="F1273" t="s">
+        <v>1295</v>
+      </c>
+      <c r="G1273" t="s">
+        <v>1296</v>
+      </c>
+      <c r="H1273" t="s">
+        <v>156</v>
+      </c>
+      <c r="I1273" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1273">
+        <v>1</v>
+      </c>
+      <c r="K1273">
+        <v>1230000</v>
+      </c>
+      <c r="L1273">
+        <v>1230000</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:12">
+      <c r="A1274">
+        <v>1271</v>
+      </c>
+      <c r="B1274">
+        <v>403829</v>
+      </c>
+      <c r="C1274" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1274" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E1274" t="s">
+        <v>1294</v>
+      </c>
+      <c r="F1274" t="s">
+        <v>1295</v>
+      </c>
+      <c r="G1274" t="s">
+        <v>1296</v>
+      </c>
+      <c r="H1274" t="s">
+        <v>157</v>
+      </c>
+      <c r="I1274" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1274">
+        <v>1</v>
+      </c>
+      <c r="K1274">
+        <v>1070000</v>
+      </c>
+      <c r="L1274">
+        <v>1070000</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:12">
+      <c r="A1275">
+        <v>1272</v>
+      </c>
+      <c r="B1275">
+        <v>403829</v>
+      </c>
+      <c r="C1275" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1275" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E1275" t="s">
+        <v>1294</v>
+      </c>
+      <c r="F1275" t="s">
+        <v>1295</v>
+      </c>
+      <c r="G1275" t="s">
+        <v>1296</v>
+      </c>
+      <c r="H1275" t="s">
+        <v>158</v>
+      </c>
+      <c r="I1275" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1275">
+        <v>1</v>
+      </c>
+      <c r="K1275">
+        <v>2400000</v>
+      </c>
+      <c r="L1275">
+        <v>2400000</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:12">
+      <c r="A1276">
+        <v>1273</v>
+      </c>
+      <c r="B1276">
+        <v>403829</v>
+      </c>
+      <c r="C1276" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1276" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E1276" t="s">
+        <v>1294</v>
+      </c>
+      <c r="F1276" t="s">
+        <v>1295</v>
+      </c>
+      <c r="G1276" t="s">
+        <v>1296</v>
+      </c>
+      <c r="H1276" t="s">
+        <v>159</v>
+      </c>
+      <c r="I1276" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1276">
+        <v>1</v>
+      </c>
+      <c r="K1276">
+        <v>180000</v>
+      </c>
+      <c r="L1276">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:12">
+      <c r="A1277">
+        <v>1274</v>
+      </c>
+      <c r="B1277">
+        <v>403829</v>
+      </c>
+      <c r="C1277" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1277" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E1277" t="s">
+        <v>1297</v>
+      </c>
+      <c r="F1277" t="s">
+        <v>1298</v>
+      </c>
+      <c r="G1277" t="s">
+        <v>1299</v>
+      </c>
+      <c r="H1277" t="s">
+        <v>1300</v>
+      </c>
+      <c r="I1277" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1277">
+        <v>1</v>
+      </c>
+      <c r="K1277">
+        <v>21600000</v>
+      </c>
+      <c r="L1277">
+        <v>21600000</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:12">
+      <c r="A1278">
+        <v>1275</v>
+      </c>
+      <c r="B1278">
+        <v>403829</v>
+      </c>
+      <c r="C1278" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1278" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E1278" t="s">
+        <v>1297</v>
+      </c>
+      <c r="F1278" t="s">
+        <v>1298</v>
+      </c>
+      <c r="G1278" t="s">
+        <v>1299</v>
+      </c>
+      <c r="H1278" t="s">
+        <v>1301</v>
+      </c>
+      <c r="I1278" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1278">
+        <v>1</v>
+      </c>
+      <c r="K1278">
+        <v>239200000</v>
+      </c>
+      <c r="L1278">
+        <v>239200000</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:12">
+      <c r="A1279">
+        <v>1276</v>
+      </c>
+      <c r="B1279">
+        <v>403829</v>
+      </c>
+      <c r="C1279" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1279" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E1279" t="s">
+        <v>1297</v>
+      </c>
+      <c r="F1279" t="s">
+        <v>1298</v>
+      </c>
+      <c r="G1279" t="s">
+        <v>1299</v>
+      </c>
+      <c r="H1279" t="s">
+        <v>1302</v>
+      </c>
+      <c r="I1279" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1279">
+        <v>1</v>
+      </c>
+      <c r="K1279">
+        <v>5600000</v>
+      </c>
+      <c r="L1279">
+        <v>5600000</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:12">
+      <c r="A1280">
+        <v>1277</v>
+      </c>
+      <c r="B1280">
+        <v>403829</v>
+      </c>
+      <c r="C1280" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1280" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E1280" t="s">
+        <v>1303</v>
+      </c>
+      <c r="F1280" t="s">
+        <v>1304</v>
+      </c>
+      <c r="G1280" t="s">
+        <v>1305</v>
+      </c>
+      <c r="H1280" t="s">
+        <v>1300</v>
+      </c>
+      <c r="I1280" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1280">
+        <v>1</v>
+      </c>
+      <c r="K1280">
+        <v>21600000</v>
+      </c>
+      <c r="L1280">
+        <v>21600000</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:12">
+      <c r="A1281">
+        <v>1278</v>
+      </c>
+      <c r="B1281">
+        <v>403829</v>
+      </c>
+      <c r="C1281" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1281" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E1281" t="s">
+        <v>1303</v>
+      </c>
+      <c r="F1281" t="s">
+        <v>1304</v>
+      </c>
+      <c r="G1281" t="s">
+        <v>1305</v>
+      </c>
+      <c r="H1281" t="s">
+        <v>1301</v>
+      </c>
+      <c r="I1281" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1281">
+        <v>1</v>
+      </c>
+      <c r="K1281">
+        <v>205400000</v>
+      </c>
+      <c r="L1281">
+        <v>205400000</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:12">
+      <c r="A1282">
+        <v>1279</v>
+      </c>
+      <c r="B1282">
+        <v>403829</v>
+      </c>
+      <c r="C1282" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1282" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E1282" t="s">
+        <v>1303</v>
+      </c>
+      <c r="F1282" t="s">
+        <v>1304</v>
+      </c>
+      <c r="G1282" t="s">
+        <v>1305</v>
+      </c>
+      <c r="H1282" t="s">
+        <v>1302</v>
+      </c>
+      <c r="I1282" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1282">
+        <v>1</v>
+      </c>
+      <c r="K1282">
+        <v>8400000</v>
+      </c>
+      <c r="L1282">
+        <v>8400000</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:12">
+      <c r="A1283">
+        <v>1280</v>
+      </c>
+      <c r="B1283">
+        <v>403829</v>
+      </c>
+      <c r="C1283" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1283" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E1283" t="s">
+        <v>1307</v>
+      </c>
+      <c r="F1283" t="s">
+        <v>1308</v>
+      </c>
+      <c r="G1283" t="s">
+        <v>1309</v>
+      </c>
+      <c r="H1283" t="s">
+        <v>203</v>
+      </c>
+      <c r="I1283" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1283">
+        <v>1</v>
+      </c>
+      <c r="K1283">
+        <v>184486500</v>
+      </c>
+      <c r="L1283">
+        <v>184486500</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:12">
+      <c r="A1284">
+        <v>1281</v>
+      </c>
+      <c r="B1284">
+        <v>403829</v>
+      </c>
+      <c r="C1284" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1284" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1284" t="s">
+        <v>1311</v>
+      </c>
+      <c r="F1284" t="s">
+        <v>1312</v>
+      </c>
+      <c r="G1284" t="s">
+        <v>1313</v>
+      </c>
+      <c r="H1284" t="s">
+        <v>128</v>
+      </c>
+      <c r="I1284" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1284">
+        <v>1</v>
+      </c>
+      <c r="K1284">
+        <v>5565207</v>
+      </c>
+      <c r="L1284">
+        <v>5565207</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:12">
+      <c r="A1285">
+        <v>1282</v>
+      </c>
+      <c r="B1285">
+        <v>403829</v>
+      </c>
+      <c r="C1285" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1285" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1285" t="s">
+        <v>1314</v>
+      </c>
+      <c r="F1285" t="s">
+        <v>1315</v>
+      </c>
+      <c r="G1285" t="s">
+        <v>1316</v>
+      </c>
+      <c r="H1285" t="s">
+        <v>797</v>
+      </c>
+      <c r="I1285" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1285">
+        <v>1</v>
+      </c>
+      <c r="K1285">
+        <v>1700452</v>
+      </c>
+      <c r="L1285">
+        <v>1700452</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:12">
+      <c r="A1286">
+        <v>1283</v>
+      </c>
+      <c r="B1286">
+        <v>403829</v>
+      </c>
+      <c r="C1286" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1286" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1286" t="s">
+        <v>1317</v>
+      </c>
+      <c r="F1286" t="s">
+        <v>1318</v>
+      </c>
+      <c r="G1286" t="s">
+        <v>1319</v>
+      </c>
+      <c r="H1286" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1286" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1286">
+        <v>1</v>
+      </c>
+      <c r="K1286">
+        <v>6790000</v>
+      </c>
+      <c r="L1286">
+        <v>6790000</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:12">
+      <c r="A1287">
+        <v>1284</v>
+      </c>
+      <c r="B1287">
+        <v>403829</v>
+      </c>
+      <c r="C1287" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1287" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1287" t="s">
+        <v>1317</v>
+      </c>
+      <c r="F1287" t="s">
+        <v>1318</v>
+      </c>
+      <c r="G1287" t="s">
+        <v>1319</v>
+      </c>
+      <c r="H1287" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1287" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1287">
+        <v>1</v>
+      </c>
+      <c r="K1287">
+        <v>28712000</v>
+      </c>
+      <c r="L1287">
+        <v>28712000</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:12">
+      <c r="A1288">
+        <v>1285</v>
+      </c>
+      <c r="B1288">
+        <v>403829</v>
+      </c>
+      <c r="C1288" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1288" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1288" t="s">
+        <v>1320</v>
+      </c>
+      <c r="F1288" t="s">
+        <v>1321</v>
+      </c>
+      <c r="G1288" t="s">
+        <v>1322</v>
+      </c>
+      <c r="H1288" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1288" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1288">
+        <v>1</v>
+      </c>
+      <c r="K1288">
+        <v>1400000</v>
+      </c>
+      <c r="L1288">
+        <v>1400000</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:12">
+      <c r="A1289">
+        <v>1286</v>
+      </c>
+      <c r="B1289">
+        <v>403829</v>
+      </c>
+      <c r="C1289" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1289" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1289" t="s">
+        <v>1320</v>
+      </c>
+      <c r="F1289" t="s">
+        <v>1321</v>
+      </c>
+      <c r="G1289" t="s">
+        <v>1322</v>
+      </c>
+      <c r="H1289" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1289" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1289">
+        <v>1</v>
+      </c>
+      <c r="K1289">
+        <v>43290000</v>
+      </c>
+      <c r="L1289">
+        <v>43290000</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:12">
+      <c r="A1290">
+        <v>1287</v>
+      </c>
+      <c r="B1290">
+        <v>403829</v>
+      </c>
+      <c r="C1290" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1290" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1290" t="s">
+        <v>1323</v>
+      </c>
+      <c r="F1290" t="s">
+        <v>1324</v>
+      </c>
+      <c r="G1290" t="s">
+        <v>1325</v>
+      </c>
+      <c r="H1290" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1290" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1290">
+        <v>1</v>
+      </c>
+      <c r="K1290">
+        <v>2100000</v>
+      </c>
+      <c r="L1290">
+        <v>2100000</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:12">
+      <c r="A1291">
+        <v>1288</v>
+      </c>
+      <c r="B1291">
+        <v>403829</v>
+      </c>
+      <c r="C1291" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1291" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1291" t="s">
+        <v>1323</v>
+      </c>
+      <c r="F1291" t="s">
+        <v>1324</v>
+      </c>
+      <c r="G1291" t="s">
+        <v>1325</v>
+      </c>
+      <c r="H1291" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1291" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1291">
+        <v>1</v>
+      </c>
+      <c r="K1291">
+        <v>22422000</v>
+      </c>
+      <c r="L1291">
+        <v>22422000</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:12">
+      <c r="A1292">
+        <v>1289</v>
+      </c>
+      <c r="B1292">
+        <v>403829</v>
+      </c>
+      <c r="C1292" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1292" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1292" t="s">
+        <v>1326</v>
+      </c>
+      <c r="F1292" t="s">
+        <v>1327</v>
+      </c>
+      <c r="G1292" t="s">
+        <v>1328</v>
+      </c>
+      <c r="H1292" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1292" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1292">
+        <v>1</v>
+      </c>
+      <c r="K1292">
+        <v>1330000</v>
+      </c>
+      <c r="L1292">
+        <v>1330000</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:12">
+      <c r="A1293">
+        <v>1290</v>
+      </c>
+      <c r="B1293">
+        <v>403829</v>
+      </c>
+      <c r="C1293" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1293" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1293" t="s">
+        <v>1326</v>
+      </c>
+      <c r="F1293" t="s">
+        <v>1327</v>
+      </c>
+      <c r="G1293" t="s">
+        <v>1328</v>
+      </c>
+      <c r="H1293" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1293" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1293">
+        <v>1</v>
+      </c>
+      <c r="K1293">
+        <v>13838000</v>
+      </c>
+      <c r="L1293">
+        <v>13838000</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:12">
+      <c r="A1294">
+        <v>1291</v>
+      </c>
+      <c r="B1294">
+        <v>403829</v>
+      </c>
+      <c r="C1294" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1294" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1294" t="s">
+        <v>1329</v>
+      </c>
+      <c r="F1294" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G1294" t="s">
+        <v>1331</v>
+      </c>
+      <c r="H1294" t="s">
+        <v>241</v>
+      </c>
+      <c r="I1294" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1294">
+        <v>1</v>
+      </c>
+      <c r="K1294">
+        <v>1400000</v>
+      </c>
+      <c r="L1294">
+        <v>1400000</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:12">
+      <c r="A1295">
+        <v>1292</v>
+      </c>
+      <c r="B1295">
+        <v>403829</v>
+      </c>
+      <c r="C1295" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1295" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1295" t="s">
+        <v>1329</v>
+      </c>
+      <c r="F1295" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G1295" t="s">
+        <v>1331</v>
+      </c>
+      <c r="H1295" t="s">
+        <v>149</v>
+      </c>
+      <c r="I1295" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1295">
+        <v>1</v>
+      </c>
+      <c r="K1295">
+        <v>21312000</v>
+      </c>
+      <c r="L1295">
+        <v>21312000</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:12">
+      <c r="A1296">
+        <v>1293</v>
+      </c>
+      <c r="B1296">
+        <v>403829</v>
+      </c>
+      <c r="C1296" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1296" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1296" t="s">
+        <v>1329</v>
+      </c>
+      <c r="F1296" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G1296" t="s">
+        <v>1331</v>
+      </c>
+      <c r="H1296" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1296" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1296">
+        <v>1</v>
+      </c>
+      <c r="K1296">
+        <v>2214000</v>
+      </c>
+      <c r="L1296">
+        <v>2214000</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:12">
+      <c r="A1297">
+        <v>1294</v>
+      </c>
+      <c r="B1297">
+        <v>403829</v>
+      </c>
+      <c r="C1297" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1297" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1297" t="s">
+        <v>1332</v>
+      </c>
+      <c r="F1297" t="s">
+        <v>1333</v>
+      </c>
+      <c r="G1297" t="s">
+        <v>1334</v>
+      </c>
+      <c r="H1297" t="s">
+        <v>266</v>
+      </c>
+      <c r="I1297" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1297">
+        <v>1</v>
+      </c>
+      <c r="K1297">
+        <v>10395000</v>
+      </c>
+      <c r="L1297">
+        <v>10395000</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:12">
+      <c r="A1298">
+        <v>1295</v>
+      </c>
+      <c r="B1298">
+        <v>403829</v>
+      </c>
+      <c r="C1298" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1298" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1298" t="s">
+        <v>1332</v>
+      </c>
+      <c r="F1298" t="s">
+        <v>1333</v>
+      </c>
+      <c r="G1298" t="s">
+        <v>1334</v>
+      </c>
+      <c r="H1298" t="s">
+        <v>267</v>
+      </c>
+      <c r="I1298" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1298">
+        <v>1</v>
+      </c>
+      <c r="K1298">
+        <v>64935000</v>
+      </c>
+      <c r="L1298">
+        <v>64935000</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:12">
+      <c r="A1299">
+        <v>1296</v>
+      </c>
+      <c r="B1299">
+        <v>403829</v>
+      </c>
+      <c r="C1299" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1299" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1299" t="s">
+        <v>1332</v>
+      </c>
+      <c r="F1299" t="s">
+        <v>1333</v>
+      </c>
+      <c r="G1299" t="s">
+        <v>1334</v>
+      </c>
+      <c r="H1299" t="s">
+        <v>268</v>
+      </c>
+      <c r="I1299" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1299">
+        <v>1</v>
+      </c>
+      <c r="K1299">
+        <v>21853000</v>
+      </c>
+      <c r="L1299">
+        <v>21853000</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:12">
+      <c r="A1300">
+        <v>1297</v>
+      </c>
+      <c r="B1300">
+        <v>403829</v>
+      </c>
+      <c r="C1300" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1300" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1300" t="s">
+        <v>1335</v>
+      </c>
+      <c r="F1300" t="s">
+        <v>1336</v>
+      </c>
+      <c r="G1300" t="s">
+        <v>1337</v>
+      </c>
+      <c r="H1300" t="s">
+        <v>149</v>
+      </c>
+      <c r="I1300" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1300">
+        <v>1</v>
+      </c>
+      <c r="K1300">
+        <v>2183000</v>
+      </c>
+      <c r="L1300">
+        <v>2183000</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:12">
+      <c r="A1301">
+        <v>1298</v>
+      </c>
+      <c r="B1301">
+        <v>403829</v>
+      </c>
+      <c r="C1301" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1301" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1301" t="s">
+        <v>1335</v>
+      </c>
+      <c r="F1301" t="s">
+        <v>1336</v>
+      </c>
+      <c r="G1301" t="s">
+        <v>1337</v>
+      </c>
+      <c r="H1301" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1301" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1301">
+        <v>1</v>
+      </c>
+      <c r="K1301">
+        <v>1599000</v>
+      </c>
+      <c r="L1301">
+        <v>1599000</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:12">
+      <c r="A1302">
+        <v>1299</v>
+      </c>
+      <c r="B1302">
+        <v>403829</v>
+      </c>
+      <c r="C1302" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1302" t="s">
+        <v>1338</v>
+      </c>
+      <c r="E1302" t="s">
+        <v>1339</v>
+      </c>
+      <c r="F1302" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G1302" t="s">
+        <v>1341</v>
+      </c>
+      <c r="H1302" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1302" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1302">
+        <v>1</v>
+      </c>
+      <c r="K1302">
+        <v>546300</v>
+      </c>
+      <c r="L1302">
+        <v>546300</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:12">
+      <c r="A1303">
+        <v>1300</v>
+      </c>
+      <c r="B1303">
+        <v>403829</v>
+      </c>
+      <c r="C1303" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1303" t="s">
+        <v>1338</v>
+      </c>
+      <c r="E1303" t="s">
+        <v>1342</v>
+      </c>
+      <c r="F1303" t="s">
+        <v>1343</v>
+      </c>
+      <c r="G1303" t="s">
+        <v>1344</v>
+      </c>
+      <c r="H1303" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1303" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1303">
+        <v>1</v>
+      </c>
+      <c r="K1303">
+        <v>6670000</v>
+      </c>
+      <c r="L1303">
+        <v>6670000</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:12">
+      <c r="A1304">
+        <v>1301</v>
+      </c>
+      <c r="B1304">
+        <v>403829</v>
+      </c>
+      <c r="C1304" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1304" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E1304" t="s">
+        <v>1346</v>
+      </c>
+      <c r="F1304" t="s">
+        <v>1347</v>
+      </c>
+      <c r="G1304" t="s">
+        <v>1348</v>
+      </c>
+      <c r="H1304" t="s">
+        <v>266</v>
+      </c>
+      <c r="I1304" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1304">
+        <v>1</v>
+      </c>
+      <c r="K1304">
+        <v>10325000</v>
+      </c>
+      <c r="L1304">
+        <v>10325000</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:12">
+      <c r="A1305">
+        <v>1302</v>
+      </c>
+      <c r="B1305">
+        <v>403829</v>
+      </c>
+      <c r="C1305" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1305" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E1305" t="s">
+        <v>1346</v>
+      </c>
+      <c r="F1305" t="s">
+        <v>1347</v>
+      </c>
+      <c r="G1305" t="s">
+        <v>1348</v>
+      </c>
+      <c r="H1305" t="s">
+        <v>267</v>
+      </c>
+      <c r="I1305" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1305">
+        <v>1</v>
+      </c>
+      <c r="K1305">
+        <v>94535000</v>
+      </c>
+      <c r="L1305">
+        <v>94535000</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:12">
+      <c r="A1306">
+        <v>1303</v>
+      </c>
+      <c r="B1306">
+        <v>403829</v>
+      </c>
+      <c r="C1306" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1306" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E1306" t="s">
+        <v>1346</v>
+      </c>
+      <c r="F1306" t="s">
+        <v>1347</v>
+      </c>
+      <c r="G1306" t="s">
+        <v>1348</v>
+      </c>
+      <c r="H1306" t="s">
+        <v>268</v>
+      </c>
+      <c r="I1306" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1306">
+        <v>1</v>
+      </c>
+      <c r="K1306">
+        <v>19393000</v>
+      </c>
+      <c r="L1306">
+        <v>19393000</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:12">
+      <c r="A1307">
+        <v>1304</v>
+      </c>
+      <c r="B1307">
+        <v>403829</v>
+      </c>
+      <c r="C1307" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1307" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E1307" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F1307" t="s">
+        <v>1350</v>
+      </c>
+      <c r="G1307" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1307" t="s">
+        <v>172</v>
+      </c>
+      <c r="I1307" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1307">
+        <v>1</v>
+      </c>
+      <c r="K1307">
+        <v>342900</v>
+      </c>
+      <c r="L1307">
+        <v>342900</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:12">
+      <c r="A1308">
+        <v>1305</v>
+      </c>
+      <c r="B1308">
+        <v>403829</v>
+      </c>
+      <c r="C1308" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1308" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E1308" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F1308" t="s">
+        <v>1350</v>
+      </c>
+      <c r="G1308" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1308" t="s">
+        <v>173</v>
+      </c>
+      <c r="I1308" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1308">
+        <v>1</v>
+      </c>
+      <c r="K1308">
+        <v>3941431</v>
+      </c>
+      <c r="L1308">
+        <v>3941431</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:12">
+      <c r="A1309">
+        <v>1306</v>
+      </c>
+      <c r="B1309">
+        <v>403829</v>
+      </c>
+      <c r="C1309" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1309" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E1309" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F1309" t="s">
+        <v>1350</v>
+      </c>
+      <c r="G1309" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1309" t="s">
+        <v>1351</v>
+      </c>
+      <c r="I1309" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1309">
+        <v>1</v>
+      </c>
+      <c r="K1309">
+        <v>2709720</v>
+      </c>
+      <c r="L1309">
+        <v>2709720</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:12">
+      <c r="A1310">
+        <v>1307</v>
+      </c>
+      <c r="B1310">
+        <v>403829</v>
+      </c>
+      <c r="C1310" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1310" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E1310" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F1310" t="s">
+        <v>1350</v>
+      </c>
+      <c r="G1310" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1310" t="s">
+        <v>386</v>
+      </c>
+      <c r="I1310" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1310">
+        <v>1</v>
+      </c>
+      <c r="K1310">
+        <v>300000</v>
+      </c>
+      <c r="L1310">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:12">
+      <c r="A1311">
+        <v>1308</v>
+      </c>
+      <c r="B1311">
+        <v>403829</v>
+      </c>
+      <c r="C1311" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1311" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E1311" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F1311" t="s">
+        <v>1350</v>
+      </c>
+      <c r="G1311" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1311" t="s">
+        <v>159</v>
+      </c>
+      <c r="I1311" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1311">
+        <v>1</v>
+      </c>
+      <c r="K1311">
+        <v>180000</v>
+      </c>
+      <c r="L1311">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:12">
+      <c r="A1312">
+        <v>1309</v>
+      </c>
+      <c r="B1312">
+        <v>403829</v>
+      </c>
+      <c r="C1312" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1312" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E1312" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F1312" t="s">
+        <v>1350</v>
+      </c>
+      <c r="G1312" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1312" t="s">
+        <v>174</v>
+      </c>
+      <c r="I1312" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1312">
+        <v>1</v>
+      </c>
+      <c r="K1312">
+        <v>1399500</v>
+      </c>
+      <c r="L1312">
+        <v>1399500</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:12">
+      <c r="A1313">
+        <v>1310</v>
+      </c>
+      <c r="B1313">
+        <v>403829</v>
+      </c>
+      <c r="C1313" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1313" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E1313" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F1313" t="s">
+        <v>1350</v>
+      </c>
+      <c r="G1313" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1313" t="s">
+        <v>175</v>
+      </c>
+      <c r="I1313" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1313">
+        <v>1</v>
+      </c>
+      <c r="K1313">
+        <v>8738180</v>
+      </c>
+      <c r="L1313">
+        <v>8738180</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:12">
+      <c r="A1314">
+        <v>1311</v>
+      </c>
+      <c r="B1314">
+        <v>403829</v>
+      </c>
+      <c r="C1314" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1314" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E1314" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F1314" t="s">
+        <v>1350</v>
+      </c>
+      <c r="G1314" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1314" t="s">
+        <v>254</v>
+      </c>
+      <c r="I1314" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1314">
+        <v>1</v>
+      </c>
+      <c r="K1314">
+        <v>957800</v>
+      </c>
+      <c r="L1314">
+        <v>957800</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:12">
+      <c r="A1315">
+        <v>1312</v>
+      </c>
+      <c r="B1315">
+        <v>403829</v>
+      </c>
+      <c r="C1315" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1315" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E1315" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F1315" t="s">
+        <v>1350</v>
+      </c>
+      <c r="G1315" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1315" t="s">
+        <v>176</v>
+      </c>
+      <c r="I1315" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1315">
+        <v>1</v>
+      </c>
+      <c r="K1315">
+        <v>19675000</v>
+      </c>
+      <c r="L1315">
+        <v>19675000</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:12">
+      <c r="A1316">
+        <v>1313</v>
+      </c>
+      <c r="B1316">
+        <v>403829</v>
+      </c>
+      <c r="C1316" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1316" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E1316" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F1316" t="s">
+        <v>1350</v>
+      </c>
+      <c r="G1316" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1316" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1316" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1316">
+        <v>1</v>
+      </c>
+      <c r="K1316">
+        <v>1522300</v>
+      </c>
+      <c r="L1316">
+        <v>1522300</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:12">
+      <c r="A1317">
+        <v>1314</v>
+      </c>
+      <c r="B1317">
+        <v>403829</v>
+      </c>
+      <c r="C1317" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1317" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E1317" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F1317" t="s">
+        <v>1350</v>
+      </c>
+      <c r="G1317" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1317" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1317" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1317">
+        <v>1</v>
+      </c>
+      <c r="K1317">
+        <v>525200</v>
+      </c>
+      <c r="L1317">
+        <v>525200</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:12">
+      <c r="A1318">
+        <v>1315</v>
+      </c>
+      <c r="B1318">
+        <v>403829</v>
+      </c>
+      <c r="C1318" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1318" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E1318" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F1318" t="s">
+        <v>1350</v>
+      </c>
+      <c r="G1318" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1318" t="s">
+        <v>177</v>
+      </c>
+      <c r="I1318" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1318">
+        <v>1</v>
+      </c>
+      <c r="K1318">
+        <v>41321696</v>
+      </c>
+      <c r="L1318">
+        <v>41321696</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:12">
+      <c r="A1319">
+        <v>1316</v>
+      </c>
+      <c r="B1319">
+        <v>403829</v>
+      </c>
+      <c r="C1319" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1319" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E1319" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F1319" t="s">
+        <v>1350</v>
+      </c>
+      <c r="G1319" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1319" t="s">
+        <v>178</v>
+      </c>
+      <c r="I1319" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1319">
+        <v>1</v>
+      </c>
+      <c r="K1319">
+        <v>9468528</v>
+      </c>
+      <c r="L1319">
+        <v>9468528</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:12">
+      <c r="A1320">
+        <v>1317</v>
+      </c>
+      <c r="B1320">
+        <v>403829</v>
+      </c>
+      <c r="C1320" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1320" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E1320" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F1320" t="s">
+        <v>1350</v>
+      </c>
+      <c r="G1320" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1320" t="s">
+        <v>179</v>
+      </c>
+      <c r="I1320" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1320">
+        <v>1</v>
+      </c>
+      <c r="K1320">
+        <v>13729784</v>
+      </c>
+      <c r="L1320">
+        <v>13729784</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:12">
+      <c r="A1321">
+        <v>1318</v>
+      </c>
+      <c r="B1321">
+        <v>403829</v>
+      </c>
+      <c r="C1321" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1321" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E1321" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F1321" t="s">
+        <v>1350</v>
+      </c>
+      <c r="G1321" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1321" t="s">
+        <v>180</v>
+      </c>
+      <c r="I1321" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1321">
+        <v>1</v>
+      </c>
+      <c r="K1321">
+        <v>4629928</v>
+      </c>
+      <c r="L1321">
+        <v>4629928</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:12">
+      <c r="A1322">
+        <v>1319</v>
+      </c>
+      <c r="B1322">
+        <v>403829</v>
+      </c>
+      <c r="C1322" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1322" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E1322" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F1322" t="s">
+        <v>1350</v>
+      </c>
+      <c r="G1322" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1322" t="s">
+        <v>184</v>
+      </c>
+      <c r="I1322" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1322">
+        <v>1</v>
+      </c>
+      <c r="K1322">
+        <v>475000</v>
+      </c>
+      <c r="L1322">
+        <v>475000</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:12">
+      <c r="A1323">
+        <v>1320</v>
+      </c>
+      <c r="B1323">
+        <v>403829</v>
+      </c>
+      <c r="C1323" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1323" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E1323" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F1323" t="s">
+        <v>1350</v>
+      </c>
+      <c r="G1323" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1323" t="s">
+        <v>185</v>
+      </c>
+      <c r="I1323" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1323">
+        <v>1</v>
+      </c>
+      <c r="K1323">
+        <v>1370000</v>
+      </c>
+      <c r="L1323">
+        <v>1370000</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:12">
+      <c r="A1324">
+        <v>1321</v>
+      </c>
+      <c r="B1324">
+        <v>403829</v>
+      </c>
+      <c r="C1324" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1324" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E1324" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F1324" t="s">
+        <v>1350</v>
+      </c>
+      <c r="G1324" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1324" t="s">
+        <v>1352</v>
+      </c>
+      <c r="I1324" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1324">
+        <v>1</v>
+      </c>
+      <c r="K1324">
+        <v>350000</v>
+      </c>
+      <c r="L1324">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:12">
+      <c r="A1325">
+        <v>1322</v>
+      </c>
+      <c r="B1325">
+        <v>403829</v>
+      </c>
+      <c r="C1325" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1325" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E1325" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F1325" t="s">
+        <v>1350</v>
+      </c>
+      <c r="G1325" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1325" t="s">
+        <v>186</v>
+      </c>
+      <c r="I1325" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1325">
+        <v>1</v>
+      </c>
+      <c r="K1325">
+        <v>3390000</v>
+      </c>
+      <c r="L1325">
+        <v>3390000</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:12">
+      <c r="A1326">
+        <v>1323</v>
+      </c>
+      <c r="B1326">
+        <v>403829</v>
+      </c>
+      <c r="C1326" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1326" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E1326" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F1326" t="s">
+        <v>1350</v>
+      </c>
+      <c r="G1326" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1326" t="s">
+        <v>187</v>
+      </c>
+      <c r="I1326" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1326">
+        <v>1</v>
+      </c>
+      <c r="K1326">
+        <v>544027</v>
+      </c>
+      <c r="L1326">
+        <v>544027</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:12">
+      <c r="A1327">
+        <v>1324</v>
+      </c>
+      <c r="B1327">
+        <v>403829</v>
+      </c>
+      <c r="C1327" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1327" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E1327" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F1327" t="s">
+        <v>1350</v>
+      </c>
+      <c r="G1327" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1327" t="s">
+        <v>188</v>
+      </c>
+      <c r="I1327" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1327">
+        <v>1</v>
+      </c>
+      <c r="K1327">
+        <v>158480</v>
+      </c>
+      <c r="L1327">
+        <v>158480</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:12">
+      <c r="A1328">
+        <v>1325</v>
+      </c>
+      <c r="B1328">
+        <v>403829</v>
+      </c>
+      <c r="C1328" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1328" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E1328" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F1328" t="s">
+        <v>1350</v>
+      </c>
+      <c r="G1328" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1328" t="s">
+        <v>189</v>
+      </c>
+      <c r="I1328" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1328">
+        <v>1</v>
+      </c>
+      <c r="K1328">
+        <v>728900</v>
+      </c>
+      <c r="L1328">
+        <v>728900</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:12">
+      <c r="A1329">
+        <v>1326</v>
+      </c>
+      <c r="B1329">
+        <v>403829</v>
+      </c>
+      <c r="C1329" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1329" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E1329" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F1329" t="s">
+        <v>1350</v>
+      </c>
+      <c r="G1329" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1329" t="s">
+        <v>191</v>
+      </c>
+      <c r="I1329" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1329">
+        <v>1</v>
+      </c>
+      <c r="K1329">
+        <v>243360</v>
+      </c>
+      <c r="L1329">
+        <v>243360</v>
       </c>
     </row>
   </sheetData>

--- a/Database/MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D.xlsx
+++ b/Database/MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1466">
   <si>
     <t>MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D</t>
   </si>
@@ -50,12 +50,12 @@
     <t>KURS</t>
   </si>
   <si>
+    <t>NILAI VALAS</t>
+  </si>
+  <si>
     <t>NILAI RUPIAH</t>
   </si>
   <si>
-    <t>NILAI_VALAS</t>
-  </si>
-  <si>
     <t>BALAI RISET PERIKANAN BUDIDAYA AIR TAWAR DAN PENYULUHAN PERIKANAN</t>
   </si>
   <si>
@@ -3968,6 +3968,72 @@
     <t>Pembayaran Belanja Barang sesuai SPD No. 0039-0048/BRPBATPP/KP.440/VII/2025 Tanggal 18 Juni 2025 sd 17 agustus 2025</t>
   </si>
   <si>
+    <t>2025-10-01</t>
+  </si>
+  <si>
+    <t>'00377T</t>
+  </si>
+  <si>
+    <t>'259991530066007</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Oktober 2025 untuk 36 pegawai/102 Jiwa</t>
+  </si>
+  <si>
+    <t>'00378T</t>
+  </si>
+  <si>
+    <t>'259991530066008</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Oktober 2025 untuk 130 Pegawai/382 Jiwa</t>
+  </si>
+  <si>
+    <t>'00379T</t>
+  </si>
+  <si>
+    <t>'259991525028391</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Oktober 2025 untuk 5 Pegawai/17 Jiwa</t>
+  </si>
+  <si>
+    <t>'00380T</t>
+  </si>
+  <si>
+    <t>'259991530066009</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Oktober 2025 untuk 50 Pegawai/126 Jiwa</t>
+  </si>
+  <si>
+    <t>'00381T</t>
+  </si>
+  <si>
+    <t>'259991531011782</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Oktober 2025 untuk 63 Pegwai/182 Jiwa</t>
+  </si>
+  <si>
+    <t>'00382T</t>
+  </si>
+  <si>
+    <t>'259991530066010</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Oktober 2025 untuk 35 Pegawai/101 Jiwa</t>
+  </si>
+  <si>
+    <t>'00383T</t>
+  </si>
+  <si>
+    <t>'259991531011783</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Oktober 2025 untuk 23 Pegawai/52 Jiwa</t>
+  </si>
+  <si>
     <t>'00384T</t>
   </si>
   <si>
@@ -4043,6 +4109,18 @@
     <t>Pembayaran Belanja Barang berupa Tagihan PDAM Bulan Agustus 2025 Idpel No. 1249-1046 An Lemb Perikanan Darat</t>
   </si>
   <si>
+    <t>2025-09-18</t>
+  </si>
+  <si>
+    <t>'00392T</t>
+  </si>
+  <si>
+    <t>'259991310602726</t>
+  </si>
+  <si>
+    <t>Pembayaran belanja barang berupa tagihan telepon bulan September 2025 untuk 12 invoice</t>
+  </si>
+  <si>
     <t>'00393T</t>
   </si>
   <si>
@@ -4074,6 +4152,267 @@
   </si>
   <si>
     <t>'403829.023.523121.03212WA.2378EBA.A000000001.00000.2.0252.2.000000.000000.994.002.DC.000176</t>
+  </si>
+  <si>
+    <t>'00396T</t>
+  </si>
+  <si>
+    <t>'259991320325728</t>
+  </si>
+  <si>
+    <t>Pembayaran belanja barang berupa tagihan listrik bulan September 2025 untuk 10 invoice</t>
+  </si>
+  <si>
+    <t>'00397T</t>
+  </si>
+  <si>
+    <t>'259991531011781</t>
+  </si>
+  <si>
+    <t>Pembayaran belanja Pegawai berupa Gaji Induk Bulan Oktober 2025 untuk 169 Pegawai/531 Jiwa</t>
+  </si>
+  <si>
+    <t>2025-09-12</t>
+  </si>
+  <si>
+    <t>'00399T</t>
+  </si>
+  <si>
+    <t>'259991310637860</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Agustus tahun 2025 untuk 50 Pegawai</t>
+  </si>
+  <si>
+    <t>'00400T</t>
+  </si>
+  <si>
+    <t>'259991330212404</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Agustus tahun 2025 untuk 63 Pegawai</t>
+  </si>
+  <si>
+    <t>'00402T</t>
+  </si>
+  <si>
+    <t>'259991330212405</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Agustus tahun 2025 untuk 23 Pegawai</t>
+  </si>
+  <si>
+    <t>'00403T</t>
+  </si>
+  <si>
+    <t>'259991310637859</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Agustus tahun 2025 untuk 132 Pegawai</t>
+  </si>
+  <si>
+    <t>'00404T</t>
+  </si>
+  <si>
+    <t>'259991330212403</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja  bulan Agustus tahun 2025 untuk 169 Pegawai</t>
+  </si>
+  <si>
+    <t>'00405T</t>
+  </si>
+  <si>
+    <t>'259991310637861</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Agustus tahun 2025 untuk 35 Pegawai</t>
+  </si>
+  <si>
+    <t>2025-09-17</t>
+  </si>
+  <si>
+    <t>'00406T</t>
+  </si>
+  <si>
+    <t>'259991310664434</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Kekurangan Gaji Bulan Agustus 2025 untuk 1 Pegawai/4 Jiwa</t>
+  </si>
+  <si>
+    <t>'00407T</t>
+  </si>
+  <si>
+    <t>'259991310664436</t>
+  </si>
+  <si>
+    <t>'00408T</t>
+  </si>
+  <si>
+    <t>'259991530074913</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan September Tahun 2025 untuk 16 Pegawai.sesuaiSK No. B4/BRPBATPP/KP.340/I/2025 tanggal 2 Januari 2025</t>
+  </si>
+  <si>
+    <t>'00409T</t>
+  </si>
+  <si>
+    <t>'259991531014088</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan September Tahun 2025 untuk 91 Pegawai.sesuai Sk no. 9 Tahun 2025 tanggal 6 januari 2025</t>
+  </si>
+  <si>
+    <t>'00410T</t>
+  </si>
+  <si>
+    <t>'259991530074912</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan September Tahun 2025 untuk 103 Pegawai.sesuai SK No. 9 Tahun 2025 Tanggal 6 Januari 2025</t>
+  </si>
+  <si>
+    <t>'00411T</t>
+  </si>
+  <si>
+    <t>'259991310699199</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Oktober tahun 2025 untuk 35 Pegawai/</t>
+  </si>
+  <si>
+    <t>'00412T</t>
+  </si>
+  <si>
+    <t>'259991305146122</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Oktober tahun 2025 untuk 5 Pegawai</t>
+  </si>
+  <si>
+    <t>2025-10-02</t>
+  </si>
+  <si>
+    <t>'00413T</t>
+  </si>
+  <si>
+    <t>'259991310748516</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja barang berupa Honor Pengelola Keuangan Bulan September 2025 untuk 8 Pegawai sesuai Sk No B.1/BRPBATPP/KU.110/I/2025 tanggal 2 Januari 2025</t>
+  </si>
+  <si>
+    <t>2025-10-07</t>
+  </si>
+  <si>
+    <t>'00414T</t>
+  </si>
+  <si>
+    <t>'259991310791734</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang termin ke 9 Sesuai SPK No.2/BRPBATPP/PPK/PL.400/I/2025 Tanggal 2 Januari2025 dan BAPP No B.610/BRPBATPP/PPK/PL.400/IX/2025 Tanggal 30 September 2025</t>
+  </si>
+  <si>
+    <t>2025-10-09</t>
+  </si>
+  <si>
+    <t>'00415T</t>
+  </si>
+  <si>
+    <t>'259991320447856</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang berupa Tagihan PDAM Bulan September 2025 Idpel No.1249-1046 An Lemb Perikanan Darat</t>
+  </si>
+  <si>
+    <t>'00416T</t>
+  </si>
+  <si>
+    <t>'259991310813285</t>
+  </si>
+  <si>
+    <t>'00417T</t>
+  </si>
+  <si>
+    <t>'259991310813283</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Kekurangan Gaji Bulan juni 2025 sd september 2025 untuk 10 Pegawai/30 jiwa</t>
+  </si>
+  <si>
+    <t>'00418T</t>
+  </si>
+  <si>
+    <t>'259991330279573</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Kekurangan Gaji Bulan September 2025 untuk 1 Pegawai/2 Jiwa</t>
+  </si>
+  <si>
+    <t>'00421T</t>
+  </si>
+  <si>
+    <t>'259991310821552</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK bulan September 2025 untuk 50  Pegawai</t>
+  </si>
+  <si>
+    <t>'00423T</t>
+  </si>
+  <si>
+    <t>'259991330280936</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan September 2025 untuk 62 Pegawai</t>
+  </si>
+  <si>
+    <t>'00424T</t>
+  </si>
+  <si>
+    <t>'259991330280937</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK bulan september 2025 untuk 22 Pegawai</t>
+  </si>
+  <si>
+    <t>'00425T</t>
+  </si>
+  <si>
+    <t>'259991310821606</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan September 2025 untuk 35 Pegawai</t>
+  </si>
+  <si>
+    <t>'00426T</t>
+  </si>
+  <si>
+    <t>'259991310821551</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan September 2025 untuk 130 Pegawai</t>
+  </si>
+  <si>
+    <t>'00427T</t>
+  </si>
+  <si>
+    <t>'259991330280935</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan September 2025 untuk 169 Pegawai</t>
+  </si>
+  <si>
+    <t>'00428T</t>
+  </si>
+  <si>
+    <t>'259991305172543</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan September 2025 untuk 5 Pegawai</t>
   </si>
 </sst>
 </file>
@@ -4416,7 +4755,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:L1329"/>
+  <dimension ref="A1:L1464"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -53190,19 +53529,19 @@
         <v>13</v>
       </c>
       <c r="D1286" t="s">
-        <v>1310</v>
+        <v>1317</v>
       </c>
       <c r="E1286" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="F1286" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="G1286" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="H1286" t="s">
-        <v>233</v>
+        <v>18</v>
       </c>
       <c r="I1286" t="s">
         <v>19</v>
@@ -53211,10 +53550,10 @@
         <v>1</v>
       </c>
       <c r="K1286">
-        <v>6790000</v>
+        <v>143856600</v>
       </c>
       <c r="L1286">
-        <v>6790000</v>
+        <v>143856600</v>
       </c>
     </row>
     <row r="1287" spans="1:12">
@@ -53228,19 +53567,19 @@
         <v>13</v>
       </c>
       <c r="D1287" t="s">
-        <v>1310</v>
+        <v>1317</v>
       </c>
       <c r="E1287" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="F1287" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="G1287" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="H1287" t="s">
-        <v>234</v>
+        <v>20</v>
       </c>
       <c r="I1287" t="s">
         <v>19</v>
@@ -53249,10 +53588,10 @@
         <v>1</v>
       </c>
       <c r="K1287">
-        <v>28712000</v>
+        <v>1695</v>
       </c>
       <c r="L1287">
-        <v>28712000</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="1288" spans="1:12">
@@ -53266,19 +53605,19 @@
         <v>13</v>
       </c>
       <c r="D1288" t="s">
-        <v>1310</v>
+        <v>1317</v>
       </c>
       <c r="E1288" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F1288" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G1288" t="s">
         <v>1320</v>
       </c>
-      <c r="F1288" t="s">
-        <v>1321</v>
-      </c>
-      <c r="G1288" t="s">
-        <v>1322</v>
-      </c>
       <c r="H1288" t="s">
-        <v>233</v>
+        <v>21</v>
       </c>
       <c r="I1288" t="s">
         <v>19</v>
@@ -53287,10 +53626,10 @@
         <v>1</v>
       </c>
       <c r="K1288">
-        <v>1400000</v>
+        <v>10913750</v>
       </c>
       <c r="L1288">
-        <v>1400000</v>
+        <v>10913750</v>
       </c>
     </row>
     <row r="1289" spans="1:12">
@@ -53304,19 +53643,19 @@
         <v>13</v>
       </c>
       <c r="D1289" t="s">
-        <v>1310</v>
+        <v>1317</v>
       </c>
       <c r="E1289" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F1289" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G1289" t="s">
         <v>1320</v>
       </c>
-      <c r="F1289" t="s">
-        <v>1321</v>
-      </c>
-      <c r="G1289" t="s">
-        <v>1322</v>
-      </c>
       <c r="H1289" t="s">
-        <v>234</v>
+        <v>22</v>
       </c>
       <c r="I1289" t="s">
         <v>19</v>
@@ -53325,10 +53664,10 @@
         <v>1</v>
       </c>
       <c r="K1289">
-        <v>43290000</v>
+        <v>3150736</v>
       </c>
       <c r="L1289">
-        <v>43290000</v>
+        <v>3150736</v>
       </c>
     </row>
     <row r="1290" spans="1:12">
@@ -53342,19 +53681,19 @@
         <v>13</v>
       </c>
       <c r="D1290" t="s">
-        <v>1310</v>
+        <v>1317</v>
       </c>
       <c r="E1290" t="s">
-        <v>1323</v>
+        <v>1318</v>
       </c>
       <c r="F1290" t="s">
-        <v>1324</v>
+        <v>1319</v>
       </c>
       <c r="G1290" t="s">
-        <v>1325</v>
+        <v>1320</v>
       </c>
       <c r="H1290" t="s">
-        <v>233</v>
+        <v>23</v>
       </c>
       <c r="I1290" t="s">
         <v>19</v>
@@ -53363,10 +53702,10 @@
         <v>1</v>
       </c>
       <c r="K1290">
-        <v>2100000</v>
+        <v>1260000</v>
       </c>
       <c r="L1290">
-        <v>2100000</v>
+        <v>1260000</v>
       </c>
     </row>
     <row r="1291" spans="1:12">
@@ -53380,19 +53719,19 @@
         <v>13</v>
       </c>
       <c r="D1291" t="s">
-        <v>1310</v>
+        <v>1317</v>
       </c>
       <c r="E1291" t="s">
-        <v>1323</v>
+        <v>1318</v>
       </c>
       <c r="F1291" t="s">
-        <v>1324</v>
+        <v>1319</v>
       </c>
       <c r="G1291" t="s">
-        <v>1325</v>
+        <v>1320</v>
       </c>
       <c r="H1291" t="s">
-        <v>234</v>
+        <v>24</v>
       </c>
       <c r="I1291" t="s">
         <v>19</v>
@@ -53401,10 +53740,10 @@
         <v>1</v>
       </c>
       <c r="K1291">
-        <v>22422000</v>
+        <v>8494000</v>
       </c>
       <c r="L1291">
-        <v>22422000</v>
+        <v>8494000</v>
       </c>
     </row>
     <row r="1292" spans="1:12">
@@ -53418,19 +53757,19 @@
         <v>13</v>
       </c>
       <c r="D1292" t="s">
-        <v>1310</v>
+        <v>1317</v>
       </c>
       <c r="E1292" t="s">
-        <v>1326</v>
+        <v>1318</v>
       </c>
       <c r="F1292" t="s">
-        <v>1327</v>
+        <v>1319</v>
       </c>
       <c r="G1292" t="s">
-        <v>1328</v>
+        <v>1320</v>
       </c>
       <c r="H1292" t="s">
-        <v>233</v>
+        <v>25</v>
       </c>
       <c r="I1292" t="s">
         <v>19</v>
@@ -53439,10 +53778,10 @@
         <v>1</v>
       </c>
       <c r="K1292">
-        <v>1330000</v>
+        <v>183429</v>
       </c>
       <c r="L1292">
-        <v>1330000</v>
+        <v>183429</v>
       </c>
     </row>
     <row r="1293" spans="1:12">
@@ -53456,19 +53795,19 @@
         <v>13</v>
       </c>
       <c r="D1293" t="s">
-        <v>1310</v>
+        <v>1317</v>
       </c>
       <c r="E1293" t="s">
-        <v>1326</v>
+        <v>1318</v>
       </c>
       <c r="F1293" t="s">
-        <v>1327</v>
+        <v>1319</v>
       </c>
       <c r="G1293" t="s">
-        <v>1328</v>
+        <v>1320</v>
       </c>
       <c r="H1293" t="s">
-        <v>234</v>
+        <v>26</v>
       </c>
       <c r="I1293" t="s">
         <v>19</v>
@@ -53477,10 +53816,10 @@
         <v>1</v>
       </c>
       <c r="K1293">
-        <v>13838000</v>
+        <v>7386840</v>
       </c>
       <c r="L1293">
-        <v>13838000</v>
+        <v>7386840</v>
       </c>
     </row>
     <row r="1294" spans="1:12">
@@ -53494,19 +53833,19 @@
         <v>13</v>
       </c>
       <c r="D1294" t="s">
-        <v>1310</v>
+        <v>1317</v>
       </c>
       <c r="E1294" t="s">
-        <v>1329</v>
+        <v>1318</v>
       </c>
       <c r="F1294" t="s">
-        <v>1330</v>
+        <v>1319</v>
       </c>
       <c r="G1294" t="s">
-        <v>1331</v>
+        <v>1320</v>
       </c>
       <c r="H1294" t="s">
-        <v>241</v>
+        <v>27</v>
       </c>
       <c r="I1294" t="s">
         <v>19</v>
@@ -53515,10 +53854,10 @@
         <v>1</v>
       </c>
       <c r="K1294">
-        <v>1400000</v>
+        <v>4065000</v>
       </c>
       <c r="L1294">
-        <v>1400000</v>
+        <v>4065000</v>
       </c>
     </row>
     <row r="1295" spans="1:12">
@@ -53532,19 +53871,19 @@
         <v>13</v>
       </c>
       <c r="D1295" t="s">
-        <v>1310</v>
+        <v>1317</v>
       </c>
       <c r="E1295" t="s">
-        <v>1329</v>
+        <v>1321</v>
       </c>
       <c r="F1295" t="s">
-        <v>1330</v>
+        <v>1322</v>
       </c>
       <c r="G1295" t="s">
-        <v>1331</v>
+        <v>1323</v>
       </c>
       <c r="H1295" t="s">
-        <v>149</v>
+        <v>31</v>
       </c>
       <c r="I1295" t="s">
         <v>19</v>
@@ -53553,10 +53892,10 @@
         <v>1</v>
       </c>
       <c r="K1295">
-        <v>21312000</v>
+        <v>521686100</v>
       </c>
       <c r="L1295">
-        <v>21312000</v>
+        <v>521686100</v>
       </c>
     </row>
     <row r="1296" spans="1:12">
@@ -53570,19 +53909,19 @@
         <v>13</v>
       </c>
       <c r="D1296" t="s">
-        <v>1310</v>
+        <v>1317</v>
       </c>
       <c r="E1296" t="s">
-        <v>1329</v>
+        <v>1321</v>
       </c>
       <c r="F1296" t="s">
-        <v>1330</v>
+        <v>1322</v>
       </c>
       <c r="G1296" t="s">
-        <v>1331</v>
+        <v>1323</v>
       </c>
       <c r="H1296" t="s">
-        <v>242</v>
+        <v>32</v>
       </c>
       <c r="I1296" t="s">
         <v>19</v>
@@ -53591,10 +53930,10 @@
         <v>1</v>
       </c>
       <c r="K1296">
-        <v>2214000</v>
+        <v>6577</v>
       </c>
       <c r="L1296">
-        <v>2214000</v>
+        <v>6577</v>
       </c>
     </row>
     <row r="1297" spans="1:12">
@@ -53608,19 +53947,19 @@
         <v>13</v>
       </c>
       <c r="D1297" t="s">
-        <v>1310</v>
+        <v>1317</v>
       </c>
       <c r="E1297" t="s">
-        <v>1332</v>
+        <v>1321</v>
       </c>
       <c r="F1297" t="s">
-        <v>1333</v>
+        <v>1322</v>
       </c>
       <c r="G1297" t="s">
-        <v>1334</v>
+        <v>1323</v>
       </c>
       <c r="H1297" t="s">
-        <v>266</v>
+        <v>33</v>
       </c>
       <c r="I1297" t="s">
         <v>19</v>
@@ -53629,10 +53968,10 @@
         <v>1</v>
       </c>
       <c r="K1297">
-        <v>10395000</v>
+        <v>39962350</v>
       </c>
       <c r="L1297">
-        <v>10395000</v>
+        <v>39962350</v>
       </c>
     </row>
     <row r="1298" spans="1:12">
@@ -53646,19 +53985,19 @@
         <v>13</v>
       </c>
       <c r="D1298" t="s">
-        <v>1310</v>
+        <v>1317</v>
       </c>
       <c r="E1298" t="s">
-        <v>1332</v>
+        <v>1321</v>
       </c>
       <c r="F1298" t="s">
-        <v>1333</v>
+        <v>1322</v>
       </c>
       <c r="G1298" t="s">
-        <v>1334</v>
+        <v>1323</v>
       </c>
       <c r="H1298" t="s">
-        <v>267</v>
+        <v>34</v>
       </c>
       <c r="I1298" t="s">
         <v>19</v>
@@ -53667,10 +54006,10 @@
         <v>1</v>
       </c>
       <c r="K1298">
-        <v>64935000</v>
+        <v>11989480</v>
       </c>
       <c r="L1298">
-        <v>64935000</v>
+        <v>11989480</v>
       </c>
     </row>
     <row r="1299" spans="1:12">
@@ -53684,19 +54023,19 @@
         <v>13</v>
       </c>
       <c r="D1299" t="s">
-        <v>1310</v>
+        <v>1317</v>
       </c>
       <c r="E1299" t="s">
-        <v>1332</v>
+        <v>1321</v>
       </c>
       <c r="F1299" t="s">
-        <v>1333</v>
+        <v>1322</v>
       </c>
       <c r="G1299" t="s">
-        <v>1334</v>
+        <v>1323</v>
       </c>
       <c r="H1299" t="s">
-        <v>268</v>
+        <v>35</v>
       </c>
       <c r="I1299" t="s">
         <v>19</v>
@@ -53705,10 +54044,10 @@
         <v>1</v>
       </c>
       <c r="K1299">
-        <v>21853000</v>
+        <v>108900000</v>
       </c>
       <c r="L1299">
-        <v>21853000</v>
+        <v>108900000</v>
       </c>
     </row>
     <row r="1300" spans="1:12">
@@ -53722,19 +54061,19 @@
         <v>13</v>
       </c>
       <c r="D1300" t="s">
-        <v>1310</v>
+        <v>1317</v>
       </c>
       <c r="E1300" t="s">
-        <v>1335</v>
+        <v>1321</v>
       </c>
       <c r="F1300" t="s">
-        <v>1336</v>
+        <v>1322</v>
       </c>
       <c r="G1300" t="s">
-        <v>1337</v>
+        <v>1323</v>
       </c>
       <c r="H1300" t="s">
-        <v>149</v>
+        <v>36</v>
       </c>
       <c r="I1300" t="s">
         <v>19</v>
@@ -53743,10 +54082,10 @@
         <v>1</v>
       </c>
       <c r="K1300">
-        <v>2183000</v>
+        <v>1853611</v>
       </c>
       <c r="L1300">
-        <v>2183000</v>
+        <v>1853611</v>
       </c>
     </row>
     <row r="1301" spans="1:12">
@@ -53760,19 +54099,19 @@
         <v>13</v>
       </c>
       <c r="D1301" t="s">
-        <v>1310</v>
+        <v>1317</v>
       </c>
       <c r="E1301" t="s">
-        <v>1335</v>
+        <v>1321</v>
       </c>
       <c r="F1301" t="s">
-        <v>1336</v>
+        <v>1322</v>
       </c>
       <c r="G1301" t="s">
-        <v>1337</v>
+        <v>1323</v>
       </c>
       <c r="H1301" t="s">
-        <v>242</v>
+        <v>37</v>
       </c>
       <c r="I1301" t="s">
         <v>19</v>
@@ -53781,10 +54120,10 @@
         <v>1</v>
       </c>
       <c r="K1301">
-        <v>1599000</v>
+        <v>27664440</v>
       </c>
       <c r="L1301">
-        <v>1599000</v>
+        <v>27664440</v>
       </c>
     </row>
     <row r="1302" spans="1:12">
@@ -53798,19 +54137,19 @@
         <v>13</v>
       </c>
       <c r="D1302" t="s">
-        <v>1338</v>
+        <v>1317</v>
       </c>
       <c r="E1302" t="s">
-        <v>1339</v>
+        <v>1321</v>
       </c>
       <c r="F1302" t="s">
-        <v>1340</v>
+        <v>1322</v>
       </c>
       <c r="G1302" t="s">
-        <v>1341</v>
+        <v>1323</v>
       </c>
       <c r="H1302" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="I1302" t="s">
         <v>19</v>
@@ -53819,10 +54158,10 @@
         <v>1</v>
       </c>
       <c r="K1302">
-        <v>546300</v>
+        <v>185000</v>
       </c>
       <c r="L1302">
-        <v>546300</v>
+        <v>185000</v>
       </c>
     </row>
     <row r="1303" spans="1:12">
@@ -53836,19 +54175,19 @@
         <v>13</v>
       </c>
       <c r="D1303" t="s">
-        <v>1338</v>
+        <v>1317</v>
       </c>
       <c r="E1303" t="s">
-        <v>1342</v>
+        <v>1324</v>
       </c>
       <c r="F1303" t="s">
-        <v>1343</v>
+        <v>1325</v>
       </c>
       <c r="G1303" t="s">
-        <v>1344</v>
+        <v>1326</v>
       </c>
       <c r="H1303" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="I1303" t="s">
         <v>19</v>
@@ -53857,10 +54196,10 @@
         <v>1</v>
       </c>
       <c r="K1303">
-        <v>6670000</v>
+        <v>20825000</v>
       </c>
       <c r="L1303">
-        <v>6670000</v>
+        <v>20825000</v>
       </c>
     </row>
     <row r="1304" spans="1:12">
@@ -53874,19 +54213,19 @@
         <v>13</v>
       </c>
       <c r="D1304" t="s">
-        <v>1345</v>
+        <v>1317</v>
       </c>
       <c r="E1304" t="s">
-        <v>1346</v>
+        <v>1324</v>
       </c>
       <c r="F1304" t="s">
-        <v>1347</v>
+        <v>1325</v>
       </c>
       <c r="G1304" t="s">
-        <v>1348</v>
+        <v>1326</v>
       </c>
       <c r="H1304" t="s">
-        <v>266</v>
+        <v>20</v>
       </c>
       <c r="I1304" t="s">
         <v>19</v>
@@ -53895,10 +54234,10 @@
         <v>1</v>
       </c>
       <c r="K1304">
-        <v>10325000</v>
+        <v>180</v>
       </c>
       <c r="L1304">
-        <v>10325000</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1305" spans="1:12">
@@ -53912,19 +54251,19 @@
         <v>13</v>
       </c>
       <c r="D1305" t="s">
-        <v>1345</v>
+        <v>1317</v>
       </c>
       <c r="E1305" t="s">
-        <v>1346</v>
+        <v>1324</v>
       </c>
       <c r="F1305" t="s">
-        <v>1347</v>
+        <v>1325</v>
       </c>
       <c r="G1305" t="s">
-        <v>1348</v>
+        <v>1326</v>
       </c>
       <c r="H1305" t="s">
-        <v>267</v>
+        <v>21</v>
       </c>
       <c r="I1305" t="s">
         <v>19</v>
@@ -53933,10 +54272,10 @@
         <v>1</v>
       </c>
       <c r="K1305">
-        <v>94535000</v>
+        <v>1620070</v>
       </c>
       <c r="L1305">
-        <v>94535000</v>
+        <v>1620070</v>
       </c>
     </row>
     <row r="1306" spans="1:12">
@@ -53950,19 +54289,19 @@
         <v>13</v>
       </c>
       <c r="D1306" t="s">
-        <v>1345</v>
+        <v>1317</v>
       </c>
       <c r="E1306" t="s">
-        <v>1346</v>
+        <v>1324</v>
       </c>
       <c r="F1306" t="s">
-        <v>1347</v>
+        <v>1325</v>
       </c>
       <c r="G1306" t="s">
-        <v>1348</v>
+        <v>1326</v>
       </c>
       <c r="H1306" t="s">
-        <v>268</v>
+        <v>22</v>
       </c>
       <c r="I1306" t="s">
         <v>19</v>
@@ -53971,10 +54310,10 @@
         <v>1</v>
       </c>
       <c r="K1306">
-        <v>19393000</v>
+        <v>648028</v>
       </c>
       <c r="L1306">
-        <v>19393000</v>
+        <v>648028</v>
       </c>
     </row>
     <row r="1307" spans="1:12">
@@ -53988,19 +54327,19 @@
         <v>13</v>
       </c>
       <c r="D1307" t="s">
-        <v>1345</v>
+        <v>1317</v>
       </c>
       <c r="E1307" t="s">
-        <v>1349</v>
+        <v>1324</v>
       </c>
       <c r="F1307" t="s">
-        <v>1350</v>
+        <v>1325</v>
       </c>
       <c r="G1307" t="s">
-        <v>171</v>
+        <v>1326</v>
       </c>
       <c r="H1307" t="s">
-        <v>172</v>
+        <v>23</v>
       </c>
       <c r="I1307" t="s">
         <v>19</v>
@@ -54009,10 +54348,10 @@
         <v>1</v>
       </c>
       <c r="K1307">
-        <v>342900</v>
+        <v>540000</v>
       </c>
       <c r="L1307">
-        <v>342900</v>
+        <v>540000</v>
       </c>
     </row>
     <row r="1308" spans="1:12">
@@ -54026,19 +54365,19 @@
         <v>13</v>
       </c>
       <c r="D1308" t="s">
-        <v>1345</v>
+        <v>1317</v>
       </c>
       <c r="E1308" t="s">
-        <v>1349</v>
+        <v>1324</v>
       </c>
       <c r="F1308" t="s">
-        <v>1350</v>
+        <v>1325</v>
       </c>
       <c r="G1308" t="s">
-        <v>171</v>
+        <v>1326</v>
       </c>
       <c r="H1308" t="s">
-        <v>173</v>
+        <v>24</v>
       </c>
       <c r="I1308" t="s">
         <v>19</v>
@@ -54047,10 +54386,10 @@
         <v>1</v>
       </c>
       <c r="K1308">
-        <v>3941431</v>
+        <v>1900000</v>
       </c>
       <c r="L1308">
-        <v>3941431</v>
+        <v>1900000</v>
       </c>
     </row>
     <row r="1309" spans="1:12">
@@ -54064,19 +54403,19 @@
         <v>13</v>
       </c>
       <c r="D1309" t="s">
-        <v>1345</v>
+        <v>1317</v>
       </c>
       <c r="E1309" t="s">
-        <v>1349</v>
+        <v>1324</v>
       </c>
       <c r="F1309" t="s">
-        <v>1350</v>
+        <v>1325</v>
       </c>
       <c r="G1309" t="s">
-        <v>171</v>
+        <v>1326</v>
       </c>
       <c r="H1309" t="s">
-        <v>1351</v>
+        <v>25</v>
       </c>
       <c r="I1309" t="s">
         <v>19</v>
@@ -54085,10 +54424,10 @@
         <v>1</v>
       </c>
       <c r="K1309">
-        <v>2709720</v>
+        <v>13741</v>
       </c>
       <c r="L1309">
-        <v>2709720</v>
+        <v>13741</v>
       </c>
     </row>
     <row r="1310" spans="1:12">
@@ -54102,19 +54441,19 @@
         <v>13</v>
       </c>
       <c r="D1310" t="s">
-        <v>1345</v>
+        <v>1317</v>
       </c>
       <c r="E1310" t="s">
-        <v>1349</v>
+        <v>1324</v>
       </c>
       <c r="F1310" t="s">
-        <v>1350</v>
+        <v>1325</v>
       </c>
       <c r="G1310" t="s">
-        <v>171</v>
+        <v>1326</v>
       </c>
       <c r="H1310" t="s">
-        <v>386</v>
+        <v>26</v>
       </c>
       <c r="I1310" t="s">
         <v>19</v>
@@ -54123,10 +54462,10 @@
         <v>1</v>
       </c>
       <c r="K1310">
-        <v>300000</v>
+        <v>1231140</v>
       </c>
       <c r="L1310">
-        <v>300000</v>
+        <v>1231140</v>
       </c>
     </row>
     <row r="1311" spans="1:12">
@@ -54140,19 +54479,19 @@
         <v>13</v>
       </c>
       <c r="D1311" t="s">
-        <v>1345</v>
+        <v>1317</v>
       </c>
       <c r="E1311" t="s">
-        <v>1349</v>
+        <v>1324</v>
       </c>
       <c r="F1311" t="s">
-        <v>1350</v>
+        <v>1325</v>
       </c>
       <c r="G1311" t="s">
-        <v>171</v>
+        <v>1326</v>
       </c>
       <c r="H1311" t="s">
-        <v>159</v>
+        <v>27</v>
       </c>
       <c r="I1311" t="s">
         <v>19</v>
@@ -54161,10 +54500,10 @@
         <v>1</v>
       </c>
       <c r="K1311">
-        <v>180000</v>
+        <v>375000</v>
       </c>
       <c r="L1311">
-        <v>180000</v>
+        <v>375000</v>
       </c>
     </row>
     <row r="1312" spans="1:12">
@@ -54178,19 +54517,19 @@
         <v>13</v>
       </c>
       <c r="D1312" t="s">
-        <v>1345</v>
+        <v>1317</v>
       </c>
       <c r="E1312" t="s">
-        <v>1349</v>
+        <v>1327</v>
       </c>
       <c r="F1312" t="s">
-        <v>1350</v>
+        <v>1328</v>
       </c>
       <c r="G1312" t="s">
-        <v>171</v>
+        <v>1329</v>
       </c>
       <c r="H1312" t="s">
-        <v>174</v>
+        <v>48</v>
       </c>
       <c r="I1312" t="s">
         <v>19</v>
@@ -54199,10 +54538,10 @@
         <v>1</v>
       </c>
       <c r="K1312">
-        <v>1399500</v>
+        <v>158344800</v>
       </c>
       <c r="L1312">
-        <v>1399500</v>
+        <v>158344800</v>
       </c>
     </row>
     <row r="1313" spans="1:12">
@@ -54216,19 +54555,19 @@
         <v>13</v>
       </c>
       <c r="D1313" t="s">
-        <v>1345</v>
+        <v>1317</v>
       </c>
       <c r="E1313" t="s">
-        <v>1349</v>
+        <v>1327</v>
       </c>
       <c r="F1313" t="s">
-        <v>1350</v>
+        <v>1328</v>
       </c>
       <c r="G1313" t="s">
-        <v>171</v>
+        <v>1329</v>
       </c>
       <c r="H1313" t="s">
-        <v>175</v>
+        <v>49</v>
       </c>
       <c r="I1313" t="s">
         <v>19</v>
@@ -54237,10 +54576,10 @@
         <v>1</v>
       </c>
       <c r="K1313">
-        <v>8738180</v>
+        <v>3238</v>
       </c>
       <c r="L1313">
-        <v>8738180</v>
+        <v>3238</v>
       </c>
     </row>
     <row r="1314" spans="1:12">
@@ -54254,19 +54593,19 @@
         <v>13</v>
       </c>
       <c r="D1314" t="s">
-        <v>1345</v>
+        <v>1317</v>
       </c>
       <c r="E1314" t="s">
-        <v>1349</v>
+        <v>1327</v>
       </c>
       <c r="F1314" t="s">
-        <v>1350</v>
+        <v>1328</v>
       </c>
       <c r="G1314" t="s">
-        <v>171</v>
+        <v>1329</v>
       </c>
       <c r="H1314" t="s">
-        <v>254</v>
+        <v>50</v>
       </c>
       <c r="I1314" t="s">
         <v>19</v>
@@ -54275,10 +54614,10 @@
         <v>1</v>
       </c>
       <c r="K1314">
-        <v>957800</v>
+        <v>9474480</v>
       </c>
       <c r="L1314">
-        <v>957800</v>
+        <v>9474480</v>
       </c>
     </row>
     <row r="1315" spans="1:12">
@@ -54292,19 +54631,19 @@
         <v>13</v>
       </c>
       <c r="D1315" t="s">
-        <v>1345</v>
+        <v>1317</v>
       </c>
       <c r="E1315" t="s">
-        <v>1349</v>
+        <v>1327</v>
       </c>
       <c r="F1315" t="s">
-        <v>1350</v>
+        <v>1328</v>
       </c>
       <c r="G1315" t="s">
-        <v>171</v>
+        <v>1329</v>
       </c>
       <c r="H1315" t="s">
-        <v>176</v>
+        <v>51</v>
       </c>
       <c r="I1315" t="s">
         <v>19</v>
@@ -54313,10 +54652,10 @@
         <v>1</v>
       </c>
       <c r="K1315">
-        <v>19675000</v>
+        <v>2901696</v>
       </c>
       <c r="L1315">
-        <v>19675000</v>
+        <v>2901696</v>
       </c>
     </row>
     <row r="1316" spans="1:12">
@@ -54330,19 +54669,19 @@
         <v>13</v>
       </c>
       <c r="D1316" t="s">
-        <v>1345</v>
+        <v>1317</v>
       </c>
       <c r="E1316" t="s">
-        <v>1349</v>
+        <v>1327</v>
       </c>
       <c r="F1316" t="s">
-        <v>1350</v>
+        <v>1328</v>
       </c>
       <c r="G1316" t="s">
-        <v>171</v>
+        <v>1329</v>
       </c>
       <c r="H1316" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="I1316" t="s">
         <v>19</v>
@@ -54351,10 +54690,10 @@
         <v>1</v>
       </c>
       <c r="K1316">
-        <v>1522300</v>
+        <v>25200000</v>
       </c>
       <c r="L1316">
-        <v>1522300</v>
+        <v>25200000</v>
       </c>
     </row>
     <row r="1317" spans="1:12">
@@ -54368,19 +54707,19 @@
         <v>13</v>
       </c>
       <c r="D1317" t="s">
-        <v>1345</v>
+        <v>1317</v>
       </c>
       <c r="E1317" t="s">
-        <v>1349</v>
+        <v>1327</v>
       </c>
       <c r="F1317" t="s">
-        <v>1350</v>
+        <v>1328</v>
       </c>
       <c r="G1317" t="s">
-        <v>171</v>
+        <v>1329</v>
       </c>
       <c r="H1317" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="I1317" t="s">
         <v>19</v>
@@ -54389,10 +54728,10 @@
         <v>1</v>
       </c>
       <c r="K1317">
-        <v>525200</v>
+        <v>9124920</v>
       </c>
       <c r="L1317">
-        <v>525200</v>
+        <v>9124920</v>
       </c>
     </row>
     <row r="1318" spans="1:12">
@@ -54406,19 +54745,19 @@
         <v>13</v>
       </c>
       <c r="D1318" t="s">
-        <v>1345</v>
+        <v>1317</v>
       </c>
       <c r="E1318" t="s">
-        <v>1349</v>
+        <v>1330</v>
       </c>
       <c r="F1318" t="s">
-        <v>1350</v>
+        <v>1331</v>
       </c>
       <c r="G1318" t="s">
-        <v>171</v>
+        <v>1332</v>
       </c>
       <c r="H1318" t="s">
-        <v>177</v>
+        <v>48</v>
       </c>
       <c r="I1318" t="s">
         <v>19</v>
@@ -54427,10 +54766,10 @@
         <v>1</v>
       </c>
       <c r="K1318">
-        <v>41321696</v>
+        <v>207286000</v>
       </c>
       <c r="L1318">
-        <v>41321696</v>
+        <v>207286000</v>
       </c>
     </row>
     <row r="1319" spans="1:12">
@@ -54444,19 +54783,19 @@
         <v>13</v>
       </c>
       <c r="D1319" t="s">
-        <v>1345</v>
+        <v>1317</v>
       </c>
       <c r="E1319" t="s">
-        <v>1349</v>
+        <v>1330</v>
       </c>
       <c r="F1319" t="s">
-        <v>1350</v>
+        <v>1331</v>
       </c>
       <c r="G1319" t="s">
-        <v>171</v>
+        <v>1332</v>
       </c>
       <c r="H1319" t="s">
-        <v>178</v>
+        <v>49</v>
       </c>
       <c r="I1319" t="s">
         <v>19</v>
@@ -54465,10 +54804,10 @@
         <v>1</v>
       </c>
       <c r="K1319">
-        <v>9468528</v>
+        <v>2970</v>
       </c>
       <c r="L1319">
-        <v>9468528</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="1320" spans="1:12">
@@ -54482,19 +54821,19 @@
         <v>13</v>
       </c>
       <c r="D1320" t="s">
-        <v>1345</v>
+        <v>1317</v>
       </c>
       <c r="E1320" t="s">
-        <v>1349</v>
+        <v>1330</v>
       </c>
       <c r="F1320" t="s">
-        <v>1350</v>
+        <v>1331</v>
       </c>
       <c r="G1320" t="s">
-        <v>171</v>
+        <v>1332</v>
       </c>
       <c r="H1320" t="s">
-        <v>179</v>
+        <v>50</v>
       </c>
       <c r="I1320" t="s">
         <v>19</v>
@@ -54503,10 +54842,10 @@
         <v>1</v>
       </c>
       <c r="K1320">
-        <v>13729784</v>
+        <v>15441560</v>
       </c>
       <c r="L1320">
-        <v>13729784</v>
+        <v>15441560</v>
       </c>
     </row>
     <row r="1321" spans="1:12">
@@ -54520,19 +54859,19 @@
         <v>13</v>
       </c>
       <c r="D1321" t="s">
-        <v>1345</v>
+        <v>1317</v>
       </c>
       <c r="E1321" t="s">
-        <v>1349</v>
+        <v>1330</v>
       </c>
       <c r="F1321" t="s">
-        <v>1350</v>
+        <v>1331</v>
       </c>
       <c r="G1321" t="s">
-        <v>171</v>
+        <v>1332</v>
       </c>
       <c r="H1321" t="s">
-        <v>180</v>
+        <v>51</v>
       </c>
       <c r="I1321" t="s">
         <v>19</v>
@@ -54541,10 +54880,10 @@
         <v>1</v>
       </c>
       <c r="K1321">
-        <v>4629928</v>
+        <v>4722688</v>
       </c>
       <c r="L1321">
-        <v>4629928</v>
+        <v>4722688</v>
       </c>
     </row>
     <row r="1322" spans="1:12">
@@ -54558,19 +54897,19 @@
         <v>13</v>
       </c>
       <c r="D1322" t="s">
-        <v>1345</v>
+        <v>1317</v>
       </c>
       <c r="E1322" t="s">
-        <v>1349</v>
+        <v>1330</v>
       </c>
       <c r="F1322" t="s">
-        <v>1350</v>
+        <v>1331</v>
       </c>
       <c r="G1322" t="s">
-        <v>171</v>
+        <v>1332</v>
       </c>
       <c r="H1322" t="s">
-        <v>184</v>
+        <v>52</v>
       </c>
       <c r="I1322" t="s">
         <v>19</v>
@@ -54579,10 +54918,10 @@
         <v>1</v>
       </c>
       <c r="K1322">
-        <v>475000</v>
+        <v>33660000</v>
       </c>
       <c r="L1322">
-        <v>475000</v>
+        <v>33660000</v>
       </c>
     </row>
     <row r="1323" spans="1:12">
@@ -54596,19 +54935,19 @@
         <v>13</v>
       </c>
       <c r="D1323" t="s">
-        <v>1345</v>
+        <v>1317</v>
       </c>
       <c r="E1323" t="s">
-        <v>1349</v>
+        <v>1330</v>
       </c>
       <c r="F1323" t="s">
-        <v>1350</v>
+        <v>1331</v>
       </c>
       <c r="G1323" t="s">
-        <v>171</v>
+        <v>1332</v>
       </c>
       <c r="H1323" t="s">
-        <v>185</v>
+        <v>53</v>
       </c>
       <c r="I1323" t="s">
         <v>19</v>
@@ -54617,10 +54956,10 @@
         <v>1</v>
       </c>
       <c r="K1323">
-        <v>1370000</v>
+        <v>13180440</v>
       </c>
       <c r="L1323">
-        <v>1370000</v>
+        <v>13180440</v>
       </c>
     </row>
     <row r="1324" spans="1:12">
@@ -54634,19 +54973,19 @@
         <v>13</v>
       </c>
       <c r="D1324" t="s">
-        <v>1345</v>
+        <v>1317</v>
       </c>
       <c r="E1324" t="s">
-        <v>1349</v>
+        <v>1333</v>
       </c>
       <c r="F1324" t="s">
-        <v>1350</v>
+        <v>1334</v>
       </c>
       <c r="G1324" t="s">
-        <v>171</v>
+        <v>1335</v>
       </c>
       <c r="H1324" t="s">
-        <v>1352</v>
+        <v>48</v>
       </c>
       <c r="I1324" t="s">
         <v>19</v>
@@ -54655,10 +54994,10 @@
         <v>1</v>
       </c>
       <c r="K1324">
-        <v>350000</v>
+        <v>111091600</v>
       </c>
       <c r="L1324">
-        <v>350000</v>
+        <v>111091600</v>
       </c>
     </row>
     <row r="1325" spans="1:12">
@@ -54672,19 +55011,19 @@
         <v>13</v>
       </c>
       <c r="D1325" t="s">
-        <v>1345</v>
+        <v>1317</v>
       </c>
       <c r="E1325" t="s">
-        <v>1349</v>
+        <v>1333</v>
       </c>
       <c r="F1325" t="s">
-        <v>1350</v>
+        <v>1334</v>
       </c>
       <c r="G1325" t="s">
-        <v>171</v>
+        <v>1335</v>
       </c>
       <c r="H1325" t="s">
-        <v>186</v>
+        <v>49</v>
       </c>
       <c r="I1325" t="s">
         <v>19</v>
@@ -54693,10 +55032,10 @@
         <v>1</v>
       </c>
       <c r="K1325">
-        <v>3390000</v>
+        <v>2345</v>
       </c>
       <c r="L1325">
-        <v>3390000</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="1326" spans="1:12">
@@ -54710,19 +55049,19 @@
         <v>13</v>
       </c>
       <c r="D1326" t="s">
-        <v>1345</v>
+        <v>1317</v>
       </c>
       <c r="E1326" t="s">
-        <v>1349</v>
+        <v>1333</v>
       </c>
       <c r="F1326" t="s">
-        <v>1350</v>
+        <v>1334</v>
       </c>
       <c r="G1326" t="s">
-        <v>171</v>
+        <v>1335</v>
       </c>
       <c r="H1326" t="s">
-        <v>187</v>
+        <v>50</v>
       </c>
       <c r="I1326" t="s">
         <v>19</v>
@@ -54731,10 +55070,10 @@
         <v>1</v>
       </c>
       <c r="K1326">
-        <v>544027</v>
+        <v>8580760</v>
       </c>
       <c r="L1326">
-        <v>544027</v>
+        <v>8580760</v>
       </c>
     </row>
     <row r="1327" spans="1:12">
@@ -54748,19 +55087,19 @@
         <v>13</v>
       </c>
       <c r="D1327" t="s">
-        <v>1345</v>
+        <v>1317</v>
       </c>
       <c r="E1327" t="s">
-        <v>1349</v>
+        <v>1333</v>
       </c>
       <c r="F1327" t="s">
-        <v>1350</v>
+        <v>1334</v>
       </c>
       <c r="G1327" t="s">
-        <v>171</v>
+        <v>1335</v>
       </c>
       <c r="H1327" t="s">
-        <v>188</v>
+        <v>51</v>
       </c>
       <c r="I1327" t="s">
         <v>19</v>
@@ -54769,10 +55108,10 @@
         <v>1</v>
       </c>
       <c r="K1327">
-        <v>158480</v>
+        <v>2478120</v>
       </c>
       <c r="L1327">
-        <v>158480</v>
+        <v>2478120</v>
       </c>
     </row>
     <row r="1328" spans="1:12">
@@ -54786,19 +55125,19 @@
         <v>13</v>
       </c>
       <c r="D1328" t="s">
-        <v>1345</v>
+        <v>1317</v>
       </c>
       <c r="E1328" t="s">
-        <v>1349</v>
+        <v>1333</v>
       </c>
       <c r="F1328" t="s">
-        <v>1350</v>
+        <v>1334</v>
       </c>
       <c r="G1328" t="s">
-        <v>171</v>
+        <v>1335</v>
       </c>
       <c r="H1328" t="s">
-        <v>189</v>
+        <v>52</v>
       </c>
       <c r="I1328" t="s">
         <v>19</v>
@@ -54807,10 +55146,10 @@
         <v>1</v>
       </c>
       <c r="K1328">
-        <v>728900</v>
+        <v>18360000</v>
       </c>
       <c r="L1328">
-        <v>728900</v>
+        <v>18360000</v>
       </c>
     </row>
     <row r="1329" spans="1:12">
@@ -54824,31 +55163,5161 @@
         <v>13</v>
       </c>
       <c r="D1329" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E1329" t="s">
+        <v>1333</v>
+      </c>
+      <c r="F1329" t="s">
+        <v>1334</v>
+      </c>
+      <c r="G1329" t="s">
+        <v>1335</v>
+      </c>
+      <c r="H1329" t="s">
+        <v>53</v>
+      </c>
+      <c r="I1329" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1329">
+        <v>1</v>
+      </c>
+      <c r="K1329">
+        <v>7314420</v>
+      </c>
+      <c r="L1329">
+        <v>7314420</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:12">
+      <c r="A1330">
+        <v>1327</v>
+      </c>
+      <c r="B1330">
+        <v>403829</v>
+      </c>
+      <c r="C1330" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1330" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E1330" t="s">
+        <v>1336</v>
+      </c>
+      <c r="F1330" t="s">
+        <v>1337</v>
+      </c>
+      <c r="G1330" t="s">
+        <v>1338</v>
+      </c>
+      <c r="H1330" t="s">
+        <v>48</v>
+      </c>
+      <c r="I1330" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1330">
+        <v>1</v>
+      </c>
+      <c r="K1330">
+        <v>72648400</v>
+      </c>
+      <c r="L1330">
+        <v>72648400</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:12">
+      <c r="A1331">
+        <v>1328</v>
+      </c>
+      <c r="B1331">
+        <v>403829</v>
+      </c>
+      <c r="C1331" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1331" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E1331" t="s">
+        <v>1336</v>
+      </c>
+      <c r="F1331" t="s">
+        <v>1337</v>
+      </c>
+      <c r="G1331" t="s">
+        <v>1338</v>
+      </c>
+      <c r="H1331" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1331" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1331">
+        <v>1</v>
+      </c>
+      <c r="K1331">
+        <v>1467</v>
+      </c>
+      <c r="L1331">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:12">
+      <c r="A1332">
+        <v>1329</v>
+      </c>
+      <c r="B1332">
+        <v>403829</v>
+      </c>
+      <c r="C1332" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1332" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E1332" t="s">
+        <v>1336</v>
+      </c>
+      <c r="F1332" t="s">
+        <v>1337</v>
+      </c>
+      <c r="G1332" t="s">
+        <v>1338</v>
+      </c>
+      <c r="H1332" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1332" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1332">
+        <v>1</v>
+      </c>
+      <c r="K1332">
+        <v>4416080</v>
+      </c>
+      <c r="L1332">
+        <v>4416080</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:12">
+      <c r="A1333">
+        <v>1330</v>
+      </c>
+      <c r="B1333">
+        <v>403829</v>
+      </c>
+      <c r="C1333" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1333" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E1333" t="s">
+        <v>1336</v>
+      </c>
+      <c r="F1333" t="s">
+        <v>1337</v>
+      </c>
+      <c r="G1333" t="s">
+        <v>1338</v>
+      </c>
+      <c r="H1333" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1333" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1333">
+        <v>1</v>
+      </c>
+      <c r="K1333">
+        <v>940392</v>
+      </c>
+      <c r="L1333">
+        <v>940392</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:12">
+      <c r="A1334">
+        <v>1331</v>
+      </c>
+      <c r="B1334">
+        <v>403829</v>
+      </c>
+      <c r="C1334" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1334" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E1334" t="s">
+        <v>1336</v>
+      </c>
+      <c r="F1334" t="s">
+        <v>1337</v>
+      </c>
+      <c r="G1334" t="s">
+        <v>1338</v>
+      </c>
+      <c r="H1334" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1334" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1334">
+        <v>1</v>
+      </c>
+      <c r="K1334">
+        <v>11520000</v>
+      </c>
+      <c r="L1334">
+        <v>11520000</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:12">
+      <c r="A1335">
+        <v>1332</v>
+      </c>
+      <c r="B1335">
+        <v>403829</v>
+      </c>
+      <c r="C1335" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1335" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E1335" t="s">
+        <v>1336</v>
+      </c>
+      <c r="F1335" t="s">
+        <v>1337</v>
+      </c>
+      <c r="G1335" t="s">
+        <v>1338</v>
+      </c>
+      <c r="H1335" t="s">
+        <v>53</v>
+      </c>
+      <c r="I1335" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1335">
+        <v>1</v>
+      </c>
+      <c r="K1335">
+        <v>3765840</v>
+      </c>
+      <c r="L1335">
+        <v>3765840</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:12">
+      <c r="A1336">
+        <v>1333</v>
+      </c>
+      <c r="B1336">
+        <v>403829</v>
+      </c>
+      <c r="C1336" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1336" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1336" t="s">
+        <v>1339</v>
+      </c>
+      <c r="F1336" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G1336" t="s">
+        <v>1341</v>
+      </c>
+      <c r="H1336" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1336" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1336">
+        <v>1</v>
+      </c>
+      <c r="K1336">
+        <v>6790000</v>
+      </c>
+      <c r="L1336">
+        <v>6790000</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:12">
+      <c r="A1337">
+        <v>1334</v>
+      </c>
+      <c r="B1337">
+        <v>403829</v>
+      </c>
+      <c r="C1337" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1337" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1337" t="s">
+        <v>1339</v>
+      </c>
+      <c r="F1337" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G1337" t="s">
+        <v>1341</v>
+      </c>
+      <c r="H1337" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1337" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1337">
+        <v>1</v>
+      </c>
+      <c r="K1337">
+        <v>28712000</v>
+      </c>
+      <c r="L1337">
+        <v>28712000</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:12">
+      <c r="A1338">
+        <v>1335</v>
+      </c>
+      <c r="B1338">
+        <v>403829</v>
+      </c>
+      <c r="C1338" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1338" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1338" t="s">
+        <v>1342</v>
+      </c>
+      <c r="F1338" t="s">
+        <v>1343</v>
+      </c>
+      <c r="G1338" t="s">
+        <v>1344</v>
+      </c>
+      <c r="H1338" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1338" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1338">
+        <v>1</v>
+      </c>
+      <c r="K1338">
+        <v>1400000</v>
+      </c>
+      <c r="L1338">
+        <v>1400000</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:12">
+      <c r="A1339">
+        <v>1336</v>
+      </c>
+      <c r="B1339">
+        <v>403829</v>
+      </c>
+      <c r="C1339" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1339" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1339" t="s">
+        <v>1342</v>
+      </c>
+      <c r="F1339" t="s">
+        <v>1343</v>
+      </c>
+      <c r="G1339" t="s">
+        <v>1344</v>
+      </c>
+      <c r="H1339" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1339" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1339">
+        <v>1</v>
+      </c>
+      <c r="K1339">
+        <v>43290000</v>
+      </c>
+      <c r="L1339">
+        <v>43290000</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:12">
+      <c r="A1340">
+        <v>1337</v>
+      </c>
+      <c r="B1340">
+        <v>403829</v>
+      </c>
+      <c r="C1340" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1340" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1340" t="s">
         <v>1345</v>
       </c>
-      <c r="E1329" t="s">
+      <c r="F1340" t="s">
+        <v>1346</v>
+      </c>
+      <c r="G1340" t="s">
+        <v>1347</v>
+      </c>
+      <c r="H1340" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1340" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1340">
+        <v>1</v>
+      </c>
+      <c r="K1340">
+        <v>2100000</v>
+      </c>
+      <c r="L1340">
+        <v>2100000</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:12">
+      <c r="A1341">
+        <v>1338</v>
+      </c>
+      <c r="B1341">
+        <v>403829</v>
+      </c>
+      <c r="C1341" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1341" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1341" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F1341" t="s">
+        <v>1346</v>
+      </c>
+      <c r="G1341" t="s">
+        <v>1347</v>
+      </c>
+      <c r="H1341" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1341" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1341">
+        <v>1</v>
+      </c>
+      <c r="K1341">
+        <v>22422000</v>
+      </c>
+      <c r="L1341">
+        <v>22422000</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:12">
+      <c r="A1342">
+        <v>1339</v>
+      </c>
+      <c r="B1342">
+        <v>403829</v>
+      </c>
+      <c r="C1342" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1342" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1342" t="s">
+        <v>1348</v>
+      </c>
+      <c r="F1342" t="s">
         <v>1349</v>
       </c>
-      <c r="F1329" t="s">
+      <c r="G1342" t="s">
         <v>1350</v>
       </c>
-      <c r="G1329" t="s">
+      <c r="H1342" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1342" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1342">
+        <v>1</v>
+      </c>
+      <c r="K1342">
+        <v>1330000</v>
+      </c>
+      <c r="L1342">
+        <v>1330000</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:12">
+      <c r="A1343">
+        <v>1340</v>
+      </c>
+      <c r="B1343">
+        <v>403829</v>
+      </c>
+      <c r="C1343" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1343" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1343" t="s">
+        <v>1348</v>
+      </c>
+      <c r="F1343" t="s">
+        <v>1349</v>
+      </c>
+      <c r="G1343" t="s">
+        <v>1350</v>
+      </c>
+      <c r="H1343" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1343" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1343">
+        <v>1</v>
+      </c>
+      <c r="K1343">
+        <v>13838000</v>
+      </c>
+      <c r="L1343">
+        <v>13838000</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:12">
+      <c r="A1344">
+        <v>1341</v>
+      </c>
+      <c r="B1344">
+        <v>403829</v>
+      </c>
+      <c r="C1344" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1344" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1344" t="s">
+        <v>1351</v>
+      </c>
+      <c r="F1344" t="s">
+        <v>1352</v>
+      </c>
+      <c r="G1344" t="s">
+        <v>1353</v>
+      </c>
+      <c r="H1344" t="s">
+        <v>241</v>
+      </c>
+      <c r="I1344" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1344">
+        <v>1</v>
+      </c>
+      <c r="K1344">
+        <v>1400000</v>
+      </c>
+      <c r="L1344">
+        <v>1400000</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:12">
+      <c r="A1345">
+        <v>1342</v>
+      </c>
+      <c r="B1345">
+        <v>403829</v>
+      </c>
+      <c r="C1345" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1345" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1345" t="s">
+        <v>1351</v>
+      </c>
+      <c r="F1345" t="s">
+        <v>1352</v>
+      </c>
+      <c r="G1345" t="s">
+        <v>1353</v>
+      </c>
+      <c r="H1345" t="s">
+        <v>149</v>
+      </c>
+      <c r="I1345" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1345">
+        <v>1</v>
+      </c>
+      <c r="K1345">
+        <v>21312000</v>
+      </c>
+      <c r="L1345">
+        <v>21312000</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:12">
+      <c r="A1346">
+        <v>1343</v>
+      </c>
+      <c r="B1346">
+        <v>403829</v>
+      </c>
+      <c r="C1346" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1346" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1346" t="s">
+        <v>1351</v>
+      </c>
+      <c r="F1346" t="s">
+        <v>1352</v>
+      </c>
+      <c r="G1346" t="s">
+        <v>1353</v>
+      </c>
+      <c r="H1346" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1346" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1346">
+        <v>1</v>
+      </c>
+      <c r="K1346">
+        <v>2214000</v>
+      </c>
+      <c r="L1346">
+        <v>2214000</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:12">
+      <c r="A1347">
+        <v>1344</v>
+      </c>
+      <c r="B1347">
+        <v>403829</v>
+      </c>
+      <c r="C1347" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1347" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1347" t="s">
+        <v>1354</v>
+      </c>
+      <c r="F1347" t="s">
+        <v>1355</v>
+      </c>
+      <c r="G1347" t="s">
+        <v>1356</v>
+      </c>
+      <c r="H1347" t="s">
+        <v>266</v>
+      </c>
+      <c r="I1347" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1347">
+        <v>1</v>
+      </c>
+      <c r="K1347">
+        <v>10395000</v>
+      </c>
+      <c r="L1347">
+        <v>10395000</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:12">
+      <c r="A1348">
+        <v>1345</v>
+      </c>
+      <c r="B1348">
+        <v>403829</v>
+      </c>
+      <c r="C1348" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1348" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1348" t="s">
+        <v>1354</v>
+      </c>
+      <c r="F1348" t="s">
+        <v>1355</v>
+      </c>
+      <c r="G1348" t="s">
+        <v>1356</v>
+      </c>
+      <c r="H1348" t="s">
+        <v>267</v>
+      </c>
+      <c r="I1348" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1348">
+        <v>1</v>
+      </c>
+      <c r="K1348">
+        <v>64935000</v>
+      </c>
+      <c r="L1348">
+        <v>64935000</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:12">
+      <c r="A1349">
+        <v>1346</v>
+      </c>
+      <c r="B1349">
+        <v>403829</v>
+      </c>
+      <c r="C1349" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1349" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1349" t="s">
+        <v>1354</v>
+      </c>
+      <c r="F1349" t="s">
+        <v>1355</v>
+      </c>
+      <c r="G1349" t="s">
+        <v>1356</v>
+      </c>
+      <c r="H1349" t="s">
+        <v>268</v>
+      </c>
+      <c r="I1349" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1349">
+        <v>1</v>
+      </c>
+      <c r="K1349">
+        <v>21853000</v>
+      </c>
+      <c r="L1349">
+        <v>21853000</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:12">
+      <c r="A1350">
+        <v>1347</v>
+      </c>
+      <c r="B1350">
+        <v>403829</v>
+      </c>
+      <c r="C1350" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1350" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1350" t="s">
+        <v>1357</v>
+      </c>
+      <c r="F1350" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G1350" t="s">
+        <v>1359</v>
+      </c>
+      <c r="H1350" t="s">
+        <v>149</v>
+      </c>
+      <c r="I1350" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1350">
+        <v>1</v>
+      </c>
+      <c r="K1350">
+        <v>2183000</v>
+      </c>
+      <c r="L1350">
+        <v>2183000</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:12">
+      <c r="A1351">
+        <v>1348</v>
+      </c>
+      <c r="B1351">
+        <v>403829</v>
+      </c>
+      <c r="C1351" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1351" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1351" t="s">
+        <v>1357</v>
+      </c>
+      <c r="F1351" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G1351" t="s">
+        <v>1359</v>
+      </c>
+      <c r="H1351" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1351" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1351">
+        <v>1</v>
+      </c>
+      <c r="K1351">
+        <v>1599000</v>
+      </c>
+      <c r="L1351">
+        <v>1599000</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:12">
+      <c r="A1352">
+        <v>1349</v>
+      </c>
+      <c r="B1352">
+        <v>403829</v>
+      </c>
+      <c r="C1352" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1352" t="s">
+        <v>1360</v>
+      </c>
+      <c r="E1352" t="s">
+        <v>1361</v>
+      </c>
+      <c r="F1352" t="s">
+        <v>1362</v>
+      </c>
+      <c r="G1352" t="s">
+        <v>1363</v>
+      </c>
+      <c r="H1352" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1352" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1352">
+        <v>1</v>
+      </c>
+      <c r="K1352">
+        <v>546300</v>
+      </c>
+      <c r="L1352">
+        <v>546300</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:12">
+      <c r="A1353">
+        <v>1350</v>
+      </c>
+      <c r="B1353">
+        <v>403829</v>
+      </c>
+      <c r="C1353" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1353" t="s">
+        <v>1364</v>
+      </c>
+      <c r="E1353" t="s">
+        <v>1365</v>
+      </c>
+      <c r="F1353" t="s">
+        <v>1366</v>
+      </c>
+      <c r="G1353" t="s">
+        <v>1367</v>
+      </c>
+      <c r="H1353" t="s">
+        <v>83</v>
+      </c>
+      <c r="I1353" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1353">
+        <v>1</v>
+      </c>
+      <c r="K1353">
+        <v>263514</v>
+      </c>
+      <c r="L1353">
+        <v>263514</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:12">
+      <c r="A1354">
+        <v>1351</v>
+      </c>
+      <c r="B1354">
+        <v>403829</v>
+      </c>
+      <c r="C1354" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1354" t="s">
+        <v>1364</v>
+      </c>
+      <c r="E1354" t="s">
+        <v>1365</v>
+      </c>
+      <c r="F1354" t="s">
+        <v>1366</v>
+      </c>
+      <c r="G1354" t="s">
+        <v>1367</v>
+      </c>
+      <c r="H1354" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1354" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1354">
+        <v>1</v>
+      </c>
+      <c r="K1354">
+        <v>2580750</v>
+      </c>
+      <c r="L1354">
+        <v>2580750</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:12">
+      <c r="A1355">
+        <v>1352</v>
+      </c>
+      <c r="B1355">
+        <v>403829</v>
+      </c>
+      <c r="C1355" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1355" t="s">
+        <v>1360</v>
+      </c>
+      <c r="E1355" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F1355" t="s">
+        <v>1369</v>
+      </c>
+      <c r="G1355" t="s">
+        <v>1370</v>
+      </c>
+      <c r="H1355" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1355" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1355">
+        <v>1</v>
+      </c>
+      <c r="K1355">
+        <v>6670000</v>
+      </c>
+      <c r="L1355">
+        <v>6670000</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:12">
+      <c r="A1356">
+        <v>1353</v>
+      </c>
+      <c r="B1356">
+        <v>403829</v>
+      </c>
+      <c r="C1356" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1356" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E1356" t="s">
+        <v>1372</v>
+      </c>
+      <c r="F1356" t="s">
+        <v>1373</v>
+      </c>
+      <c r="G1356" t="s">
+        <v>1374</v>
+      </c>
+      <c r="H1356" t="s">
+        <v>266</v>
+      </c>
+      <c r="I1356" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1356">
+        <v>1</v>
+      </c>
+      <c r="K1356">
+        <v>10325000</v>
+      </c>
+      <c r="L1356">
+        <v>10325000</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:12">
+      <c r="A1357">
+        <v>1354</v>
+      </c>
+      <c r="B1357">
+        <v>403829</v>
+      </c>
+      <c r="C1357" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1357" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E1357" t="s">
+        <v>1372</v>
+      </c>
+      <c r="F1357" t="s">
+        <v>1373</v>
+      </c>
+      <c r="G1357" t="s">
+        <v>1374</v>
+      </c>
+      <c r="H1357" t="s">
+        <v>267</v>
+      </c>
+      <c r="I1357" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1357">
+        <v>1</v>
+      </c>
+      <c r="K1357">
+        <v>94535000</v>
+      </c>
+      <c r="L1357">
+        <v>94535000</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:12">
+      <c r="A1358">
+        <v>1355</v>
+      </c>
+      <c r="B1358">
+        <v>403829</v>
+      </c>
+      <c r="C1358" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1358" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E1358" t="s">
+        <v>1372</v>
+      </c>
+      <c r="F1358" t="s">
+        <v>1373</v>
+      </c>
+      <c r="G1358" t="s">
+        <v>1374</v>
+      </c>
+      <c r="H1358" t="s">
+        <v>268</v>
+      </c>
+      <c r="I1358" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1358">
+        <v>1</v>
+      </c>
+      <c r="K1358">
+        <v>19393000</v>
+      </c>
+      <c r="L1358">
+        <v>19393000</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:12">
+      <c r="A1359">
+        <v>1356</v>
+      </c>
+      <c r="B1359">
+        <v>403829</v>
+      </c>
+      <c r="C1359" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1359" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E1359" t="s">
+        <v>1375</v>
+      </c>
+      <c r="F1359" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G1359" t="s">
         <v>171</v>
       </c>
-      <c r="H1329" t="s">
+      <c r="H1359" t="s">
+        <v>172</v>
+      </c>
+      <c r="I1359" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1359">
+        <v>1</v>
+      </c>
+      <c r="K1359">
+        <v>342900</v>
+      </c>
+      <c r="L1359">
+        <v>342900</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:12">
+      <c r="A1360">
+        <v>1357</v>
+      </c>
+      <c r="B1360">
+        <v>403829</v>
+      </c>
+      <c r="C1360" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1360" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E1360" t="s">
+        <v>1375</v>
+      </c>
+      <c r="F1360" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G1360" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1360" t="s">
+        <v>173</v>
+      </c>
+      <c r="I1360" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1360">
+        <v>1</v>
+      </c>
+      <c r="K1360">
+        <v>3941431</v>
+      </c>
+      <c r="L1360">
+        <v>3941431</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:12">
+      <c r="A1361">
+        <v>1358</v>
+      </c>
+      <c r="B1361">
+        <v>403829</v>
+      </c>
+      <c r="C1361" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1361" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E1361" t="s">
+        <v>1375</v>
+      </c>
+      <c r="F1361" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G1361" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1361" t="s">
+        <v>1377</v>
+      </c>
+      <c r="I1361" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1361">
+        <v>1</v>
+      </c>
+      <c r="K1361">
+        <v>2709720</v>
+      </c>
+      <c r="L1361">
+        <v>2709720</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:12">
+      <c r="A1362">
+        <v>1359</v>
+      </c>
+      <c r="B1362">
+        <v>403829</v>
+      </c>
+      <c r="C1362" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1362" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E1362" t="s">
+        <v>1375</v>
+      </c>
+      <c r="F1362" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G1362" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1362" t="s">
+        <v>386</v>
+      </c>
+      <c r="I1362" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1362">
+        <v>1</v>
+      </c>
+      <c r="K1362">
+        <v>300000</v>
+      </c>
+      <c r="L1362">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:12">
+      <c r="A1363">
+        <v>1360</v>
+      </c>
+      <c r="B1363">
+        <v>403829</v>
+      </c>
+      <c r="C1363" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1363" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E1363" t="s">
+        <v>1375</v>
+      </c>
+      <c r="F1363" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G1363" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1363" t="s">
+        <v>159</v>
+      </c>
+      <c r="I1363" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1363">
+        <v>1</v>
+      </c>
+      <c r="K1363">
+        <v>180000</v>
+      </c>
+      <c r="L1363">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:12">
+      <c r="A1364">
+        <v>1361</v>
+      </c>
+      <c r="B1364">
+        <v>403829</v>
+      </c>
+      <c r="C1364" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1364" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E1364" t="s">
+        <v>1375</v>
+      </c>
+      <c r="F1364" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G1364" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1364" t="s">
+        <v>174</v>
+      </c>
+      <c r="I1364" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1364">
+        <v>1</v>
+      </c>
+      <c r="K1364">
+        <v>1399500</v>
+      </c>
+      <c r="L1364">
+        <v>1399500</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:12">
+      <c r="A1365">
+        <v>1362</v>
+      </c>
+      <c r="B1365">
+        <v>403829</v>
+      </c>
+      <c r="C1365" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1365" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E1365" t="s">
+        <v>1375</v>
+      </c>
+      <c r="F1365" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G1365" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1365" t="s">
+        <v>175</v>
+      </c>
+      <c r="I1365" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1365">
+        <v>1</v>
+      </c>
+      <c r="K1365">
+        <v>8738180</v>
+      </c>
+      <c r="L1365">
+        <v>8738180</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:12">
+      <c r="A1366">
+        <v>1363</v>
+      </c>
+      <c r="B1366">
+        <v>403829</v>
+      </c>
+      <c r="C1366" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1366" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E1366" t="s">
+        <v>1375</v>
+      </c>
+      <c r="F1366" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G1366" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1366" t="s">
+        <v>254</v>
+      </c>
+      <c r="I1366" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1366">
+        <v>1</v>
+      </c>
+      <c r="K1366">
+        <v>957800</v>
+      </c>
+      <c r="L1366">
+        <v>957800</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:12">
+      <c r="A1367">
+        <v>1364</v>
+      </c>
+      <c r="B1367">
+        <v>403829</v>
+      </c>
+      <c r="C1367" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1367" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E1367" t="s">
+        <v>1375</v>
+      </c>
+      <c r="F1367" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G1367" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1367" t="s">
+        <v>176</v>
+      </c>
+      <c r="I1367" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1367">
+        <v>1</v>
+      </c>
+      <c r="K1367">
+        <v>19675000</v>
+      </c>
+      <c r="L1367">
+        <v>19675000</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:12">
+      <c r="A1368">
+        <v>1365</v>
+      </c>
+      <c r="B1368">
+        <v>403829</v>
+      </c>
+      <c r="C1368" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1368" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E1368" t="s">
+        <v>1375</v>
+      </c>
+      <c r="F1368" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G1368" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1368" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1368" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1368">
+        <v>1</v>
+      </c>
+      <c r="K1368">
+        <v>1522300</v>
+      </c>
+      <c r="L1368">
+        <v>1522300</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:12">
+      <c r="A1369">
+        <v>1366</v>
+      </c>
+      <c r="B1369">
+        <v>403829</v>
+      </c>
+      <c r="C1369" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1369" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E1369" t="s">
+        <v>1375</v>
+      </c>
+      <c r="F1369" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G1369" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1369" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1369" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1369">
+        <v>1</v>
+      </c>
+      <c r="K1369">
+        <v>525200</v>
+      </c>
+      <c r="L1369">
+        <v>525200</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:12">
+      <c r="A1370">
+        <v>1367</v>
+      </c>
+      <c r="B1370">
+        <v>403829</v>
+      </c>
+      <c r="C1370" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1370" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E1370" t="s">
+        <v>1375</v>
+      </c>
+      <c r="F1370" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G1370" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1370" t="s">
+        <v>177</v>
+      </c>
+      <c r="I1370" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1370">
+        <v>1</v>
+      </c>
+      <c r="K1370">
+        <v>41321696</v>
+      </c>
+      <c r="L1370">
+        <v>41321696</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:12">
+      <c r="A1371">
+        <v>1368</v>
+      </c>
+      <c r="B1371">
+        <v>403829</v>
+      </c>
+      <c r="C1371" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1371" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E1371" t="s">
+        <v>1375</v>
+      </c>
+      <c r="F1371" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G1371" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1371" t="s">
+        <v>178</v>
+      </c>
+      <c r="I1371" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1371">
+        <v>1</v>
+      </c>
+      <c r="K1371">
+        <v>9468528</v>
+      </c>
+      <c r="L1371">
+        <v>9468528</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:12">
+      <c r="A1372">
+        <v>1369</v>
+      </c>
+      <c r="B1372">
+        <v>403829</v>
+      </c>
+      <c r="C1372" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1372" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E1372" t="s">
+        <v>1375</v>
+      </c>
+      <c r="F1372" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G1372" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1372" t="s">
+        <v>179</v>
+      </c>
+      <c r="I1372" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1372">
+        <v>1</v>
+      </c>
+      <c r="K1372">
+        <v>13729784</v>
+      </c>
+      <c r="L1372">
+        <v>13729784</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:12">
+      <c r="A1373">
+        <v>1370</v>
+      </c>
+      <c r="B1373">
+        <v>403829</v>
+      </c>
+      <c r="C1373" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1373" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E1373" t="s">
+        <v>1375</v>
+      </c>
+      <c r="F1373" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G1373" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1373" t="s">
+        <v>180</v>
+      </c>
+      <c r="I1373" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1373">
+        <v>1</v>
+      </c>
+      <c r="K1373">
+        <v>4629928</v>
+      </c>
+      <c r="L1373">
+        <v>4629928</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:12">
+      <c r="A1374">
+        <v>1371</v>
+      </c>
+      <c r="B1374">
+        <v>403829</v>
+      </c>
+      <c r="C1374" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1374" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E1374" t="s">
+        <v>1375</v>
+      </c>
+      <c r="F1374" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G1374" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1374" t="s">
+        <v>184</v>
+      </c>
+      <c r="I1374" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1374">
+        <v>1</v>
+      </c>
+      <c r="K1374">
+        <v>475000</v>
+      </c>
+      <c r="L1374">
+        <v>475000</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:12">
+      <c r="A1375">
+        <v>1372</v>
+      </c>
+      <c r="B1375">
+        <v>403829</v>
+      </c>
+      <c r="C1375" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1375" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E1375" t="s">
+        <v>1375</v>
+      </c>
+      <c r="F1375" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G1375" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1375" t="s">
+        <v>185</v>
+      </c>
+      <c r="I1375" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1375">
+        <v>1</v>
+      </c>
+      <c r="K1375">
+        <v>1370000</v>
+      </c>
+      <c r="L1375">
+        <v>1370000</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:12">
+      <c r="A1376">
+        <v>1373</v>
+      </c>
+      <c r="B1376">
+        <v>403829</v>
+      </c>
+      <c r="C1376" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1376" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E1376" t="s">
+        <v>1375</v>
+      </c>
+      <c r="F1376" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G1376" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1376" t="s">
+        <v>1378</v>
+      </c>
+      <c r="I1376" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1376">
+        <v>1</v>
+      </c>
+      <c r="K1376">
+        <v>350000</v>
+      </c>
+      <c r="L1376">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:12">
+      <c r="A1377">
+        <v>1374</v>
+      </c>
+      <c r="B1377">
+        <v>403829</v>
+      </c>
+      <c r="C1377" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1377" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E1377" t="s">
+        <v>1375</v>
+      </c>
+      <c r="F1377" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G1377" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1377" t="s">
+        <v>186</v>
+      </c>
+      <c r="I1377" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1377">
+        <v>1</v>
+      </c>
+      <c r="K1377">
+        <v>3390000</v>
+      </c>
+      <c r="L1377">
+        <v>3390000</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:12">
+      <c r="A1378">
+        <v>1375</v>
+      </c>
+      <c r="B1378">
+        <v>403829</v>
+      </c>
+      <c r="C1378" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1378" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E1378" t="s">
+        <v>1375</v>
+      </c>
+      <c r="F1378" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G1378" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1378" t="s">
+        <v>187</v>
+      </c>
+      <c r="I1378" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1378">
+        <v>1</v>
+      </c>
+      <c r="K1378">
+        <v>544027</v>
+      </c>
+      <c r="L1378">
+        <v>544027</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:12">
+      <c r="A1379">
+        <v>1376</v>
+      </c>
+      <c r="B1379">
+        <v>403829</v>
+      </c>
+      <c r="C1379" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1379" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E1379" t="s">
+        <v>1375</v>
+      </c>
+      <c r="F1379" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G1379" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1379" t="s">
+        <v>188</v>
+      </c>
+      <c r="I1379" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1379">
+        <v>1</v>
+      </c>
+      <c r="K1379">
+        <v>158480</v>
+      </c>
+      <c r="L1379">
+        <v>158480</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:12">
+      <c r="A1380">
+        <v>1377</v>
+      </c>
+      <c r="B1380">
+        <v>403829</v>
+      </c>
+      <c r="C1380" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1380" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E1380" t="s">
+        <v>1375</v>
+      </c>
+      <c r="F1380" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G1380" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1380" t="s">
+        <v>189</v>
+      </c>
+      <c r="I1380" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1380">
+        <v>1</v>
+      </c>
+      <c r="K1380">
+        <v>728900</v>
+      </c>
+      <c r="L1380">
+        <v>728900</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:12">
+      <c r="A1381">
+        <v>1378</v>
+      </c>
+      <c r="B1381">
+        <v>403829</v>
+      </c>
+      <c r="C1381" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1381" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E1381" t="s">
+        <v>1375</v>
+      </c>
+      <c r="F1381" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G1381" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1381" t="s">
         <v>191</v>
       </c>
-      <c r="I1329" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1329">
-        <v>1</v>
-      </c>
-      <c r="K1329">
+      <c r="I1381" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1381">
+        <v>1</v>
+      </c>
+      <c r="K1381">
         <v>243360</v>
       </c>
-      <c r="L1329">
+      <c r="L1381">
         <v>243360</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:12">
+      <c r="A1382">
+        <v>1379</v>
+      </c>
+      <c r="B1382">
+        <v>403829</v>
+      </c>
+      <c r="C1382" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1382" t="s">
+        <v>1364</v>
+      </c>
+      <c r="E1382" t="s">
+        <v>1379</v>
+      </c>
+      <c r="F1382" t="s">
+        <v>1380</v>
+      </c>
+      <c r="G1382" t="s">
+        <v>1381</v>
+      </c>
+      <c r="H1382" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1382" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1382">
+        <v>1</v>
+      </c>
+      <c r="K1382">
+        <v>38612524</v>
+      </c>
+      <c r="L1382">
+        <v>38612524</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:12">
+      <c r="A1383">
+        <v>1380</v>
+      </c>
+      <c r="B1383">
+        <v>403829</v>
+      </c>
+      <c r="C1383" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1383" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E1383" t="s">
+        <v>1382</v>
+      </c>
+      <c r="F1383" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G1383" t="s">
+        <v>1384</v>
+      </c>
+      <c r="H1383" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1383" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1383">
+        <v>1</v>
+      </c>
+      <c r="K1383">
+        <v>660178100</v>
+      </c>
+      <c r="L1383">
+        <v>660178100</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:12">
+      <c r="A1384">
+        <v>1381</v>
+      </c>
+      <c r="B1384">
+        <v>403829</v>
+      </c>
+      <c r="C1384" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1384" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E1384" t="s">
+        <v>1382</v>
+      </c>
+      <c r="F1384" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G1384" t="s">
+        <v>1384</v>
+      </c>
+      <c r="H1384" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1384" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1384">
+        <v>1</v>
+      </c>
+      <c r="K1384">
+        <v>8958</v>
+      </c>
+      <c r="L1384">
+        <v>8958</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:12">
+      <c r="A1385">
+        <v>1382</v>
+      </c>
+      <c r="B1385">
+        <v>403829</v>
+      </c>
+      <c r="C1385" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1385" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E1385" t="s">
+        <v>1382</v>
+      </c>
+      <c r="F1385" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G1385" t="s">
+        <v>1384</v>
+      </c>
+      <c r="H1385" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1385" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1385">
+        <v>1</v>
+      </c>
+      <c r="K1385">
+        <v>53255630</v>
+      </c>
+      <c r="L1385">
+        <v>53255630</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:12">
+      <c r="A1386">
+        <v>1383</v>
+      </c>
+      <c r="B1386">
+        <v>403829</v>
+      </c>
+      <c r="C1386" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1386" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E1386" t="s">
+        <v>1382</v>
+      </c>
+      <c r="F1386" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G1386" t="s">
+        <v>1384</v>
+      </c>
+      <c r="H1386" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1386" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1386">
+        <v>1</v>
+      </c>
+      <c r="K1386">
+        <v>17754204</v>
+      </c>
+      <c r="L1386">
+        <v>17754204</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:12">
+      <c r="A1387">
+        <v>1384</v>
+      </c>
+      <c r="B1387">
+        <v>403829</v>
+      </c>
+      <c r="C1387" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1387" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E1387" t="s">
+        <v>1382</v>
+      </c>
+      <c r="F1387" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G1387" t="s">
+        <v>1384</v>
+      </c>
+      <c r="H1387" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1387" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1387">
+        <v>1</v>
+      </c>
+      <c r="K1387">
+        <v>145080000</v>
+      </c>
+      <c r="L1387">
+        <v>145080000</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:12">
+      <c r="A1388">
+        <v>1385</v>
+      </c>
+      <c r="B1388">
+        <v>403829</v>
+      </c>
+      <c r="C1388" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1388" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E1388" t="s">
+        <v>1382</v>
+      </c>
+      <c r="F1388" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G1388" t="s">
+        <v>1384</v>
+      </c>
+      <c r="H1388" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1388" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1388">
+        <v>1</v>
+      </c>
+      <c r="K1388">
+        <v>1383315</v>
+      </c>
+      <c r="L1388">
+        <v>1383315</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:12">
+      <c r="A1389">
+        <v>1386</v>
+      </c>
+      <c r="B1389">
+        <v>403829</v>
+      </c>
+      <c r="C1389" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1389" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E1389" t="s">
+        <v>1382</v>
+      </c>
+      <c r="F1389" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G1389" t="s">
+        <v>1384</v>
+      </c>
+      <c r="H1389" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1389" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1389">
+        <v>1</v>
+      </c>
+      <c r="K1389">
+        <v>38455020</v>
+      </c>
+      <c r="L1389">
+        <v>38455020</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:12">
+      <c r="A1390">
+        <v>1387</v>
+      </c>
+      <c r="B1390">
+        <v>403829</v>
+      </c>
+      <c r="C1390" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1390" t="s">
+        <v>1385</v>
+      </c>
+      <c r="E1390" t="s">
+        <v>1386</v>
+      </c>
+      <c r="F1390" t="s">
+        <v>1387</v>
+      </c>
+      <c r="G1390" t="s">
+        <v>1388</v>
+      </c>
+      <c r="H1390" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1390" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1390">
+        <v>1</v>
+      </c>
+      <c r="K1390">
+        <v>218760764</v>
+      </c>
+      <c r="L1390">
+        <v>218760764</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:12">
+      <c r="A1391">
+        <v>1388</v>
+      </c>
+      <c r="B1391">
+        <v>403829</v>
+      </c>
+      <c r="C1391" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1391" t="s">
+        <v>1385</v>
+      </c>
+      <c r="E1391" t="s">
+        <v>1389</v>
+      </c>
+      <c r="F1391" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G1391" t="s">
+        <v>1391</v>
+      </c>
+      <c r="H1391" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1391" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1391">
+        <v>1</v>
+      </c>
+      <c r="K1391">
+        <v>286726557</v>
+      </c>
+      <c r="L1391">
+        <v>286726557</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:12">
+      <c r="A1392">
+        <v>1389</v>
+      </c>
+      <c r="B1392">
+        <v>403829</v>
+      </c>
+      <c r="C1392" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1392" t="s">
+        <v>1385</v>
+      </c>
+      <c r="E1392" t="s">
+        <v>1392</v>
+      </c>
+      <c r="F1392" t="s">
+        <v>1393</v>
+      </c>
+      <c r="G1392" t="s">
+        <v>1394</v>
+      </c>
+      <c r="H1392" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1392" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1392">
+        <v>1</v>
+      </c>
+      <c r="K1392">
+        <v>102164682</v>
+      </c>
+      <c r="L1392">
+        <v>102164682</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:12">
+      <c r="A1393">
+        <v>1390</v>
+      </c>
+      <c r="B1393">
+        <v>403829</v>
+      </c>
+      <c r="C1393" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1393" t="s">
+        <v>1385</v>
+      </c>
+      <c r="E1393" t="s">
+        <v>1395</v>
+      </c>
+      <c r="F1393" t="s">
+        <v>1396</v>
+      </c>
+      <c r="G1393" t="s">
+        <v>1397</v>
+      </c>
+      <c r="H1393" t="s">
+        <v>272</v>
+      </c>
+      <c r="I1393" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1393">
+        <v>1</v>
+      </c>
+      <c r="K1393">
+        <v>857134320</v>
+      </c>
+      <c r="L1393">
+        <v>857134320</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:12">
+      <c r="A1394">
+        <v>1391</v>
+      </c>
+      <c r="B1394">
+        <v>403829</v>
+      </c>
+      <c r="C1394" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1394" t="s">
+        <v>1385</v>
+      </c>
+      <c r="E1394" t="s">
+        <v>1398</v>
+      </c>
+      <c r="F1394" t="s">
+        <v>1399</v>
+      </c>
+      <c r="G1394" t="s">
+        <v>1400</v>
+      </c>
+      <c r="H1394" t="s">
+        <v>272</v>
+      </c>
+      <c r="I1394" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1394">
+        <v>1</v>
+      </c>
+      <c r="K1394">
+        <v>1061890818</v>
+      </c>
+      <c r="L1394">
+        <v>1061890818</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:12">
+      <c r="A1395">
+        <v>1392</v>
+      </c>
+      <c r="B1395">
+        <v>403829</v>
+      </c>
+      <c r="C1395" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1395" t="s">
+        <v>1385</v>
+      </c>
+      <c r="E1395" t="s">
+        <v>1401</v>
+      </c>
+      <c r="F1395" t="s">
+        <v>1402</v>
+      </c>
+      <c r="G1395" t="s">
+        <v>1403</v>
+      </c>
+      <c r="H1395" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1395" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1395">
+        <v>1</v>
+      </c>
+      <c r="K1395">
+        <v>157503489</v>
+      </c>
+      <c r="L1395">
+        <v>157503489</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:12">
+      <c r="A1396">
+        <v>1393</v>
+      </c>
+      <c r="B1396">
+        <v>403829</v>
+      </c>
+      <c r="C1396" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1396" t="s">
+        <v>1404</v>
+      </c>
+      <c r="E1396" t="s">
+        <v>1405</v>
+      </c>
+      <c r="F1396" t="s">
+        <v>1406</v>
+      </c>
+      <c r="G1396" t="s">
+        <v>1407</v>
+      </c>
+      <c r="H1396" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1396" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1396">
+        <v>1</v>
+      </c>
+      <c r="K1396">
+        <v>208100</v>
+      </c>
+      <c r="L1396">
+        <v>208100</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:12">
+      <c r="A1397">
+        <v>1394</v>
+      </c>
+      <c r="B1397">
+        <v>403829</v>
+      </c>
+      <c r="C1397" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1397" t="s">
+        <v>1404</v>
+      </c>
+      <c r="E1397" t="s">
+        <v>1405</v>
+      </c>
+      <c r="F1397" t="s">
+        <v>1406</v>
+      </c>
+      <c r="G1397" t="s">
+        <v>1407</v>
+      </c>
+      <c r="H1397" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1397" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1397">
+        <v>1</v>
+      </c>
+      <c r="K1397">
+        <v>44</v>
+      </c>
+      <c r="L1397">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:12">
+      <c r="A1398">
+        <v>1395</v>
+      </c>
+      <c r="B1398">
+        <v>403829</v>
+      </c>
+      <c r="C1398" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1398" t="s">
+        <v>1404</v>
+      </c>
+      <c r="E1398" t="s">
+        <v>1405</v>
+      </c>
+      <c r="F1398" t="s">
+        <v>1406</v>
+      </c>
+      <c r="G1398" t="s">
+        <v>1407</v>
+      </c>
+      <c r="H1398" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1398" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1398">
+        <v>1</v>
+      </c>
+      <c r="K1398">
+        <v>20810</v>
+      </c>
+      <c r="L1398">
+        <v>20810</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:12">
+      <c r="A1399">
+        <v>1396</v>
+      </c>
+      <c r="B1399">
+        <v>403829</v>
+      </c>
+      <c r="C1399" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1399" t="s">
+        <v>1404</v>
+      </c>
+      <c r="E1399" t="s">
+        <v>1405</v>
+      </c>
+      <c r="F1399" t="s">
+        <v>1406</v>
+      </c>
+      <c r="G1399" t="s">
+        <v>1407</v>
+      </c>
+      <c r="H1399" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1399" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1399">
+        <v>1</v>
+      </c>
+      <c r="K1399">
+        <v>8324</v>
+      </c>
+      <c r="L1399">
+        <v>8324</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:12">
+      <c r="A1400">
+        <v>1397</v>
+      </c>
+      <c r="B1400">
+        <v>403829</v>
+      </c>
+      <c r="C1400" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1400" t="s">
+        <v>1404</v>
+      </c>
+      <c r="E1400" t="s">
+        <v>1408</v>
+      </c>
+      <c r="F1400" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G1400" t="s">
+        <v>206</v>
+      </c>
+      <c r="H1400" t="s">
+        <v>173</v>
+      </c>
+      <c r="I1400" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1400">
+        <v>1</v>
+      </c>
+      <c r="K1400">
+        <v>5483963</v>
+      </c>
+      <c r="L1400">
+        <v>5483963</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:12">
+      <c r="A1401">
+        <v>1398</v>
+      </c>
+      <c r="B1401">
+        <v>403829</v>
+      </c>
+      <c r="C1401" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1401" t="s">
+        <v>1404</v>
+      </c>
+      <c r="E1401" t="s">
+        <v>1408</v>
+      </c>
+      <c r="F1401" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G1401" t="s">
+        <v>206</v>
+      </c>
+      <c r="H1401" t="s">
+        <v>186</v>
+      </c>
+      <c r="I1401" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1401">
+        <v>1</v>
+      </c>
+      <c r="K1401">
+        <v>9716300</v>
+      </c>
+      <c r="L1401">
+        <v>9716300</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:12">
+      <c r="A1402">
+        <v>1399</v>
+      </c>
+      <c r="B1402">
+        <v>403829</v>
+      </c>
+      <c r="C1402" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1402" t="s">
+        <v>1404</v>
+      </c>
+      <c r="E1402" t="s">
+        <v>1408</v>
+      </c>
+      <c r="F1402" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G1402" t="s">
+        <v>206</v>
+      </c>
+      <c r="H1402" t="s">
+        <v>187</v>
+      </c>
+      <c r="I1402" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1402">
+        <v>1</v>
+      </c>
+      <c r="K1402">
+        <v>50000</v>
+      </c>
+      <c r="L1402">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:12">
+      <c r="A1403">
+        <v>1400</v>
+      </c>
+      <c r="B1403">
+        <v>403829</v>
+      </c>
+      <c r="C1403" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1403" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E1403" t="s">
+        <v>1410</v>
+      </c>
+      <c r="F1403" t="s">
+        <v>1411</v>
+      </c>
+      <c r="G1403" t="s">
+        <v>1412</v>
+      </c>
+      <c r="H1403" t="s">
+        <v>111</v>
+      </c>
+      <c r="I1403" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1403">
+        <v>1</v>
+      </c>
+      <c r="K1403">
+        <v>63500000</v>
+      </c>
+      <c r="L1403">
+        <v>63500000</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:12">
+      <c r="A1404">
+        <v>1401</v>
+      </c>
+      <c r="B1404">
+        <v>403829</v>
+      </c>
+      <c r="C1404" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1404" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E1404" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F1404" t="s">
+        <v>1414</v>
+      </c>
+      <c r="G1404" t="s">
+        <v>1415</v>
+      </c>
+      <c r="H1404" t="s">
+        <v>1300</v>
+      </c>
+      <c r="I1404" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1404">
+        <v>1</v>
+      </c>
+      <c r="K1404">
+        <v>21600000</v>
+      </c>
+      <c r="L1404">
+        <v>21600000</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:12">
+      <c r="A1405">
+        <v>1402</v>
+      </c>
+      <c r="B1405">
+        <v>403829</v>
+      </c>
+      <c r="C1405" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1405" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E1405" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F1405" t="s">
+        <v>1414</v>
+      </c>
+      <c r="G1405" t="s">
+        <v>1415</v>
+      </c>
+      <c r="H1405" t="s">
+        <v>1301</v>
+      </c>
+      <c r="I1405" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1405">
+        <v>1</v>
+      </c>
+      <c r="K1405">
+        <v>205400000</v>
+      </c>
+      <c r="L1405">
+        <v>205400000</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:12">
+      <c r="A1406">
+        <v>1403</v>
+      </c>
+      <c r="B1406">
+        <v>403829</v>
+      </c>
+      <c r="C1406" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1406" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E1406" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F1406" t="s">
+        <v>1414</v>
+      </c>
+      <c r="G1406" t="s">
+        <v>1415</v>
+      </c>
+      <c r="H1406" t="s">
+        <v>1302</v>
+      </c>
+      <c r="I1406" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1406">
+        <v>1</v>
+      </c>
+      <c r="K1406">
+        <v>8400000</v>
+      </c>
+      <c r="L1406">
+        <v>8400000</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:12">
+      <c r="A1407">
+        <v>1404</v>
+      </c>
+      <c r="B1407">
+        <v>403829</v>
+      </c>
+      <c r="C1407" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1407" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E1407" t="s">
+        <v>1416</v>
+      </c>
+      <c r="F1407" t="s">
+        <v>1417</v>
+      </c>
+      <c r="G1407" t="s">
+        <v>1418</v>
+      </c>
+      <c r="H1407" t="s">
+        <v>1300</v>
+      </c>
+      <c r="I1407" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1407">
+        <v>1</v>
+      </c>
+      <c r="K1407">
+        <v>21600000</v>
+      </c>
+      <c r="L1407">
+        <v>21600000</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:12">
+      <c r="A1408">
+        <v>1405</v>
+      </c>
+      <c r="B1408">
+        <v>403829</v>
+      </c>
+      <c r="C1408" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1408" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E1408" t="s">
+        <v>1416</v>
+      </c>
+      <c r="F1408" t="s">
+        <v>1417</v>
+      </c>
+      <c r="G1408" t="s">
+        <v>1418</v>
+      </c>
+      <c r="H1408" t="s">
+        <v>1301</v>
+      </c>
+      <c r="I1408" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1408">
+        <v>1</v>
+      </c>
+      <c r="K1408">
+        <v>239200000</v>
+      </c>
+      <c r="L1408">
+        <v>239200000</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:12">
+      <c r="A1409">
+        <v>1406</v>
+      </c>
+      <c r="B1409">
+        <v>403829</v>
+      </c>
+      <c r="C1409" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1409" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E1409" t="s">
+        <v>1416</v>
+      </c>
+      <c r="F1409" t="s">
+        <v>1417</v>
+      </c>
+      <c r="G1409" t="s">
+        <v>1418</v>
+      </c>
+      <c r="H1409" t="s">
+        <v>1302</v>
+      </c>
+      <c r="I1409" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1409">
+        <v>1</v>
+      </c>
+      <c r="K1409">
+        <v>5600000</v>
+      </c>
+      <c r="L1409">
+        <v>5600000</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:12">
+      <c r="A1410">
+        <v>1407</v>
+      </c>
+      <c r="B1410">
+        <v>403829</v>
+      </c>
+      <c r="C1410" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1410" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E1410" t="s">
+        <v>1419</v>
+      </c>
+      <c r="F1410" t="s">
+        <v>1420</v>
+      </c>
+      <c r="G1410" t="s">
+        <v>1421</v>
+      </c>
+      <c r="H1410" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1410" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1410">
+        <v>1</v>
+      </c>
+      <c r="K1410">
+        <v>150358818</v>
+      </c>
+      <c r="L1410">
+        <v>150358818</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:12">
+      <c r="A1411">
+        <v>1408</v>
+      </c>
+      <c r="B1411">
+        <v>403829</v>
+      </c>
+      <c r="C1411" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1411" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E1411" t="s">
+        <v>1422</v>
+      </c>
+      <c r="F1411" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G1411" t="s">
+        <v>1424</v>
+      </c>
+      <c r="H1411" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1411" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1411">
+        <v>1</v>
+      </c>
+      <c r="K1411">
+        <v>26094884</v>
+      </c>
+      <c r="L1411">
+        <v>26094884</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:12">
+      <c r="A1412">
+        <v>1409</v>
+      </c>
+      <c r="B1412">
+        <v>403829</v>
+      </c>
+      <c r="C1412" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1412" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E1412" t="s">
+        <v>1426</v>
+      </c>
+      <c r="F1412" t="s">
+        <v>1427</v>
+      </c>
+      <c r="G1412" t="s">
+        <v>1428</v>
+      </c>
+      <c r="H1412" t="s">
+        <v>154</v>
+      </c>
+      <c r="I1412" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1412">
+        <v>1</v>
+      </c>
+      <c r="K1412">
+        <v>2550000</v>
+      </c>
+      <c r="L1412">
+        <v>2550000</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:12">
+      <c r="A1413">
+        <v>1410</v>
+      </c>
+      <c r="B1413">
+        <v>403829</v>
+      </c>
+      <c r="C1413" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1413" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E1413" t="s">
+        <v>1426</v>
+      </c>
+      <c r="F1413" t="s">
+        <v>1427</v>
+      </c>
+      <c r="G1413" t="s">
+        <v>1428</v>
+      </c>
+      <c r="H1413" t="s">
+        <v>155</v>
+      </c>
+      <c r="I1413" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1413">
+        <v>1</v>
+      </c>
+      <c r="K1413">
+        <v>2480000</v>
+      </c>
+      <c r="L1413">
+        <v>2480000</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:12">
+      <c r="A1414">
+        <v>1411</v>
+      </c>
+      <c r="B1414">
+        <v>403829</v>
+      </c>
+      <c r="C1414" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1414" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E1414" t="s">
+        <v>1426</v>
+      </c>
+      <c r="F1414" t="s">
+        <v>1427</v>
+      </c>
+      <c r="G1414" t="s">
+        <v>1428</v>
+      </c>
+      <c r="H1414" t="s">
+        <v>156</v>
+      </c>
+      <c r="I1414" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1414">
+        <v>1</v>
+      </c>
+      <c r="K1414">
+        <v>1230000</v>
+      </c>
+      <c r="L1414">
+        <v>1230000</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:12">
+      <c r="A1415">
+        <v>1412</v>
+      </c>
+      <c r="B1415">
+        <v>403829</v>
+      </c>
+      <c r="C1415" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1415" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E1415" t="s">
+        <v>1426</v>
+      </c>
+      <c r="F1415" t="s">
+        <v>1427</v>
+      </c>
+      <c r="G1415" t="s">
+        <v>1428</v>
+      </c>
+      <c r="H1415" t="s">
+        <v>157</v>
+      </c>
+      <c r="I1415" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1415">
+        <v>1</v>
+      </c>
+      <c r="K1415">
+        <v>1070000</v>
+      </c>
+      <c r="L1415">
+        <v>1070000</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:12">
+      <c r="A1416">
+        <v>1413</v>
+      </c>
+      <c r="B1416">
+        <v>403829</v>
+      </c>
+      <c r="C1416" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1416" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E1416" t="s">
+        <v>1426</v>
+      </c>
+      <c r="F1416" t="s">
+        <v>1427</v>
+      </c>
+      <c r="G1416" t="s">
+        <v>1428</v>
+      </c>
+      <c r="H1416" t="s">
+        <v>158</v>
+      </c>
+      <c r="I1416" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1416">
+        <v>1</v>
+      </c>
+      <c r="K1416">
+        <v>2400000</v>
+      </c>
+      <c r="L1416">
+        <v>2400000</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:12">
+      <c r="A1417">
+        <v>1414</v>
+      </c>
+      <c r="B1417">
+        <v>403829</v>
+      </c>
+      <c r="C1417" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1417" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E1417" t="s">
+        <v>1426</v>
+      </c>
+      <c r="F1417" t="s">
+        <v>1427</v>
+      </c>
+      <c r="G1417" t="s">
+        <v>1428</v>
+      </c>
+      <c r="H1417" t="s">
+        <v>159</v>
+      </c>
+      <c r="I1417" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1417">
+        <v>1</v>
+      </c>
+      <c r="K1417">
+        <v>180000</v>
+      </c>
+      <c r="L1417">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:12">
+      <c r="A1418">
+        <v>1415</v>
+      </c>
+      <c r="B1418">
+        <v>403829</v>
+      </c>
+      <c r="C1418" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1418" t="s">
+        <v>1429</v>
+      </c>
+      <c r="E1418" t="s">
+        <v>1430</v>
+      </c>
+      <c r="F1418" t="s">
+        <v>1431</v>
+      </c>
+      <c r="G1418" t="s">
+        <v>1432</v>
+      </c>
+      <c r="H1418" t="s">
+        <v>203</v>
+      </c>
+      <c r="I1418" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1418">
+        <v>1</v>
+      </c>
+      <c r="K1418">
+        <v>184486500</v>
+      </c>
+      <c r="L1418">
+        <v>184486500</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:12">
+      <c r="A1419">
+        <v>1416</v>
+      </c>
+      <c r="B1419">
+        <v>403829</v>
+      </c>
+      <c r="C1419" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1419" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1419" t="s">
+        <v>1434</v>
+      </c>
+      <c r="F1419" t="s">
+        <v>1435</v>
+      </c>
+      <c r="G1419" t="s">
+        <v>1436</v>
+      </c>
+      <c r="H1419" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1419" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1419">
+        <v>1</v>
+      </c>
+      <c r="K1419">
+        <v>662300</v>
+      </c>
+      <c r="L1419">
+        <v>662300</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:12">
+      <c r="A1420">
+        <v>1417</v>
+      </c>
+      <c r="B1420">
+        <v>403829</v>
+      </c>
+      <c r="C1420" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1420" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1420" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F1420" t="s">
+        <v>1438</v>
+      </c>
+      <c r="G1420" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1420" t="s">
+        <v>172</v>
+      </c>
+      <c r="I1420" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1420">
+        <v>1</v>
+      </c>
+      <c r="K1420">
+        <v>342900</v>
+      </c>
+      <c r="L1420">
+        <v>342900</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:12">
+      <c r="A1421">
+        <v>1418</v>
+      </c>
+      <c r="B1421">
+        <v>403829</v>
+      </c>
+      <c r="C1421" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1421" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1421" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F1421" t="s">
+        <v>1438</v>
+      </c>
+      <c r="G1421" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1421" t="s">
+        <v>173</v>
+      </c>
+      <c r="I1421" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1421">
+        <v>1</v>
+      </c>
+      <c r="K1421">
+        <v>1569509</v>
+      </c>
+      <c r="L1421">
+        <v>1569509</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:12">
+      <c r="A1422">
+        <v>1419</v>
+      </c>
+      <c r="B1422">
+        <v>403829</v>
+      </c>
+      <c r="C1422" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1422" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1422" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F1422" t="s">
+        <v>1438</v>
+      </c>
+      <c r="G1422" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1422" t="s">
+        <v>1377</v>
+      </c>
+      <c r="I1422" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1422">
+        <v>1</v>
+      </c>
+      <c r="K1422">
+        <v>2709720</v>
+      </c>
+      <c r="L1422">
+        <v>2709720</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:12">
+      <c r="A1423">
+        <v>1420</v>
+      </c>
+      <c r="B1423">
+        <v>403829</v>
+      </c>
+      <c r="C1423" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1423" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1423" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F1423" t="s">
+        <v>1438</v>
+      </c>
+      <c r="G1423" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1423" t="s">
+        <v>386</v>
+      </c>
+      <c r="I1423" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1423">
+        <v>1</v>
+      </c>
+      <c r="K1423">
+        <v>300000</v>
+      </c>
+      <c r="L1423">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:12">
+      <c r="A1424">
+        <v>1421</v>
+      </c>
+      <c r="B1424">
+        <v>403829</v>
+      </c>
+      <c r="C1424" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1424" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1424" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F1424" t="s">
+        <v>1438</v>
+      </c>
+      <c r="G1424" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1424" t="s">
+        <v>159</v>
+      </c>
+      <c r="I1424" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1424">
+        <v>1</v>
+      </c>
+      <c r="K1424">
+        <v>180000</v>
+      </c>
+      <c r="L1424">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:12">
+      <c r="A1425">
+        <v>1422</v>
+      </c>
+      <c r="B1425">
+        <v>403829</v>
+      </c>
+      <c r="C1425" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1425" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1425" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F1425" t="s">
+        <v>1438</v>
+      </c>
+      <c r="G1425" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1425" t="s">
+        <v>174</v>
+      </c>
+      <c r="I1425" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1425">
+        <v>1</v>
+      </c>
+      <c r="K1425">
+        <v>716000</v>
+      </c>
+      <c r="L1425">
+        <v>716000</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:12">
+      <c r="A1426">
+        <v>1423</v>
+      </c>
+      <c r="B1426">
+        <v>403829</v>
+      </c>
+      <c r="C1426" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1426" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1426" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F1426" t="s">
+        <v>1438</v>
+      </c>
+      <c r="G1426" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1426" t="s">
+        <v>252</v>
+      </c>
+      <c r="I1426" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1426">
+        <v>1</v>
+      </c>
+      <c r="K1426">
+        <v>404000</v>
+      </c>
+      <c r="L1426">
+        <v>404000</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:12">
+      <c r="A1427">
+        <v>1424</v>
+      </c>
+      <c r="B1427">
+        <v>403829</v>
+      </c>
+      <c r="C1427" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1427" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1427" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F1427" t="s">
+        <v>1438</v>
+      </c>
+      <c r="G1427" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1427" t="s">
+        <v>175</v>
+      </c>
+      <c r="I1427" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1427">
+        <v>1</v>
+      </c>
+      <c r="K1427">
+        <v>4145000</v>
+      </c>
+      <c r="L1427">
+        <v>4145000</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:12">
+      <c r="A1428">
+        <v>1425</v>
+      </c>
+      <c r="B1428">
+        <v>403829</v>
+      </c>
+      <c r="C1428" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1428" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1428" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F1428" t="s">
+        <v>1438</v>
+      </c>
+      <c r="G1428" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1428" t="s">
+        <v>1040</v>
+      </c>
+      <c r="I1428" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1428">
+        <v>1</v>
+      </c>
+      <c r="K1428">
+        <v>10020000</v>
+      </c>
+      <c r="L1428">
+        <v>10020000</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:12">
+      <c r="A1429">
+        <v>1426</v>
+      </c>
+      <c r="B1429">
+        <v>403829</v>
+      </c>
+      <c r="C1429" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1429" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1429" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F1429" t="s">
+        <v>1438</v>
+      </c>
+      <c r="G1429" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1429" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1429" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1429">
+        <v>1</v>
+      </c>
+      <c r="K1429">
+        <v>724800</v>
+      </c>
+      <c r="L1429">
+        <v>724800</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:12">
+      <c r="A1430">
+        <v>1427</v>
+      </c>
+      <c r="B1430">
+        <v>403829</v>
+      </c>
+      <c r="C1430" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1430" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1430" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F1430" t="s">
+        <v>1438</v>
+      </c>
+      <c r="G1430" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1430" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1430" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1430">
+        <v>1</v>
+      </c>
+      <c r="K1430">
+        <v>525200</v>
+      </c>
+      <c r="L1430">
+        <v>525200</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:12">
+      <c r="A1431">
+        <v>1428</v>
+      </c>
+      <c r="B1431">
+        <v>403829</v>
+      </c>
+      <c r="C1431" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1431" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1431" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F1431" t="s">
+        <v>1438</v>
+      </c>
+      <c r="G1431" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1431" t="s">
+        <v>177</v>
+      </c>
+      <c r="I1431" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1431">
+        <v>1</v>
+      </c>
+      <c r="K1431">
+        <v>41321696</v>
+      </c>
+      <c r="L1431">
+        <v>41321696</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:12">
+      <c r="A1432">
+        <v>1429</v>
+      </c>
+      <c r="B1432">
+        <v>403829</v>
+      </c>
+      <c r="C1432" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1432" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1432" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F1432" t="s">
+        <v>1438</v>
+      </c>
+      <c r="G1432" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1432" t="s">
+        <v>178</v>
+      </c>
+      <c r="I1432" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1432">
+        <v>1</v>
+      </c>
+      <c r="K1432">
+        <v>9468528</v>
+      </c>
+      <c r="L1432">
+        <v>9468528</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:12">
+      <c r="A1433">
+        <v>1430</v>
+      </c>
+      <c r="B1433">
+        <v>403829</v>
+      </c>
+      <c r="C1433" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1433" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1433" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F1433" t="s">
+        <v>1438</v>
+      </c>
+      <c r="G1433" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1433" t="s">
+        <v>179</v>
+      </c>
+      <c r="I1433" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1433">
+        <v>1</v>
+      </c>
+      <c r="K1433">
+        <v>13729784</v>
+      </c>
+      <c r="L1433">
+        <v>13729784</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:12">
+      <c r="A1434">
+        <v>1431</v>
+      </c>
+      <c r="B1434">
+        <v>403829</v>
+      </c>
+      <c r="C1434" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1434" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1434" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F1434" t="s">
+        <v>1438</v>
+      </c>
+      <c r="G1434" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1434" t="s">
+        <v>180</v>
+      </c>
+      <c r="I1434" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1434">
+        <v>1</v>
+      </c>
+      <c r="K1434">
+        <v>4629928</v>
+      </c>
+      <c r="L1434">
+        <v>4629928</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:12">
+      <c r="A1435">
+        <v>1432</v>
+      </c>
+      <c r="B1435">
+        <v>403829</v>
+      </c>
+      <c r="C1435" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1435" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1435" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F1435" t="s">
+        <v>1438</v>
+      </c>
+      <c r="G1435" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1435" t="s">
+        <v>185</v>
+      </c>
+      <c r="I1435" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1435">
+        <v>1</v>
+      </c>
+      <c r="K1435">
+        <v>1385000</v>
+      </c>
+      <c r="L1435">
+        <v>1385000</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:12">
+      <c r="A1436">
+        <v>1433</v>
+      </c>
+      <c r="B1436">
+        <v>403829</v>
+      </c>
+      <c r="C1436" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1436" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1436" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F1436" t="s">
+        <v>1438</v>
+      </c>
+      <c r="G1436" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1436" t="s">
+        <v>208</v>
+      </c>
+      <c r="I1436" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1436">
+        <v>1</v>
+      </c>
+      <c r="K1436">
+        <v>500000</v>
+      </c>
+      <c r="L1436">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:12">
+      <c r="A1437">
+        <v>1434</v>
+      </c>
+      <c r="B1437">
+        <v>403829</v>
+      </c>
+      <c r="C1437" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1437" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1437" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F1437" t="s">
+        <v>1438</v>
+      </c>
+      <c r="G1437" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1437" t="s">
+        <v>186</v>
+      </c>
+      <c r="I1437" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1437">
+        <v>1</v>
+      </c>
+      <c r="K1437">
+        <v>3550000</v>
+      </c>
+      <c r="L1437">
+        <v>3550000</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:12">
+      <c r="A1438">
+        <v>1435</v>
+      </c>
+      <c r="B1438">
+        <v>403829</v>
+      </c>
+      <c r="C1438" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1438" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1438" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F1438" t="s">
+        <v>1438</v>
+      </c>
+      <c r="G1438" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1438" t="s">
+        <v>187</v>
+      </c>
+      <c r="I1438" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1438">
+        <v>1</v>
+      </c>
+      <c r="K1438">
+        <v>135000</v>
+      </c>
+      <c r="L1438">
+        <v>135000</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:12">
+      <c r="A1439">
+        <v>1436</v>
+      </c>
+      <c r="B1439">
+        <v>403829</v>
+      </c>
+      <c r="C1439" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1439" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1439" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F1439" t="s">
+        <v>1438</v>
+      </c>
+      <c r="G1439" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1439" t="s">
+        <v>189</v>
+      </c>
+      <c r="I1439" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1439">
+        <v>1</v>
+      </c>
+      <c r="K1439">
+        <v>910000</v>
+      </c>
+      <c r="L1439">
+        <v>910000</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:12">
+      <c r="A1440">
+        <v>1437</v>
+      </c>
+      <c r="B1440">
+        <v>403829</v>
+      </c>
+      <c r="C1440" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1440" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1440" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F1440" t="s">
+        <v>1438</v>
+      </c>
+      <c r="G1440" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1440" t="s">
+        <v>1167</v>
+      </c>
+      <c r="I1440" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1440">
+        <v>1</v>
+      </c>
+      <c r="K1440">
+        <v>230000</v>
+      </c>
+      <c r="L1440">
+        <v>230000</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:12">
+      <c r="A1441">
+        <v>1438</v>
+      </c>
+      <c r="B1441">
+        <v>403829</v>
+      </c>
+      <c r="C1441" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1441" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1441" t="s">
+        <v>1439</v>
+      </c>
+      <c r="F1441" t="s">
+        <v>1440</v>
+      </c>
+      <c r="G1441" t="s">
+        <v>1441</v>
+      </c>
+      <c r="H1441" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1441" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1441">
+        <v>1</v>
+      </c>
+      <c r="K1441">
+        <v>4033200</v>
+      </c>
+      <c r="L1441">
+        <v>4033200</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:12">
+      <c r="A1442">
+        <v>1439</v>
+      </c>
+      <c r="B1442">
+        <v>403829</v>
+      </c>
+      <c r="C1442" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1442" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1442" t="s">
+        <v>1439</v>
+      </c>
+      <c r="F1442" t="s">
+        <v>1440</v>
+      </c>
+      <c r="G1442" t="s">
+        <v>1441</v>
+      </c>
+      <c r="H1442" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1442" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1442">
+        <v>1</v>
+      </c>
+      <c r="K1442">
+        <v>158</v>
+      </c>
+      <c r="L1442">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:12">
+      <c r="A1443">
+        <v>1440</v>
+      </c>
+      <c r="B1443">
+        <v>403829</v>
+      </c>
+      <c r="C1443" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1443" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1443" t="s">
+        <v>1439</v>
+      </c>
+      <c r="F1443" t="s">
+        <v>1440</v>
+      </c>
+      <c r="G1443" t="s">
+        <v>1441</v>
+      </c>
+      <c r="H1443" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1443" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1443">
+        <v>1</v>
+      </c>
+      <c r="K1443">
+        <v>365040</v>
+      </c>
+      <c r="L1443">
+        <v>365040</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:12">
+      <c r="A1444">
+        <v>1441</v>
+      </c>
+      <c r="B1444">
+        <v>403829</v>
+      </c>
+      <c r="C1444" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1444" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1444" t="s">
+        <v>1439</v>
+      </c>
+      <c r="F1444" t="s">
+        <v>1440</v>
+      </c>
+      <c r="G1444" t="s">
+        <v>1441</v>
+      </c>
+      <c r="H1444" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1444" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1444">
+        <v>1</v>
+      </c>
+      <c r="K1444">
+        <v>113440</v>
+      </c>
+      <c r="L1444">
+        <v>113440</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:12">
+      <c r="A1445">
+        <v>1442</v>
+      </c>
+      <c r="B1445">
+        <v>403829</v>
+      </c>
+      <c r="C1445" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1445" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1445" t="s">
+        <v>1439</v>
+      </c>
+      <c r="F1445" t="s">
+        <v>1440</v>
+      </c>
+      <c r="G1445" t="s">
+        <v>1441</v>
+      </c>
+      <c r="H1445" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1445" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1445">
+        <v>1</v>
+      </c>
+      <c r="K1445">
+        <v>104351</v>
+      </c>
+      <c r="L1445">
+        <v>104351</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:12">
+      <c r="A1446">
+        <v>1443</v>
+      </c>
+      <c r="B1446">
+        <v>403829</v>
+      </c>
+      <c r="C1446" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1446" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1446" t="s">
+        <v>1442</v>
+      </c>
+      <c r="F1446" t="s">
+        <v>1443</v>
+      </c>
+      <c r="G1446" t="s">
+        <v>1444</v>
+      </c>
+      <c r="H1446" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1446" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1446">
+        <v>1</v>
+      </c>
+      <c r="K1446">
+        <v>228400</v>
+      </c>
+      <c r="L1446">
+        <v>228400</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:12">
+      <c r="A1447">
+        <v>1444</v>
+      </c>
+      <c r="B1447">
+        <v>403829</v>
+      </c>
+      <c r="C1447" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1447" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1447" t="s">
+        <v>1442</v>
+      </c>
+      <c r="F1447" t="s">
+        <v>1443</v>
+      </c>
+      <c r="G1447" t="s">
+        <v>1444</v>
+      </c>
+      <c r="H1447" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1447" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1447">
+        <v>1</v>
+      </c>
+      <c r="K1447">
+        <v>22840</v>
+      </c>
+      <c r="L1447">
+        <v>22840</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:12">
+      <c r="A1448">
+        <v>1445</v>
+      </c>
+      <c r="B1448">
+        <v>403829</v>
+      </c>
+      <c r="C1448" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1448" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1448" t="s">
+        <v>1445</v>
+      </c>
+      <c r="F1448" t="s">
+        <v>1446</v>
+      </c>
+      <c r="G1448" t="s">
+        <v>1447</v>
+      </c>
+      <c r="H1448" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1448" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1448">
+        <v>1</v>
+      </c>
+      <c r="K1448">
+        <v>7105000</v>
+      </c>
+      <c r="L1448">
+        <v>7105000</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:12">
+      <c r="A1449">
+        <v>1446</v>
+      </c>
+      <c r="B1449">
+        <v>403829</v>
+      </c>
+      <c r="C1449" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1449" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1449" t="s">
+        <v>1445</v>
+      </c>
+      <c r="F1449" t="s">
+        <v>1446</v>
+      </c>
+      <c r="G1449" t="s">
+        <v>1447</v>
+      </c>
+      <c r="H1449" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1449" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1449">
+        <v>1</v>
+      </c>
+      <c r="K1449">
+        <v>30636000</v>
+      </c>
+      <c r="L1449">
+        <v>30636000</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:12">
+      <c r="A1450">
+        <v>1447</v>
+      </c>
+      <c r="B1450">
+        <v>403829</v>
+      </c>
+      <c r="C1450" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1450" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1450" t="s">
+        <v>1448</v>
+      </c>
+      <c r="F1450" t="s">
+        <v>1449</v>
+      </c>
+      <c r="G1450" t="s">
+        <v>1450</v>
+      </c>
+      <c r="H1450" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1450" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1450">
+        <v>1</v>
+      </c>
+      <c r="K1450">
+        <v>1470000</v>
+      </c>
+      <c r="L1450">
+        <v>1470000</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:12">
+      <c r="A1451">
+        <v>1448</v>
+      </c>
+      <c r="B1451">
+        <v>403829</v>
+      </c>
+      <c r="C1451" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1451" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1451" t="s">
+        <v>1448</v>
+      </c>
+      <c r="F1451" t="s">
+        <v>1449</v>
+      </c>
+      <c r="G1451" t="s">
+        <v>1450</v>
+      </c>
+      <c r="H1451" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1451" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1451">
+        <v>1</v>
+      </c>
+      <c r="K1451">
+        <v>45843000</v>
+      </c>
+      <c r="L1451">
+        <v>45843000</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:12">
+      <c r="A1452">
+        <v>1449</v>
+      </c>
+      <c r="B1452">
+        <v>403829</v>
+      </c>
+      <c r="C1452" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1452" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1452" t="s">
+        <v>1451</v>
+      </c>
+      <c r="F1452" t="s">
+        <v>1452</v>
+      </c>
+      <c r="G1452" t="s">
+        <v>1453</v>
+      </c>
+      <c r="H1452" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1452" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1452">
+        <v>1</v>
+      </c>
+      <c r="K1452">
+        <v>2170000</v>
+      </c>
+      <c r="L1452">
+        <v>2170000</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:12">
+      <c r="A1453">
+        <v>1450</v>
+      </c>
+      <c r="B1453">
+        <v>403829</v>
+      </c>
+      <c r="C1453" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1453" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1453" t="s">
+        <v>1451</v>
+      </c>
+      <c r="F1453" t="s">
+        <v>1452</v>
+      </c>
+      <c r="G1453" t="s">
+        <v>1453</v>
+      </c>
+      <c r="H1453" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1453" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1453">
+        <v>1</v>
+      </c>
+      <c r="K1453">
+        <v>14763000</v>
+      </c>
+      <c r="L1453">
+        <v>14763000</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:12">
+      <c r="A1454">
+        <v>1451</v>
+      </c>
+      <c r="B1454">
+        <v>403829</v>
+      </c>
+      <c r="C1454" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1454" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1454" t="s">
+        <v>1454</v>
+      </c>
+      <c r="F1454" t="s">
+        <v>1455</v>
+      </c>
+      <c r="G1454" t="s">
+        <v>1456</v>
+      </c>
+      <c r="H1454" t="s">
+        <v>241</v>
+      </c>
+      <c r="I1454" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1454">
+        <v>1</v>
+      </c>
+      <c r="K1454">
+        <v>1470000</v>
+      </c>
+      <c r="L1454">
+        <v>1470000</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:12">
+      <c r="A1455">
+        <v>1452</v>
+      </c>
+      <c r="B1455">
+        <v>403829</v>
+      </c>
+      <c r="C1455" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1455" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1455" t="s">
+        <v>1454</v>
+      </c>
+      <c r="F1455" t="s">
+        <v>1455</v>
+      </c>
+      <c r="G1455" t="s">
+        <v>1456</v>
+      </c>
+      <c r="H1455" t="s">
+        <v>149</v>
+      </c>
+      <c r="I1455" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1455">
+        <v>1</v>
+      </c>
+      <c r="K1455">
+        <v>22829000</v>
+      </c>
+      <c r="L1455">
+        <v>22829000</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:12">
+      <c r="A1456">
+        <v>1453</v>
+      </c>
+      <c r="B1456">
+        <v>403829</v>
+      </c>
+      <c r="C1456" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1456" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1456" t="s">
+        <v>1454</v>
+      </c>
+      <c r="F1456" t="s">
+        <v>1455</v>
+      </c>
+      <c r="G1456" t="s">
+        <v>1456</v>
+      </c>
+      <c r="H1456" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1456" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1456">
+        <v>1</v>
+      </c>
+      <c r="K1456">
+        <v>2419000</v>
+      </c>
+      <c r="L1456">
+        <v>2419000</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:12">
+      <c r="A1457">
+        <v>1454</v>
+      </c>
+      <c r="B1457">
+        <v>403829</v>
+      </c>
+      <c r="C1457" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1457" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1457" t="s">
+        <v>1457</v>
+      </c>
+      <c r="F1457" t="s">
+        <v>1458</v>
+      </c>
+      <c r="G1457" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1457" t="s">
+        <v>266</v>
+      </c>
+      <c r="I1457" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1457">
+        <v>1</v>
+      </c>
+      <c r="K1457">
+        <v>10710000</v>
+      </c>
+      <c r="L1457">
+        <v>10710000</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:12">
+      <c r="A1458">
+        <v>1455</v>
+      </c>
+      <c r="B1458">
+        <v>403829</v>
+      </c>
+      <c r="C1458" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1458" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1458" t="s">
+        <v>1457</v>
+      </c>
+      <c r="F1458" t="s">
+        <v>1458</v>
+      </c>
+      <c r="G1458" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1458" t="s">
+        <v>267</v>
+      </c>
+      <c r="I1458" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1458">
+        <v>1</v>
+      </c>
+      <c r="K1458">
+        <v>67599000</v>
+      </c>
+      <c r="L1458">
+        <v>67599000</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:12">
+      <c r="A1459">
+        <v>1456</v>
+      </c>
+      <c r="B1459">
+        <v>403829</v>
+      </c>
+      <c r="C1459" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1459" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1459" t="s">
+        <v>1457</v>
+      </c>
+      <c r="F1459" t="s">
+        <v>1458</v>
+      </c>
+      <c r="G1459" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H1459" t="s">
+        <v>268</v>
+      </c>
+      <c r="I1459" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1459">
+        <v>1</v>
+      </c>
+      <c r="K1459">
+        <v>23247000</v>
+      </c>
+      <c r="L1459">
+        <v>23247000</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:12">
+      <c r="A1460">
+        <v>1457</v>
+      </c>
+      <c r="B1460">
+        <v>403829</v>
+      </c>
+      <c r="C1460" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1460" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1460" t="s">
+        <v>1460</v>
+      </c>
+      <c r="F1460" t="s">
+        <v>1461</v>
+      </c>
+      <c r="G1460" t="s">
+        <v>1462</v>
+      </c>
+      <c r="H1460" t="s">
+        <v>266</v>
+      </c>
+      <c r="I1460" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1460">
+        <v>1</v>
+      </c>
+      <c r="K1460">
+        <v>10780000</v>
+      </c>
+      <c r="L1460">
+        <v>10780000</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:12">
+      <c r="A1461">
+        <v>1458</v>
+      </c>
+      <c r="B1461">
+        <v>403829</v>
+      </c>
+      <c r="C1461" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1461" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1461" t="s">
+        <v>1460</v>
+      </c>
+      <c r="F1461" t="s">
+        <v>1461</v>
+      </c>
+      <c r="G1461" t="s">
+        <v>1462</v>
+      </c>
+      <c r="H1461" t="s">
+        <v>267</v>
+      </c>
+      <c r="I1461" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1461">
+        <v>1</v>
+      </c>
+      <c r="K1461">
+        <v>100085000</v>
+      </c>
+      <c r="L1461">
+        <v>100085000</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:12">
+      <c r="A1462">
+        <v>1459</v>
+      </c>
+      <c r="B1462">
+        <v>403829</v>
+      </c>
+      <c r="C1462" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1462" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1462" t="s">
+        <v>1460</v>
+      </c>
+      <c r="F1462" t="s">
+        <v>1461</v>
+      </c>
+      <c r="G1462" t="s">
+        <v>1462</v>
+      </c>
+      <c r="H1462" t="s">
+        <v>268</v>
+      </c>
+      <c r="I1462" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1462">
+        <v>1</v>
+      </c>
+      <c r="K1462">
+        <v>20254000</v>
+      </c>
+      <c r="L1462">
+        <v>20254000</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:12">
+      <c r="A1463">
+        <v>1460</v>
+      </c>
+      <c r="B1463">
+        <v>403829</v>
+      </c>
+      <c r="C1463" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1463" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1463" t="s">
+        <v>1463</v>
+      </c>
+      <c r="F1463" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1463" t="s">
+        <v>1465</v>
+      </c>
+      <c r="H1463" t="s">
+        <v>149</v>
+      </c>
+      <c r="I1463" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1463">
+        <v>1</v>
+      </c>
+      <c r="K1463">
+        <v>2072000</v>
+      </c>
+      <c r="L1463">
+        <v>2072000</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:12">
+      <c r="A1464">
+        <v>1461</v>
+      </c>
+      <c r="B1464">
+        <v>403829</v>
+      </c>
+      <c r="C1464" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1464" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1464" t="s">
+        <v>1463</v>
+      </c>
+      <c r="F1464" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G1464" t="s">
+        <v>1465</v>
+      </c>
+      <c r="H1464" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1464" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1464">
+        <v>1</v>
+      </c>
+      <c r="K1464">
+        <v>1722000</v>
+      </c>
+      <c r="L1464">
+        <v>1722000</v>
       </c>
     </row>
   </sheetData>

--- a/Database/MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D.xlsx
+++ b/Database/MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1502">
   <si>
     <t>MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D</t>
   </si>
@@ -4352,6 +4352,27 @@
     <t>Pembayaran Belanja Pegawai berupa Kekurangan Gaji Bulan September 2025 untuk 1 Pegawai/2 Jiwa</t>
   </si>
   <si>
+    <t>2025-10-17</t>
+  </si>
+  <si>
+    <t>'00419T</t>
+  </si>
+  <si>
+    <t>'259991310815027</t>
+  </si>
+  <si>
+    <t>Pembayaran belanja barang berupa tagihan telepon bulan Oktober 2025 untuk 12 invoice</t>
+  </si>
+  <si>
+    <t>'00420T</t>
+  </si>
+  <si>
+    <t>'259991320454564</t>
+  </si>
+  <si>
+    <t>Pembayaran belanja barang berupa tagihan listrik bulan Oktober 2025 untuk 6 invoice</t>
+  </si>
+  <si>
     <t>'00421T</t>
   </si>
   <si>
@@ -4413,6 +4434,93 @@
   </si>
   <si>
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan September 2025 untuk 5 Pegawai</t>
+  </si>
+  <si>
+    <t>2025-10-16</t>
+  </si>
+  <si>
+    <t>'00437T</t>
+  </si>
+  <si>
+    <t>'259991320487988</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang berupa Tagihan Internet Bulan September 2025 idpel No.GO18A106 An Balai Riset Perikanan Budidaya Air Tawar dan Penyuluhan Perikanan</t>
+  </si>
+  <si>
+    <t>'00438T</t>
+  </si>
+  <si>
+    <t>'259991330302342</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan September tahun 2025 untuk 169 Pegawai</t>
+  </si>
+  <si>
+    <t>'00439T</t>
+  </si>
+  <si>
+    <t>'259991310881244</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan September tahun 2025 untuk 131 Pegawai</t>
+  </si>
+  <si>
+    <t>'00440T</t>
+  </si>
+  <si>
+    <t>'259991310881247</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan September 2025 untuk 34 Pegawai</t>
+  </si>
+  <si>
+    <t>'00441T</t>
+  </si>
+  <si>
+    <t>'259991310881245</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan September tahun 2025 untuk 50 Pegawai</t>
+  </si>
+  <si>
+    <t>'00442T</t>
+  </si>
+  <si>
+    <t>'259991330302343</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan September tahun 2025 untuk 63 Pegawai</t>
+  </si>
+  <si>
+    <t>'00443T</t>
+  </si>
+  <si>
+    <t>'259991310881246</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan September tahun 2025 untuk 35 Pegawai</t>
+  </si>
+  <si>
+    <t>'00444T</t>
+  </si>
+  <si>
+    <t>'259991330302344</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan September tahun 2025 untuk 23 Pegawai</t>
+  </si>
+  <si>
+    <t>2025-10-21</t>
+  </si>
+  <si>
+    <t>'00445T</t>
+  </si>
+  <si>
+    <t>'259991310895627</t>
+  </si>
+  <si>
+    <t>'403829.023.521811.03212WA.2378EBA.A000000001.00000.2.0252.2.000000.000000.994.002.DA.000292</t>
   </si>
 </sst>
 </file>
@@ -4755,7 +4863,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:L1464"/>
+  <dimension ref="A1:L1478"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -59685,19 +59793,19 @@
         <v>13</v>
       </c>
       <c r="D1448" t="s">
-        <v>1433</v>
+        <v>1445</v>
       </c>
       <c r="E1448" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="F1448" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="G1448" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="H1448" t="s">
-        <v>233</v>
+        <v>83</v>
       </c>
       <c r="I1448" t="s">
         <v>19</v>
@@ -59706,10 +59814,10 @@
         <v>1</v>
       </c>
       <c r="K1448">
-        <v>7105000</v>
+        <v>266844</v>
       </c>
       <c r="L1448">
-        <v>7105000</v>
+        <v>266844</v>
       </c>
     </row>
     <row r="1449" spans="1:12">
@@ -59723,19 +59831,19 @@
         <v>13</v>
       </c>
       <c r="D1449" t="s">
-        <v>1433</v>
+        <v>1445</v>
       </c>
       <c r="E1449" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="F1449" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="G1449" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="H1449" t="s">
-        <v>234</v>
+        <v>84</v>
       </c>
       <c r="I1449" t="s">
         <v>19</v>
@@ -59744,10 +59852,10 @@
         <v>1</v>
       </c>
       <c r="K1449">
-        <v>30636000</v>
+        <v>2580750</v>
       </c>
       <c r="L1449">
-        <v>30636000</v>
+        <v>2580750</v>
       </c>
     </row>
     <row r="1450" spans="1:12">
@@ -59761,19 +59869,19 @@
         <v>13</v>
       </c>
       <c r="D1450" t="s">
-        <v>1433</v>
+        <v>1445</v>
       </c>
       <c r="E1450" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="F1450" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="G1450" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="H1450" t="s">
-        <v>233</v>
+        <v>79</v>
       </c>
       <c r="I1450" t="s">
         <v>19</v>
@@ -59782,10 +59890,10 @@
         <v>1</v>
       </c>
       <c r="K1450">
-        <v>1470000</v>
+        <v>39011162</v>
       </c>
       <c r="L1450">
-        <v>1470000</v>
+        <v>39011162</v>
       </c>
     </row>
     <row r="1451" spans="1:12">
@@ -59802,16 +59910,16 @@
         <v>1433</v>
       </c>
       <c r="E1451" t="s">
-        <v>1448</v>
+        <v>1452</v>
       </c>
       <c r="F1451" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="G1451" t="s">
-        <v>1450</v>
+        <v>1454</v>
       </c>
       <c r="H1451" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I1451" t="s">
         <v>19</v>
@@ -59820,10 +59928,10 @@
         <v>1</v>
       </c>
       <c r="K1451">
-        <v>45843000</v>
+        <v>7105000</v>
       </c>
       <c r="L1451">
-        <v>45843000</v>
+        <v>7105000</v>
       </c>
     </row>
     <row r="1452" spans="1:12">
@@ -59840,16 +59948,16 @@
         <v>1433</v>
       </c>
       <c r="E1452" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="F1452" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="G1452" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="H1452" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I1452" t="s">
         <v>19</v>
@@ -59858,10 +59966,10 @@
         <v>1</v>
       </c>
       <c r="K1452">
-        <v>2170000</v>
+        <v>30636000</v>
       </c>
       <c r="L1452">
-        <v>2170000</v>
+        <v>30636000</v>
       </c>
     </row>
     <row r="1453" spans="1:12">
@@ -59878,16 +59986,16 @@
         <v>1433</v>
       </c>
       <c r="E1453" t="s">
-        <v>1451</v>
+        <v>1455</v>
       </c>
       <c r="F1453" t="s">
-        <v>1452</v>
+        <v>1456</v>
       </c>
       <c r="G1453" t="s">
-        <v>1453</v>
+        <v>1457</v>
       </c>
       <c r="H1453" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I1453" t="s">
         <v>19</v>
@@ -59896,10 +60004,10 @@
         <v>1</v>
       </c>
       <c r="K1453">
-        <v>14763000</v>
+        <v>1470000</v>
       </c>
       <c r="L1453">
-        <v>14763000</v>
+        <v>1470000</v>
       </c>
     </row>
     <row r="1454" spans="1:12">
@@ -59916,16 +60024,16 @@
         <v>1433</v>
       </c>
       <c r="E1454" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="F1454" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="G1454" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="H1454" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="I1454" t="s">
         <v>19</v>
@@ -59934,10 +60042,10 @@
         <v>1</v>
       </c>
       <c r="K1454">
-        <v>1470000</v>
+        <v>45843000</v>
       </c>
       <c r="L1454">
-        <v>1470000</v>
+        <v>45843000</v>
       </c>
     </row>
     <row r="1455" spans="1:12">
@@ -59954,16 +60062,16 @@
         <v>1433</v>
       </c>
       <c r="E1455" t="s">
-        <v>1454</v>
+        <v>1458</v>
       </c>
       <c r="F1455" t="s">
-        <v>1455</v>
+        <v>1459</v>
       </c>
       <c r="G1455" t="s">
-        <v>1456</v>
+        <v>1460</v>
       </c>
       <c r="H1455" t="s">
-        <v>149</v>
+        <v>233</v>
       </c>
       <c r="I1455" t="s">
         <v>19</v>
@@ -59972,10 +60080,10 @@
         <v>1</v>
       </c>
       <c r="K1455">
-        <v>22829000</v>
+        <v>2170000</v>
       </c>
       <c r="L1455">
-        <v>22829000</v>
+        <v>2170000</v>
       </c>
     </row>
     <row r="1456" spans="1:12">
@@ -59992,16 +60100,16 @@
         <v>1433</v>
       </c>
       <c r="E1456" t="s">
-        <v>1454</v>
+        <v>1458</v>
       </c>
       <c r="F1456" t="s">
-        <v>1455</v>
+        <v>1459</v>
       </c>
       <c r="G1456" t="s">
-        <v>1456</v>
+        <v>1460</v>
       </c>
       <c r="H1456" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="I1456" t="s">
         <v>19</v>
@@ -60010,10 +60118,10 @@
         <v>1</v>
       </c>
       <c r="K1456">
-        <v>2419000</v>
+        <v>14763000</v>
       </c>
       <c r="L1456">
-        <v>2419000</v>
+        <v>14763000</v>
       </c>
     </row>
     <row r="1457" spans="1:12">
@@ -60030,16 +60138,16 @@
         <v>1433</v>
       </c>
       <c r="E1457" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="F1457" t="s">
-        <v>1458</v>
+        <v>1462</v>
       </c>
       <c r="G1457" t="s">
-        <v>1459</v>
+        <v>1463</v>
       </c>
       <c r="H1457" t="s">
-        <v>266</v>
+        <v>241</v>
       </c>
       <c r="I1457" t="s">
         <v>19</v>
@@ -60048,10 +60156,10 @@
         <v>1</v>
       </c>
       <c r="K1457">
-        <v>10710000</v>
+        <v>1470000</v>
       </c>
       <c r="L1457">
-        <v>10710000</v>
+        <v>1470000</v>
       </c>
     </row>
     <row r="1458" spans="1:12">
@@ -60068,16 +60176,16 @@
         <v>1433</v>
       </c>
       <c r="E1458" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="F1458" t="s">
-        <v>1458</v>
+        <v>1462</v>
       </c>
       <c r="G1458" t="s">
-        <v>1459</v>
+        <v>1463</v>
       </c>
       <c r="H1458" t="s">
-        <v>267</v>
+        <v>149</v>
       </c>
       <c r="I1458" t="s">
         <v>19</v>
@@ -60086,10 +60194,10 @@
         <v>1</v>
       </c>
       <c r="K1458">
-        <v>67599000</v>
+        <v>22829000</v>
       </c>
       <c r="L1458">
-        <v>67599000</v>
+        <v>22829000</v>
       </c>
     </row>
     <row r="1459" spans="1:12">
@@ -60106,16 +60214,16 @@
         <v>1433</v>
       </c>
       <c r="E1459" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="F1459" t="s">
-        <v>1458</v>
+        <v>1462</v>
       </c>
       <c r="G1459" t="s">
-        <v>1459</v>
+        <v>1463</v>
       </c>
       <c r="H1459" t="s">
-        <v>268</v>
+        <v>242</v>
       </c>
       <c r="I1459" t="s">
         <v>19</v>
@@ -60124,10 +60232,10 @@
         <v>1</v>
       </c>
       <c r="K1459">
-        <v>23247000</v>
+        <v>2419000</v>
       </c>
       <c r="L1459">
-        <v>23247000</v>
+        <v>2419000</v>
       </c>
     </row>
     <row r="1460" spans="1:12">
@@ -60144,13 +60252,13 @@
         <v>1433</v>
       </c>
       <c r="E1460" t="s">
-        <v>1460</v>
+        <v>1464</v>
       </c>
       <c r="F1460" t="s">
-        <v>1461</v>
+        <v>1465</v>
       </c>
       <c r="G1460" t="s">
-        <v>1462</v>
+        <v>1466</v>
       </c>
       <c r="H1460" t="s">
         <v>266</v>
@@ -60162,10 +60270,10 @@
         <v>1</v>
       </c>
       <c r="K1460">
-        <v>10780000</v>
+        <v>10710000</v>
       </c>
       <c r="L1460">
-        <v>10780000</v>
+        <v>10710000</v>
       </c>
     </row>
     <row r="1461" spans="1:12">
@@ -60182,13 +60290,13 @@
         <v>1433</v>
       </c>
       <c r="E1461" t="s">
-        <v>1460</v>
+        <v>1464</v>
       </c>
       <c r="F1461" t="s">
-        <v>1461</v>
+        <v>1465</v>
       </c>
       <c r="G1461" t="s">
-        <v>1462</v>
+        <v>1466</v>
       </c>
       <c r="H1461" t="s">
         <v>267</v>
@@ -60200,10 +60308,10 @@
         <v>1</v>
       </c>
       <c r="K1461">
-        <v>100085000</v>
+        <v>67599000</v>
       </c>
       <c r="L1461">
-        <v>100085000</v>
+        <v>67599000</v>
       </c>
     </row>
     <row r="1462" spans="1:12">
@@ -60220,13 +60328,13 @@
         <v>1433</v>
       </c>
       <c r="E1462" t="s">
-        <v>1460</v>
+        <v>1464</v>
       </c>
       <c r="F1462" t="s">
-        <v>1461</v>
+        <v>1465</v>
       </c>
       <c r="G1462" t="s">
-        <v>1462</v>
+        <v>1466</v>
       </c>
       <c r="H1462" t="s">
         <v>268</v>
@@ -60238,10 +60346,10 @@
         <v>1</v>
       </c>
       <c r="K1462">
-        <v>20254000</v>
+        <v>23247000</v>
       </c>
       <c r="L1462">
-        <v>20254000</v>
+        <v>23247000</v>
       </c>
     </row>
     <row r="1463" spans="1:12">
@@ -60258,16 +60366,16 @@
         <v>1433</v>
       </c>
       <c r="E1463" t="s">
-        <v>1463</v>
+        <v>1467</v>
       </c>
       <c r="F1463" t="s">
-        <v>1464</v>
+        <v>1468</v>
       </c>
       <c r="G1463" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="H1463" t="s">
-        <v>149</v>
+        <v>266</v>
       </c>
       <c r="I1463" t="s">
         <v>19</v>
@@ -60276,10 +60384,10 @@
         <v>1</v>
       </c>
       <c r="K1463">
-        <v>2072000</v>
+        <v>10780000</v>
       </c>
       <c r="L1463">
-        <v>2072000</v>
+        <v>10780000</v>
       </c>
     </row>
     <row r="1464" spans="1:12">
@@ -60296,28 +60404,560 @@
         <v>1433</v>
       </c>
       <c r="E1464" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F1464" t="s">
+        <v>1468</v>
+      </c>
+      <c r="G1464" t="s">
+        <v>1469</v>
+      </c>
+      <c r="H1464" t="s">
+        <v>267</v>
+      </c>
+      <c r="I1464" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1464">
+        <v>1</v>
+      </c>
+      <c r="K1464">
+        <v>100085000</v>
+      </c>
+      <c r="L1464">
+        <v>100085000</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:12">
+      <c r="A1465">
+        <v>1462</v>
+      </c>
+      <c r="B1465">
+        <v>403829</v>
+      </c>
+      <c r="C1465" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1465" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1465" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F1465" t="s">
+        <v>1468</v>
+      </c>
+      <c r="G1465" t="s">
+        <v>1469</v>
+      </c>
+      <c r="H1465" t="s">
+        <v>268</v>
+      </c>
+      <c r="I1465" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1465">
+        <v>1</v>
+      </c>
+      <c r="K1465">
+        <v>20254000</v>
+      </c>
+      <c r="L1465">
+        <v>20254000</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:12">
+      <c r="A1466">
         <v>1463</v>
       </c>
-      <c r="F1464" t="s">
+      <c r="B1466">
+        <v>403829</v>
+      </c>
+      <c r="C1466" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1466" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1466" t="s">
+        <v>1470</v>
+      </c>
+      <c r="F1466" t="s">
+        <v>1471</v>
+      </c>
+      <c r="G1466" t="s">
+        <v>1472</v>
+      </c>
+      <c r="H1466" t="s">
+        <v>149</v>
+      </c>
+      <c r="I1466" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1466">
+        <v>1</v>
+      </c>
+      <c r="K1466">
+        <v>2072000</v>
+      </c>
+      <c r="L1466">
+        <v>2072000</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:12">
+      <c r="A1467">
         <v>1464</v>
       </c>
-      <c r="G1464" t="s">
+      <c r="B1467">
+        <v>403829</v>
+      </c>
+      <c r="C1467" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1467" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E1467" t="s">
+        <v>1470</v>
+      </c>
+      <c r="F1467" t="s">
+        <v>1471</v>
+      </c>
+      <c r="G1467" t="s">
+        <v>1472</v>
+      </c>
+      <c r="H1467" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1467" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1467">
+        <v>1</v>
+      </c>
+      <c r="K1467">
+        <v>1722000</v>
+      </c>
+      <c r="L1467">
+        <v>1722000</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:12">
+      <c r="A1468">
         <v>1465</v>
       </c>
-      <c r="H1464" t="s">
-        <v>242</v>
-      </c>
-      <c r="I1464" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1464">
-        <v>1</v>
-      </c>
-      <c r="K1464">
-        <v>1722000</v>
-      </c>
-      <c r="L1464">
-        <v>1722000</v>
+      <c r="B1468">
+        <v>403829</v>
+      </c>
+      <c r="C1468" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1468" t="s">
+        <v>1473</v>
+      </c>
+      <c r="E1468" t="s">
+        <v>1474</v>
+      </c>
+      <c r="F1468" t="s">
+        <v>1475</v>
+      </c>
+      <c r="G1468" t="s">
+        <v>1476</v>
+      </c>
+      <c r="H1468" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1468" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1468">
+        <v>1</v>
+      </c>
+      <c r="K1468">
+        <v>6670000</v>
+      </c>
+      <c r="L1468">
+        <v>6670000</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:12">
+      <c r="A1469">
+        <v>1466</v>
+      </c>
+      <c r="B1469">
+        <v>403829</v>
+      </c>
+      <c r="C1469" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1469" t="s">
+        <v>1445</v>
+      </c>
+      <c r="E1469" t="s">
+        <v>1477</v>
+      </c>
+      <c r="F1469" t="s">
+        <v>1478</v>
+      </c>
+      <c r="G1469" t="s">
+        <v>1479</v>
+      </c>
+      <c r="H1469" t="s">
+        <v>272</v>
+      </c>
+      <c r="I1469" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1469">
+        <v>1</v>
+      </c>
+      <c r="K1469">
+        <v>1061323190</v>
+      </c>
+      <c r="L1469">
+        <v>1061323190</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:12">
+      <c r="A1470">
+        <v>1467</v>
+      </c>
+      <c r="B1470">
+        <v>403829</v>
+      </c>
+      <c r="C1470" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1470" t="s">
+        <v>1445</v>
+      </c>
+      <c r="E1470" t="s">
+        <v>1480</v>
+      </c>
+      <c r="F1470" t="s">
+        <v>1481</v>
+      </c>
+      <c r="G1470" t="s">
+        <v>1482</v>
+      </c>
+      <c r="H1470" t="s">
+        <v>272</v>
+      </c>
+      <c r="I1470" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1470">
+        <v>1</v>
+      </c>
+      <c r="K1470">
+        <v>847674315</v>
+      </c>
+      <c r="L1470">
+        <v>847674315</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:12">
+      <c r="A1471">
+        <v>1468</v>
+      </c>
+      <c r="B1471">
+        <v>403829</v>
+      </c>
+      <c r="C1471" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1471" t="s">
+        <v>1445</v>
+      </c>
+      <c r="E1471" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F1471" t="s">
+        <v>1484</v>
+      </c>
+      <c r="G1471" t="s">
+        <v>1485</v>
+      </c>
+      <c r="H1471" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1471" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1471">
+        <v>1</v>
+      </c>
+      <c r="K1471">
+        <v>2205000</v>
+      </c>
+      <c r="L1471">
+        <v>2205000</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:12">
+      <c r="A1472">
+        <v>1469</v>
+      </c>
+      <c r="B1472">
+        <v>403829</v>
+      </c>
+      <c r="C1472" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1472" t="s">
+        <v>1445</v>
+      </c>
+      <c r="E1472" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F1472" t="s">
+        <v>1484</v>
+      </c>
+      <c r="G1472" t="s">
+        <v>1485</v>
+      </c>
+      <c r="H1472" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1472" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1472">
+        <v>1</v>
+      </c>
+      <c r="K1472">
+        <v>23421000</v>
+      </c>
+      <c r="L1472">
+        <v>23421000</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:12">
+      <c r="A1473">
+        <v>1470</v>
+      </c>
+      <c r="B1473">
+        <v>403829</v>
+      </c>
+      <c r="C1473" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1473" t="s">
+        <v>1445</v>
+      </c>
+      <c r="E1473" t="s">
+        <v>1486</v>
+      </c>
+      <c r="F1473" t="s">
+        <v>1487</v>
+      </c>
+      <c r="G1473" t="s">
+        <v>1488</v>
+      </c>
+      <c r="H1473" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1473" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1473">
+        <v>1</v>
+      </c>
+      <c r="K1473">
+        <v>218763054</v>
+      </c>
+      <c r="L1473">
+        <v>218763054</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:12">
+      <c r="A1474">
+        <v>1471</v>
+      </c>
+      <c r="B1474">
+        <v>403829</v>
+      </c>
+      <c r="C1474" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1474" t="s">
+        <v>1445</v>
+      </c>
+      <c r="E1474" t="s">
+        <v>1489</v>
+      </c>
+      <c r="F1474" t="s">
+        <v>1490</v>
+      </c>
+      <c r="G1474" t="s">
+        <v>1491</v>
+      </c>
+      <c r="H1474" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1474" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1474">
+        <v>1</v>
+      </c>
+      <c r="K1474">
+        <v>287197847</v>
+      </c>
+      <c r="L1474">
+        <v>287197847</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:12">
+      <c r="A1475">
+        <v>1472</v>
+      </c>
+      <c r="B1475">
+        <v>403829</v>
+      </c>
+      <c r="C1475" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1475" t="s">
+        <v>1445</v>
+      </c>
+      <c r="E1475" t="s">
+        <v>1492</v>
+      </c>
+      <c r="F1475" t="s">
+        <v>1493</v>
+      </c>
+      <c r="G1475" t="s">
+        <v>1494</v>
+      </c>
+      <c r="H1475" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1475" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1475">
+        <v>1</v>
+      </c>
+      <c r="K1475">
+        <v>157533431</v>
+      </c>
+      <c r="L1475">
+        <v>157533431</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:12">
+      <c r="A1476">
+        <v>1473</v>
+      </c>
+      <c r="B1476">
+        <v>403829</v>
+      </c>
+      <c r="C1476" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1476" t="s">
+        <v>1445</v>
+      </c>
+      <c r="E1476" t="s">
+        <v>1495</v>
+      </c>
+      <c r="F1476" t="s">
+        <v>1496</v>
+      </c>
+      <c r="G1476" t="s">
+        <v>1497</v>
+      </c>
+      <c r="H1476" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1476" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1476">
+        <v>1</v>
+      </c>
+      <c r="K1476">
+        <v>102164682</v>
+      </c>
+      <c r="L1476">
+        <v>102164682</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:12">
+      <c r="A1477">
+        <v>1474</v>
+      </c>
+      <c r="B1477">
+        <v>403829</v>
+      </c>
+      <c r="C1477" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1477" t="s">
+        <v>1498</v>
+      </c>
+      <c r="E1477" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F1477" t="s">
+        <v>1500</v>
+      </c>
+      <c r="G1477" t="s">
+        <v>206</v>
+      </c>
+      <c r="H1477" t="s">
+        <v>1501</v>
+      </c>
+      <c r="I1477" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1477">
+        <v>1</v>
+      </c>
+      <c r="K1477">
+        <v>310000</v>
+      </c>
+      <c r="L1477">
+        <v>310000</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:12">
+      <c r="A1478">
+        <v>1475</v>
+      </c>
+      <c r="B1478">
+        <v>403829</v>
+      </c>
+      <c r="C1478" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1478" t="s">
+        <v>1498</v>
+      </c>
+      <c r="E1478" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F1478" t="s">
+        <v>1500</v>
+      </c>
+      <c r="G1478" t="s">
+        <v>206</v>
+      </c>
+      <c r="H1478" t="s">
+        <v>186</v>
+      </c>
+      <c r="I1478" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1478">
+        <v>1</v>
+      </c>
+      <c r="K1478">
+        <v>1000000</v>
+      </c>
+      <c r="L1478">
+        <v>1000000</v>
       </c>
     </row>
   </sheetData>

--- a/Database/MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D.xlsx
+++ b/Database/MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\1. SEMPUR\Realisasi_SAKTI\TA2025\Database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{202B06BF-A95F-422E-A764-FCB41F75D44C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF051CE9-7527-4153-9D3A-940D45A5D4EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10947" uniqueCount="1553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10989" uniqueCount="1557">
   <si>
     <t>MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D</t>
   </si>
@@ -4679,6 +4679,18 @@
   </si>
   <si>
     <t>'259991310957288</t>
+  </si>
+  <si>
+    <t>2025-11-04</t>
+  </si>
+  <si>
+    <t>'00452T</t>
+  </si>
+  <si>
+    <t>'259991310972315</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja barang berupa Honor Pengelola Keuangan Bulan Oktober 2025 untuk 8 Pegawai sesuai SkNoB.1/BRPBATPP/KU.110/I/2025 tanggal 2 Januari 202</t>
   </si>
 </sst>
 </file>
@@ -5021,7 +5033,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1565"/>
+  <dimension ref="A1:L1571"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -64423,6 +64435,234 @@
         <v>750000</v>
       </c>
     </row>
+    <row r="1566" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1566">
+        <v>1563</v>
+      </c>
+      <c r="B1566">
+        <v>403829</v>
+      </c>
+      <c r="C1566" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1566" t="s">
+        <v>1553</v>
+      </c>
+      <c r="E1566" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F1566" t="s">
+        <v>1555</v>
+      </c>
+      <c r="G1566" t="s">
+        <v>1556</v>
+      </c>
+      <c r="H1566" t="s">
+        <v>154</v>
+      </c>
+      <c r="I1566" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1566">
+        <v>1</v>
+      </c>
+      <c r="K1566">
+        <v>2550000</v>
+      </c>
+      <c r="L1566">
+        <v>2550000</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1567">
+        <v>1564</v>
+      </c>
+      <c r="B1567">
+        <v>403829</v>
+      </c>
+      <c r="C1567" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1567" t="s">
+        <v>1553</v>
+      </c>
+      <c r="E1567" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F1567" t="s">
+        <v>1555</v>
+      </c>
+      <c r="G1567" t="s">
+        <v>1556</v>
+      </c>
+      <c r="H1567" t="s">
+        <v>155</v>
+      </c>
+      <c r="I1567" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1567">
+        <v>1</v>
+      </c>
+      <c r="K1567">
+        <v>2480000</v>
+      </c>
+      <c r="L1567">
+        <v>2480000</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1568">
+        <v>1565</v>
+      </c>
+      <c r="B1568">
+        <v>403829</v>
+      </c>
+      <c r="C1568" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1568" t="s">
+        <v>1553</v>
+      </c>
+      <c r="E1568" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F1568" t="s">
+        <v>1555</v>
+      </c>
+      <c r="G1568" t="s">
+        <v>1556</v>
+      </c>
+      <c r="H1568" t="s">
+        <v>156</v>
+      </c>
+      <c r="I1568" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1568">
+        <v>1</v>
+      </c>
+      <c r="K1568">
+        <v>1230000</v>
+      </c>
+      <c r="L1568">
+        <v>1230000</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1569">
+        <v>1566</v>
+      </c>
+      <c r="B1569">
+        <v>403829</v>
+      </c>
+      <c r="C1569" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1569" t="s">
+        <v>1553</v>
+      </c>
+      <c r="E1569" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F1569" t="s">
+        <v>1555</v>
+      </c>
+      <c r="G1569" t="s">
+        <v>1556</v>
+      </c>
+      <c r="H1569" t="s">
+        <v>157</v>
+      </c>
+      <c r="I1569" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1569">
+        <v>1</v>
+      </c>
+      <c r="K1569">
+        <v>1070000</v>
+      </c>
+      <c r="L1569">
+        <v>1070000</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1570">
+        <v>1567</v>
+      </c>
+      <c r="B1570">
+        <v>403829</v>
+      </c>
+      <c r="C1570" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1570" t="s">
+        <v>1553</v>
+      </c>
+      <c r="E1570" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F1570" t="s">
+        <v>1555</v>
+      </c>
+      <c r="G1570" t="s">
+        <v>1556</v>
+      </c>
+      <c r="H1570" t="s">
+        <v>158</v>
+      </c>
+      <c r="I1570" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1570">
+        <v>1</v>
+      </c>
+      <c r="K1570">
+        <v>2400000</v>
+      </c>
+      <c r="L1570">
+        <v>2400000</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1571">
+        <v>1568</v>
+      </c>
+      <c r="B1571">
+        <v>403829</v>
+      </c>
+      <c r="C1571" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1571" t="s">
+        <v>1553</v>
+      </c>
+      <c r="E1571" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F1571" t="s">
+        <v>1555</v>
+      </c>
+      <c r="G1571" t="s">
+        <v>1556</v>
+      </c>
+      <c r="H1571" t="s">
+        <v>159</v>
+      </c>
+      <c r="I1571" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1571">
+        <v>1</v>
+      </c>
+      <c r="K1571">
+        <v>180000</v>
+      </c>
+      <c r="L1571">
+        <v>180000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" orientation="landscape"/>

--- a/Database/MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D.xlsx
+++ b/Database/MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\1. SEMPUR\Realisasi_SAKTI\TA2025\Database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF051CE9-7527-4153-9D3A-940D45A5D4EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{34F95243-F256-4089-A0B3-EFF40C113C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Database/MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D.xlsx
+++ b/Database/MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\1. SEMPUR\Realisasi_SAKTI\TA2025\Database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{53A63C9A-675F-47C9-A8F5-A71216C40503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2185C961-E1D0-488B-BEFE-E356FD75C5A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="14925" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="600" windowWidth="14925" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11360" uniqueCount="1631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11675" uniqueCount="1682">
   <si>
     <t>MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D</t>
   </si>
@@ -4913,6 +4913,159 @@
   </si>
   <si>
     <t>Pembayaran tunjangan kinerja bulan Oktober tahun 2025 untuk 168 Pegawai</t>
+  </si>
+  <si>
+    <t>2025-11-24</t>
+  </si>
+  <si>
+    <t>'00485T</t>
+  </si>
+  <si>
+    <t>'259991330406455</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Kekurangan Gaji PPPK Bulan Januari 2024 sd Juli 2025  untuk 61 Pegawai/172 Jiwa</t>
+  </si>
+  <si>
+    <t>2025-11-21</t>
+  </si>
+  <si>
+    <t>'00486T</t>
+  </si>
+  <si>
+    <t>'259991305238590</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Oktober 2025 untuk 167 Pegawai</t>
+  </si>
+  <si>
+    <t>'00487T</t>
+  </si>
+  <si>
+    <t>'259991311156021</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Oktober 2025 untuk 50 Pegawai</t>
+  </si>
+  <si>
+    <t>'00488T</t>
+  </si>
+  <si>
+    <t>'259991311156022</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Oktober 2025 untuk 33 Pegawai</t>
+  </si>
+  <si>
+    <t>'00489T</t>
+  </si>
+  <si>
+    <t>'259991330404922</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Oktober 2025 untuk 22 Pegawai</t>
+  </si>
+  <si>
+    <t>'00490T</t>
+  </si>
+  <si>
+    <t>'259991330404921</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Oktober 2025 untuk 62 Pegawai</t>
+  </si>
+  <si>
+    <t>'00491T</t>
+  </si>
+  <si>
+    <t>'259991305238589</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Oktober 2025 untuk 37 Pegawai</t>
+  </si>
+  <si>
+    <t>'403829.023.511628.03212WA.2378EBA.A000000001.00000.2.0252.2.000000.000000.994.001.DB.000071</t>
+  </si>
+  <si>
+    <t>'403829.023.511628.03212WA.2378EBA.A000000001.00000.2.0252.2.000000.000000.994.001.DB.000300</t>
+  </si>
+  <si>
+    <t>'00492T</t>
+  </si>
+  <si>
+    <t>'259991311161794</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Oktober tahun 2025 untuk 50 Pegawai</t>
+  </si>
+  <si>
+    <t>'00493T</t>
+  </si>
+  <si>
+    <t>'259991330406454</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Oktober tahun 2025 untuk 63 Pegawai</t>
+  </si>
+  <si>
+    <t>'00494T</t>
+  </si>
+  <si>
+    <t>'259991311161795</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Oktober tahun 2025 untuk 35 Pegawai</t>
+  </si>
+  <si>
+    <t>'00495T</t>
+  </si>
+  <si>
+    <t>'259991330406391</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Oktober tahun 2025 untuk 23 Pegawai</t>
+  </si>
+  <si>
+    <t>'00496T</t>
+  </si>
+  <si>
+    <t>'259991305239428</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Oktober tahun 2025 untuk 38 Pegawai</t>
+  </si>
+  <si>
+    <t>'403829.023.512414.03212WA.2378EBA.A000000001.00000.2.0252.2.000000.000000.994.001.DB.000072</t>
+  </si>
+  <si>
+    <t>'00497T</t>
+  </si>
+  <si>
+    <t>'259991305239509</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Oktober tahun 2025 untuk 167 Pegawai</t>
+  </si>
+  <si>
+    <t>'00498T</t>
+  </si>
+  <si>
+    <t>'259991311161796</t>
+  </si>
+  <si>
+    <t>'00499T</t>
+  </si>
+  <si>
+    <t>'259991311162740</t>
+  </si>
+  <si>
+    <t>'403829.023.522191.03212WA.2378EBA.A000000001.00000.2.0252.2.000000.000000.994.002.DA.000296</t>
+  </si>
+  <si>
+    <t>'403829.023.522191.03212WA.2378EBA.A000000001.00000.2.0252.2.000000.000000.994.002.DA.000297</t>
+  </si>
+  <si>
+    <t>'403829.023.523121.03212WA.2378EBA.A000000001.00000.2.0252.2.000000.000000.994.002.DC.000299</t>
   </si>
 </sst>
 </file>
@@ -5255,7 +5408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1624"/>
+  <dimension ref="A1:L1669"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -66899,6 +67052,1716 @@
         <v>1050297970</v>
       </c>
     </row>
+    <row r="1625" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1625">
+        <v>1622</v>
+      </c>
+      <c r="B1625">
+        <v>403829</v>
+      </c>
+      <c r="C1625" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1625" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1625" t="s">
+        <v>1632</v>
+      </c>
+      <c r="F1625" t="s">
+        <v>1633</v>
+      </c>
+      <c r="G1625" t="s">
+        <v>1634</v>
+      </c>
+      <c r="H1625" t="s">
+        <v>48</v>
+      </c>
+      <c r="I1625" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1625">
+        <v>1</v>
+      </c>
+      <c r="K1625">
+        <v>107755200</v>
+      </c>
+      <c r="L1625">
+        <v>107755200</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1626">
+        <v>1623</v>
+      </c>
+      <c r="B1626">
+        <v>403829</v>
+      </c>
+      <c r="C1626" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1626" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1626" t="s">
+        <v>1632</v>
+      </c>
+      <c r="F1626" t="s">
+        <v>1633</v>
+      </c>
+      <c r="G1626" t="s">
+        <v>1634</v>
+      </c>
+      <c r="H1626" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1626" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1626">
+        <v>1</v>
+      </c>
+      <c r="K1626">
+        <v>33406</v>
+      </c>
+      <c r="L1626">
+        <v>33406</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1627">
+        <v>1624</v>
+      </c>
+      <c r="B1627">
+        <v>403829</v>
+      </c>
+      <c r="C1627" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1627" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1627" t="s">
+        <v>1632</v>
+      </c>
+      <c r="F1627" t="s">
+        <v>1633</v>
+      </c>
+      <c r="G1627" t="s">
+        <v>1634</v>
+      </c>
+      <c r="H1627" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1627" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1627">
+        <v>1</v>
+      </c>
+      <c r="K1627">
+        <v>8255520</v>
+      </c>
+      <c r="L1627">
+        <v>8255520</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1628">
+        <v>1625</v>
+      </c>
+      <c r="B1628">
+        <v>403829</v>
+      </c>
+      <c r="C1628" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1628" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1628" t="s">
+        <v>1632</v>
+      </c>
+      <c r="F1628" t="s">
+        <v>1633</v>
+      </c>
+      <c r="G1628" t="s">
+        <v>1634</v>
+      </c>
+      <c r="H1628" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1628" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1628">
+        <v>1</v>
+      </c>
+      <c r="K1628">
+        <v>2382912</v>
+      </c>
+      <c r="L1628">
+        <v>2382912</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1629">
+        <v>1626</v>
+      </c>
+      <c r="B1629">
+        <v>403829</v>
+      </c>
+      <c r="C1629" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1629" t="s">
+        <v>1635</v>
+      </c>
+      <c r="E1629" t="s">
+        <v>1636</v>
+      </c>
+      <c r="F1629" t="s">
+        <v>1637</v>
+      </c>
+      <c r="G1629" t="s">
+        <v>1638</v>
+      </c>
+      <c r="H1629" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1629" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1629">
+        <v>1</v>
+      </c>
+      <c r="K1629">
+        <v>11235000</v>
+      </c>
+      <c r="L1629">
+        <v>11235000</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1630">
+        <v>1627</v>
+      </c>
+      <c r="B1630">
+        <v>403829</v>
+      </c>
+      <c r="C1630" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1630" t="s">
+        <v>1635</v>
+      </c>
+      <c r="E1630" t="s">
+        <v>1636</v>
+      </c>
+      <c r="F1630" t="s">
+        <v>1637</v>
+      </c>
+      <c r="G1630" t="s">
+        <v>1638</v>
+      </c>
+      <c r="H1630" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1630" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1630">
+        <v>1</v>
+      </c>
+      <c r="K1630">
+        <v>129167000</v>
+      </c>
+      <c r="L1630">
+        <v>129167000</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1631">
+        <v>1628</v>
+      </c>
+      <c r="B1631">
+        <v>403829</v>
+      </c>
+      <c r="C1631" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1631" t="s">
+        <v>1635</v>
+      </c>
+      <c r="E1631" t="s">
+        <v>1639</v>
+      </c>
+      <c r="F1631" t="s">
+        <v>1640</v>
+      </c>
+      <c r="G1631" t="s">
+        <v>1641</v>
+      </c>
+      <c r="H1631" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1631" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1631">
+        <v>1</v>
+      </c>
+      <c r="K1631">
+        <v>7665000</v>
+      </c>
+      <c r="L1631">
+        <v>7665000</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1632">
+        <v>1629</v>
+      </c>
+      <c r="B1632">
+        <v>403829</v>
+      </c>
+      <c r="C1632" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1632" t="s">
+        <v>1635</v>
+      </c>
+      <c r="E1632" t="s">
+        <v>1639</v>
+      </c>
+      <c r="F1632" t="s">
+        <v>1640</v>
+      </c>
+      <c r="G1632" t="s">
+        <v>1641</v>
+      </c>
+      <c r="H1632" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1632" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1632">
+        <v>1</v>
+      </c>
+      <c r="K1632">
+        <v>33559000</v>
+      </c>
+      <c r="L1632">
+        <v>33559000</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1633">
+        <v>1630</v>
+      </c>
+      <c r="B1633">
+        <v>403829</v>
+      </c>
+      <c r="C1633" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1633" t="s">
+        <v>1635</v>
+      </c>
+      <c r="E1633" t="s">
+        <v>1642</v>
+      </c>
+      <c r="F1633" t="s">
+        <v>1643</v>
+      </c>
+      <c r="G1633" t="s">
+        <v>1644</v>
+      </c>
+      <c r="H1633" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1633" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1633">
+        <v>1</v>
+      </c>
+      <c r="K1633">
+        <v>2415000</v>
+      </c>
+      <c r="L1633">
+        <v>2415000</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1634">
+        <v>1631</v>
+      </c>
+      <c r="B1634">
+        <v>403829</v>
+      </c>
+      <c r="C1634" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1634" t="s">
+        <v>1635</v>
+      </c>
+      <c r="E1634" t="s">
+        <v>1642</v>
+      </c>
+      <c r="F1634" t="s">
+        <v>1643</v>
+      </c>
+      <c r="G1634" t="s">
+        <v>1644</v>
+      </c>
+      <c r="H1634" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1634" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1634">
+        <v>1</v>
+      </c>
+      <c r="K1634">
+        <v>24235000</v>
+      </c>
+      <c r="L1634">
+        <v>24235000</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1635">
+        <v>1632</v>
+      </c>
+      <c r="B1635">
+        <v>403829</v>
+      </c>
+      <c r="C1635" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1635" t="s">
+        <v>1635</v>
+      </c>
+      <c r="E1635" t="s">
+        <v>1645</v>
+      </c>
+      <c r="F1635" t="s">
+        <v>1646</v>
+      </c>
+      <c r="G1635" t="s">
+        <v>1647</v>
+      </c>
+      <c r="H1635" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1635" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1635">
+        <v>1</v>
+      </c>
+      <c r="K1635">
+        <v>2415000</v>
+      </c>
+      <c r="L1635">
+        <v>2415000</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1636">
+        <v>1633</v>
+      </c>
+      <c r="B1636">
+        <v>403829</v>
+      </c>
+      <c r="C1636" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1636" t="s">
+        <v>1635</v>
+      </c>
+      <c r="E1636" t="s">
+        <v>1645</v>
+      </c>
+      <c r="F1636" t="s">
+        <v>1646</v>
+      </c>
+      <c r="G1636" t="s">
+        <v>1647</v>
+      </c>
+      <c r="H1636" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1636" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1636">
+        <v>1</v>
+      </c>
+      <c r="K1636">
+        <v>16132000</v>
+      </c>
+      <c r="L1636">
+        <v>16132000</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1637">
+        <v>1634</v>
+      </c>
+      <c r="B1637">
+        <v>403829</v>
+      </c>
+      <c r="C1637" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1637" t="s">
+        <v>1635</v>
+      </c>
+      <c r="E1637" t="s">
+        <v>1648</v>
+      </c>
+      <c r="F1637" t="s">
+        <v>1649</v>
+      </c>
+      <c r="G1637" t="s">
+        <v>1650</v>
+      </c>
+      <c r="H1637" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1637" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1637">
+        <v>1</v>
+      </c>
+      <c r="K1637">
+        <v>1610000</v>
+      </c>
+      <c r="L1637">
+        <v>1610000</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1638">
+        <v>1635</v>
+      </c>
+      <c r="B1638">
+        <v>403829</v>
+      </c>
+      <c r="C1638" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1638" t="s">
+        <v>1635</v>
+      </c>
+      <c r="E1638" t="s">
+        <v>1648</v>
+      </c>
+      <c r="F1638" t="s">
+        <v>1649</v>
+      </c>
+      <c r="G1638" t="s">
+        <v>1650</v>
+      </c>
+      <c r="H1638" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1638" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1638">
+        <v>1</v>
+      </c>
+      <c r="K1638">
+        <v>50505000</v>
+      </c>
+      <c r="L1638">
+        <v>50505000</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1639">
+        <v>1636</v>
+      </c>
+      <c r="B1639">
+        <v>403829</v>
+      </c>
+      <c r="C1639" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1639" t="s">
+        <v>1635</v>
+      </c>
+      <c r="E1639" t="s">
+        <v>1651</v>
+      </c>
+      <c r="F1639" t="s">
+        <v>1652</v>
+      </c>
+      <c r="G1639" t="s">
+        <v>1653</v>
+      </c>
+      <c r="H1639" t="s">
+        <v>1654</v>
+      </c>
+      <c r="I1639" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1639">
+        <v>1</v>
+      </c>
+      <c r="K1639">
+        <v>8855000</v>
+      </c>
+      <c r="L1639">
+        <v>8855000</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1640">
+        <v>1637</v>
+      </c>
+      <c r="B1640">
+        <v>403829</v>
+      </c>
+      <c r="C1640" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1640" t="s">
+        <v>1635</v>
+      </c>
+      <c r="E1640" t="s">
+        <v>1651</v>
+      </c>
+      <c r="F1640" t="s">
+        <v>1652</v>
+      </c>
+      <c r="G1640" t="s">
+        <v>1653</v>
+      </c>
+      <c r="H1640" t="s">
+        <v>1655</v>
+      </c>
+      <c r="I1640" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1640">
+        <v>1</v>
+      </c>
+      <c r="K1640">
+        <v>21978000</v>
+      </c>
+      <c r="L1640">
+        <v>21978000</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1641">
+        <v>1638</v>
+      </c>
+      <c r="B1641">
+        <v>403829</v>
+      </c>
+      <c r="C1641" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1641" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1641" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F1641" t="s">
+        <v>1657</v>
+      </c>
+      <c r="G1641" t="s">
+        <v>1658</v>
+      </c>
+      <c r="H1641" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1641" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1641">
+        <v>1</v>
+      </c>
+      <c r="K1641">
+        <v>218806976</v>
+      </c>
+      <c r="L1641">
+        <v>218806976</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1642">
+        <v>1639</v>
+      </c>
+      <c r="B1642">
+        <v>403829</v>
+      </c>
+      <c r="C1642" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1642" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1642" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F1642" t="s">
+        <v>1660</v>
+      </c>
+      <c r="G1642" t="s">
+        <v>1661</v>
+      </c>
+      <c r="H1642" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1642" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1642">
+        <v>1</v>
+      </c>
+      <c r="K1642">
+        <v>287255749</v>
+      </c>
+      <c r="L1642">
+        <v>287255749</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1643">
+        <v>1640</v>
+      </c>
+      <c r="B1643">
+        <v>403829</v>
+      </c>
+      <c r="C1643" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1643" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1643" t="s">
+        <v>1662</v>
+      </c>
+      <c r="F1643" t="s">
+        <v>1663</v>
+      </c>
+      <c r="G1643" t="s">
+        <v>1664</v>
+      </c>
+      <c r="H1643" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1643" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1643">
+        <v>1</v>
+      </c>
+      <c r="K1643">
+        <v>157497319</v>
+      </c>
+      <c r="L1643">
+        <v>157497319</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1644">
+        <v>1641</v>
+      </c>
+      <c r="B1644">
+        <v>403829</v>
+      </c>
+      <c r="C1644" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1644" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1644" t="s">
+        <v>1665</v>
+      </c>
+      <c r="F1644" t="s">
+        <v>1666</v>
+      </c>
+      <c r="G1644" t="s">
+        <v>1667</v>
+      </c>
+      <c r="H1644" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1644" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1644">
+        <v>1</v>
+      </c>
+      <c r="K1644">
+        <v>102408293</v>
+      </c>
+      <c r="L1644">
+        <v>102408293</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1645">
+        <v>1642</v>
+      </c>
+      <c r="B1645">
+        <v>403829</v>
+      </c>
+      <c r="C1645" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1645" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1645" t="s">
+        <v>1668</v>
+      </c>
+      <c r="F1645" t="s">
+        <v>1669</v>
+      </c>
+      <c r="G1645" t="s">
+        <v>1670</v>
+      </c>
+      <c r="H1645" t="s">
+        <v>1671</v>
+      </c>
+      <c r="I1645" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1645">
+        <v>1</v>
+      </c>
+      <c r="K1645">
+        <v>142100114</v>
+      </c>
+      <c r="L1645">
+        <v>142100114</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1646">
+        <v>1643</v>
+      </c>
+      <c r="B1646">
+        <v>403829</v>
+      </c>
+      <c r="C1646" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1646" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1646" t="s">
+        <v>1672</v>
+      </c>
+      <c r="F1646" t="s">
+        <v>1673</v>
+      </c>
+      <c r="G1646" t="s">
+        <v>1674</v>
+      </c>
+      <c r="H1646" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1646" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1646">
+        <v>1</v>
+      </c>
+      <c r="K1646">
+        <v>751848354</v>
+      </c>
+      <c r="L1646">
+        <v>751848354</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1647">
+        <v>1644</v>
+      </c>
+      <c r="B1647">
+        <v>403829</v>
+      </c>
+      <c r="C1647" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1647" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1647" t="s">
+        <v>1675</v>
+      </c>
+      <c r="F1647" t="s">
+        <v>1676</v>
+      </c>
+      <c r="G1647" t="s">
+        <v>206</v>
+      </c>
+      <c r="H1647" t="s">
+        <v>173</v>
+      </c>
+      <c r="I1647" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1647">
+        <v>1</v>
+      </c>
+      <c r="K1647">
+        <v>10000</v>
+      </c>
+      <c r="L1647">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1648">
+        <v>1645</v>
+      </c>
+      <c r="B1648">
+        <v>403829</v>
+      </c>
+      <c r="C1648" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1648" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1648" t="s">
+        <v>1675</v>
+      </c>
+      <c r="F1648" t="s">
+        <v>1676</v>
+      </c>
+      <c r="G1648" t="s">
+        <v>206</v>
+      </c>
+      <c r="H1648" t="s">
+        <v>186</v>
+      </c>
+      <c r="I1648" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1648">
+        <v>1</v>
+      </c>
+      <c r="K1648">
+        <v>23560619</v>
+      </c>
+      <c r="L1648">
+        <v>23560619</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1649">
+        <v>1646</v>
+      </c>
+      <c r="B1649">
+        <v>403829</v>
+      </c>
+      <c r="C1649" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1649" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1649" t="s">
+        <v>1677</v>
+      </c>
+      <c r="F1649" t="s">
+        <v>1678</v>
+      </c>
+      <c r="G1649" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1649" t="s">
+        <v>173</v>
+      </c>
+      <c r="I1649" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1649">
+        <v>1</v>
+      </c>
+      <c r="K1649">
+        <v>2698197</v>
+      </c>
+      <c r="L1649">
+        <v>2698197</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1650">
+        <v>1647</v>
+      </c>
+      <c r="B1650">
+        <v>403829</v>
+      </c>
+      <c r="C1650" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1650" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1650" t="s">
+        <v>1677</v>
+      </c>
+      <c r="F1650" t="s">
+        <v>1678</v>
+      </c>
+      <c r="G1650" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1650" t="s">
+        <v>1571</v>
+      </c>
+      <c r="I1650" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1650">
+        <v>1</v>
+      </c>
+      <c r="K1650">
+        <v>25300800</v>
+      </c>
+      <c r="L1650">
+        <v>25300800</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1651">
+        <v>1648</v>
+      </c>
+      <c r="B1651">
+        <v>403829</v>
+      </c>
+      <c r="C1651" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1651" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1651" t="s">
+        <v>1677</v>
+      </c>
+      <c r="F1651" t="s">
+        <v>1678</v>
+      </c>
+      <c r="G1651" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1651" t="s">
+        <v>252</v>
+      </c>
+      <c r="I1651" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1651">
+        <v>1</v>
+      </c>
+      <c r="K1651">
+        <v>404000</v>
+      </c>
+      <c r="L1651">
+        <v>404000</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1652">
+        <v>1649</v>
+      </c>
+      <c r="B1652">
+        <v>403829</v>
+      </c>
+      <c r="C1652" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1652" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1652" t="s">
+        <v>1677</v>
+      </c>
+      <c r="F1652" t="s">
+        <v>1678</v>
+      </c>
+      <c r="G1652" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1652" t="s">
+        <v>175</v>
+      </c>
+      <c r="I1652" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1652">
+        <v>1</v>
+      </c>
+      <c r="K1652">
+        <v>2722500</v>
+      </c>
+      <c r="L1652">
+        <v>2722500</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1653">
+        <v>1650</v>
+      </c>
+      <c r="B1653">
+        <v>403829</v>
+      </c>
+      <c r="C1653" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1653" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1653" t="s">
+        <v>1677</v>
+      </c>
+      <c r="F1653" t="s">
+        <v>1678</v>
+      </c>
+      <c r="G1653" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1653" t="s">
+        <v>254</v>
+      </c>
+      <c r="I1653" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1653">
+        <v>1</v>
+      </c>
+      <c r="K1653">
+        <v>1017000</v>
+      </c>
+      <c r="L1653">
+        <v>1017000</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1654">
+        <v>1651</v>
+      </c>
+      <c r="B1654">
+        <v>403829</v>
+      </c>
+      <c r="C1654" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1654" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1654" t="s">
+        <v>1677</v>
+      </c>
+      <c r="F1654" t="s">
+        <v>1678</v>
+      </c>
+      <c r="G1654" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1654" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1654" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1654">
+        <v>1</v>
+      </c>
+      <c r="K1654">
+        <v>110300</v>
+      </c>
+      <c r="L1654">
+        <v>110300</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1655">
+        <v>1652</v>
+      </c>
+      <c r="B1655">
+        <v>403829</v>
+      </c>
+      <c r="C1655" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1655" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1655" t="s">
+        <v>1677</v>
+      </c>
+      <c r="F1655" t="s">
+        <v>1678</v>
+      </c>
+      <c r="G1655" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1655" t="s">
+        <v>207</v>
+      </c>
+      <c r="I1655" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1655">
+        <v>1</v>
+      </c>
+      <c r="K1655">
+        <v>1444358</v>
+      </c>
+      <c r="L1655">
+        <v>1444358</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1656">
+        <v>1653</v>
+      </c>
+      <c r="B1656">
+        <v>403829</v>
+      </c>
+      <c r="C1656" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1656" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1656" t="s">
+        <v>1677</v>
+      </c>
+      <c r="F1656" t="s">
+        <v>1678</v>
+      </c>
+      <c r="G1656" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1656" t="s">
+        <v>178</v>
+      </c>
+      <c r="I1656" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1656">
+        <v>1</v>
+      </c>
+      <c r="K1656">
+        <v>9468528</v>
+      </c>
+      <c r="L1656">
+        <v>9468528</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1657">
+        <v>1654</v>
+      </c>
+      <c r="B1657">
+        <v>403829</v>
+      </c>
+      <c r="C1657" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1657" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1657" t="s">
+        <v>1677</v>
+      </c>
+      <c r="F1657" t="s">
+        <v>1678</v>
+      </c>
+      <c r="G1657" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1657" t="s">
+        <v>1679</v>
+      </c>
+      <c r="I1657" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1657">
+        <v>1</v>
+      </c>
+      <c r="K1657">
+        <v>22953312</v>
+      </c>
+      <c r="L1657">
+        <v>22953312</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1658">
+        <v>1655</v>
+      </c>
+      <c r="B1658">
+        <v>403829</v>
+      </c>
+      <c r="C1658" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1658" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1658" t="s">
+        <v>1677</v>
+      </c>
+      <c r="F1658" t="s">
+        <v>1678</v>
+      </c>
+      <c r="G1658" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1658" t="s">
+        <v>1680</v>
+      </c>
+      <c r="I1658" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1658">
+        <v>1</v>
+      </c>
+      <c r="K1658">
+        <v>4629928</v>
+      </c>
+      <c r="L1658">
+        <v>4629928</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1659">
+        <v>1656</v>
+      </c>
+      <c r="B1659">
+        <v>403829</v>
+      </c>
+      <c r="C1659" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1659" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1659" t="s">
+        <v>1677</v>
+      </c>
+      <c r="F1659" t="s">
+        <v>1678</v>
+      </c>
+      <c r="G1659" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1659" t="s">
+        <v>181</v>
+      </c>
+      <c r="I1659" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1659">
+        <v>1</v>
+      </c>
+      <c r="K1659">
+        <v>8951000</v>
+      </c>
+      <c r="L1659">
+        <v>8951000</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1660">
+        <v>1657</v>
+      </c>
+      <c r="B1660">
+        <v>403829</v>
+      </c>
+      <c r="C1660" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1660" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1660" t="s">
+        <v>1677</v>
+      </c>
+      <c r="F1660" t="s">
+        <v>1678</v>
+      </c>
+      <c r="G1660" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1660" t="s">
+        <v>116</v>
+      </c>
+      <c r="I1660" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1660">
+        <v>1</v>
+      </c>
+      <c r="K1660">
+        <v>1946000</v>
+      </c>
+      <c r="L1660">
+        <v>1946000</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1661">
+        <v>1658</v>
+      </c>
+      <c r="B1661">
+        <v>403829</v>
+      </c>
+      <c r="C1661" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1661" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1661" t="s">
+        <v>1677</v>
+      </c>
+      <c r="F1661" t="s">
+        <v>1678</v>
+      </c>
+      <c r="G1661" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1661" t="s">
+        <v>1378</v>
+      </c>
+      <c r="I1661" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1661">
+        <v>1</v>
+      </c>
+      <c r="K1661">
+        <v>937928</v>
+      </c>
+      <c r="L1661">
+        <v>937928</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1662">
+        <v>1659</v>
+      </c>
+      <c r="B1662">
+        <v>403829</v>
+      </c>
+      <c r="C1662" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1662" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1662" t="s">
+        <v>1677</v>
+      </c>
+      <c r="F1662" t="s">
+        <v>1678</v>
+      </c>
+      <c r="G1662" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1662" t="s">
+        <v>208</v>
+      </c>
+      <c r="I1662" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1662">
+        <v>1</v>
+      </c>
+      <c r="K1662">
+        <v>509000</v>
+      </c>
+      <c r="L1662">
+        <v>509000</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1663">
+        <v>1660</v>
+      </c>
+      <c r="B1663">
+        <v>403829</v>
+      </c>
+      <c r="C1663" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1663" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1663" t="s">
+        <v>1677</v>
+      </c>
+      <c r="F1663" t="s">
+        <v>1678</v>
+      </c>
+      <c r="G1663" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1663" t="s">
+        <v>186</v>
+      </c>
+      <c r="I1663" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1663">
+        <v>1</v>
+      </c>
+      <c r="K1663">
+        <v>2520000</v>
+      </c>
+      <c r="L1663">
+        <v>2520000</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1664">
+        <v>1661</v>
+      </c>
+      <c r="B1664">
+        <v>403829</v>
+      </c>
+      <c r="C1664" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1664" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1664" t="s">
+        <v>1677</v>
+      </c>
+      <c r="F1664" t="s">
+        <v>1678</v>
+      </c>
+      <c r="G1664" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1664" t="s">
+        <v>187</v>
+      </c>
+      <c r="I1664" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1664">
+        <v>1</v>
+      </c>
+      <c r="K1664">
+        <v>182090</v>
+      </c>
+      <c r="L1664">
+        <v>182090</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1665">
+        <v>1662</v>
+      </c>
+      <c r="B1665">
+        <v>403829</v>
+      </c>
+      <c r="C1665" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1665" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1665" t="s">
+        <v>1677</v>
+      </c>
+      <c r="F1665" t="s">
+        <v>1678</v>
+      </c>
+      <c r="G1665" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1665" t="s">
+        <v>209</v>
+      </c>
+      <c r="I1665" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1665">
+        <v>1</v>
+      </c>
+      <c r="K1665">
+        <v>104700</v>
+      </c>
+      <c r="L1665">
+        <v>104700</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1666">
+        <v>1663</v>
+      </c>
+      <c r="B1666">
+        <v>403829</v>
+      </c>
+      <c r="C1666" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1666" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1666" t="s">
+        <v>1677</v>
+      </c>
+      <c r="F1666" t="s">
+        <v>1678</v>
+      </c>
+      <c r="G1666" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1666" t="s">
+        <v>188</v>
+      </c>
+      <c r="I1666" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1666">
+        <v>1</v>
+      </c>
+      <c r="K1666">
+        <v>300000</v>
+      </c>
+      <c r="L1666">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1667">
+        <v>1664</v>
+      </c>
+      <c r="B1667">
+        <v>403829</v>
+      </c>
+      <c r="C1667" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1667" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1667" t="s">
+        <v>1677</v>
+      </c>
+      <c r="F1667" t="s">
+        <v>1678</v>
+      </c>
+      <c r="G1667" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1667" t="s">
+        <v>189</v>
+      </c>
+      <c r="I1667" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1667">
+        <v>1</v>
+      </c>
+      <c r="K1667">
+        <v>94643</v>
+      </c>
+      <c r="L1667">
+        <v>94643</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1668">
+        <v>1665</v>
+      </c>
+      <c r="B1668">
+        <v>403829</v>
+      </c>
+      <c r="C1668" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1668" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1668" t="s">
+        <v>1677</v>
+      </c>
+      <c r="F1668" t="s">
+        <v>1678</v>
+      </c>
+      <c r="G1668" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1668" t="s">
+        <v>191</v>
+      </c>
+      <c r="I1668" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1668">
+        <v>1</v>
+      </c>
+      <c r="K1668">
+        <v>2547512</v>
+      </c>
+      <c r="L1668">
+        <v>2547512</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1669">
+        <v>1666</v>
+      </c>
+      <c r="B1669">
+        <v>403829</v>
+      </c>
+      <c r="C1669" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1669" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E1669" t="s">
+        <v>1677</v>
+      </c>
+      <c r="F1669" t="s">
+        <v>1678</v>
+      </c>
+      <c r="G1669" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1669" t="s">
+        <v>1681</v>
+      </c>
+      <c r="I1669" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1669">
+        <v>1</v>
+      </c>
+      <c r="K1669">
+        <v>7889000</v>
+      </c>
+      <c r="L1669">
+        <v>7889000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" orientation="landscape"/>

--- a/Database/MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D.xlsx
+++ b/Database/MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1686">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1730">
   <si>
     <t>MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D</t>
   </si>
@@ -4700,6 +4700,45 @@
     <t>PPembayaran Belanja Barang termin ke 10 Sesuai SPKNo.2/BRPBATPP/PPK/PL.400/I/2025 Tanggal 2 Januari2025 dan BAPP No.B. 663/BRPBATPP/PPK/PL.400/X/2025 Tanggal 31 Oktober 2025</t>
   </si>
   <si>
+    <t>2025-12-01</t>
+  </si>
+  <si>
+    <t>'00454T</t>
+  </si>
+  <si>
+    <t>'259991530101767</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Desember 2025 untuk 35 Pegawai/98 Jiwa</t>
+  </si>
+  <si>
+    <t>'00455T</t>
+  </si>
+  <si>
+    <t>'259991530101768</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Desember 2025 untuk 128 Pegawai/377 Jiwa</t>
+  </si>
+  <si>
+    <t>'00456T</t>
+  </si>
+  <si>
+    <t>'259991531020710</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Desember 2025 untuk 166 Pegawai/522 Jiwa</t>
+  </si>
+  <si>
+    <t>'00457T</t>
+  </si>
+  <si>
+    <t>'259991525043007</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk Bulan Desember 2025 untuk 5 Pegawai/17 Jiwa</t>
+  </si>
+  <si>
     <t>'00458T</t>
   </si>
   <si>
@@ -4892,6 +4931,60 @@
     <t>Pembayaran Belanja Pegawai berupa kekurangan Gaji Bulan oktober 2025 sd November 2025 untuk 3 Pegawai/7 Jiwa</t>
   </si>
   <si>
+    <t>'00477T</t>
+  </si>
+  <si>
+    <t>'259991530101769</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Desember 2025 untuk 50 Pegawai/126 Jiwa</t>
+  </si>
+  <si>
+    <t>'00478T</t>
+  </si>
+  <si>
+    <t>'259991531020711</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Desember 2025 untuk 63 Pegawai/182 Jiwa</t>
+  </si>
+  <si>
+    <t>'00479T</t>
+  </si>
+  <si>
+    <t>'259991530101770</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK bulan Desember 2025 untuk 35 Pegawai/102 Jiwa</t>
+  </si>
+  <si>
+    <t>'00480T</t>
+  </si>
+  <si>
+    <t>'259991531020712</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK bulan Desember 2025 untuk 23 Pegawai/53 jiwa</t>
+  </si>
+  <si>
+    <t>'00481T</t>
+  </si>
+  <si>
+    <t>'259991525043008</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan desember 2025 untuk 38 Pegawai/107 Jiwa</t>
+  </si>
+  <si>
+    <t>'00482T</t>
+  </si>
+  <si>
+    <t>'259991525043009</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Induk PPPK Bulan Desember 2025 untuk 167 Pegawai/443 jiwa</t>
+  </si>
+  <si>
     <t>'00483T</t>
   </si>
   <si>
@@ -5063,6 +5156,27 @@
     <t>'403829.023.523121.03212WA.2378EBA.A000000001.00000.2.0252.2.000000.000000.994.002.DC.000299</t>
   </si>
   <si>
+    <t>'00500T</t>
+  </si>
+  <si>
+    <t>'259991530114927</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan November Tahun 2025 untuk 7 Pegawai.sesuai Sk No. 9 Tahun 2025 Tanggal 6 Januari 2025</t>
+  </si>
+  <si>
+    <t>'403829.023.521111.03212WA.2378EBA.A000000001.00000.2.0252.2.000000.000000.994.002.DA.000301</t>
+  </si>
+  <si>
+    <t>'00501T</t>
+  </si>
+  <si>
+    <t>'259991531021578</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan November Tahun 2025 untuk 2 Pegawai.Sesuai Sk No.09 Tahun 2025 Tanggal 6 Januari 2025</t>
+  </si>
+  <si>
     <t>2025-11-25</t>
   </si>
   <si>
@@ -5073,6 +5187,24 @@
   </si>
   <si>
     <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Oktober 2025 untuk 1 Pegawai</t>
+  </si>
+  <si>
+    <t>'00503T</t>
+  </si>
+  <si>
+    <t>'259991311214610</t>
+  </si>
+  <si>
+    <t>'403829.023.523111.03212WA.2378EBA.A000000001.00000.2.0252.2.000000.000000.994.002.DC.000303</t>
+  </si>
+  <si>
+    <t>'00506T</t>
+  </si>
+  <si>
+    <t>'259991311215735</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Desember tahun 2025 untuk 35 Pegawai</t>
   </si>
 </sst>
 </file>
@@ -5415,7 +5547,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:L1670"/>
+  <dimension ref="A1:L1758"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -65095,19 +65227,19 @@
         <v>13</v>
       </c>
       <c r="D1573" t="s">
-        <v>1557</v>
+        <v>1561</v>
       </c>
       <c r="E1573" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="F1573" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="G1573" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="H1573" t="s">
-        <v>1544</v>
+        <v>18</v>
       </c>
       <c r="I1573" t="s">
         <v>19</v>
@@ -65116,10 +65248,10 @@
         <v>1</v>
       </c>
       <c r="K1573">
-        <v>112205200</v>
+        <v>140036700</v>
       </c>
       <c r="L1573">
-        <v>112205200</v>
+        <v>140036700</v>
       </c>
     </row>
     <row r="1574" spans="1:12">
@@ -65133,19 +65265,19 @@
         <v>13</v>
       </c>
       <c r="D1574" t="s">
-        <v>1557</v>
+        <v>1561</v>
       </c>
       <c r="E1574" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="F1574" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="G1574" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="H1574" t="s">
-        <v>1545</v>
+        <v>20</v>
       </c>
       <c r="I1574" t="s">
         <v>19</v>
@@ -65154,10 +65286,10 @@
         <v>1</v>
       </c>
       <c r="K1574">
-        <v>2086</v>
+        <v>1624</v>
       </c>
       <c r="L1574">
-        <v>2086</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="1575" spans="1:12">
@@ -65171,19 +65303,19 @@
         <v>13</v>
       </c>
       <c r="D1575" t="s">
-        <v>1557</v>
+        <v>1561</v>
       </c>
       <c r="E1575" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="F1575" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="G1575" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="H1575" t="s">
-        <v>1546</v>
+        <v>21</v>
       </c>
       <c r="I1575" t="s">
         <v>19</v>
@@ -65192,10 +65324,10 @@
         <v>1</v>
       </c>
       <c r="K1575">
-        <v>7571670</v>
+        <v>10518630</v>
       </c>
       <c r="L1575">
-        <v>7571670</v>
+        <v>10518630</v>
       </c>
     </row>
     <row r="1576" spans="1:12">
@@ -65209,19 +65341,19 @@
         <v>13</v>
       </c>
       <c r="D1576" t="s">
-        <v>1557</v>
+        <v>1561</v>
       </c>
       <c r="E1576" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="F1576" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="G1576" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="H1576" t="s">
-        <v>1547</v>
+        <v>22</v>
       </c>
       <c r="I1576" t="s">
         <v>19</v>
@@ -65230,10 +65362,10 @@
         <v>1</v>
       </c>
       <c r="K1576">
-        <v>2630444</v>
+        <v>2988192</v>
       </c>
       <c r="L1576">
-        <v>2630444</v>
+        <v>2988192</v>
       </c>
     </row>
     <row r="1577" spans="1:12">
@@ -65247,19 +65379,19 @@
         <v>13</v>
       </c>
       <c r="D1577" t="s">
-        <v>1557</v>
+        <v>1561</v>
       </c>
       <c r="E1577" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="F1577" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="G1577" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="H1577" t="s">
-        <v>1548</v>
+        <v>23</v>
       </c>
       <c r="I1577" t="s">
         <v>19</v>
@@ -65268,10 +65400,10 @@
         <v>1</v>
       </c>
       <c r="K1577">
-        <v>7676520</v>
+        <v>1260000</v>
       </c>
       <c r="L1577">
-        <v>7676520</v>
+        <v>1260000</v>
       </c>
     </row>
     <row r="1578" spans="1:12">
@@ -65285,19 +65417,19 @@
         <v>13</v>
       </c>
       <c r="D1578" t="s">
-        <v>1557</v>
+        <v>1561</v>
       </c>
       <c r="E1578" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="F1578" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="G1578" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="H1578" t="s">
-        <v>1549</v>
+        <v>24</v>
       </c>
       <c r="I1578" t="s">
         <v>19</v>
@@ -65306,10 +65438,10 @@
         <v>1</v>
       </c>
       <c r="K1578">
-        <v>6780000</v>
+        <v>8494000</v>
       </c>
       <c r="L1578">
-        <v>6780000</v>
+        <v>8494000</v>
       </c>
     </row>
     <row r="1579" spans="1:12">
@@ -65323,19 +65455,19 @@
         <v>13</v>
       </c>
       <c r="D1579" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1579" t="s">
+        <v>1562</v>
+      </c>
+      <c r="F1579" t="s">
+        <v>1563</v>
+      </c>
+      <c r="G1579" t="s">
         <v>1564</v>
       </c>
-      <c r="E1579" t="s">
-        <v>1565</v>
-      </c>
-      <c r="F1579" t="s">
-        <v>1566</v>
-      </c>
-      <c r="G1579" t="s">
-        <v>1567</v>
-      </c>
       <c r="H1579" t="s">
-        <v>209</v>
+        <v>25</v>
       </c>
       <c r="I1579" t="s">
         <v>19</v>
@@ -65344,10 +65476,10 @@
         <v>1</v>
       </c>
       <c r="K1579">
-        <v>9448320</v>
+        <v>289137</v>
       </c>
       <c r="L1579">
-        <v>9448320</v>
+        <v>289137</v>
       </c>
     </row>
     <row r="1580" spans="1:12">
@@ -65361,19 +65493,19 @@
         <v>13</v>
       </c>
       <c r="D1580" t="s">
-        <v>1557</v>
+        <v>1561</v>
       </c>
       <c r="E1580" t="s">
-        <v>1568</v>
+        <v>1562</v>
       </c>
       <c r="F1580" t="s">
-        <v>1569</v>
+        <v>1563</v>
       </c>
       <c r="G1580" t="s">
-        <v>1570</v>
+        <v>1564</v>
       </c>
       <c r="H1580" t="s">
-        <v>1571</v>
+        <v>26</v>
       </c>
       <c r="I1580" t="s">
         <v>19</v>
@@ -65382,10 +65514,10 @@
         <v>1</v>
       </c>
       <c r="K1580">
-        <v>5200000</v>
+        <v>7097160</v>
       </c>
       <c r="L1580">
-        <v>5200000</v>
+        <v>7097160</v>
       </c>
     </row>
     <row r="1581" spans="1:12">
@@ -65399,19 +65531,19 @@
         <v>13</v>
       </c>
       <c r="D1581" t="s">
-        <v>1557</v>
+        <v>1561</v>
       </c>
       <c r="E1581" t="s">
-        <v>1572</v>
+        <v>1562</v>
       </c>
       <c r="F1581" t="s">
-        <v>1573</v>
+        <v>1563</v>
       </c>
       <c r="G1581" t="s">
-        <v>1574</v>
+        <v>1564</v>
       </c>
       <c r="H1581" t="s">
-        <v>1571</v>
+        <v>27</v>
       </c>
       <c r="I1581" t="s">
         <v>19</v>
@@ -65420,10 +65552,10 @@
         <v>1</v>
       </c>
       <c r="K1581">
-        <v>18200000</v>
+        <v>3875000</v>
       </c>
       <c r="L1581">
-        <v>18200000</v>
+        <v>3875000</v>
       </c>
     </row>
     <row r="1582" spans="1:12">
@@ -65437,19 +65569,19 @@
         <v>13</v>
       </c>
       <c r="D1582" t="s">
-        <v>1557</v>
+        <v>1561</v>
       </c>
       <c r="E1582" t="s">
-        <v>1575</v>
+        <v>1565</v>
       </c>
       <c r="F1582" t="s">
-        <v>1576</v>
+        <v>1566</v>
       </c>
       <c r="G1582" t="s">
-        <v>1577</v>
+        <v>1567</v>
       </c>
       <c r="H1582" t="s">
-        <v>1544</v>
+        <v>31</v>
       </c>
       <c r="I1582" t="s">
         <v>19</v>
@@ -65458,10 +65590,10 @@
         <v>1</v>
       </c>
       <c r="K1582">
-        <v>6407200</v>
+        <v>511376300</v>
       </c>
       <c r="L1582">
-        <v>6407200</v>
+        <v>511376300</v>
       </c>
     </row>
     <row r="1583" spans="1:12">
@@ -65475,19 +65607,19 @@
         <v>13</v>
       </c>
       <c r="D1583" t="s">
-        <v>1557</v>
+        <v>1561</v>
       </c>
       <c r="E1583" t="s">
-        <v>1575</v>
+        <v>1565</v>
       </c>
       <c r="F1583" t="s">
-        <v>1576</v>
+        <v>1566</v>
       </c>
       <c r="G1583" t="s">
-        <v>1577</v>
+        <v>1567</v>
       </c>
       <c r="H1583" t="s">
-        <v>1545</v>
+        <v>32</v>
       </c>
       <c r="I1583" t="s">
         <v>19</v>
@@ -65496,10 +65628,10 @@
         <v>1</v>
       </c>
       <c r="K1583">
-        <v>76</v>
+        <v>6397</v>
       </c>
       <c r="L1583">
-        <v>76</v>
+        <v>6397</v>
       </c>
     </row>
     <row r="1584" spans="1:12">
@@ -65513,19 +65645,19 @@
         <v>13</v>
       </c>
       <c r="D1584" t="s">
-        <v>1557</v>
+        <v>1561</v>
       </c>
       <c r="E1584" t="s">
-        <v>1575</v>
+        <v>1565</v>
       </c>
       <c r="F1584" t="s">
-        <v>1576</v>
+        <v>1566</v>
       </c>
       <c r="G1584" t="s">
-        <v>1577</v>
+        <v>1567</v>
       </c>
       <c r="H1584" t="s">
-        <v>1548</v>
+        <v>33</v>
       </c>
       <c r="I1584" t="s">
         <v>19</v>
@@ -65534,10 +65666,10 @@
         <v>1</v>
       </c>
       <c r="K1584">
-        <v>144840</v>
+        <v>38898030</v>
       </c>
       <c r="L1584">
-        <v>144840</v>
+        <v>38898030</v>
       </c>
     </row>
     <row r="1585" spans="1:12">
@@ -65551,19 +65683,19 @@
         <v>13</v>
       </c>
       <c r="D1585" t="s">
-        <v>1557</v>
+        <v>1561</v>
       </c>
       <c r="E1585" t="s">
-        <v>1575</v>
+        <v>1565</v>
       </c>
       <c r="F1585" t="s">
-        <v>1576</v>
+        <v>1566</v>
       </c>
       <c r="G1585" t="s">
-        <v>1577</v>
+        <v>1567</v>
       </c>
       <c r="H1585" t="s">
-        <v>1549</v>
+        <v>34</v>
       </c>
       <c r="I1585" t="s">
         <v>19</v>
@@ -65572,10 +65704,10 @@
         <v>1</v>
       </c>
       <c r="K1585">
-        <v>370000</v>
+        <v>11928270</v>
       </c>
       <c r="L1585">
-        <v>370000</v>
+        <v>11928270</v>
       </c>
     </row>
     <row r="1586" spans="1:12">
@@ -65589,19 +65721,19 @@
         <v>13</v>
       </c>
       <c r="D1586" t="s">
-        <v>1578</v>
+        <v>1561</v>
       </c>
       <c r="E1586" t="s">
-        <v>1579</v>
+        <v>1565</v>
       </c>
       <c r="F1586" t="s">
-        <v>1580</v>
+        <v>1566</v>
       </c>
       <c r="G1586" t="s">
-        <v>1581</v>
+        <v>1567</v>
       </c>
       <c r="H1586" t="s">
-        <v>241</v>
+        <v>35</v>
       </c>
       <c r="I1586" t="s">
         <v>19</v>
@@ -65610,10 +65742,10 @@
         <v>1</v>
       </c>
       <c r="K1586">
-        <v>1610000</v>
+        <v>106380000</v>
       </c>
       <c r="L1586">
-        <v>1610000</v>
+        <v>106380000</v>
       </c>
     </row>
     <row r="1587" spans="1:12">
@@ -65627,19 +65759,19 @@
         <v>13</v>
       </c>
       <c r="D1587" t="s">
-        <v>1578</v>
+        <v>1561</v>
       </c>
       <c r="E1587" t="s">
-        <v>1579</v>
+        <v>1565</v>
       </c>
       <c r="F1587" t="s">
-        <v>1580</v>
+        <v>1566</v>
       </c>
       <c r="G1587" t="s">
-        <v>1581</v>
+        <v>1567</v>
       </c>
       <c r="H1587" t="s">
-        <v>149</v>
+        <v>36</v>
       </c>
       <c r="I1587" t="s">
         <v>19</v>
@@ -65648,10 +65780,10 @@
         <v>1</v>
       </c>
       <c r="K1587">
-        <v>24531000</v>
+        <v>750493</v>
       </c>
       <c r="L1587">
-        <v>24531000</v>
+        <v>750493</v>
       </c>
     </row>
     <row r="1588" spans="1:12">
@@ -65665,19 +65797,19 @@
         <v>13</v>
       </c>
       <c r="D1588" t="s">
-        <v>1578</v>
+        <v>1561</v>
       </c>
       <c r="E1588" t="s">
-        <v>1579</v>
+        <v>1565</v>
       </c>
       <c r="F1588" t="s">
-        <v>1580</v>
+        <v>1566</v>
       </c>
       <c r="G1588" t="s">
-        <v>1581</v>
+        <v>1567</v>
       </c>
       <c r="H1588" t="s">
-        <v>242</v>
+        <v>37</v>
       </c>
       <c r="I1588" t="s">
         <v>19</v>
@@ -65686,10 +65818,10 @@
         <v>1</v>
       </c>
       <c r="K1588">
-        <v>1476000</v>
+        <v>27302340</v>
       </c>
       <c r="L1588">
-        <v>1476000</v>
+        <v>27302340</v>
       </c>
     </row>
     <row r="1589" spans="1:12">
@@ -65703,19 +65835,19 @@
         <v>13</v>
       </c>
       <c r="D1589" t="s">
-        <v>1578</v>
+        <v>1561</v>
       </c>
       <c r="E1589" t="s">
-        <v>1582</v>
+        <v>1565</v>
       </c>
       <c r="F1589" t="s">
-        <v>1583</v>
+        <v>1566</v>
       </c>
       <c r="G1589" t="s">
-        <v>1584</v>
+        <v>1567</v>
       </c>
       <c r="H1589" t="s">
-        <v>149</v>
+        <v>38</v>
       </c>
       <c r="I1589" t="s">
         <v>19</v>
@@ -65724,10 +65856,10 @@
         <v>1</v>
       </c>
       <c r="K1589">
-        <v>2368000</v>
+        <v>185000</v>
       </c>
       <c r="L1589">
-        <v>2368000</v>
+        <v>185000</v>
       </c>
     </row>
     <row r="1590" spans="1:12">
@@ -65741,19 +65873,19 @@
         <v>13</v>
       </c>
       <c r="D1590" t="s">
-        <v>1578</v>
+        <v>1561</v>
       </c>
       <c r="E1590" t="s">
-        <v>1582</v>
+        <v>1568</v>
       </c>
       <c r="F1590" t="s">
-        <v>1583</v>
+        <v>1569</v>
       </c>
       <c r="G1590" t="s">
-        <v>1584</v>
+        <v>1570</v>
       </c>
       <c r="H1590" t="s">
-        <v>242</v>
+        <v>31</v>
       </c>
       <c r="I1590" t="s">
         <v>19</v>
@@ -65762,10 +65894,10 @@
         <v>1</v>
       </c>
       <c r="K1590">
-        <v>1763000</v>
+        <v>643419000</v>
       </c>
       <c r="L1590">
-        <v>1763000</v>
+        <v>643419000</v>
       </c>
     </row>
     <row r="1591" spans="1:12">
@@ -65779,19 +65911,19 @@
         <v>13</v>
       </c>
       <c r="D1591" t="s">
-        <v>1578</v>
+        <v>1561</v>
       </c>
       <c r="E1591" t="s">
-        <v>1585</v>
+        <v>1568</v>
       </c>
       <c r="F1591" t="s">
-        <v>1586</v>
+        <v>1569</v>
       </c>
       <c r="G1591" t="s">
-        <v>1587</v>
+        <v>1570</v>
       </c>
       <c r="H1591" t="s">
-        <v>266</v>
+        <v>32</v>
       </c>
       <c r="I1591" t="s">
         <v>19</v>
@@ -65800,10 +65932,10 @@
         <v>1</v>
       </c>
       <c r="K1591">
-        <v>11970000</v>
+        <v>8606</v>
       </c>
       <c r="L1591">
-        <v>11970000</v>
+        <v>8606</v>
       </c>
     </row>
     <row r="1592" spans="1:12">
@@ -65817,19 +65949,19 @@
         <v>13</v>
       </c>
       <c r="D1592" t="s">
-        <v>1578</v>
+        <v>1561</v>
       </c>
       <c r="E1592" t="s">
-        <v>1585</v>
+        <v>1568</v>
       </c>
       <c r="F1592" t="s">
-        <v>1586</v>
+        <v>1569</v>
       </c>
       <c r="G1592" t="s">
-        <v>1587</v>
+        <v>1570</v>
       </c>
       <c r="H1592" t="s">
-        <v>267</v>
+        <v>33</v>
       </c>
       <c r="I1592" t="s">
         <v>19</v>
@@ -65838,10 +65970,10 @@
         <v>1</v>
       </c>
       <c r="K1592">
-        <v>73741000</v>
+        <v>52166360</v>
       </c>
       <c r="L1592">
-        <v>73741000</v>
+        <v>52166360</v>
       </c>
     </row>
     <row r="1593" spans="1:12">
@@ -65855,19 +65987,19 @@
         <v>13</v>
       </c>
       <c r="D1593" t="s">
-        <v>1578</v>
+        <v>1561</v>
       </c>
       <c r="E1593" t="s">
-        <v>1585</v>
+        <v>1568</v>
       </c>
       <c r="F1593" t="s">
-        <v>1586</v>
+        <v>1569</v>
       </c>
       <c r="G1593" t="s">
-        <v>1587</v>
+        <v>1570</v>
       </c>
       <c r="H1593" t="s">
-        <v>268</v>
+        <v>34</v>
       </c>
       <c r="I1593" t="s">
         <v>19</v>
@@ -65876,10 +66008,10 @@
         <v>1</v>
       </c>
       <c r="K1593">
-        <v>23903000</v>
+        <v>17357858</v>
       </c>
       <c r="L1593">
-        <v>23903000</v>
+        <v>17357858</v>
       </c>
     </row>
     <row r="1594" spans="1:12">
@@ -65893,19 +66025,19 @@
         <v>13</v>
       </c>
       <c r="D1594" t="s">
-        <v>1578</v>
+        <v>1561</v>
       </c>
       <c r="E1594" t="s">
-        <v>1588</v>
+        <v>1568</v>
       </c>
       <c r="F1594" t="s">
-        <v>1589</v>
+        <v>1569</v>
       </c>
       <c r="G1594" t="s">
-        <v>1590</v>
+        <v>1570</v>
       </c>
       <c r="H1594" t="s">
-        <v>266</v>
+        <v>35</v>
       </c>
       <c r="I1594" t="s">
         <v>19</v>
@@ -65914,10 +66046,10 @@
         <v>1</v>
       </c>
       <c r="K1594">
-        <v>12040000</v>
+        <v>141300000</v>
       </c>
       <c r="L1594">
-        <v>12040000</v>
+        <v>141300000</v>
       </c>
     </row>
     <row r="1595" spans="1:12">
@@ -65931,19 +66063,19 @@
         <v>13</v>
       </c>
       <c r="D1595" t="s">
-        <v>1578</v>
+        <v>1561</v>
       </c>
       <c r="E1595" t="s">
-        <v>1588</v>
+        <v>1568</v>
       </c>
       <c r="F1595" t="s">
-        <v>1589</v>
+        <v>1569</v>
       </c>
       <c r="G1595" t="s">
-        <v>1590</v>
+        <v>1570</v>
       </c>
       <c r="H1595" t="s">
-        <v>267</v>
+        <v>36</v>
       </c>
       <c r="I1595" t="s">
         <v>19</v>
@@ -65952,10 +66084,10 @@
         <v>1</v>
       </c>
       <c r="K1595">
-        <v>109446000</v>
+        <v>1279160</v>
       </c>
       <c r="L1595">
-        <v>109446000</v>
+        <v>1279160</v>
       </c>
     </row>
     <row r="1596" spans="1:12">
@@ -65969,19 +66101,19 @@
         <v>13</v>
       </c>
       <c r="D1596" t="s">
-        <v>1578</v>
+        <v>1561</v>
       </c>
       <c r="E1596" t="s">
-        <v>1588</v>
+        <v>1568</v>
       </c>
       <c r="F1596" t="s">
-        <v>1589</v>
+        <v>1569</v>
       </c>
       <c r="G1596" t="s">
-        <v>1590</v>
+        <v>1570</v>
       </c>
       <c r="H1596" t="s">
-        <v>268</v>
+        <v>37</v>
       </c>
       <c r="I1596" t="s">
         <v>19</v>
@@ -65990,10 +66122,10 @@
         <v>1</v>
       </c>
       <c r="K1596">
-        <v>21689000</v>
+        <v>37803240</v>
       </c>
       <c r="L1596">
-        <v>21689000</v>
+        <v>37803240</v>
       </c>
     </row>
     <row r="1597" spans="1:12">
@@ -66007,19 +66139,19 @@
         <v>13</v>
       </c>
       <c r="D1597" t="s">
-        <v>1591</v>
+        <v>1561</v>
       </c>
       <c r="E1597" t="s">
-        <v>1592</v>
+        <v>1571</v>
       </c>
       <c r="F1597" t="s">
-        <v>1593</v>
+        <v>1572</v>
       </c>
       <c r="G1597" t="s">
-        <v>1594</v>
+        <v>1573</v>
       </c>
       <c r="H1597" t="s">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="I1597" t="s">
         <v>19</v>
@@ -66028,10 +66160,10 @@
         <v>1</v>
       </c>
       <c r="K1597">
-        <v>691300</v>
+        <v>21194100</v>
       </c>
       <c r="L1597">
-        <v>691300</v>
+        <v>21194100</v>
       </c>
     </row>
     <row r="1598" spans="1:12">
@@ -66045,19 +66177,19 @@
         <v>13</v>
       </c>
       <c r="D1598" t="s">
-        <v>1595</v>
+        <v>1561</v>
       </c>
       <c r="E1598" t="s">
-        <v>1596</v>
+        <v>1571</v>
       </c>
       <c r="F1598" t="s">
-        <v>1597</v>
+        <v>1572</v>
       </c>
       <c r="G1598" t="s">
-        <v>1598</v>
+        <v>1573</v>
       </c>
       <c r="H1598" t="s">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="I1598" t="s">
         <v>19</v>
@@ -66066,10 +66198,10 @@
         <v>1</v>
       </c>
       <c r="K1598">
-        <v>266012</v>
+        <v>179</v>
       </c>
       <c r="L1598">
-        <v>266012</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1599" spans="1:12">
@@ -66083,19 +66215,19 @@
         <v>13</v>
       </c>
       <c r="D1599" t="s">
-        <v>1595</v>
+        <v>1561</v>
       </c>
       <c r="E1599" t="s">
-        <v>1596</v>
+        <v>1571</v>
       </c>
       <c r="F1599" t="s">
-        <v>1597</v>
+        <v>1572</v>
       </c>
       <c r="G1599" t="s">
-        <v>1598</v>
+        <v>1573</v>
       </c>
       <c r="H1599" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="I1599" t="s">
         <v>19</v>
@@ -66104,10 +66236,10 @@
         <v>1</v>
       </c>
       <c r="K1599">
-        <v>2580750</v>
+        <v>1656980</v>
       </c>
       <c r="L1599">
-        <v>2580750</v>
+        <v>1656980</v>
       </c>
     </row>
     <row r="1600" spans="1:12">
@@ -66121,19 +66253,19 @@
         <v>13</v>
       </c>
       <c r="D1600" t="s">
-        <v>1595</v>
+        <v>1561</v>
       </c>
       <c r="E1600" t="s">
-        <v>1599</v>
+        <v>1571</v>
       </c>
       <c r="F1600" t="s">
-        <v>1600</v>
+        <v>1572</v>
       </c>
       <c r="G1600" t="s">
-        <v>1601</v>
+        <v>1573</v>
       </c>
       <c r="H1600" t="s">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="I1600" t="s">
         <v>19</v>
@@ -66142,10 +66274,10 @@
         <v>1</v>
       </c>
       <c r="K1600">
-        <v>40247519</v>
+        <v>662792</v>
       </c>
       <c r="L1600">
-        <v>40247519</v>
+        <v>662792</v>
       </c>
     </row>
     <row r="1601" spans="1:12">
@@ -66159,19 +66291,19 @@
         <v>13</v>
       </c>
       <c r="D1601" t="s">
-        <v>1591</v>
+        <v>1561</v>
       </c>
       <c r="E1601" t="s">
-        <v>1602</v>
+        <v>1571</v>
       </c>
       <c r="F1601" t="s">
-        <v>1603</v>
+        <v>1572</v>
       </c>
       <c r="G1601" t="s">
-        <v>1604</v>
+        <v>1573</v>
       </c>
       <c r="H1601" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="I1601" t="s">
         <v>19</v>
@@ -66180,10 +66312,10 @@
         <v>1</v>
       </c>
       <c r="K1601">
-        <v>1053940800</v>
+        <v>540000</v>
       </c>
       <c r="L1601">
-        <v>1053940800</v>
+        <v>540000</v>
       </c>
     </row>
     <row r="1602" spans="1:12">
@@ -66197,19 +66329,19 @@
         <v>13</v>
       </c>
       <c r="D1602" t="s">
-        <v>1591</v>
+        <v>1561</v>
       </c>
       <c r="E1602" t="s">
-        <v>1602</v>
+        <v>1571</v>
       </c>
       <c r="F1602" t="s">
-        <v>1603</v>
+        <v>1572</v>
       </c>
       <c r="G1602" t="s">
-        <v>1604</v>
+        <v>1573</v>
       </c>
       <c r="H1602" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="I1602" t="s">
         <v>19</v>
@@ -66218,10 +66350,10 @@
         <v>1</v>
       </c>
       <c r="K1602">
-        <v>5888</v>
+        <v>1900000</v>
       </c>
       <c r="L1602">
-        <v>5888</v>
+        <v>1900000</v>
       </c>
     </row>
     <row r="1603" spans="1:12">
@@ -66235,19 +66367,19 @@
         <v>13</v>
       </c>
       <c r="D1603" t="s">
-        <v>1591</v>
+        <v>1561</v>
       </c>
       <c r="E1603" t="s">
-        <v>1602</v>
+        <v>1571</v>
       </c>
       <c r="F1603" t="s">
-        <v>1603</v>
+        <v>1572</v>
       </c>
       <c r="G1603" t="s">
-        <v>1604</v>
+        <v>1573</v>
       </c>
       <c r="H1603" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I1603" t="s">
         <v>19</v>
@@ -66256,10 +66388,10 @@
         <v>1</v>
       </c>
       <c r="K1603">
-        <v>70065440</v>
+        <v>18269</v>
       </c>
       <c r="L1603">
-        <v>70065440</v>
+        <v>18269</v>
       </c>
     </row>
     <row r="1604" spans="1:12">
@@ -66273,19 +66405,19 @@
         <v>13</v>
       </c>
       <c r="D1604" t="s">
-        <v>1591</v>
+        <v>1561</v>
       </c>
       <c r="E1604" t="s">
-        <v>1602</v>
+        <v>1571</v>
       </c>
       <c r="F1604" t="s">
-        <v>1603</v>
+        <v>1572</v>
       </c>
       <c r="G1604" t="s">
-        <v>1604</v>
+        <v>1573</v>
       </c>
       <c r="H1604" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="I1604" t="s">
         <v>19</v>
@@ -66294,10 +66426,10 @@
         <v>1</v>
       </c>
       <c r="K1604">
-        <v>20735760</v>
+        <v>1231140</v>
       </c>
       <c r="L1604">
-        <v>20735760</v>
+        <v>1231140</v>
       </c>
     </row>
     <row r="1605" spans="1:12">
@@ -66311,19 +66443,19 @@
         <v>13</v>
       </c>
       <c r="D1605" t="s">
-        <v>1591</v>
+        <v>1561</v>
       </c>
       <c r="E1605" t="s">
-        <v>1602</v>
+        <v>1571</v>
       </c>
       <c r="F1605" t="s">
-        <v>1603</v>
+        <v>1572</v>
       </c>
       <c r="G1605" t="s">
-        <v>1604</v>
+        <v>1573</v>
       </c>
       <c r="H1605" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="I1605" t="s">
         <v>19</v>
@@ -66332,10 +66464,10 @@
         <v>1</v>
       </c>
       <c r="K1605">
-        <v>174240000</v>
+        <v>375000</v>
       </c>
       <c r="L1605">
-        <v>174240000</v>
+        <v>375000</v>
       </c>
     </row>
     <row r="1606" spans="1:12">
@@ -66349,19 +66481,19 @@
         <v>13</v>
       </c>
       <c r="D1606" t="s">
-        <v>1591</v>
+        <v>1557</v>
       </c>
       <c r="E1606" t="s">
-        <v>1602</v>
+        <v>1574</v>
       </c>
       <c r="F1606" t="s">
-        <v>1603</v>
+        <v>1575</v>
       </c>
       <c r="G1606" t="s">
-        <v>1604</v>
+        <v>1576</v>
       </c>
       <c r="H1606" t="s">
-        <v>53</v>
+        <v>1544</v>
       </c>
       <c r="I1606" t="s">
         <v>19</v>
@@ -66370,10 +66502,10 @@
         <v>1</v>
       </c>
       <c r="K1606">
-        <v>63584760</v>
+        <v>112205200</v>
       </c>
       <c r="L1606">
-        <v>63584760</v>
+        <v>112205200</v>
       </c>
     </row>
     <row r="1607" spans="1:12">
@@ -66387,19 +66519,19 @@
         <v>13</v>
       </c>
       <c r="D1607" t="s">
-        <v>1605</v>
+        <v>1557</v>
       </c>
       <c r="E1607" t="s">
-        <v>1606</v>
+        <v>1574</v>
       </c>
       <c r="F1607" t="s">
-        <v>1607</v>
+        <v>1575</v>
       </c>
       <c r="G1607" t="s">
-        <v>1608</v>
+        <v>1576</v>
       </c>
       <c r="H1607" t="s">
-        <v>84</v>
+        <v>1545</v>
       </c>
       <c r="I1607" t="s">
         <v>19</v>
@@ -66408,10 +66540,10 @@
         <v>1</v>
       </c>
       <c r="K1607">
-        <v>6670000</v>
+        <v>2086</v>
       </c>
       <c r="L1607">
-        <v>6670000</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="1608" spans="1:12">
@@ -66425,19 +66557,19 @@
         <v>13</v>
       </c>
       <c r="D1608" t="s">
-        <v>1609</v>
+        <v>1557</v>
       </c>
       <c r="E1608" t="s">
-        <v>1610</v>
+        <v>1574</v>
       </c>
       <c r="F1608" t="s">
-        <v>1611</v>
+        <v>1575</v>
       </c>
       <c r="G1608" t="s">
-        <v>1612</v>
+        <v>1576</v>
       </c>
       <c r="H1608" t="s">
-        <v>797</v>
+        <v>1546</v>
       </c>
       <c r="I1608" t="s">
         <v>19</v>
@@ -66446,10 +66578,10 @@
         <v>1</v>
       </c>
       <c r="K1608">
-        <v>1500000</v>
+        <v>7571670</v>
       </c>
       <c r="L1608">
-        <v>1500000</v>
+        <v>7571670</v>
       </c>
     </row>
     <row r="1609" spans="1:12">
@@ -66463,19 +66595,19 @@
         <v>13</v>
       </c>
       <c r="D1609" t="s">
-        <v>1609</v>
+        <v>1557</v>
       </c>
       <c r="E1609" t="s">
-        <v>1613</v>
+        <v>1574</v>
       </c>
       <c r="F1609" t="s">
-        <v>1614</v>
+        <v>1575</v>
       </c>
       <c r="G1609" t="s">
-        <v>1615</v>
+        <v>1576</v>
       </c>
       <c r="H1609" t="s">
-        <v>797</v>
+        <v>1547</v>
       </c>
       <c r="I1609" t="s">
         <v>19</v>
@@ -66484,10 +66616,10 @@
         <v>1</v>
       </c>
       <c r="K1609">
-        <v>300000</v>
+        <v>2630444</v>
       </c>
       <c r="L1609">
-        <v>300000</v>
+        <v>2630444</v>
       </c>
     </row>
     <row r="1610" spans="1:12">
@@ -66501,19 +66633,19 @@
         <v>13</v>
       </c>
       <c r="D1610" t="s">
-        <v>1605</v>
+        <v>1557</v>
       </c>
       <c r="E1610" t="s">
-        <v>1616</v>
+        <v>1574</v>
       </c>
       <c r="F1610" t="s">
-        <v>1617</v>
+        <v>1575</v>
       </c>
       <c r="G1610" t="s">
-        <v>1618</v>
+        <v>1576</v>
       </c>
       <c r="H1610" t="s">
-        <v>48</v>
+        <v>1548</v>
       </c>
       <c r="I1610" t="s">
         <v>19</v>
@@ -66522,10 +66654,10 @@
         <v>1</v>
       </c>
       <c r="K1610">
-        <v>6407200</v>
+        <v>7676520</v>
       </c>
       <c r="L1610">
-        <v>6407200</v>
+        <v>7676520</v>
       </c>
     </row>
     <row r="1611" spans="1:12">
@@ -66539,19 +66671,19 @@
         <v>13</v>
       </c>
       <c r="D1611" t="s">
-        <v>1605</v>
+        <v>1557</v>
       </c>
       <c r="E1611" t="s">
-        <v>1616</v>
+        <v>1574</v>
       </c>
       <c r="F1611" t="s">
-        <v>1617</v>
+        <v>1575</v>
       </c>
       <c r="G1611" t="s">
-        <v>1618</v>
+        <v>1576</v>
       </c>
       <c r="H1611" t="s">
-        <v>49</v>
+        <v>1549</v>
       </c>
       <c r="I1611" t="s">
         <v>19</v>
@@ -66560,10 +66692,10 @@
         <v>1</v>
       </c>
       <c r="K1611">
-        <v>32</v>
+        <v>6780000</v>
       </c>
       <c r="L1611">
-        <v>32</v>
+        <v>6780000</v>
       </c>
     </row>
     <row r="1612" spans="1:12">
@@ -66577,19 +66709,19 @@
         <v>13</v>
       </c>
       <c r="D1612" t="s">
-        <v>1605</v>
+        <v>1577</v>
       </c>
       <c r="E1612" t="s">
-        <v>1616</v>
+        <v>1578</v>
       </c>
       <c r="F1612" t="s">
-        <v>1617</v>
+        <v>1579</v>
       </c>
       <c r="G1612" t="s">
-        <v>1618</v>
+        <v>1580</v>
       </c>
       <c r="H1612" t="s">
-        <v>52</v>
+        <v>209</v>
       </c>
       <c r="I1612" t="s">
         <v>19</v>
@@ -66598,10 +66730,10 @@
         <v>1</v>
       </c>
       <c r="K1612">
-        <v>1080000</v>
+        <v>9448320</v>
       </c>
       <c r="L1612">
-        <v>1080000</v>
+        <v>9448320</v>
       </c>
     </row>
     <row r="1613" spans="1:12">
@@ -66615,19 +66747,19 @@
         <v>13</v>
       </c>
       <c r="D1613" t="s">
-        <v>1605</v>
+        <v>1557</v>
       </c>
       <c r="E1613" t="s">
-        <v>1616</v>
+        <v>1581</v>
       </c>
       <c r="F1613" t="s">
-        <v>1617</v>
+        <v>1582</v>
       </c>
       <c r="G1613" t="s">
-        <v>1618</v>
+        <v>1583</v>
       </c>
       <c r="H1613" t="s">
-        <v>53</v>
+        <v>1584</v>
       </c>
       <c r="I1613" t="s">
         <v>19</v>
@@ -66636,10 +66768,10 @@
         <v>1</v>
       </c>
       <c r="K1613">
-        <v>144840</v>
+        <v>5200000</v>
       </c>
       <c r="L1613">
-        <v>144840</v>
+        <v>5200000</v>
       </c>
     </row>
     <row r="1614" spans="1:12">
@@ -66653,19 +66785,19 @@
         <v>13</v>
       </c>
       <c r="D1614" t="s">
-        <v>1609</v>
+        <v>1557</v>
       </c>
       <c r="E1614" t="s">
-        <v>1619</v>
+        <v>1585</v>
       </c>
       <c r="F1614" t="s">
-        <v>1620</v>
+        <v>1586</v>
       </c>
       <c r="G1614" t="s">
-        <v>1621</v>
+        <v>1587</v>
       </c>
       <c r="H1614" t="s">
-        <v>31</v>
+        <v>1584</v>
       </c>
       <c r="I1614" t="s">
         <v>19</v>
@@ -66674,10 +66806,10 @@
         <v>1</v>
       </c>
       <c r="K1614">
-        <v>486200</v>
+        <v>18200000</v>
       </c>
       <c r="L1614">
-        <v>486200</v>
+        <v>18200000</v>
       </c>
     </row>
     <row r="1615" spans="1:12">
@@ -66691,19 +66823,19 @@
         <v>13</v>
       </c>
       <c r="D1615" t="s">
-        <v>1609</v>
+        <v>1557</v>
       </c>
       <c r="E1615" t="s">
-        <v>1619</v>
+        <v>1588</v>
       </c>
       <c r="F1615" t="s">
-        <v>1620</v>
+        <v>1589</v>
       </c>
       <c r="G1615" t="s">
-        <v>1621</v>
+        <v>1590</v>
       </c>
       <c r="H1615" t="s">
-        <v>32</v>
+        <v>1544</v>
       </c>
       <c r="I1615" t="s">
         <v>19</v>
@@ -66712,10 +66844,10 @@
         <v>1</v>
       </c>
       <c r="K1615">
-        <v>66</v>
+        <v>6407200</v>
       </c>
       <c r="L1615">
-        <v>66</v>
+        <v>6407200</v>
       </c>
     </row>
     <row r="1616" spans="1:12">
@@ -66729,19 +66861,19 @@
         <v>13</v>
       </c>
       <c r="D1616" t="s">
-        <v>1609</v>
+        <v>1557</v>
       </c>
       <c r="E1616" t="s">
-        <v>1619</v>
+        <v>1588</v>
       </c>
       <c r="F1616" t="s">
-        <v>1620</v>
+        <v>1589</v>
       </c>
       <c r="G1616" t="s">
-        <v>1621</v>
+        <v>1590</v>
       </c>
       <c r="H1616" t="s">
-        <v>33</v>
+        <v>1545</v>
       </c>
       <c r="I1616" t="s">
         <v>19</v>
@@ -66750,10 +66882,10 @@
         <v>1</v>
       </c>
       <c r="K1616">
-        <v>48620</v>
+        <v>76</v>
       </c>
       <c r="L1616">
-        <v>48620</v>
+        <v>76</v>
       </c>
     </row>
     <row r="1617" spans="1:12">
@@ -66767,19 +66899,19 @@
         <v>13</v>
       </c>
       <c r="D1617" t="s">
-        <v>1609</v>
+        <v>1557</v>
       </c>
       <c r="E1617" t="s">
-        <v>1619</v>
+        <v>1588</v>
       </c>
       <c r="F1617" t="s">
-        <v>1620</v>
+        <v>1589</v>
       </c>
       <c r="G1617" t="s">
-        <v>1621</v>
+        <v>1590</v>
       </c>
       <c r="H1617" t="s">
-        <v>36</v>
+        <v>1548</v>
       </c>
       <c r="I1617" t="s">
         <v>19</v>
@@ -66788,10 +66920,10 @@
         <v>1</v>
       </c>
       <c r="K1617">
-        <v>4094</v>
+        <v>144840</v>
       </c>
       <c r="L1617">
-        <v>4094</v>
+        <v>144840</v>
       </c>
     </row>
     <row r="1618" spans="1:12">
@@ -66805,19 +66937,19 @@
         <v>13</v>
       </c>
       <c r="D1618" t="s">
-        <v>1609</v>
+        <v>1557</v>
       </c>
       <c r="E1618" t="s">
-        <v>1622</v>
+        <v>1588</v>
       </c>
       <c r="F1618" t="s">
-        <v>1623</v>
+        <v>1589</v>
       </c>
       <c r="G1618" t="s">
-        <v>1624</v>
+        <v>1590</v>
       </c>
       <c r="H1618" t="s">
-        <v>31</v>
+        <v>1549</v>
       </c>
       <c r="I1618" t="s">
         <v>19</v>
@@ -66826,10 +66958,10 @@
         <v>1</v>
       </c>
       <c r="K1618">
-        <v>724600</v>
+        <v>370000</v>
       </c>
       <c r="L1618">
-        <v>724600</v>
+        <v>370000</v>
       </c>
     </row>
     <row r="1619" spans="1:12">
@@ -66843,19 +66975,19 @@
         <v>13</v>
       </c>
       <c r="D1619" t="s">
-        <v>1609</v>
+        <v>1591</v>
       </c>
       <c r="E1619" t="s">
-        <v>1622</v>
+        <v>1592</v>
       </c>
       <c r="F1619" t="s">
-        <v>1623</v>
+        <v>1593</v>
       </c>
       <c r="G1619" t="s">
-        <v>1624</v>
+        <v>1594</v>
       </c>
       <c r="H1619" t="s">
-        <v>32</v>
+        <v>241</v>
       </c>
       <c r="I1619" t="s">
         <v>19</v>
@@ -66864,10 +66996,10 @@
         <v>1</v>
       </c>
       <c r="K1619">
-        <v>58</v>
+        <v>1610000</v>
       </c>
       <c r="L1619">
-        <v>58</v>
+        <v>1610000</v>
       </c>
     </row>
     <row r="1620" spans="1:12">
@@ -66881,19 +67013,19 @@
         <v>13</v>
       </c>
       <c r="D1620" t="s">
-        <v>1609</v>
+        <v>1591</v>
       </c>
       <c r="E1620" t="s">
-        <v>1622</v>
+        <v>1592</v>
       </c>
       <c r="F1620" t="s">
-        <v>1623</v>
+        <v>1593</v>
       </c>
       <c r="G1620" t="s">
-        <v>1624</v>
+        <v>1594</v>
       </c>
       <c r="H1620" t="s">
-        <v>33</v>
+        <v>149</v>
       </c>
       <c r="I1620" t="s">
         <v>19</v>
@@ -66902,10 +67034,10 @@
         <v>1</v>
       </c>
       <c r="K1620">
-        <v>47650</v>
+        <v>24531000</v>
       </c>
       <c r="L1620">
-        <v>47650</v>
+        <v>24531000</v>
       </c>
     </row>
     <row r="1621" spans="1:12">
@@ -66919,19 +67051,19 @@
         <v>13</v>
       </c>
       <c r="D1621" t="s">
-        <v>1609</v>
+        <v>1591</v>
       </c>
       <c r="E1621" t="s">
-        <v>1622</v>
+        <v>1592</v>
       </c>
       <c r="F1621" t="s">
-        <v>1623</v>
+        <v>1593</v>
       </c>
       <c r="G1621" t="s">
-        <v>1624</v>
+        <v>1594</v>
       </c>
       <c r="H1621" t="s">
-        <v>34</v>
+        <v>242</v>
       </c>
       <c r="I1621" t="s">
         <v>19</v>
@@ -66940,10 +67072,10 @@
         <v>1</v>
       </c>
       <c r="K1621">
-        <v>9530</v>
+        <v>1476000</v>
       </c>
       <c r="L1621">
-        <v>9530</v>
+        <v>1476000</v>
       </c>
     </row>
     <row r="1622" spans="1:12">
@@ -66957,19 +67089,19 @@
         <v>13</v>
       </c>
       <c r="D1622" t="s">
-        <v>1609</v>
+        <v>1591</v>
       </c>
       <c r="E1622" t="s">
-        <v>1622</v>
+        <v>1595</v>
       </c>
       <c r="F1622" t="s">
-        <v>1623</v>
+        <v>1596</v>
       </c>
       <c r="G1622" t="s">
-        <v>1624</v>
+        <v>1597</v>
       </c>
       <c r="H1622" t="s">
-        <v>36</v>
+        <v>149</v>
       </c>
       <c r="I1622" t="s">
         <v>19</v>
@@ -66978,10 +67110,10 @@
         <v>1</v>
       </c>
       <c r="K1622">
-        <v>5880</v>
+        <v>2368000</v>
       </c>
       <c r="L1622">
-        <v>5880</v>
+        <v>2368000</v>
       </c>
     </row>
     <row r="1623" spans="1:12">
@@ -66995,19 +67127,19 @@
         <v>13</v>
       </c>
       <c r="D1623" t="s">
-        <v>1609</v>
+        <v>1591</v>
       </c>
       <c r="E1623" t="s">
-        <v>1625</v>
+        <v>1595</v>
       </c>
       <c r="F1623" t="s">
-        <v>1626</v>
+        <v>1596</v>
       </c>
       <c r="G1623" t="s">
-        <v>1627</v>
+        <v>1597</v>
       </c>
       <c r="H1623" t="s">
-        <v>272</v>
+        <v>242</v>
       </c>
       <c r="I1623" t="s">
         <v>19</v>
@@ -67016,10 +67148,10 @@
         <v>1</v>
       </c>
       <c r="K1623">
-        <v>841674471</v>
+        <v>1763000</v>
       </c>
       <c r="L1623">
-        <v>841674471</v>
+        <v>1763000</v>
       </c>
     </row>
     <row r="1624" spans="1:12">
@@ -67033,19 +67165,19 @@
         <v>13</v>
       </c>
       <c r="D1624" t="s">
-        <v>1609</v>
+        <v>1591</v>
       </c>
       <c r="E1624" t="s">
-        <v>1628</v>
+        <v>1598</v>
       </c>
       <c r="F1624" t="s">
-        <v>1629</v>
+        <v>1599</v>
       </c>
       <c r="G1624" t="s">
-        <v>1630</v>
+        <v>1600</v>
       </c>
       <c r="H1624" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="I1624" t="s">
         <v>19</v>
@@ -67054,10 +67186,10 @@
         <v>1</v>
       </c>
       <c r="K1624">
-        <v>1050297970</v>
+        <v>11970000</v>
       </c>
       <c r="L1624">
-        <v>1050297970</v>
+        <v>11970000</v>
       </c>
     </row>
     <row r="1625" spans="1:12">
@@ -67071,19 +67203,19 @@
         <v>13</v>
       </c>
       <c r="D1625" t="s">
-        <v>1631</v>
+        <v>1591</v>
       </c>
       <c r="E1625" t="s">
-        <v>1632</v>
+        <v>1598</v>
       </c>
       <c r="F1625" t="s">
-        <v>1633</v>
+        <v>1599</v>
       </c>
       <c r="G1625" t="s">
-        <v>1634</v>
+        <v>1600</v>
       </c>
       <c r="H1625" t="s">
-        <v>48</v>
+        <v>267</v>
       </c>
       <c r="I1625" t="s">
         <v>19</v>
@@ -67092,10 +67224,10 @@
         <v>1</v>
       </c>
       <c r="K1625">
-        <v>107755200</v>
+        <v>73741000</v>
       </c>
       <c r="L1625">
-        <v>107755200</v>
+        <v>73741000</v>
       </c>
     </row>
     <row r="1626" spans="1:12">
@@ -67109,19 +67241,19 @@
         <v>13</v>
       </c>
       <c r="D1626" t="s">
-        <v>1631</v>
+        <v>1591</v>
       </c>
       <c r="E1626" t="s">
-        <v>1632</v>
+        <v>1598</v>
       </c>
       <c r="F1626" t="s">
-        <v>1633</v>
+        <v>1599</v>
       </c>
       <c r="G1626" t="s">
-        <v>1634</v>
+        <v>1600</v>
       </c>
       <c r="H1626" t="s">
-        <v>49</v>
+        <v>268</v>
       </c>
       <c r="I1626" t="s">
         <v>19</v>
@@ -67130,10 +67262,10 @@
         <v>1</v>
       </c>
       <c r="K1626">
-        <v>33406</v>
+        <v>23903000</v>
       </c>
       <c r="L1626">
-        <v>33406</v>
+        <v>23903000</v>
       </c>
     </row>
     <row r="1627" spans="1:12">
@@ -67147,19 +67279,19 @@
         <v>13</v>
       </c>
       <c r="D1627" t="s">
-        <v>1631</v>
+        <v>1591</v>
       </c>
       <c r="E1627" t="s">
-        <v>1632</v>
+        <v>1601</v>
       </c>
       <c r="F1627" t="s">
-        <v>1633</v>
+        <v>1602</v>
       </c>
       <c r="G1627" t="s">
-        <v>1634</v>
+        <v>1603</v>
       </c>
       <c r="H1627" t="s">
-        <v>50</v>
+        <v>266</v>
       </c>
       <c r="I1627" t="s">
         <v>19</v>
@@ -67168,10 +67300,10 @@
         <v>1</v>
       </c>
       <c r="K1627">
-        <v>8255520</v>
+        <v>12040000</v>
       </c>
       <c r="L1627">
-        <v>8255520</v>
+        <v>12040000</v>
       </c>
     </row>
     <row r="1628" spans="1:12">
@@ -67185,19 +67317,19 @@
         <v>13</v>
       </c>
       <c r="D1628" t="s">
-        <v>1631</v>
+        <v>1591</v>
       </c>
       <c r="E1628" t="s">
-        <v>1632</v>
+        <v>1601</v>
       </c>
       <c r="F1628" t="s">
-        <v>1633</v>
+        <v>1602</v>
       </c>
       <c r="G1628" t="s">
-        <v>1634</v>
+        <v>1603</v>
       </c>
       <c r="H1628" t="s">
-        <v>51</v>
+        <v>267</v>
       </c>
       <c r="I1628" t="s">
         <v>19</v>
@@ -67206,10 +67338,10 @@
         <v>1</v>
       </c>
       <c r="K1628">
-        <v>2382912</v>
+        <v>109446000</v>
       </c>
       <c r="L1628">
-        <v>2382912</v>
+        <v>109446000</v>
       </c>
     </row>
     <row r="1629" spans="1:12">
@@ -67223,19 +67355,19 @@
         <v>13</v>
       </c>
       <c r="D1629" t="s">
-        <v>1635</v>
+        <v>1591</v>
       </c>
       <c r="E1629" t="s">
-        <v>1636</v>
+        <v>1601</v>
       </c>
       <c r="F1629" t="s">
-        <v>1637</v>
+        <v>1602</v>
       </c>
       <c r="G1629" t="s">
-        <v>1638</v>
+        <v>1603</v>
       </c>
       <c r="H1629" t="s">
-        <v>233</v>
+        <v>268</v>
       </c>
       <c r="I1629" t="s">
         <v>19</v>
@@ -67244,10 +67376,10 @@
         <v>1</v>
       </c>
       <c r="K1629">
-        <v>11235000</v>
+        <v>21689000</v>
       </c>
       <c r="L1629">
-        <v>11235000</v>
+        <v>21689000</v>
       </c>
     </row>
     <row r="1630" spans="1:12">
@@ -67261,19 +67393,19 @@
         <v>13</v>
       </c>
       <c r="D1630" t="s">
-        <v>1635</v>
+        <v>1604</v>
       </c>
       <c r="E1630" t="s">
-        <v>1636</v>
+        <v>1605</v>
       </c>
       <c r="F1630" t="s">
-        <v>1637</v>
+        <v>1606</v>
       </c>
       <c r="G1630" t="s">
-        <v>1638</v>
+        <v>1607</v>
       </c>
       <c r="H1630" t="s">
-        <v>234</v>
+        <v>64</v>
       </c>
       <c r="I1630" t="s">
         <v>19</v>
@@ -67282,10 +67414,10 @@
         <v>1</v>
       </c>
       <c r="K1630">
-        <v>129167000</v>
+        <v>691300</v>
       </c>
       <c r="L1630">
-        <v>129167000</v>
+        <v>691300</v>
       </c>
     </row>
     <row r="1631" spans="1:12">
@@ -67299,19 +67431,19 @@
         <v>13</v>
       </c>
       <c r="D1631" t="s">
-        <v>1635</v>
+        <v>1608</v>
       </c>
       <c r="E1631" t="s">
-        <v>1639</v>
+        <v>1609</v>
       </c>
       <c r="F1631" t="s">
-        <v>1640</v>
+        <v>1610</v>
       </c>
       <c r="G1631" t="s">
-        <v>1641</v>
+        <v>1611</v>
       </c>
       <c r="H1631" t="s">
-        <v>233</v>
+        <v>83</v>
       </c>
       <c r="I1631" t="s">
         <v>19</v>
@@ -67320,10 +67452,10 @@
         <v>1</v>
       </c>
       <c r="K1631">
-        <v>7665000</v>
+        <v>266012</v>
       </c>
       <c r="L1631">
-        <v>7665000</v>
+        <v>266012</v>
       </c>
     </row>
     <row r="1632" spans="1:12">
@@ -67337,19 +67469,19 @@
         <v>13</v>
       </c>
       <c r="D1632" t="s">
-        <v>1635</v>
+        <v>1608</v>
       </c>
       <c r="E1632" t="s">
-        <v>1639</v>
+        <v>1609</v>
       </c>
       <c r="F1632" t="s">
-        <v>1640</v>
+        <v>1610</v>
       </c>
       <c r="G1632" t="s">
-        <v>1641</v>
+        <v>1611</v>
       </c>
       <c r="H1632" t="s">
-        <v>234</v>
+        <v>84</v>
       </c>
       <c r="I1632" t="s">
         <v>19</v>
@@ -67358,10 +67490,10 @@
         <v>1</v>
       </c>
       <c r="K1632">
-        <v>33559000</v>
+        <v>2580750</v>
       </c>
       <c r="L1632">
-        <v>33559000</v>
+        <v>2580750</v>
       </c>
     </row>
     <row r="1633" spans="1:12">
@@ -67375,19 +67507,19 @@
         <v>13</v>
       </c>
       <c r="D1633" t="s">
-        <v>1635</v>
+        <v>1608</v>
       </c>
       <c r="E1633" t="s">
-        <v>1642</v>
+        <v>1612</v>
       </c>
       <c r="F1633" t="s">
-        <v>1643</v>
+        <v>1613</v>
       </c>
       <c r="G1633" t="s">
-        <v>1644</v>
+        <v>1614</v>
       </c>
       <c r="H1633" t="s">
-        <v>233</v>
+        <v>79</v>
       </c>
       <c r="I1633" t="s">
         <v>19</v>
@@ -67396,10 +67528,10 @@
         <v>1</v>
       </c>
       <c r="K1633">
-        <v>2415000</v>
+        <v>40247519</v>
       </c>
       <c r="L1633">
-        <v>2415000</v>
+        <v>40247519</v>
       </c>
     </row>
     <row r="1634" spans="1:12">
@@ -67413,19 +67545,19 @@
         <v>13</v>
       </c>
       <c r="D1634" t="s">
-        <v>1635</v>
+        <v>1604</v>
       </c>
       <c r="E1634" t="s">
-        <v>1642</v>
+        <v>1615</v>
       </c>
       <c r="F1634" t="s">
-        <v>1643</v>
+        <v>1616</v>
       </c>
       <c r="G1634" t="s">
-        <v>1644</v>
+        <v>1617</v>
       </c>
       <c r="H1634" t="s">
-        <v>234</v>
+        <v>48</v>
       </c>
       <c r="I1634" t="s">
         <v>19</v>
@@ -67434,10 +67566,10 @@
         <v>1</v>
       </c>
       <c r="K1634">
-        <v>24235000</v>
+        <v>1053940800</v>
       </c>
       <c r="L1634">
-        <v>24235000</v>
+        <v>1053940800</v>
       </c>
     </row>
     <row r="1635" spans="1:12">
@@ -67451,19 +67583,19 @@
         <v>13</v>
       </c>
       <c r="D1635" t="s">
-        <v>1635</v>
+        <v>1604</v>
       </c>
       <c r="E1635" t="s">
-        <v>1645</v>
+        <v>1615</v>
       </c>
       <c r="F1635" t="s">
-        <v>1646</v>
+        <v>1616</v>
       </c>
       <c r="G1635" t="s">
-        <v>1647</v>
+        <v>1617</v>
       </c>
       <c r="H1635" t="s">
-        <v>233</v>
+        <v>49</v>
       </c>
       <c r="I1635" t="s">
         <v>19</v>
@@ -67472,10 +67604,10 @@
         <v>1</v>
       </c>
       <c r="K1635">
-        <v>2415000</v>
+        <v>5888</v>
       </c>
       <c r="L1635">
-        <v>2415000</v>
+        <v>5888</v>
       </c>
     </row>
     <row r="1636" spans="1:12">
@@ -67489,19 +67621,19 @@
         <v>13</v>
       </c>
       <c r="D1636" t="s">
-        <v>1635</v>
+        <v>1604</v>
       </c>
       <c r="E1636" t="s">
-        <v>1645</v>
+        <v>1615</v>
       </c>
       <c r="F1636" t="s">
-        <v>1646</v>
+        <v>1616</v>
       </c>
       <c r="G1636" t="s">
-        <v>1647</v>
+        <v>1617</v>
       </c>
       <c r="H1636" t="s">
-        <v>234</v>
+        <v>50</v>
       </c>
       <c r="I1636" t="s">
         <v>19</v>
@@ -67510,10 +67642,10 @@
         <v>1</v>
       </c>
       <c r="K1636">
-        <v>16132000</v>
+        <v>70065440</v>
       </c>
       <c r="L1636">
-        <v>16132000</v>
+        <v>70065440</v>
       </c>
     </row>
     <row r="1637" spans="1:12">
@@ -67527,19 +67659,19 @@
         <v>13</v>
       </c>
       <c r="D1637" t="s">
-        <v>1635</v>
+        <v>1604</v>
       </c>
       <c r="E1637" t="s">
-        <v>1648</v>
+        <v>1615</v>
       </c>
       <c r="F1637" t="s">
-        <v>1649</v>
+        <v>1616</v>
       </c>
       <c r="G1637" t="s">
-        <v>1650</v>
+        <v>1617</v>
       </c>
       <c r="H1637" t="s">
-        <v>233</v>
+        <v>51</v>
       </c>
       <c r="I1637" t="s">
         <v>19</v>
@@ -67548,10 +67680,10 @@
         <v>1</v>
       </c>
       <c r="K1637">
-        <v>1610000</v>
+        <v>20735760</v>
       </c>
       <c r="L1637">
-        <v>1610000</v>
+        <v>20735760</v>
       </c>
     </row>
     <row r="1638" spans="1:12">
@@ -67565,19 +67697,19 @@
         <v>13</v>
       </c>
       <c r="D1638" t="s">
-        <v>1635</v>
+        <v>1604</v>
       </c>
       <c r="E1638" t="s">
-        <v>1648</v>
+        <v>1615</v>
       </c>
       <c r="F1638" t="s">
-        <v>1649</v>
+        <v>1616</v>
       </c>
       <c r="G1638" t="s">
-        <v>1650</v>
+        <v>1617</v>
       </c>
       <c r="H1638" t="s">
-        <v>234</v>
+        <v>52</v>
       </c>
       <c r="I1638" t="s">
         <v>19</v>
@@ -67586,10 +67718,10 @@
         <v>1</v>
       </c>
       <c r="K1638">
-        <v>50505000</v>
+        <v>174240000</v>
       </c>
       <c r="L1638">
-        <v>50505000</v>
+        <v>174240000</v>
       </c>
     </row>
     <row r="1639" spans="1:12">
@@ -67603,19 +67735,19 @@
         <v>13</v>
       </c>
       <c r="D1639" t="s">
-        <v>1635</v>
+        <v>1604</v>
       </c>
       <c r="E1639" t="s">
-        <v>1651</v>
+        <v>1615</v>
       </c>
       <c r="F1639" t="s">
-        <v>1652</v>
+        <v>1616</v>
       </c>
       <c r="G1639" t="s">
-        <v>1653</v>
+        <v>1617</v>
       </c>
       <c r="H1639" t="s">
-        <v>1654</v>
+        <v>53</v>
       </c>
       <c r="I1639" t="s">
         <v>19</v>
@@ -67624,10 +67756,10 @@
         <v>1</v>
       </c>
       <c r="K1639">
-        <v>8855000</v>
+        <v>63584760</v>
       </c>
       <c r="L1639">
-        <v>8855000</v>
+        <v>63584760</v>
       </c>
     </row>
     <row r="1640" spans="1:12">
@@ -67641,19 +67773,19 @@
         <v>13</v>
       </c>
       <c r="D1640" t="s">
-        <v>1635</v>
+        <v>1618</v>
       </c>
       <c r="E1640" t="s">
-        <v>1651</v>
+        <v>1619</v>
       </c>
       <c r="F1640" t="s">
-        <v>1652</v>
+        <v>1620</v>
       </c>
       <c r="G1640" t="s">
-        <v>1653</v>
+        <v>1621</v>
       </c>
       <c r="H1640" t="s">
-        <v>1655</v>
+        <v>84</v>
       </c>
       <c r="I1640" t="s">
         <v>19</v>
@@ -67662,10 +67794,10 @@
         <v>1</v>
       </c>
       <c r="K1640">
-        <v>21978000</v>
+        <v>6670000</v>
       </c>
       <c r="L1640">
-        <v>21978000</v>
+        <v>6670000</v>
       </c>
     </row>
     <row r="1641" spans="1:12">
@@ -67679,19 +67811,19 @@
         <v>13</v>
       </c>
       <c r="D1641" t="s">
-        <v>1631</v>
+        <v>1622</v>
       </c>
       <c r="E1641" t="s">
-        <v>1656</v>
+        <v>1623</v>
       </c>
       <c r="F1641" t="s">
-        <v>1657</v>
+        <v>1624</v>
       </c>
       <c r="G1641" t="s">
-        <v>1658</v>
+        <v>1625</v>
       </c>
       <c r="H1641" t="s">
-        <v>276</v>
+        <v>797</v>
       </c>
       <c r="I1641" t="s">
         <v>19</v>
@@ -67700,10 +67832,10 @@
         <v>1</v>
       </c>
       <c r="K1641">
-        <v>218806976</v>
+        <v>1500000</v>
       </c>
       <c r="L1641">
-        <v>218806976</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1642" spans="1:12">
@@ -67717,19 +67849,19 @@
         <v>13</v>
       </c>
       <c r="D1642" t="s">
-        <v>1631</v>
+        <v>1622</v>
       </c>
       <c r="E1642" t="s">
-        <v>1659</v>
+        <v>1626</v>
       </c>
       <c r="F1642" t="s">
-        <v>1660</v>
+        <v>1627</v>
       </c>
       <c r="G1642" t="s">
-        <v>1661</v>
+        <v>1628</v>
       </c>
       <c r="H1642" t="s">
-        <v>276</v>
+        <v>797</v>
       </c>
       <c r="I1642" t="s">
         <v>19</v>
@@ -67738,10 +67870,10 @@
         <v>1</v>
       </c>
       <c r="K1642">
-        <v>287255749</v>
+        <v>300000</v>
       </c>
       <c r="L1642">
-        <v>287255749</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="1643" spans="1:12">
@@ -67755,19 +67887,19 @@
         <v>13</v>
       </c>
       <c r="D1643" t="s">
+        <v>1618</v>
+      </c>
+      <c r="E1643" t="s">
+        <v>1629</v>
+      </c>
+      <c r="F1643" t="s">
+        <v>1630</v>
+      </c>
+      <c r="G1643" t="s">
         <v>1631</v>
       </c>
-      <c r="E1643" t="s">
-        <v>1662</v>
-      </c>
-      <c r="F1643" t="s">
-        <v>1663</v>
-      </c>
-      <c r="G1643" t="s">
-        <v>1664</v>
-      </c>
       <c r="H1643" t="s">
-        <v>276</v>
+        <v>48</v>
       </c>
       <c r="I1643" t="s">
         <v>19</v>
@@ -67776,10 +67908,10 @@
         <v>1</v>
       </c>
       <c r="K1643">
-        <v>157497319</v>
+        <v>6407200</v>
       </c>
       <c r="L1643">
-        <v>157497319</v>
+        <v>6407200</v>
       </c>
     </row>
     <row r="1644" spans="1:12">
@@ -67793,19 +67925,19 @@
         <v>13</v>
       </c>
       <c r="D1644" t="s">
+        <v>1618</v>
+      </c>
+      <c r="E1644" t="s">
+        <v>1629</v>
+      </c>
+      <c r="F1644" t="s">
+        <v>1630</v>
+      </c>
+      <c r="G1644" t="s">
         <v>1631</v>
       </c>
-      <c r="E1644" t="s">
-        <v>1665</v>
-      </c>
-      <c r="F1644" t="s">
-        <v>1666</v>
-      </c>
-      <c r="G1644" t="s">
-        <v>1667</v>
-      </c>
       <c r="H1644" t="s">
-        <v>276</v>
+        <v>49</v>
       </c>
       <c r="I1644" t="s">
         <v>19</v>
@@ -67814,10 +67946,10 @@
         <v>1</v>
       </c>
       <c r="K1644">
-        <v>102408293</v>
+        <v>32</v>
       </c>
       <c r="L1644">
-        <v>102408293</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1645" spans="1:12">
@@ -67831,19 +67963,19 @@
         <v>13</v>
       </c>
       <c r="D1645" t="s">
+        <v>1618</v>
+      </c>
+      <c r="E1645" t="s">
+        <v>1629</v>
+      </c>
+      <c r="F1645" t="s">
+        <v>1630</v>
+      </c>
+      <c r="G1645" t="s">
         <v>1631</v>
       </c>
-      <c r="E1645" t="s">
-        <v>1668</v>
-      </c>
-      <c r="F1645" t="s">
-        <v>1669</v>
-      </c>
-      <c r="G1645" t="s">
-        <v>1670</v>
-      </c>
       <c r="H1645" t="s">
-        <v>1671</v>
+        <v>52</v>
       </c>
       <c r="I1645" t="s">
         <v>19</v>
@@ -67852,10 +67984,10 @@
         <v>1</v>
       </c>
       <c r="K1645">
-        <v>142100114</v>
+        <v>1080000</v>
       </c>
       <c r="L1645">
-        <v>142100114</v>
+        <v>1080000</v>
       </c>
     </row>
     <row r="1646" spans="1:12">
@@ -67869,19 +68001,19 @@
         <v>13</v>
       </c>
       <c r="D1646" t="s">
+        <v>1618</v>
+      </c>
+      <c r="E1646" t="s">
+        <v>1629</v>
+      </c>
+      <c r="F1646" t="s">
+        <v>1630</v>
+      </c>
+      <c r="G1646" t="s">
         <v>1631</v>
       </c>
-      <c r="E1646" t="s">
-        <v>1672</v>
-      </c>
-      <c r="F1646" t="s">
-        <v>1673</v>
-      </c>
-      <c r="G1646" t="s">
-        <v>1674</v>
-      </c>
       <c r="H1646" t="s">
-        <v>276</v>
+        <v>53</v>
       </c>
       <c r="I1646" t="s">
         <v>19</v>
@@ -67890,10 +68022,10 @@
         <v>1</v>
       </c>
       <c r="K1646">
-        <v>751848354</v>
+        <v>144840</v>
       </c>
       <c r="L1646">
-        <v>751848354</v>
+        <v>144840</v>
       </c>
     </row>
     <row r="1647" spans="1:12">
@@ -67907,19 +68039,19 @@
         <v>13</v>
       </c>
       <c r="D1647" t="s">
-        <v>1631</v>
+        <v>1622</v>
       </c>
       <c r="E1647" t="s">
-        <v>1675</v>
+        <v>1632</v>
       </c>
       <c r="F1647" t="s">
-        <v>1676</v>
+        <v>1633</v>
       </c>
       <c r="G1647" t="s">
-        <v>206</v>
+        <v>1634</v>
       </c>
       <c r="H1647" t="s">
-        <v>173</v>
+        <v>31</v>
       </c>
       <c r="I1647" t="s">
         <v>19</v>
@@ -67928,10 +68060,10 @@
         <v>1</v>
       </c>
       <c r="K1647">
-        <v>10000</v>
+        <v>486200</v>
       </c>
       <c r="L1647">
-        <v>10000</v>
+        <v>486200</v>
       </c>
     </row>
     <row r="1648" spans="1:12">
@@ -67945,19 +68077,19 @@
         <v>13</v>
       </c>
       <c r="D1648" t="s">
-        <v>1631</v>
+        <v>1622</v>
       </c>
       <c r="E1648" t="s">
-        <v>1675</v>
+        <v>1632</v>
       </c>
       <c r="F1648" t="s">
-        <v>1676</v>
+        <v>1633</v>
       </c>
       <c r="G1648" t="s">
-        <v>206</v>
+        <v>1634</v>
       </c>
       <c r="H1648" t="s">
-        <v>186</v>
+        <v>32</v>
       </c>
       <c r="I1648" t="s">
         <v>19</v>
@@ -67966,10 +68098,10 @@
         <v>1</v>
       </c>
       <c r="K1648">
-        <v>23560619</v>
+        <v>66</v>
       </c>
       <c r="L1648">
-        <v>23560619</v>
+        <v>66</v>
       </c>
     </row>
     <row r="1649" spans="1:12">
@@ -67983,19 +68115,19 @@
         <v>13</v>
       </c>
       <c r="D1649" t="s">
-        <v>1631</v>
+        <v>1622</v>
       </c>
       <c r="E1649" t="s">
-        <v>1677</v>
+        <v>1632</v>
       </c>
       <c r="F1649" t="s">
-        <v>1678</v>
+        <v>1633</v>
       </c>
       <c r="G1649" t="s">
-        <v>171</v>
+        <v>1634</v>
       </c>
       <c r="H1649" t="s">
-        <v>173</v>
+        <v>33</v>
       </c>
       <c r="I1649" t="s">
         <v>19</v>
@@ -68004,10 +68136,10 @@
         <v>1</v>
       </c>
       <c r="K1649">
-        <v>2698197</v>
+        <v>48620</v>
       </c>
       <c r="L1649">
-        <v>2698197</v>
+        <v>48620</v>
       </c>
     </row>
     <row r="1650" spans="1:12">
@@ -68021,19 +68153,19 @@
         <v>13</v>
       </c>
       <c r="D1650" t="s">
-        <v>1631</v>
+        <v>1622</v>
       </c>
       <c r="E1650" t="s">
-        <v>1677</v>
+        <v>1632</v>
       </c>
       <c r="F1650" t="s">
-        <v>1678</v>
+        <v>1633</v>
       </c>
       <c r="G1650" t="s">
-        <v>171</v>
+        <v>1634</v>
       </c>
       <c r="H1650" t="s">
-        <v>1571</v>
+        <v>36</v>
       </c>
       <c r="I1650" t="s">
         <v>19</v>
@@ -68042,10 +68174,10 @@
         <v>1</v>
       </c>
       <c r="K1650">
-        <v>25300800</v>
+        <v>4094</v>
       </c>
       <c r="L1650">
-        <v>25300800</v>
+        <v>4094</v>
       </c>
     </row>
     <row r="1651" spans="1:12">
@@ -68059,19 +68191,19 @@
         <v>13</v>
       </c>
       <c r="D1651" t="s">
-        <v>1631</v>
+        <v>1622</v>
       </c>
       <c r="E1651" t="s">
-        <v>1677</v>
+        <v>1635</v>
       </c>
       <c r="F1651" t="s">
-        <v>1678</v>
+        <v>1636</v>
       </c>
       <c r="G1651" t="s">
-        <v>171</v>
+        <v>1637</v>
       </c>
       <c r="H1651" t="s">
-        <v>252</v>
+        <v>31</v>
       </c>
       <c r="I1651" t="s">
         <v>19</v>
@@ -68080,10 +68212,10 @@
         <v>1</v>
       </c>
       <c r="K1651">
-        <v>404000</v>
+        <v>724600</v>
       </c>
       <c r="L1651">
-        <v>404000</v>
+        <v>724600</v>
       </c>
     </row>
     <row r="1652" spans="1:12">
@@ -68097,19 +68229,19 @@
         <v>13</v>
       </c>
       <c r="D1652" t="s">
-        <v>1631</v>
+        <v>1622</v>
       </c>
       <c r="E1652" t="s">
-        <v>1677</v>
+        <v>1635</v>
       </c>
       <c r="F1652" t="s">
-        <v>1678</v>
+        <v>1636</v>
       </c>
       <c r="G1652" t="s">
-        <v>171</v>
+        <v>1637</v>
       </c>
       <c r="H1652" t="s">
-        <v>175</v>
+        <v>32</v>
       </c>
       <c r="I1652" t="s">
         <v>19</v>
@@ -68118,10 +68250,10 @@
         <v>1</v>
       </c>
       <c r="K1652">
-        <v>2722500</v>
+        <v>58</v>
       </c>
       <c r="L1652">
-        <v>2722500</v>
+        <v>58</v>
       </c>
     </row>
     <row r="1653" spans="1:12">
@@ -68135,19 +68267,19 @@
         <v>13</v>
       </c>
       <c r="D1653" t="s">
-        <v>1631</v>
+        <v>1622</v>
       </c>
       <c r="E1653" t="s">
-        <v>1677</v>
+        <v>1635</v>
       </c>
       <c r="F1653" t="s">
-        <v>1678</v>
+        <v>1636</v>
       </c>
       <c r="G1653" t="s">
-        <v>171</v>
+        <v>1637</v>
       </c>
       <c r="H1653" t="s">
-        <v>254</v>
+        <v>33</v>
       </c>
       <c r="I1653" t="s">
         <v>19</v>
@@ -68156,10 +68288,10 @@
         <v>1</v>
       </c>
       <c r="K1653">
-        <v>1017000</v>
+        <v>47650</v>
       </c>
       <c r="L1653">
-        <v>1017000</v>
+        <v>47650</v>
       </c>
     </row>
     <row r="1654" spans="1:12">
@@ -68173,19 +68305,19 @@
         <v>13</v>
       </c>
       <c r="D1654" t="s">
-        <v>1631</v>
+        <v>1622</v>
       </c>
       <c r="E1654" t="s">
-        <v>1677</v>
+        <v>1635</v>
       </c>
       <c r="F1654" t="s">
-        <v>1678</v>
+        <v>1636</v>
       </c>
       <c r="G1654" t="s">
-        <v>171</v>
+        <v>1637</v>
       </c>
       <c r="H1654" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="I1654" t="s">
         <v>19</v>
@@ -68194,10 +68326,10 @@
         <v>1</v>
       </c>
       <c r="K1654">
-        <v>110300</v>
+        <v>9530</v>
       </c>
       <c r="L1654">
-        <v>110300</v>
+        <v>9530</v>
       </c>
     </row>
     <row r="1655" spans="1:12">
@@ -68211,19 +68343,19 @@
         <v>13</v>
       </c>
       <c r="D1655" t="s">
-        <v>1631</v>
+        <v>1622</v>
       </c>
       <c r="E1655" t="s">
-        <v>1677</v>
+        <v>1635</v>
       </c>
       <c r="F1655" t="s">
-        <v>1678</v>
+        <v>1636</v>
       </c>
       <c r="G1655" t="s">
-        <v>171</v>
+        <v>1637</v>
       </c>
       <c r="H1655" t="s">
-        <v>207</v>
+        <v>36</v>
       </c>
       <c r="I1655" t="s">
         <v>19</v>
@@ -68232,10 +68364,10 @@
         <v>1</v>
       </c>
       <c r="K1655">
-        <v>1444358</v>
+        <v>5880</v>
       </c>
       <c r="L1655">
-        <v>1444358</v>
+        <v>5880</v>
       </c>
     </row>
     <row r="1656" spans="1:12">
@@ -68249,19 +68381,19 @@
         <v>13</v>
       </c>
       <c r="D1656" t="s">
-        <v>1631</v>
+        <v>1561</v>
       </c>
       <c r="E1656" t="s">
-        <v>1677</v>
+        <v>1638</v>
       </c>
       <c r="F1656" t="s">
-        <v>1678</v>
+        <v>1639</v>
       </c>
       <c r="G1656" t="s">
-        <v>171</v>
+        <v>1640</v>
       </c>
       <c r="H1656" t="s">
-        <v>178</v>
+        <v>36</v>
       </c>
       <c r="I1656" t="s">
         <v>19</v>
@@ -68270,10 +68402,10 @@
         <v>1</v>
       </c>
       <c r="K1656">
-        <v>9468528</v>
+        <v>1271000</v>
       </c>
       <c r="L1656">
-        <v>9468528</v>
+        <v>1271000</v>
       </c>
     </row>
     <row r="1657" spans="1:12">
@@ -68287,19 +68419,19 @@
         <v>13</v>
       </c>
       <c r="D1657" t="s">
-        <v>1631</v>
+        <v>1561</v>
       </c>
       <c r="E1657" t="s">
-        <v>1677</v>
+        <v>1638</v>
       </c>
       <c r="F1657" t="s">
-        <v>1678</v>
+        <v>1639</v>
       </c>
       <c r="G1657" t="s">
-        <v>171</v>
+        <v>1640</v>
       </c>
       <c r="H1657" t="s">
-        <v>1679</v>
+        <v>48</v>
       </c>
       <c r="I1657" t="s">
         <v>19</v>
@@ -68308,10 +68440,10 @@
         <v>1</v>
       </c>
       <c r="K1657">
-        <v>22953312</v>
+        <v>158794800</v>
       </c>
       <c r="L1657">
-        <v>22953312</v>
+        <v>158794800</v>
       </c>
     </row>
     <row r="1658" spans="1:12">
@@ -68325,19 +68457,19 @@
         <v>13</v>
       </c>
       <c r="D1658" t="s">
-        <v>1631</v>
+        <v>1561</v>
       </c>
       <c r="E1658" t="s">
-        <v>1677</v>
+        <v>1638</v>
       </c>
       <c r="F1658" t="s">
-        <v>1678</v>
+        <v>1639</v>
       </c>
       <c r="G1658" t="s">
-        <v>171</v>
+        <v>1640</v>
       </c>
       <c r="H1658" t="s">
-        <v>1680</v>
+        <v>49</v>
       </c>
       <c r="I1658" t="s">
         <v>19</v>
@@ -68346,10 +68478,10 @@
         <v>1</v>
       </c>
       <c r="K1658">
-        <v>4629928</v>
+        <v>3024</v>
       </c>
       <c r="L1658">
-        <v>4629928</v>
+        <v>3024</v>
       </c>
     </row>
     <row r="1659" spans="1:12">
@@ -68363,19 +68495,19 @@
         <v>13</v>
       </c>
       <c r="D1659" t="s">
-        <v>1631</v>
+        <v>1561</v>
       </c>
       <c r="E1659" t="s">
-        <v>1677</v>
+        <v>1638</v>
       </c>
       <c r="F1659" t="s">
-        <v>1678</v>
+        <v>1639</v>
       </c>
       <c r="G1659" t="s">
-        <v>171</v>
+        <v>1640</v>
       </c>
       <c r="H1659" t="s">
-        <v>181</v>
+        <v>50</v>
       </c>
       <c r="I1659" t="s">
         <v>19</v>
@@ -68384,10 +68516,10 @@
         <v>1</v>
       </c>
       <c r="K1659">
-        <v>8951000</v>
+        <v>9510480</v>
       </c>
       <c r="L1659">
-        <v>8951000</v>
+        <v>9510480</v>
       </c>
     </row>
     <row r="1660" spans="1:12">
@@ -68401,19 +68533,19 @@
         <v>13</v>
       </c>
       <c r="D1660" t="s">
-        <v>1631</v>
+        <v>1561</v>
       </c>
       <c r="E1660" t="s">
-        <v>1677</v>
+        <v>1638</v>
       </c>
       <c r="F1660" t="s">
-        <v>1678</v>
+        <v>1639</v>
       </c>
       <c r="G1660" t="s">
-        <v>171</v>
+        <v>1640</v>
       </c>
       <c r="H1660" t="s">
-        <v>116</v>
+        <v>51</v>
       </c>
       <c r="I1660" t="s">
         <v>19</v>
@@ -68422,10 +68554,10 @@
         <v>1</v>
       </c>
       <c r="K1660">
-        <v>1946000</v>
+        <v>2914296</v>
       </c>
       <c r="L1660">
-        <v>1946000</v>
+        <v>2914296</v>
       </c>
     </row>
     <row r="1661" spans="1:12">
@@ -68439,19 +68571,19 @@
         <v>13</v>
       </c>
       <c r="D1661" t="s">
-        <v>1631</v>
+        <v>1561</v>
       </c>
       <c r="E1661" t="s">
-        <v>1677</v>
+        <v>1638</v>
       </c>
       <c r="F1661" t="s">
-        <v>1678</v>
+        <v>1639</v>
       </c>
       <c r="G1661" t="s">
-        <v>171</v>
+        <v>1640</v>
       </c>
       <c r="H1661" t="s">
-        <v>1378</v>
+        <v>52</v>
       </c>
       <c r="I1661" t="s">
         <v>19</v>
@@ -68460,10 +68592,10 @@
         <v>1</v>
       </c>
       <c r="K1661">
-        <v>937928</v>
+        <v>25200000</v>
       </c>
       <c r="L1661">
-        <v>937928</v>
+        <v>25200000</v>
       </c>
     </row>
     <row r="1662" spans="1:12">
@@ -68477,19 +68609,19 @@
         <v>13</v>
       </c>
       <c r="D1662" t="s">
-        <v>1631</v>
+        <v>1561</v>
       </c>
       <c r="E1662" t="s">
-        <v>1677</v>
+        <v>1638</v>
       </c>
       <c r="F1662" t="s">
-        <v>1678</v>
+        <v>1639</v>
       </c>
       <c r="G1662" t="s">
-        <v>171</v>
+        <v>1640</v>
       </c>
       <c r="H1662" t="s">
-        <v>208</v>
+        <v>53</v>
       </c>
       <c r="I1662" t="s">
         <v>19</v>
@@ -68498,10 +68630,10 @@
         <v>1</v>
       </c>
       <c r="K1662">
-        <v>509000</v>
+        <v>9124920</v>
       </c>
       <c r="L1662">
-        <v>509000</v>
+        <v>9124920</v>
       </c>
     </row>
     <row r="1663" spans="1:12">
@@ -68515,19 +68647,19 @@
         <v>13</v>
       </c>
       <c r="D1663" t="s">
-        <v>1631</v>
+        <v>1561</v>
       </c>
       <c r="E1663" t="s">
-        <v>1677</v>
+        <v>1641</v>
       </c>
       <c r="F1663" t="s">
-        <v>1678</v>
+        <v>1642</v>
       </c>
       <c r="G1663" t="s">
-        <v>171</v>
+        <v>1643</v>
       </c>
       <c r="H1663" t="s">
-        <v>186</v>
+        <v>36</v>
       </c>
       <c r="I1663" t="s">
         <v>19</v>
@@ -68536,10 +68668,10 @@
         <v>1</v>
       </c>
       <c r="K1663">
-        <v>2520000</v>
+        <v>6545800</v>
       </c>
       <c r="L1663">
-        <v>2520000</v>
+        <v>6545800</v>
       </c>
     </row>
     <row r="1664" spans="1:12">
@@ -68553,19 +68685,19 @@
         <v>13</v>
       </c>
       <c r="D1664" t="s">
-        <v>1631</v>
+        <v>1561</v>
       </c>
       <c r="E1664" t="s">
-        <v>1677</v>
+        <v>1641</v>
       </c>
       <c r="F1664" t="s">
-        <v>1678</v>
+        <v>1642</v>
       </c>
       <c r="G1664" t="s">
-        <v>171</v>
+        <v>1643</v>
       </c>
       <c r="H1664" t="s">
-        <v>187</v>
+        <v>48</v>
       </c>
       <c r="I1664" t="s">
         <v>19</v>
@@ -68574,10 +68706,10 @@
         <v>1</v>
       </c>
       <c r="K1664">
-        <v>182090</v>
+        <v>207466000</v>
       </c>
       <c r="L1664">
-        <v>182090</v>
+        <v>207466000</v>
       </c>
     </row>
     <row r="1665" spans="1:12">
@@ -68591,19 +68723,19 @@
         <v>13</v>
       </c>
       <c r="D1665" t="s">
-        <v>1631</v>
+        <v>1561</v>
       </c>
       <c r="E1665" t="s">
-        <v>1677</v>
+        <v>1641</v>
       </c>
       <c r="F1665" t="s">
-        <v>1678</v>
+        <v>1642</v>
       </c>
       <c r="G1665" t="s">
-        <v>171</v>
+        <v>1643</v>
       </c>
       <c r="H1665" t="s">
-        <v>209</v>
+        <v>49</v>
       </c>
       <c r="I1665" t="s">
         <v>19</v>
@@ -68612,10 +68744,10 @@
         <v>1</v>
       </c>
       <c r="K1665">
-        <v>104700</v>
+        <v>2922</v>
       </c>
       <c r="L1665">
-        <v>104700</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="1666" spans="1:12">
@@ -68629,19 +68761,19 @@
         <v>13</v>
       </c>
       <c r="D1666" t="s">
-        <v>1631</v>
+        <v>1561</v>
       </c>
       <c r="E1666" t="s">
-        <v>1677</v>
+        <v>1641</v>
       </c>
       <c r="F1666" t="s">
-        <v>1678</v>
+        <v>1642</v>
       </c>
       <c r="G1666" t="s">
-        <v>171</v>
+        <v>1643</v>
       </c>
       <c r="H1666" t="s">
-        <v>188</v>
+        <v>50</v>
       </c>
       <c r="I1666" t="s">
         <v>19</v>
@@ -68650,10 +68782,10 @@
         <v>1</v>
       </c>
       <c r="K1666">
-        <v>300000</v>
+        <v>15459560</v>
       </c>
       <c r="L1666">
-        <v>300000</v>
+        <v>15459560</v>
       </c>
     </row>
     <row r="1667" spans="1:12">
@@ -68667,19 +68799,19 @@
         <v>13</v>
       </c>
       <c r="D1667" t="s">
-        <v>1631</v>
+        <v>1561</v>
       </c>
       <c r="E1667" t="s">
-        <v>1677</v>
+        <v>1641</v>
       </c>
       <c r="F1667" t="s">
-        <v>1678</v>
+        <v>1642</v>
       </c>
       <c r="G1667" t="s">
-        <v>171</v>
+        <v>1643</v>
       </c>
       <c r="H1667" t="s">
-        <v>189</v>
+        <v>51</v>
       </c>
       <c r="I1667" t="s">
         <v>19</v>
@@ -68688,10 +68820,10 @@
         <v>1</v>
       </c>
       <c r="K1667">
-        <v>94643</v>
+        <v>4729888</v>
       </c>
       <c r="L1667">
-        <v>94643</v>
+        <v>4729888</v>
       </c>
     </row>
     <row r="1668" spans="1:12">
@@ -68705,19 +68837,19 @@
         <v>13</v>
       </c>
       <c r="D1668" t="s">
-        <v>1631</v>
+        <v>1561</v>
       </c>
       <c r="E1668" t="s">
-        <v>1677</v>
+        <v>1641</v>
       </c>
       <c r="F1668" t="s">
-        <v>1678</v>
+        <v>1642</v>
       </c>
       <c r="G1668" t="s">
-        <v>171</v>
+        <v>1643</v>
       </c>
       <c r="H1668" t="s">
-        <v>191</v>
+        <v>52</v>
       </c>
       <c r="I1668" t="s">
         <v>19</v>
@@ -68726,10 +68858,10 @@
         <v>1</v>
       </c>
       <c r="K1668">
-        <v>2547512</v>
+        <v>33660000</v>
       </c>
       <c r="L1668">
-        <v>2547512</v>
+        <v>33660000</v>
       </c>
     </row>
     <row r="1669" spans="1:12">
@@ -68743,19 +68875,19 @@
         <v>13</v>
       </c>
       <c r="D1669" t="s">
-        <v>1631</v>
+        <v>1561</v>
       </c>
       <c r="E1669" t="s">
-        <v>1677</v>
+        <v>1641</v>
       </c>
       <c r="F1669" t="s">
-        <v>1678</v>
+        <v>1642</v>
       </c>
       <c r="G1669" t="s">
-        <v>171</v>
+        <v>1643</v>
       </c>
       <c r="H1669" t="s">
-        <v>1681</v>
+        <v>53</v>
       </c>
       <c r="I1669" t="s">
         <v>19</v>
@@ -68764,10 +68896,10 @@
         <v>1</v>
       </c>
       <c r="K1669">
-        <v>7889000</v>
+        <v>13180440</v>
       </c>
       <c r="L1669">
-        <v>7889000</v>
+        <v>13180440</v>
       </c>
     </row>
     <row r="1670" spans="1:12">
@@ -68781,31 +68913,3375 @@
         <v>13</v>
       </c>
       <c r="D1670" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1670" t="s">
+        <v>1644</v>
+      </c>
+      <c r="F1670" t="s">
+        <v>1645</v>
+      </c>
+      <c r="G1670" t="s">
+        <v>1646</v>
+      </c>
+      <c r="H1670" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1670" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1670">
+        <v>1</v>
+      </c>
+      <c r="K1670">
+        <v>42900</v>
+      </c>
+      <c r="L1670">
+        <v>42900</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:12">
+      <c r="A1671">
+        <v>1668</v>
+      </c>
+      <c r="B1671">
+        <v>403829</v>
+      </c>
+      <c r="C1671" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1671" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1671" t="s">
+        <v>1644</v>
+      </c>
+      <c r="F1671" t="s">
+        <v>1645</v>
+      </c>
+      <c r="G1671" t="s">
+        <v>1646</v>
+      </c>
+      <c r="H1671" t="s">
+        <v>48</v>
+      </c>
+      <c r="I1671" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1671">
+        <v>1</v>
+      </c>
+      <c r="K1671">
+        <v>111091600</v>
+      </c>
+      <c r="L1671">
+        <v>111091600</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:12">
+      <c r="A1672">
+        <v>1669</v>
+      </c>
+      <c r="B1672">
+        <v>403829</v>
+      </c>
+      <c r="C1672" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1672" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1672" t="s">
+        <v>1644</v>
+      </c>
+      <c r="F1672" t="s">
+        <v>1645</v>
+      </c>
+      <c r="G1672" t="s">
+        <v>1646</v>
+      </c>
+      <c r="H1672" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1672" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1672">
+        <v>1</v>
+      </c>
+      <c r="K1672">
+        <v>2394</v>
+      </c>
+      <c r="L1672">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:12">
+      <c r="A1673">
+        <v>1670</v>
+      </c>
+      <c r="B1673">
+        <v>403829</v>
+      </c>
+      <c r="C1673" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1673" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1673" t="s">
+        <v>1644</v>
+      </c>
+      <c r="F1673" t="s">
+        <v>1645</v>
+      </c>
+      <c r="G1673" t="s">
+        <v>1646</v>
+      </c>
+      <c r="H1673" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1673" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1673">
+        <v>1</v>
+      </c>
+      <c r="K1673">
+        <v>8580760</v>
+      </c>
+      <c r="L1673">
+        <v>8580760</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:12">
+      <c r="A1674">
+        <v>1671</v>
+      </c>
+      <c r="B1674">
+        <v>403829</v>
+      </c>
+      <c r="C1674" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1674" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1674" t="s">
+        <v>1644</v>
+      </c>
+      <c r="F1674" t="s">
+        <v>1645</v>
+      </c>
+      <c r="G1674" t="s">
+        <v>1646</v>
+      </c>
+      <c r="H1674" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1674" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1674">
+        <v>1</v>
+      </c>
+      <c r="K1674">
+        <v>2542192</v>
+      </c>
+      <c r="L1674">
+        <v>2542192</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:12">
+      <c r="A1675">
+        <v>1672</v>
+      </c>
+      <c r="B1675">
+        <v>403829</v>
+      </c>
+      <c r="C1675" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1675" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1675" t="s">
+        <v>1644</v>
+      </c>
+      <c r="F1675" t="s">
+        <v>1645</v>
+      </c>
+      <c r="G1675" t="s">
+        <v>1646</v>
+      </c>
+      <c r="H1675" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1675" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1675">
+        <v>1</v>
+      </c>
+      <c r="K1675">
+        <v>18360000</v>
+      </c>
+      <c r="L1675">
+        <v>18360000</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:12">
+      <c r="A1676">
+        <v>1673</v>
+      </c>
+      <c r="B1676">
+        <v>403829</v>
+      </c>
+      <c r="C1676" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1676" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1676" t="s">
+        <v>1644</v>
+      </c>
+      <c r="F1676" t="s">
+        <v>1645</v>
+      </c>
+      <c r="G1676" t="s">
+        <v>1646</v>
+      </c>
+      <c r="H1676" t="s">
+        <v>53</v>
+      </c>
+      <c r="I1676" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1676">
+        <v>1</v>
+      </c>
+      <c r="K1676">
+        <v>7386840</v>
+      </c>
+      <c r="L1676">
+        <v>7386840</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:12">
+      <c r="A1677">
+        <v>1674</v>
+      </c>
+      <c r="B1677">
+        <v>403829</v>
+      </c>
+      <c r="C1677" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1677" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1677" t="s">
+        <v>1647</v>
+      </c>
+      <c r="F1677" t="s">
+        <v>1648</v>
+      </c>
+      <c r="G1677" t="s">
+        <v>1649</v>
+      </c>
+      <c r="H1677" t="s">
+        <v>48</v>
+      </c>
+      <c r="I1677" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1677">
+        <v>1</v>
+      </c>
+      <c r="K1677">
+        <v>72648400</v>
+      </c>
+      <c r="L1677">
+        <v>72648400</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:12">
+      <c r="A1678">
+        <v>1675</v>
+      </c>
+      <c r="B1678">
+        <v>403829</v>
+      </c>
+      <c r="C1678" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1678" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1678" t="s">
+        <v>1647</v>
+      </c>
+      <c r="F1678" t="s">
+        <v>1648</v>
+      </c>
+      <c r="G1678" t="s">
+        <v>1649</v>
+      </c>
+      <c r="H1678" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1678" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1678">
+        <v>1</v>
+      </c>
+      <c r="K1678">
+        <v>1415</v>
+      </c>
+      <c r="L1678">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:12">
+      <c r="A1679">
+        <v>1676</v>
+      </c>
+      <c r="B1679">
+        <v>403829</v>
+      </c>
+      <c r="C1679" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1679" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1679" t="s">
+        <v>1647</v>
+      </c>
+      <c r="F1679" t="s">
+        <v>1648</v>
+      </c>
+      <c r="G1679" t="s">
+        <v>1649</v>
+      </c>
+      <c r="H1679" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1679" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1679">
+        <v>1</v>
+      </c>
+      <c r="K1679">
+        <v>4416080</v>
+      </c>
+      <c r="L1679">
+        <v>4416080</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:12">
+      <c r="A1680">
+        <v>1677</v>
+      </c>
+      <c r="B1680">
+        <v>403829</v>
+      </c>
+      <c r="C1680" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1680" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1680" t="s">
+        <v>1647</v>
+      </c>
+      <c r="F1680" t="s">
+        <v>1648</v>
+      </c>
+      <c r="G1680" t="s">
+        <v>1649</v>
+      </c>
+      <c r="H1680" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1680" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1680">
+        <v>1</v>
+      </c>
+      <c r="K1680">
+        <v>1004464</v>
+      </c>
+      <c r="L1680">
+        <v>1004464</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:12">
+      <c r="A1681">
+        <v>1678</v>
+      </c>
+      <c r="B1681">
+        <v>403829</v>
+      </c>
+      <c r="C1681" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1681" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1681" t="s">
+        <v>1647</v>
+      </c>
+      <c r="F1681" t="s">
+        <v>1648</v>
+      </c>
+      <c r="G1681" t="s">
+        <v>1649</v>
+      </c>
+      <c r="H1681" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1681" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1681">
+        <v>1</v>
+      </c>
+      <c r="K1681">
+        <v>11520000</v>
+      </c>
+      <c r="L1681">
+        <v>11520000</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:12">
+      <c r="A1682">
+        <v>1679</v>
+      </c>
+      <c r="B1682">
+        <v>403829</v>
+      </c>
+      <c r="C1682" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1682" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1682" t="s">
+        <v>1647</v>
+      </c>
+      <c r="F1682" t="s">
+        <v>1648</v>
+      </c>
+      <c r="G1682" t="s">
+        <v>1649</v>
+      </c>
+      <c r="H1682" t="s">
+        <v>53</v>
+      </c>
+      <c r="I1682" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1682">
+        <v>1</v>
+      </c>
+      <c r="K1682">
+        <v>3838260</v>
+      </c>
+      <c r="L1682">
+        <v>3838260</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:12">
+      <c r="A1683">
+        <v>1680</v>
+      </c>
+      <c r="B1683">
+        <v>403829</v>
+      </c>
+      <c r="C1683" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1683" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1683" t="s">
+        <v>1650</v>
+      </c>
+      <c r="F1683" t="s">
+        <v>1651</v>
+      </c>
+      <c r="G1683" t="s">
+        <v>1652</v>
+      </c>
+      <c r="H1683" t="s">
+        <v>1544</v>
+      </c>
+      <c r="I1683" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1683">
+        <v>1</v>
+      </c>
+      <c r="K1683">
+        <v>115408800</v>
+      </c>
+      <c r="L1683">
+        <v>115408800</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:12">
+      <c r="A1684">
+        <v>1681</v>
+      </c>
+      <c r="B1684">
+        <v>403829</v>
+      </c>
+      <c r="C1684" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1684" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1684" t="s">
+        <v>1650</v>
+      </c>
+      <c r="F1684" t="s">
+        <v>1651</v>
+      </c>
+      <c r="G1684" t="s">
+        <v>1652</v>
+      </c>
+      <c r="H1684" t="s">
+        <v>1545</v>
+      </c>
+      <c r="I1684" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1684">
+        <v>1</v>
+      </c>
+      <c r="K1684">
+        <v>2111</v>
+      </c>
+      <c r="L1684">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:12">
+      <c r="A1685">
         <v>1682</v>
       </c>
-      <c r="E1670" t="s">
+      <c r="B1685">
+        <v>403829</v>
+      </c>
+      <c r="C1685" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1685" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1685" t="s">
+        <v>1650</v>
+      </c>
+      <c r="F1685" t="s">
+        <v>1651</v>
+      </c>
+      <c r="G1685" t="s">
+        <v>1652</v>
+      </c>
+      <c r="H1685" t="s">
+        <v>1546</v>
+      </c>
+      <c r="I1685" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1685">
+        <v>1</v>
+      </c>
+      <c r="K1685">
+        <v>7571670</v>
+      </c>
+      <c r="L1685">
+        <v>7571670</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:12">
+      <c r="A1686">
         <v>1683</v>
       </c>
-      <c r="F1670" t="s">
+      <c r="B1686">
+        <v>403829</v>
+      </c>
+      <c r="C1686" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1686" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1686" t="s">
+        <v>1650</v>
+      </c>
+      <c r="F1686" t="s">
+        <v>1651</v>
+      </c>
+      <c r="G1686" t="s">
+        <v>1652</v>
+      </c>
+      <c r="H1686" t="s">
+        <v>1547</v>
+      </c>
+      <c r="I1686" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1686">
+        <v>1</v>
+      </c>
+      <c r="K1686">
+        <v>2630444</v>
+      </c>
+      <c r="L1686">
+        <v>2630444</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:12">
+      <c r="A1687">
         <v>1684</v>
       </c>
-      <c r="G1670" t="s">
+      <c r="B1687">
+        <v>403829</v>
+      </c>
+      <c r="C1687" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1687" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1687" t="s">
+        <v>1650</v>
+      </c>
+      <c r="F1687" t="s">
+        <v>1651</v>
+      </c>
+      <c r="G1687" t="s">
+        <v>1652</v>
+      </c>
+      <c r="H1687" t="s">
+        <v>1548</v>
+      </c>
+      <c r="I1687" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1687">
+        <v>1</v>
+      </c>
+      <c r="K1687">
+        <v>7748940</v>
+      </c>
+      <c r="L1687">
+        <v>7748940</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:12">
+      <c r="A1688">
         <v>1685</v>
       </c>
-      <c r="H1670" t="s">
+      <c r="B1688">
+        <v>403829</v>
+      </c>
+      <c r="C1688" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1688" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1688" t="s">
+        <v>1650</v>
+      </c>
+      <c r="F1688" t="s">
+        <v>1651</v>
+      </c>
+      <c r="G1688" t="s">
+        <v>1652</v>
+      </c>
+      <c r="H1688" t="s">
+        <v>1549</v>
+      </c>
+      <c r="I1688" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1688">
+        <v>1</v>
+      </c>
+      <c r="K1688">
+        <v>6965000</v>
+      </c>
+      <c r="L1688">
+        <v>6965000</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:12">
+      <c r="A1689">
+        <v>1686</v>
+      </c>
+      <c r="B1689">
+        <v>403829</v>
+      </c>
+      <c r="C1689" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1689" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1689" t="s">
+        <v>1653</v>
+      </c>
+      <c r="F1689" t="s">
+        <v>1654</v>
+      </c>
+      <c r="G1689" t="s">
+        <v>1655</v>
+      </c>
+      <c r="H1689" t="s">
+        <v>48</v>
+      </c>
+      <c r="I1689" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1689">
+        <v>1</v>
+      </c>
+      <c r="K1689">
+        <v>530174000</v>
+      </c>
+      <c r="L1689">
+        <v>530174000</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:12">
+      <c r="A1690">
+        <v>1687</v>
+      </c>
+      <c r="B1690">
+        <v>403829</v>
+      </c>
+      <c r="C1690" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1690" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1690" t="s">
+        <v>1653</v>
+      </c>
+      <c r="F1690" t="s">
+        <v>1654</v>
+      </c>
+      <c r="G1690" t="s">
+        <v>1655</v>
+      </c>
+      <c r="H1690" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1690" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1690">
+        <v>1</v>
+      </c>
+      <c r="K1690">
+        <v>13342</v>
+      </c>
+      <c r="L1690">
+        <v>13342</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:12">
+      <c r="A1691">
+        <v>1688</v>
+      </c>
+      <c r="B1691">
+        <v>403829</v>
+      </c>
+      <c r="C1691" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1691" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1691" t="s">
+        <v>1653</v>
+      </c>
+      <c r="F1691" t="s">
+        <v>1654</v>
+      </c>
+      <c r="G1691" t="s">
+        <v>1655</v>
+      </c>
+      <c r="H1691" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1691" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1691">
+        <v>1</v>
+      </c>
+      <c r="K1691">
+        <v>35353080</v>
+      </c>
+      <c r="L1691">
+        <v>35353080</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:12">
+      <c r="A1692">
+        <v>1689</v>
+      </c>
+      <c r="B1692">
+        <v>403829</v>
+      </c>
+      <c r="C1692" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1692" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1692" t="s">
+        <v>1653</v>
+      </c>
+      <c r="F1692" t="s">
+        <v>1654</v>
+      </c>
+      <c r="G1692" t="s">
+        <v>1655</v>
+      </c>
+      <c r="H1692" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1692" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1692">
+        <v>1</v>
+      </c>
+      <c r="K1692">
+        <v>10496024</v>
+      </c>
+      <c r="L1692">
+        <v>10496024</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:12">
+      <c r="A1693">
+        <v>1690</v>
+      </c>
+      <c r="B1693">
+        <v>403829</v>
+      </c>
+      <c r="C1693" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1693" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1693" t="s">
+        <v>1653</v>
+      </c>
+      <c r="F1693" t="s">
+        <v>1654</v>
+      </c>
+      <c r="G1693" t="s">
+        <v>1655</v>
+      </c>
+      <c r="H1693" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1693" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1693">
+        <v>1</v>
+      </c>
+      <c r="K1693">
+        <v>87660000</v>
+      </c>
+      <c r="L1693">
+        <v>87660000</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:12">
+      <c r="A1694">
+        <v>1691</v>
+      </c>
+      <c r="B1694">
+        <v>403829</v>
+      </c>
+      <c r="C1694" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1694" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1694" t="s">
+        <v>1653</v>
+      </c>
+      <c r="F1694" t="s">
+        <v>1654</v>
+      </c>
+      <c r="G1694" t="s">
+        <v>1655</v>
+      </c>
+      <c r="H1694" t="s">
+        <v>53</v>
+      </c>
+      <c r="I1694" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1694">
+        <v>1</v>
+      </c>
+      <c r="K1694">
+        <v>32082060</v>
+      </c>
+      <c r="L1694">
+        <v>32082060</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:12">
+      <c r="A1695">
+        <v>1692</v>
+      </c>
+      <c r="B1695">
+        <v>403829</v>
+      </c>
+      <c r="C1695" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1695" t="s">
+        <v>1622</v>
+      </c>
+      <c r="E1695" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F1695" t="s">
+        <v>1657</v>
+      </c>
+      <c r="G1695" t="s">
+        <v>1658</v>
+      </c>
+      <c r="H1695" t="s">
+        <v>272</v>
+      </c>
+      <c r="I1695" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1695">
+        <v>1</v>
+      </c>
+      <c r="K1695">
+        <v>841674471</v>
+      </c>
+      <c r="L1695">
+        <v>841674471</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:12">
+      <c r="A1696">
+        <v>1693</v>
+      </c>
+      <c r="B1696">
+        <v>403829</v>
+      </c>
+      <c r="C1696" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1696" t="s">
+        <v>1622</v>
+      </c>
+      <c r="E1696" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F1696" t="s">
+        <v>1660</v>
+      </c>
+      <c r="G1696" t="s">
+        <v>1661</v>
+      </c>
+      <c r="H1696" t="s">
+        <v>272</v>
+      </c>
+      <c r="I1696" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1696">
+        <v>1</v>
+      </c>
+      <c r="K1696">
+        <v>1050297970</v>
+      </c>
+      <c r="L1696">
+        <v>1050297970</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:12">
+      <c r="A1697">
+        <v>1694</v>
+      </c>
+      <c r="B1697">
+        <v>403829</v>
+      </c>
+      <c r="C1697" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1697" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E1697" t="s">
+        <v>1663</v>
+      </c>
+      <c r="F1697" t="s">
+        <v>1664</v>
+      </c>
+      <c r="G1697" t="s">
+        <v>1665</v>
+      </c>
+      <c r="H1697" t="s">
+        <v>48</v>
+      </c>
+      <c r="I1697" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1697">
+        <v>1</v>
+      </c>
+      <c r="K1697">
+        <v>107755200</v>
+      </c>
+      <c r="L1697">
+        <v>107755200</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:12">
+      <c r="A1698">
+        <v>1695</v>
+      </c>
+      <c r="B1698">
+        <v>403829</v>
+      </c>
+      <c r="C1698" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1698" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E1698" t="s">
+        <v>1663</v>
+      </c>
+      <c r="F1698" t="s">
+        <v>1664</v>
+      </c>
+      <c r="G1698" t="s">
+        <v>1665</v>
+      </c>
+      <c r="H1698" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1698" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1698">
+        <v>1</v>
+      </c>
+      <c r="K1698">
+        <v>33406</v>
+      </c>
+      <c r="L1698">
+        <v>33406</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:12">
+      <c r="A1699">
+        <v>1696</v>
+      </c>
+      <c r="B1699">
+        <v>403829</v>
+      </c>
+      <c r="C1699" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1699" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E1699" t="s">
+        <v>1663</v>
+      </c>
+      <c r="F1699" t="s">
+        <v>1664</v>
+      </c>
+      <c r="G1699" t="s">
+        <v>1665</v>
+      </c>
+      <c r="H1699" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1699" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1699">
+        <v>1</v>
+      </c>
+      <c r="K1699">
+        <v>8255520</v>
+      </c>
+      <c r="L1699">
+        <v>8255520</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:12">
+      <c r="A1700">
+        <v>1697</v>
+      </c>
+      <c r="B1700">
+        <v>403829</v>
+      </c>
+      <c r="C1700" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1700" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E1700" t="s">
+        <v>1663</v>
+      </c>
+      <c r="F1700" t="s">
+        <v>1664</v>
+      </c>
+      <c r="G1700" t="s">
+        <v>1665</v>
+      </c>
+      <c r="H1700" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1700" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1700">
+        <v>1</v>
+      </c>
+      <c r="K1700">
+        <v>2382912</v>
+      </c>
+      <c r="L1700">
+        <v>2382912</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:12">
+      <c r="A1701">
+        <v>1698</v>
+      </c>
+      <c r="B1701">
+        <v>403829</v>
+      </c>
+      <c r="C1701" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1701" t="s">
+        <v>1666</v>
+      </c>
+      <c r="E1701" t="s">
+        <v>1667</v>
+      </c>
+      <c r="F1701" t="s">
+        <v>1668</v>
+      </c>
+      <c r="G1701" t="s">
+        <v>1669</v>
+      </c>
+      <c r="H1701" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1701" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1701">
+        <v>1</v>
+      </c>
+      <c r="K1701">
+        <v>11235000</v>
+      </c>
+      <c r="L1701">
+        <v>11235000</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:12">
+      <c r="A1702">
+        <v>1699</v>
+      </c>
+      <c r="B1702">
+        <v>403829</v>
+      </c>
+      <c r="C1702" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1702" t="s">
+        <v>1666</v>
+      </c>
+      <c r="E1702" t="s">
+        <v>1667</v>
+      </c>
+      <c r="F1702" t="s">
+        <v>1668</v>
+      </c>
+      <c r="G1702" t="s">
+        <v>1669</v>
+      </c>
+      <c r="H1702" t="s">
         <v>234</v>
       </c>
-      <c r="I1670" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1670">
-        <v>1</v>
-      </c>
-      <c r="K1670">
+      <c r="I1702" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1702">
+        <v>1</v>
+      </c>
+      <c r="K1702">
+        <v>129167000</v>
+      </c>
+      <c r="L1702">
+        <v>129167000</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:12">
+      <c r="A1703">
+        <v>1700</v>
+      </c>
+      <c r="B1703">
+        <v>403829</v>
+      </c>
+      <c r="C1703" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1703" t="s">
+        <v>1666</v>
+      </c>
+      <c r="E1703" t="s">
+        <v>1670</v>
+      </c>
+      <c r="F1703" t="s">
+        <v>1671</v>
+      </c>
+      <c r="G1703" t="s">
+        <v>1672</v>
+      </c>
+      <c r="H1703" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1703" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1703">
+        <v>1</v>
+      </c>
+      <c r="K1703">
+        <v>7665000</v>
+      </c>
+      <c r="L1703">
+        <v>7665000</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:12">
+      <c r="A1704">
+        <v>1701</v>
+      </c>
+      <c r="B1704">
+        <v>403829</v>
+      </c>
+      <c r="C1704" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1704" t="s">
+        <v>1666</v>
+      </c>
+      <c r="E1704" t="s">
+        <v>1670</v>
+      </c>
+      <c r="F1704" t="s">
+        <v>1671</v>
+      </c>
+      <c r="G1704" t="s">
+        <v>1672</v>
+      </c>
+      <c r="H1704" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1704" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1704">
+        <v>1</v>
+      </c>
+      <c r="K1704">
+        <v>33559000</v>
+      </c>
+      <c r="L1704">
+        <v>33559000</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:12">
+      <c r="A1705">
+        <v>1702</v>
+      </c>
+      <c r="B1705">
+        <v>403829</v>
+      </c>
+      <c r="C1705" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1705" t="s">
+        <v>1666</v>
+      </c>
+      <c r="E1705" t="s">
+        <v>1673</v>
+      </c>
+      <c r="F1705" t="s">
+        <v>1674</v>
+      </c>
+      <c r="G1705" t="s">
+        <v>1675</v>
+      </c>
+      <c r="H1705" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1705" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1705">
+        <v>1</v>
+      </c>
+      <c r="K1705">
+        <v>2415000</v>
+      </c>
+      <c r="L1705">
+        <v>2415000</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:12">
+      <c r="A1706">
+        <v>1703</v>
+      </c>
+      <c r="B1706">
+        <v>403829</v>
+      </c>
+      <c r="C1706" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1706" t="s">
+        <v>1666</v>
+      </c>
+      <c r="E1706" t="s">
+        <v>1673</v>
+      </c>
+      <c r="F1706" t="s">
+        <v>1674</v>
+      </c>
+      <c r="G1706" t="s">
+        <v>1675</v>
+      </c>
+      <c r="H1706" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1706" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1706">
+        <v>1</v>
+      </c>
+      <c r="K1706">
+        <v>24235000</v>
+      </c>
+      <c r="L1706">
+        <v>24235000</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:12">
+      <c r="A1707">
+        <v>1704</v>
+      </c>
+      <c r="B1707">
+        <v>403829</v>
+      </c>
+      <c r="C1707" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1707" t="s">
+        <v>1666</v>
+      </c>
+      <c r="E1707" t="s">
+        <v>1676</v>
+      </c>
+      <c r="F1707" t="s">
+        <v>1677</v>
+      </c>
+      <c r="G1707" t="s">
+        <v>1678</v>
+      </c>
+      <c r="H1707" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1707" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1707">
+        <v>1</v>
+      </c>
+      <c r="K1707">
+        <v>2415000</v>
+      </c>
+      <c r="L1707">
+        <v>2415000</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:12">
+      <c r="A1708">
+        <v>1705</v>
+      </c>
+      <c r="B1708">
+        <v>403829</v>
+      </c>
+      <c r="C1708" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1708" t="s">
+        <v>1666</v>
+      </c>
+      <c r="E1708" t="s">
+        <v>1676</v>
+      </c>
+      <c r="F1708" t="s">
+        <v>1677</v>
+      </c>
+      <c r="G1708" t="s">
+        <v>1678</v>
+      </c>
+      <c r="H1708" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1708" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1708">
+        <v>1</v>
+      </c>
+      <c r="K1708">
+        <v>16132000</v>
+      </c>
+      <c r="L1708">
+        <v>16132000</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:12">
+      <c r="A1709">
+        <v>1706</v>
+      </c>
+      <c r="B1709">
+        <v>403829</v>
+      </c>
+      <c r="C1709" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1709" t="s">
+        <v>1666</v>
+      </c>
+      <c r="E1709" t="s">
+        <v>1679</v>
+      </c>
+      <c r="F1709" t="s">
+        <v>1680</v>
+      </c>
+      <c r="G1709" t="s">
+        <v>1681</v>
+      </c>
+      <c r="H1709" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1709" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1709">
+        <v>1</v>
+      </c>
+      <c r="K1709">
+        <v>1610000</v>
+      </c>
+      <c r="L1709">
+        <v>1610000</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:12">
+      <c r="A1710">
+        <v>1707</v>
+      </c>
+      <c r="B1710">
+        <v>403829</v>
+      </c>
+      <c r="C1710" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1710" t="s">
+        <v>1666</v>
+      </c>
+      <c r="E1710" t="s">
+        <v>1679</v>
+      </c>
+      <c r="F1710" t="s">
+        <v>1680</v>
+      </c>
+      <c r="G1710" t="s">
+        <v>1681</v>
+      </c>
+      <c r="H1710" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1710" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1710">
+        <v>1</v>
+      </c>
+      <c r="K1710">
+        <v>50505000</v>
+      </c>
+      <c r="L1710">
+        <v>50505000</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:12">
+      <c r="A1711">
+        <v>1708</v>
+      </c>
+      <c r="B1711">
+        <v>403829</v>
+      </c>
+      <c r="C1711" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1711" t="s">
+        <v>1666</v>
+      </c>
+      <c r="E1711" t="s">
+        <v>1682</v>
+      </c>
+      <c r="F1711" t="s">
+        <v>1683</v>
+      </c>
+      <c r="G1711" t="s">
+        <v>1684</v>
+      </c>
+      <c r="H1711" t="s">
+        <v>1685</v>
+      </c>
+      <c r="I1711" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1711">
+        <v>1</v>
+      </c>
+      <c r="K1711">
+        <v>8855000</v>
+      </c>
+      <c r="L1711">
+        <v>8855000</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:12">
+      <c r="A1712">
+        <v>1709</v>
+      </c>
+      <c r="B1712">
+        <v>403829</v>
+      </c>
+      <c r="C1712" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1712" t="s">
+        <v>1666</v>
+      </c>
+      <c r="E1712" t="s">
+        <v>1682</v>
+      </c>
+      <c r="F1712" t="s">
+        <v>1683</v>
+      </c>
+      <c r="G1712" t="s">
+        <v>1684</v>
+      </c>
+      <c r="H1712" t="s">
+        <v>1686</v>
+      </c>
+      <c r="I1712" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1712">
+        <v>1</v>
+      </c>
+      <c r="K1712">
+        <v>21978000</v>
+      </c>
+      <c r="L1712">
+        <v>21978000</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:12">
+      <c r="A1713">
+        <v>1710</v>
+      </c>
+      <c r="B1713">
+        <v>403829</v>
+      </c>
+      <c r="C1713" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1713" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E1713" t="s">
+        <v>1687</v>
+      </c>
+      <c r="F1713" t="s">
+        <v>1688</v>
+      </c>
+      <c r="G1713" t="s">
+        <v>1689</v>
+      </c>
+      <c r="H1713" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1713" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1713">
+        <v>1</v>
+      </c>
+      <c r="K1713">
+        <v>218806976</v>
+      </c>
+      <c r="L1713">
+        <v>218806976</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:12">
+      <c r="A1714">
+        <v>1711</v>
+      </c>
+      <c r="B1714">
+        <v>403829</v>
+      </c>
+      <c r="C1714" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1714" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E1714" t="s">
+        <v>1690</v>
+      </c>
+      <c r="F1714" t="s">
+        <v>1691</v>
+      </c>
+      <c r="G1714" t="s">
+        <v>1692</v>
+      </c>
+      <c r="H1714" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1714" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1714">
+        <v>1</v>
+      </c>
+      <c r="K1714">
+        <v>287255749</v>
+      </c>
+      <c r="L1714">
+        <v>287255749</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:12">
+      <c r="A1715">
+        <v>1712</v>
+      </c>
+      <c r="B1715">
+        <v>403829</v>
+      </c>
+      <c r="C1715" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1715" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E1715" t="s">
+        <v>1693</v>
+      </c>
+      <c r="F1715" t="s">
+        <v>1694</v>
+      </c>
+      <c r="G1715" t="s">
+        <v>1695</v>
+      </c>
+      <c r="H1715" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1715" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1715">
+        <v>1</v>
+      </c>
+      <c r="K1715">
+        <v>157497319</v>
+      </c>
+      <c r="L1715">
+        <v>157497319</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:12">
+      <c r="A1716">
+        <v>1713</v>
+      </c>
+      <c r="B1716">
+        <v>403829</v>
+      </c>
+      <c r="C1716" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1716" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E1716" t="s">
+        <v>1696</v>
+      </c>
+      <c r="F1716" t="s">
+        <v>1697</v>
+      </c>
+      <c r="G1716" t="s">
+        <v>1698</v>
+      </c>
+      <c r="H1716" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1716" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1716">
+        <v>1</v>
+      </c>
+      <c r="K1716">
+        <v>102408293</v>
+      </c>
+      <c r="L1716">
+        <v>102408293</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:12">
+      <c r="A1717">
+        <v>1714</v>
+      </c>
+      <c r="B1717">
+        <v>403829</v>
+      </c>
+      <c r="C1717" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1717" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E1717" t="s">
+        <v>1699</v>
+      </c>
+      <c r="F1717" t="s">
+        <v>1700</v>
+      </c>
+      <c r="G1717" t="s">
+        <v>1701</v>
+      </c>
+      <c r="H1717" t="s">
+        <v>1702</v>
+      </c>
+      <c r="I1717" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1717">
+        <v>1</v>
+      </c>
+      <c r="K1717">
+        <v>142100114</v>
+      </c>
+      <c r="L1717">
+        <v>142100114</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:12">
+      <c r="A1718">
+        <v>1715</v>
+      </c>
+      <c r="B1718">
+        <v>403829</v>
+      </c>
+      <c r="C1718" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1718" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E1718" t="s">
+        <v>1703</v>
+      </c>
+      <c r="F1718" t="s">
+        <v>1704</v>
+      </c>
+      <c r="G1718" t="s">
+        <v>1705</v>
+      </c>
+      <c r="H1718" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1718" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1718">
+        <v>1</v>
+      </c>
+      <c r="K1718">
+        <v>751848354</v>
+      </c>
+      <c r="L1718">
+        <v>751848354</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:12">
+      <c r="A1719">
+        <v>1716</v>
+      </c>
+      <c r="B1719">
+        <v>403829</v>
+      </c>
+      <c r="C1719" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1719" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E1719" t="s">
+        <v>1706</v>
+      </c>
+      <c r="F1719" t="s">
+        <v>1707</v>
+      </c>
+      <c r="G1719" t="s">
+        <v>206</v>
+      </c>
+      <c r="H1719" t="s">
+        <v>173</v>
+      </c>
+      <c r="I1719" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1719">
+        <v>1</v>
+      </c>
+      <c r="K1719">
+        <v>10000</v>
+      </c>
+      <c r="L1719">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:12">
+      <c r="A1720">
+        <v>1717</v>
+      </c>
+      <c r="B1720">
+        <v>403829</v>
+      </c>
+      <c r="C1720" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1720" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E1720" t="s">
+        <v>1706</v>
+      </c>
+      <c r="F1720" t="s">
+        <v>1707</v>
+      </c>
+      <c r="G1720" t="s">
+        <v>206</v>
+      </c>
+      <c r="H1720" t="s">
+        <v>186</v>
+      </c>
+      <c r="I1720" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1720">
+        <v>1</v>
+      </c>
+      <c r="K1720">
+        <v>23560619</v>
+      </c>
+      <c r="L1720">
+        <v>23560619</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:12">
+      <c r="A1721">
+        <v>1718</v>
+      </c>
+      <c r="B1721">
+        <v>403829</v>
+      </c>
+      <c r="C1721" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1721" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E1721" t="s">
+        <v>1708</v>
+      </c>
+      <c r="F1721" t="s">
+        <v>1709</v>
+      </c>
+      <c r="G1721" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1721" t="s">
+        <v>173</v>
+      </c>
+      <c r="I1721" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1721">
+        <v>1</v>
+      </c>
+      <c r="K1721">
+        <v>2698197</v>
+      </c>
+      <c r="L1721">
+        <v>2698197</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:12">
+      <c r="A1722">
+        <v>1719</v>
+      </c>
+      <c r="B1722">
+        <v>403829</v>
+      </c>
+      <c r="C1722" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1722" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E1722" t="s">
+        <v>1708</v>
+      </c>
+      <c r="F1722" t="s">
+        <v>1709</v>
+      </c>
+      <c r="G1722" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1722" t="s">
+        <v>1584</v>
+      </c>
+      <c r="I1722" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1722">
+        <v>1</v>
+      </c>
+      <c r="K1722">
+        <v>25300800</v>
+      </c>
+      <c r="L1722">
+        <v>25300800</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:12">
+      <c r="A1723">
+        <v>1720</v>
+      </c>
+      <c r="B1723">
+        <v>403829</v>
+      </c>
+      <c r="C1723" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1723" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E1723" t="s">
+        <v>1708</v>
+      </c>
+      <c r="F1723" t="s">
+        <v>1709</v>
+      </c>
+      <c r="G1723" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1723" t="s">
+        <v>252</v>
+      </c>
+      <c r="I1723" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1723">
+        <v>1</v>
+      </c>
+      <c r="K1723">
+        <v>404000</v>
+      </c>
+      <c r="L1723">
+        <v>404000</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:12">
+      <c r="A1724">
+        <v>1721</v>
+      </c>
+      <c r="B1724">
+        <v>403829</v>
+      </c>
+      <c r="C1724" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1724" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E1724" t="s">
+        <v>1708</v>
+      </c>
+      <c r="F1724" t="s">
+        <v>1709</v>
+      </c>
+      <c r="G1724" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1724" t="s">
+        <v>175</v>
+      </c>
+      <c r="I1724" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1724">
+        <v>1</v>
+      </c>
+      <c r="K1724">
+        <v>2722500</v>
+      </c>
+      <c r="L1724">
+        <v>2722500</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:12">
+      <c r="A1725">
+        <v>1722</v>
+      </c>
+      <c r="B1725">
+        <v>403829</v>
+      </c>
+      <c r="C1725" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1725" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E1725" t="s">
+        <v>1708</v>
+      </c>
+      <c r="F1725" t="s">
+        <v>1709</v>
+      </c>
+      <c r="G1725" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1725" t="s">
+        <v>254</v>
+      </c>
+      <c r="I1725" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1725">
+        <v>1</v>
+      </c>
+      <c r="K1725">
+        <v>1017000</v>
+      </c>
+      <c r="L1725">
+        <v>1017000</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:12">
+      <c r="A1726">
+        <v>1723</v>
+      </c>
+      <c r="B1726">
+        <v>403829</v>
+      </c>
+      <c r="C1726" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1726" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E1726" t="s">
+        <v>1708</v>
+      </c>
+      <c r="F1726" t="s">
+        <v>1709</v>
+      </c>
+      <c r="G1726" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1726" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1726" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1726">
+        <v>1</v>
+      </c>
+      <c r="K1726">
+        <v>110300</v>
+      </c>
+      <c r="L1726">
+        <v>110300</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:12">
+      <c r="A1727">
+        <v>1724</v>
+      </c>
+      <c r="B1727">
+        <v>403829</v>
+      </c>
+      <c r="C1727" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1727" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E1727" t="s">
+        <v>1708</v>
+      </c>
+      <c r="F1727" t="s">
+        <v>1709</v>
+      </c>
+      <c r="G1727" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1727" t="s">
+        <v>207</v>
+      </c>
+      <c r="I1727" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1727">
+        <v>1</v>
+      </c>
+      <c r="K1727">
+        <v>1444358</v>
+      </c>
+      <c r="L1727">
+        <v>1444358</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:12">
+      <c r="A1728">
+        <v>1725</v>
+      </c>
+      <c r="B1728">
+        <v>403829</v>
+      </c>
+      <c r="C1728" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1728" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E1728" t="s">
+        <v>1708</v>
+      </c>
+      <c r="F1728" t="s">
+        <v>1709</v>
+      </c>
+      <c r="G1728" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1728" t="s">
+        <v>178</v>
+      </c>
+      <c r="I1728" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1728">
+        <v>1</v>
+      </c>
+      <c r="K1728">
+        <v>9468528</v>
+      </c>
+      <c r="L1728">
+        <v>9468528</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:12">
+      <c r="A1729">
+        <v>1726</v>
+      </c>
+      <c r="B1729">
+        <v>403829</v>
+      </c>
+      <c r="C1729" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1729" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E1729" t="s">
+        <v>1708</v>
+      </c>
+      <c r="F1729" t="s">
+        <v>1709</v>
+      </c>
+      <c r="G1729" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1729" t="s">
+        <v>1710</v>
+      </c>
+      <c r="I1729" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1729">
+        <v>1</v>
+      </c>
+      <c r="K1729">
+        <v>22953312</v>
+      </c>
+      <c r="L1729">
+        <v>22953312</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:12">
+      <c r="A1730">
+        <v>1727</v>
+      </c>
+      <c r="B1730">
+        <v>403829</v>
+      </c>
+      <c r="C1730" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1730" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E1730" t="s">
+        <v>1708</v>
+      </c>
+      <c r="F1730" t="s">
+        <v>1709</v>
+      </c>
+      <c r="G1730" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1730" t="s">
+        <v>1711</v>
+      </c>
+      <c r="I1730" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1730">
+        <v>1</v>
+      </c>
+      <c r="K1730">
+        <v>4629928</v>
+      </c>
+      <c r="L1730">
+        <v>4629928</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:12">
+      <c r="A1731">
+        <v>1728</v>
+      </c>
+      <c r="B1731">
+        <v>403829</v>
+      </c>
+      <c r="C1731" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1731" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E1731" t="s">
+        <v>1708</v>
+      </c>
+      <c r="F1731" t="s">
+        <v>1709</v>
+      </c>
+      <c r="G1731" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1731" t="s">
+        <v>181</v>
+      </c>
+      <c r="I1731" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1731">
+        <v>1</v>
+      </c>
+      <c r="K1731">
+        <v>8951000</v>
+      </c>
+      <c r="L1731">
+        <v>8951000</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:12">
+      <c r="A1732">
+        <v>1729</v>
+      </c>
+      <c r="B1732">
+        <v>403829</v>
+      </c>
+      <c r="C1732" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1732" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E1732" t="s">
+        <v>1708</v>
+      </c>
+      <c r="F1732" t="s">
+        <v>1709</v>
+      </c>
+      <c r="G1732" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1732" t="s">
+        <v>116</v>
+      </c>
+      <c r="I1732" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1732">
+        <v>1</v>
+      </c>
+      <c r="K1732">
+        <v>1946000</v>
+      </c>
+      <c r="L1732">
+        <v>1946000</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:12">
+      <c r="A1733">
+        <v>1730</v>
+      </c>
+      <c r="B1733">
+        <v>403829</v>
+      </c>
+      <c r="C1733" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1733" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E1733" t="s">
+        <v>1708</v>
+      </c>
+      <c r="F1733" t="s">
+        <v>1709</v>
+      </c>
+      <c r="G1733" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1733" t="s">
+        <v>1378</v>
+      </c>
+      <c r="I1733" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1733">
+        <v>1</v>
+      </c>
+      <c r="K1733">
+        <v>937928</v>
+      </c>
+      <c r="L1733">
+        <v>937928</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:12">
+      <c r="A1734">
+        <v>1731</v>
+      </c>
+      <c r="B1734">
+        <v>403829</v>
+      </c>
+      <c r="C1734" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1734" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E1734" t="s">
+        <v>1708</v>
+      </c>
+      <c r="F1734" t="s">
+        <v>1709</v>
+      </c>
+      <c r="G1734" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1734" t="s">
+        <v>208</v>
+      </c>
+      <c r="I1734" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1734">
+        <v>1</v>
+      </c>
+      <c r="K1734">
+        <v>509000</v>
+      </c>
+      <c r="L1734">
+        <v>509000</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:12">
+      <c r="A1735">
+        <v>1732</v>
+      </c>
+      <c r="B1735">
+        <v>403829</v>
+      </c>
+      <c r="C1735" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1735" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E1735" t="s">
+        <v>1708</v>
+      </c>
+      <c r="F1735" t="s">
+        <v>1709</v>
+      </c>
+      <c r="G1735" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1735" t="s">
+        <v>186</v>
+      </c>
+      <c r="I1735" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1735">
+        <v>1</v>
+      </c>
+      <c r="K1735">
+        <v>2520000</v>
+      </c>
+      <c r="L1735">
+        <v>2520000</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:12">
+      <c r="A1736">
+        <v>1733</v>
+      </c>
+      <c r="B1736">
+        <v>403829</v>
+      </c>
+      <c r="C1736" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1736" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E1736" t="s">
+        <v>1708</v>
+      </c>
+      <c r="F1736" t="s">
+        <v>1709</v>
+      </c>
+      <c r="G1736" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1736" t="s">
+        <v>187</v>
+      </c>
+      <c r="I1736" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1736">
+        <v>1</v>
+      </c>
+      <c r="K1736">
+        <v>182090</v>
+      </c>
+      <c r="L1736">
+        <v>182090</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:12">
+      <c r="A1737">
+        <v>1734</v>
+      </c>
+      <c r="B1737">
+        <v>403829</v>
+      </c>
+      <c r="C1737" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1737" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E1737" t="s">
+        <v>1708</v>
+      </c>
+      <c r="F1737" t="s">
+        <v>1709</v>
+      </c>
+      <c r="G1737" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1737" t="s">
+        <v>209</v>
+      </c>
+      <c r="I1737" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1737">
+        <v>1</v>
+      </c>
+      <c r="K1737">
+        <v>104700</v>
+      </c>
+      <c r="L1737">
+        <v>104700</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:12">
+      <c r="A1738">
+        <v>1735</v>
+      </c>
+      <c r="B1738">
+        <v>403829</v>
+      </c>
+      <c r="C1738" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1738" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E1738" t="s">
+        <v>1708</v>
+      </c>
+      <c r="F1738" t="s">
+        <v>1709</v>
+      </c>
+      <c r="G1738" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1738" t="s">
+        <v>188</v>
+      </c>
+      <c r="I1738" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1738">
+        <v>1</v>
+      </c>
+      <c r="K1738">
+        <v>300000</v>
+      </c>
+      <c r="L1738">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:12">
+      <c r="A1739">
+        <v>1736</v>
+      </c>
+      <c r="B1739">
+        <v>403829</v>
+      </c>
+      <c r="C1739" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1739" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E1739" t="s">
+        <v>1708</v>
+      </c>
+      <c r="F1739" t="s">
+        <v>1709</v>
+      </c>
+      <c r="G1739" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1739" t="s">
+        <v>189</v>
+      </c>
+      <c r="I1739" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1739">
+        <v>1</v>
+      </c>
+      <c r="K1739">
+        <v>94643</v>
+      </c>
+      <c r="L1739">
+        <v>94643</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:12">
+      <c r="A1740">
+        <v>1737</v>
+      </c>
+      <c r="B1740">
+        <v>403829</v>
+      </c>
+      <c r="C1740" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1740" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E1740" t="s">
+        <v>1708</v>
+      </c>
+      <c r="F1740" t="s">
+        <v>1709</v>
+      </c>
+      <c r="G1740" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1740" t="s">
+        <v>191</v>
+      </c>
+      <c r="I1740" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1740">
+        <v>1</v>
+      </c>
+      <c r="K1740">
+        <v>2547512</v>
+      </c>
+      <c r="L1740">
+        <v>2547512</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:12">
+      <c r="A1741">
+        <v>1738</v>
+      </c>
+      <c r="B1741">
+        <v>403829</v>
+      </c>
+      <c r="C1741" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1741" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E1741" t="s">
+        <v>1708</v>
+      </c>
+      <c r="F1741" t="s">
+        <v>1709</v>
+      </c>
+      <c r="G1741" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1741" t="s">
+        <v>1712</v>
+      </c>
+      <c r="I1741" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1741">
+        <v>1</v>
+      </c>
+      <c r="K1741">
+        <v>7889000</v>
+      </c>
+      <c r="L1741">
+        <v>7889000</v>
+      </c>
+    </row>
+    <row r="1742" spans="1:12">
+      <c r="A1742">
+        <v>1739</v>
+      </c>
+      <c r="B1742">
+        <v>403829</v>
+      </c>
+      <c r="C1742" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1742" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1742" t="s">
+        <v>1713</v>
+      </c>
+      <c r="F1742" t="s">
+        <v>1714</v>
+      </c>
+      <c r="G1742" t="s">
+        <v>1715</v>
+      </c>
+      <c r="H1742" t="s">
+        <v>1716</v>
+      </c>
+      <c r="I1742" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1742">
+        <v>1</v>
+      </c>
+      <c r="K1742">
+        <v>18200000</v>
+      </c>
+      <c r="L1742">
+        <v>18200000</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:12">
+      <c r="A1743">
+        <v>1740</v>
+      </c>
+      <c r="B1743">
+        <v>403829</v>
+      </c>
+      <c r="C1743" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1743" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1743" t="s">
+        <v>1717</v>
+      </c>
+      <c r="F1743" t="s">
+        <v>1718</v>
+      </c>
+      <c r="G1743" t="s">
+        <v>1719</v>
+      </c>
+      <c r="H1743" t="s">
+        <v>1716</v>
+      </c>
+      <c r="I1743" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1743">
+        <v>1</v>
+      </c>
+      <c r="K1743">
+        <v>5200000</v>
+      </c>
+      <c r="L1743">
+        <v>5200000</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:12">
+      <c r="A1744">
+        <v>1741</v>
+      </c>
+      <c r="B1744">
+        <v>403829</v>
+      </c>
+      <c r="C1744" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1744" t="s">
+        <v>1720</v>
+      </c>
+      <c r="E1744" t="s">
+        <v>1721</v>
+      </c>
+      <c r="F1744" t="s">
+        <v>1722</v>
+      </c>
+      <c r="G1744" t="s">
+        <v>1723</v>
+      </c>
+      <c r="H1744" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1744" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1744">
+        <v>1</v>
+      </c>
+      <c r="K1744">
         <v>851000</v>
       </c>
-      <c r="L1670">
+      <c r="L1744">
         <v>851000</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:12">
+      <c r="A1745">
+        <v>1742</v>
+      </c>
+      <c r="B1745">
+        <v>403829</v>
+      </c>
+      <c r="C1745" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1745" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1745" t="s">
+        <v>1724</v>
+      </c>
+      <c r="F1745" t="s">
+        <v>1725</v>
+      </c>
+      <c r="G1745" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1745" t="s">
+        <v>173</v>
+      </c>
+      <c r="I1745" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1745">
+        <v>1</v>
+      </c>
+      <c r="K1745">
+        <v>2146140</v>
+      </c>
+      <c r="L1745">
+        <v>2146140</v>
+      </c>
+    </row>
+    <row r="1746" spans="1:12">
+      <c r="A1746">
+        <v>1743</v>
+      </c>
+      <c r="B1746">
+        <v>403829</v>
+      </c>
+      <c r="C1746" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1746" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1746" t="s">
+        <v>1724</v>
+      </c>
+      <c r="F1746" t="s">
+        <v>1725</v>
+      </c>
+      <c r="G1746" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1746" t="s">
+        <v>175</v>
+      </c>
+      <c r="I1746" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1746">
+        <v>1</v>
+      </c>
+      <c r="K1746">
+        <v>6195000</v>
+      </c>
+      <c r="L1746">
+        <v>6195000</v>
+      </c>
+    </row>
+    <row r="1747" spans="1:12">
+      <c r="A1747">
+        <v>1744</v>
+      </c>
+      <c r="B1747">
+        <v>403829</v>
+      </c>
+      <c r="C1747" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1747" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1747" t="s">
+        <v>1724</v>
+      </c>
+      <c r="F1747" t="s">
+        <v>1725</v>
+      </c>
+      <c r="G1747" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1747" t="s">
+        <v>176</v>
+      </c>
+      <c r="I1747" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1747">
+        <v>1</v>
+      </c>
+      <c r="K1747">
+        <v>15125000</v>
+      </c>
+      <c r="L1747">
+        <v>15125000</v>
+      </c>
+    </row>
+    <row r="1748" spans="1:12">
+      <c r="A1748">
+        <v>1745</v>
+      </c>
+      <c r="B1748">
+        <v>403829</v>
+      </c>
+      <c r="C1748" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1748" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1748" t="s">
+        <v>1724</v>
+      </c>
+      <c r="F1748" t="s">
+        <v>1725</v>
+      </c>
+      <c r="G1748" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1748" t="s">
+        <v>1040</v>
+      </c>
+      <c r="I1748" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1748">
+        <v>1</v>
+      </c>
+      <c r="K1748">
+        <v>9907500</v>
+      </c>
+      <c r="L1748">
+        <v>9907500</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:12">
+      <c r="A1749">
+        <v>1746</v>
+      </c>
+      <c r="B1749">
+        <v>403829</v>
+      </c>
+      <c r="C1749" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1749" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1749" t="s">
+        <v>1724</v>
+      </c>
+      <c r="F1749" t="s">
+        <v>1725</v>
+      </c>
+      <c r="G1749" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1749" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1749" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1749">
+        <v>1</v>
+      </c>
+      <c r="K1749">
+        <v>611800</v>
+      </c>
+      <c r="L1749">
+        <v>611800</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:12">
+      <c r="A1750">
+        <v>1747</v>
+      </c>
+      <c r="B1750">
+        <v>403829</v>
+      </c>
+      <c r="C1750" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1750" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1750" t="s">
+        <v>1724</v>
+      </c>
+      <c r="F1750" t="s">
+        <v>1725</v>
+      </c>
+      <c r="G1750" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1750" t="s">
+        <v>1726</v>
+      </c>
+      <c r="I1750" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1750">
+        <v>1</v>
+      </c>
+      <c r="K1750">
+        <v>5413000</v>
+      </c>
+      <c r="L1750">
+        <v>5413000</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:12">
+      <c r="A1751">
+        <v>1748</v>
+      </c>
+      <c r="B1751">
+        <v>403829</v>
+      </c>
+      <c r="C1751" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1751" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1751" t="s">
+        <v>1724</v>
+      </c>
+      <c r="F1751" t="s">
+        <v>1725</v>
+      </c>
+      <c r="G1751" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1751" t="s">
+        <v>1378</v>
+      </c>
+      <c r="I1751" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1751">
+        <v>1</v>
+      </c>
+      <c r="K1751">
+        <v>1200000</v>
+      </c>
+      <c r="L1751">
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:12">
+      <c r="A1752">
+        <v>1749</v>
+      </c>
+      <c r="B1752">
+        <v>403829</v>
+      </c>
+      <c r="C1752" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1752" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1752" t="s">
+        <v>1724</v>
+      </c>
+      <c r="F1752" t="s">
+        <v>1725</v>
+      </c>
+      <c r="G1752" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1752" t="s">
+        <v>208</v>
+      </c>
+      <c r="I1752" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1752">
+        <v>1</v>
+      </c>
+      <c r="K1752">
+        <v>1804500</v>
+      </c>
+      <c r="L1752">
+        <v>1804500</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:12">
+      <c r="A1753">
+        <v>1750</v>
+      </c>
+      <c r="B1753">
+        <v>403829</v>
+      </c>
+      <c r="C1753" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1753" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1753" t="s">
+        <v>1724</v>
+      </c>
+      <c r="F1753" t="s">
+        <v>1725</v>
+      </c>
+      <c r="G1753" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1753" t="s">
+        <v>186</v>
+      </c>
+      <c r="I1753" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1753">
+        <v>1</v>
+      </c>
+      <c r="K1753">
+        <v>1205000</v>
+      </c>
+      <c r="L1753">
+        <v>1205000</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:12">
+      <c r="A1754">
+        <v>1751</v>
+      </c>
+      <c r="B1754">
+        <v>403829</v>
+      </c>
+      <c r="C1754" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1754" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1754" t="s">
+        <v>1724</v>
+      </c>
+      <c r="F1754" t="s">
+        <v>1725</v>
+      </c>
+      <c r="G1754" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1754" t="s">
+        <v>187</v>
+      </c>
+      <c r="I1754" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1754">
+        <v>1</v>
+      </c>
+      <c r="K1754">
+        <v>736000</v>
+      </c>
+      <c r="L1754">
+        <v>736000</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:12">
+      <c r="A1755">
+        <v>1752</v>
+      </c>
+      <c r="B1755">
+        <v>403829</v>
+      </c>
+      <c r="C1755" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1755" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1755" t="s">
+        <v>1724</v>
+      </c>
+      <c r="F1755" t="s">
+        <v>1725</v>
+      </c>
+      <c r="G1755" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1755" t="s">
+        <v>188</v>
+      </c>
+      <c r="I1755" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1755">
+        <v>1</v>
+      </c>
+      <c r="K1755">
+        <v>319926</v>
+      </c>
+      <c r="L1755">
+        <v>319926</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:12">
+      <c r="A1756">
+        <v>1753</v>
+      </c>
+      <c r="B1756">
+        <v>403829</v>
+      </c>
+      <c r="C1756" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1756" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1756" t="s">
+        <v>1724</v>
+      </c>
+      <c r="F1756" t="s">
+        <v>1725</v>
+      </c>
+      <c r="G1756" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1756" t="s">
+        <v>189</v>
+      </c>
+      <c r="I1756" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1756">
+        <v>1</v>
+      </c>
+      <c r="K1756">
+        <v>131028</v>
+      </c>
+      <c r="L1756">
+        <v>131028</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:12">
+      <c r="A1757">
+        <v>1754</v>
+      </c>
+      <c r="B1757">
+        <v>403829</v>
+      </c>
+      <c r="C1757" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1757" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1757" t="s">
+        <v>1724</v>
+      </c>
+      <c r="F1757" t="s">
+        <v>1725</v>
+      </c>
+      <c r="G1757" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1757" t="s">
+        <v>1041</v>
+      </c>
+      <c r="I1757" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1757">
+        <v>1</v>
+      </c>
+      <c r="K1757">
+        <v>19135000</v>
+      </c>
+      <c r="L1757">
+        <v>19135000</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:12">
+      <c r="A1758">
+        <v>1755</v>
+      </c>
+      <c r="B1758">
+        <v>403829</v>
+      </c>
+      <c r="C1758" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1758" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1758" t="s">
+        <v>1727</v>
+      </c>
+      <c r="F1758" t="s">
+        <v>1728</v>
+      </c>
+      <c r="G1758" t="s">
+        <v>1729</v>
+      </c>
+      <c r="H1758" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1758" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1758">
+        <v>1</v>
+      </c>
+      <c r="K1758">
+        <v>143953710</v>
+      </c>
+      <c r="L1758">
+        <v>143953710</v>
       </c>
     </row>
   </sheetData>

--- a/Database/MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D.xlsx
+++ b/Database/MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1730">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1783">
   <si>
     <t>MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D</t>
   </si>
@@ -5198,6 +5198,27 @@
     <t>'403829.023.523111.03212WA.2378EBA.A000000001.00000.2.0252.2.000000.000000.994.002.DC.000303</t>
   </si>
   <si>
+    <t>2025-12-02</t>
+  </si>
+  <si>
+    <t>'00504T</t>
+  </si>
+  <si>
+    <t>'259991311220447</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja barang berupa Honor Pengelola Keuangan Bulan Nopember 2025 untuk 8 Pegawai sesuai Sk No B.1/BRPBATPP/KU.110/I/2025 tanggal 2 Januari 2025</t>
+  </si>
+  <si>
+    <t>'00505T</t>
+  </si>
+  <si>
+    <t>'259991311220504</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja barang berupa Honor Pengelola Keuangan Bulan Desember 2025 untuk 8 Pegawai sesuai Sk No B.1/BRPBATPP/KU.110/I/2025 tanggal 2 Januari 2025</t>
+  </si>
+  <si>
     <t>'00506T</t>
   </si>
   <si>
@@ -5205,6 +5226,144 @@
   </si>
   <si>
     <t>Pembayaran tunjangan kinerja bulan Desember tahun 2025 untuk 35 Pegawai</t>
+  </si>
+  <si>
+    <t>'00507T</t>
+  </si>
+  <si>
+    <t>'259991305247939</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Desember tahun 2025 untuk 5 Pegawai</t>
+  </si>
+  <si>
+    <t>'00508T</t>
+  </si>
+  <si>
+    <t>'259991330435670</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Desember Tahun 2025 untuk 2 Pegawai.sesuai Sk No.  9 Tahun 2025 Tanggal 6 Januari 2025</t>
+  </si>
+  <si>
+    <t>'00509T</t>
+  </si>
+  <si>
+    <t>'259991311235475</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang Berupa Honor PPNPN Bulan Desember Tahun 2025 untuk 7 Pegawai.sesuai SK No. 9 Tahun 2025 Tanggal 6 Januari 2025</t>
+  </si>
+  <si>
+    <t>2025-12-04</t>
+  </si>
+  <si>
+    <t>'00510T</t>
+  </si>
+  <si>
+    <t>'259991311256736</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang termin ke 11 Sesuai SPK No.2/BRPBATPP/PPK/PL.400/I/2025 Tanggal 2 Januari 2025 dan BAPP No.B.710/BRPBATPP/PPK/PL.400/XI/2025 Tanggal 30 Nopember 2025</t>
+  </si>
+  <si>
+    <t>'00511T</t>
+  </si>
+  <si>
+    <t>'259991320722629</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang Sesuai Kwitansi No. 07/PHRA/KW/XI/2025 Tanggal 17 November 2025 berupa Pemeliharaan Kantor Sempur</t>
+  </si>
+  <si>
+    <t>'00513T</t>
+  </si>
+  <si>
+    <t>'259991311278614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Nopember 2025 untuk 50 Pegawai </t>
+  </si>
+  <si>
+    <t>'00514T</t>
+  </si>
+  <si>
+    <t>'259991330447855</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Nopember 2025 untuk 63 pegawai</t>
+  </si>
+  <si>
+    <t>'00515T</t>
+  </si>
+  <si>
+    <t>'259991311278615</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Nopember 2025 untuk 34 Pegawai</t>
+  </si>
+  <si>
+    <t>'00516T</t>
+  </si>
+  <si>
+    <t>'259991330447857</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Nopember 2025 untuk 23 Pegawai</t>
+  </si>
+  <si>
+    <t>'00517T</t>
+  </si>
+  <si>
+    <t>'259991305260983</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Nopember 2025 untuk 167 Pegawai</t>
+  </si>
+  <si>
+    <t>'00518T</t>
+  </si>
+  <si>
+    <t>'259991305260982</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan PPPK Bulan Nopember 2025 untuk 37 Pegawai</t>
+  </si>
+  <si>
+    <t>'00519T</t>
+  </si>
+  <si>
+    <t>'259991311278613</t>
+  </si>
+  <si>
+    <t>pembayaran Belanja Pegawai berupa Uang Makan Bulan Nopember 2025 untuk 34 Pegawai</t>
+  </si>
+  <si>
+    <t>'00520T</t>
+  </si>
+  <si>
+    <t>'259991330447856</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Nopember 2025 untuk 167 pegawai</t>
+  </si>
+  <si>
+    <t>'00521T</t>
+  </si>
+  <si>
+    <t>'259991305261056</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Nopember 2025 untuk 5 Pegawai</t>
+  </si>
+  <si>
+    <t>'00522T</t>
+  </si>
+  <si>
+    <t>'259991311278612</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Nopember 2025 untuk 129 Pegawai</t>
   </si>
 </sst>
 </file>
@@ -5547,7 +5706,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:L1758"/>
+  <dimension ref="A1:L1798"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -72257,31 +72416,1551 @@
         <v>13</v>
       </c>
       <c r="D1758" t="s">
+        <v>1727</v>
+      </c>
+      <c r="E1758" t="s">
+        <v>1728</v>
+      </c>
+      <c r="F1758" t="s">
+        <v>1729</v>
+      </c>
+      <c r="G1758" t="s">
+        <v>1730</v>
+      </c>
+      <c r="H1758" t="s">
+        <v>154</v>
+      </c>
+      <c r="I1758" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1758">
+        <v>1</v>
+      </c>
+      <c r="K1758">
+        <v>2550000</v>
+      </c>
+      <c r="L1758">
+        <v>2550000</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:12">
+      <c r="A1759">
+        <v>1756</v>
+      </c>
+      <c r="B1759">
+        <v>403829</v>
+      </c>
+      <c r="C1759" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1759" t="s">
+        <v>1727</v>
+      </c>
+      <c r="E1759" t="s">
+        <v>1728</v>
+      </c>
+      <c r="F1759" t="s">
+        <v>1729</v>
+      </c>
+      <c r="G1759" t="s">
+        <v>1730</v>
+      </c>
+      <c r="H1759" t="s">
+        <v>155</v>
+      </c>
+      <c r="I1759" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1759">
+        <v>1</v>
+      </c>
+      <c r="K1759">
+        <v>2480000</v>
+      </c>
+      <c r="L1759">
+        <v>2480000</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:12">
+      <c r="A1760">
+        <v>1757</v>
+      </c>
+      <c r="B1760">
+        <v>403829</v>
+      </c>
+      <c r="C1760" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1760" t="s">
+        <v>1727</v>
+      </c>
+      <c r="E1760" t="s">
+        <v>1728</v>
+      </c>
+      <c r="F1760" t="s">
+        <v>1729</v>
+      </c>
+      <c r="G1760" t="s">
+        <v>1730</v>
+      </c>
+      <c r="H1760" t="s">
+        <v>156</v>
+      </c>
+      <c r="I1760" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1760">
+        <v>1</v>
+      </c>
+      <c r="K1760">
+        <v>1230000</v>
+      </c>
+      <c r="L1760">
+        <v>1230000</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:12">
+      <c r="A1761">
+        <v>1758</v>
+      </c>
+      <c r="B1761">
+        <v>403829</v>
+      </c>
+      <c r="C1761" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1761" t="s">
+        <v>1727</v>
+      </c>
+      <c r="E1761" t="s">
+        <v>1728</v>
+      </c>
+      <c r="F1761" t="s">
+        <v>1729</v>
+      </c>
+      <c r="G1761" t="s">
+        <v>1730</v>
+      </c>
+      <c r="H1761" t="s">
+        <v>157</v>
+      </c>
+      <c r="I1761" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1761">
+        <v>1</v>
+      </c>
+      <c r="K1761">
+        <v>1070000</v>
+      </c>
+      <c r="L1761">
+        <v>1070000</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:12">
+      <c r="A1762">
+        <v>1759</v>
+      </c>
+      <c r="B1762">
+        <v>403829</v>
+      </c>
+      <c r="C1762" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1762" t="s">
+        <v>1727</v>
+      </c>
+      <c r="E1762" t="s">
+        <v>1728</v>
+      </c>
+      <c r="F1762" t="s">
+        <v>1729</v>
+      </c>
+      <c r="G1762" t="s">
+        <v>1730</v>
+      </c>
+      <c r="H1762" t="s">
+        <v>158</v>
+      </c>
+      <c r="I1762" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1762">
+        <v>1</v>
+      </c>
+      <c r="K1762">
+        <v>2400000</v>
+      </c>
+      <c r="L1762">
+        <v>2400000</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:12">
+      <c r="A1763">
+        <v>1760</v>
+      </c>
+      <c r="B1763">
+        <v>403829</v>
+      </c>
+      <c r="C1763" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1763" t="s">
+        <v>1727</v>
+      </c>
+      <c r="E1763" t="s">
+        <v>1728</v>
+      </c>
+      <c r="F1763" t="s">
+        <v>1729</v>
+      </c>
+      <c r="G1763" t="s">
+        <v>1730</v>
+      </c>
+      <c r="H1763" t="s">
+        <v>159</v>
+      </c>
+      <c r="I1763" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1763">
+        <v>1</v>
+      </c>
+      <c r="K1763">
+        <v>180000</v>
+      </c>
+      <c r="L1763">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:12">
+      <c r="A1764">
+        <v>1761</v>
+      </c>
+      <c r="B1764">
+        <v>403829</v>
+      </c>
+      <c r="C1764" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1764" t="s">
+        <v>1727</v>
+      </c>
+      <c r="E1764" t="s">
+        <v>1731</v>
+      </c>
+      <c r="F1764" t="s">
+        <v>1732</v>
+      </c>
+      <c r="G1764" t="s">
+        <v>1733</v>
+      </c>
+      <c r="H1764" t="s">
+        <v>154</v>
+      </c>
+      <c r="I1764" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1764">
+        <v>1</v>
+      </c>
+      <c r="K1764">
+        <v>2550000</v>
+      </c>
+      <c r="L1764">
+        <v>2550000</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:12">
+      <c r="A1765">
+        <v>1762</v>
+      </c>
+      <c r="B1765">
+        <v>403829</v>
+      </c>
+      <c r="C1765" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1765" t="s">
+        <v>1727</v>
+      </c>
+      <c r="E1765" t="s">
+        <v>1731</v>
+      </c>
+      <c r="F1765" t="s">
+        <v>1732</v>
+      </c>
+      <c r="G1765" t="s">
+        <v>1733</v>
+      </c>
+      <c r="H1765" t="s">
+        <v>155</v>
+      </c>
+      <c r="I1765" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1765">
+        <v>1</v>
+      </c>
+      <c r="K1765">
+        <v>2480000</v>
+      </c>
+      <c r="L1765">
+        <v>2480000</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:12">
+      <c r="A1766">
+        <v>1763</v>
+      </c>
+      <c r="B1766">
+        <v>403829</v>
+      </c>
+      <c r="C1766" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1766" t="s">
+        <v>1727</v>
+      </c>
+      <c r="E1766" t="s">
+        <v>1731</v>
+      </c>
+      <c r="F1766" t="s">
+        <v>1732</v>
+      </c>
+      <c r="G1766" t="s">
+        <v>1733</v>
+      </c>
+      <c r="H1766" t="s">
+        <v>156</v>
+      </c>
+      <c r="I1766" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1766">
+        <v>1</v>
+      </c>
+      <c r="K1766">
+        <v>1230000</v>
+      </c>
+      <c r="L1766">
+        <v>1230000</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:12">
+      <c r="A1767">
+        <v>1764</v>
+      </c>
+      <c r="B1767">
+        <v>403829</v>
+      </c>
+      <c r="C1767" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1767" t="s">
+        <v>1727</v>
+      </c>
+      <c r="E1767" t="s">
+        <v>1731</v>
+      </c>
+      <c r="F1767" t="s">
+        <v>1732</v>
+      </c>
+      <c r="G1767" t="s">
+        <v>1733</v>
+      </c>
+      <c r="H1767" t="s">
+        <v>157</v>
+      </c>
+      <c r="I1767" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1767">
+        <v>1</v>
+      </c>
+      <c r="K1767">
+        <v>1070000</v>
+      </c>
+      <c r="L1767">
+        <v>1070000</v>
+      </c>
+    </row>
+    <row r="1768" spans="1:12">
+      <c r="A1768">
+        <v>1765</v>
+      </c>
+      <c r="B1768">
+        <v>403829</v>
+      </c>
+      <c r="C1768" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1768" t="s">
+        <v>1727</v>
+      </c>
+      <c r="E1768" t="s">
+        <v>1731</v>
+      </c>
+      <c r="F1768" t="s">
+        <v>1732</v>
+      </c>
+      <c r="G1768" t="s">
+        <v>1733</v>
+      </c>
+      <c r="H1768" t="s">
+        <v>158</v>
+      </c>
+      <c r="I1768" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1768">
+        <v>1</v>
+      </c>
+      <c r="K1768">
+        <v>2400000</v>
+      </c>
+      <c r="L1768">
+        <v>2400000</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:12">
+      <c r="A1769">
+        <v>1766</v>
+      </c>
+      <c r="B1769">
+        <v>403829</v>
+      </c>
+      <c r="C1769" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1769" t="s">
+        <v>1727</v>
+      </c>
+      <c r="E1769" t="s">
+        <v>1731</v>
+      </c>
+      <c r="F1769" t="s">
+        <v>1732</v>
+      </c>
+      <c r="G1769" t="s">
+        <v>1733</v>
+      </c>
+      <c r="H1769" t="s">
+        <v>159</v>
+      </c>
+      <c r="I1769" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1769">
+        <v>1</v>
+      </c>
+      <c r="K1769">
+        <v>180000</v>
+      </c>
+      <c r="L1769">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="1770" spans="1:12">
+      <c r="A1770">
+        <v>1767</v>
+      </c>
+      <c r="B1770">
+        <v>403829</v>
+      </c>
+      <c r="C1770" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1770" t="s">
         <v>1561</v>
       </c>
-      <c r="E1758" t="s">
+      <c r="E1770" t="s">
+        <v>1734</v>
+      </c>
+      <c r="F1770" t="s">
+        <v>1735</v>
+      </c>
+      <c r="G1770" t="s">
+        <v>1736</v>
+      </c>
+      <c r="H1770" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1770" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1770">
+        <v>1</v>
+      </c>
+      <c r="K1770">
+        <v>143953710</v>
+      </c>
+      <c r="L1770">
+        <v>143953710</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:12">
+      <c r="A1771">
+        <v>1768</v>
+      </c>
+      <c r="B1771">
+        <v>403829</v>
+      </c>
+      <c r="C1771" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1771" t="s">
+        <v>1561</v>
+      </c>
+      <c r="E1771" t="s">
+        <v>1737</v>
+      </c>
+      <c r="F1771" t="s">
+        <v>1738</v>
+      </c>
+      <c r="G1771" t="s">
+        <v>1739</v>
+      </c>
+      <c r="H1771" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1771" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1771">
+        <v>1</v>
+      </c>
+      <c r="K1771">
+        <v>24871599</v>
+      </c>
+      <c r="L1771">
+        <v>24871599</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:12">
+      <c r="A1772">
+        <v>1769</v>
+      </c>
+      <c r="B1772">
+        <v>403829</v>
+      </c>
+      <c r="C1772" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1772" t="s">
         <v>1727</v>
       </c>
-      <c r="F1758" t="s">
-        <v>1728</v>
-      </c>
-      <c r="G1758" t="s">
-        <v>1729</v>
-      </c>
-      <c r="H1758" t="s">
-        <v>133</v>
-      </c>
-      <c r="I1758" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1758">
-        <v>1</v>
-      </c>
-      <c r="K1758">
-        <v>143953710</v>
-      </c>
-      <c r="L1758">
-        <v>143953710</v>
+      <c r="E1772" t="s">
+        <v>1740</v>
+      </c>
+      <c r="F1772" t="s">
+        <v>1741</v>
+      </c>
+      <c r="G1772" t="s">
+        <v>1742</v>
+      </c>
+      <c r="H1772" t="s">
+        <v>1584</v>
+      </c>
+      <c r="I1772" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1772">
+        <v>1</v>
+      </c>
+      <c r="K1772">
+        <v>5200000</v>
+      </c>
+      <c r="L1772">
+        <v>5200000</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:12">
+      <c r="A1773">
+        <v>1770</v>
+      </c>
+      <c r="B1773">
+        <v>403829</v>
+      </c>
+      <c r="C1773" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1773" t="s">
+        <v>1727</v>
+      </c>
+      <c r="E1773" t="s">
+        <v>1743</v>
+      </c>
+      <c r="F1773" t="s">
+        <v>1744</v>
+      </c>
+      <c r="G1773" t="s">
+        <v>1745</v>
+      </c>
+      <c r="H1773" t="s">
+        <v>1584</v>
+      </c>
+      <c r="I1773" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1773">
+        <v>1</v>
+      </c>
+      <c r="K1773">
+        <v>18200000</v>
+      </c>
+      <c r="L1773">
+        <v>18200000</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:12">
+      <c r="A1774">
+        <v>1771</v>
+      </c>
+      <c r="B1774">
+        <v>403829</v>
+      </c>
+      <c r="C1774" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1774" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E1774" t="s">
+        <v>1747</v>
+      </c>
+      <c r="F1774" t="s">
+        <v>1748</v>
+      </c>
+      <c r="G1774" t="s">
+        <v>1749</v>
+      </c>
+      <c r="H1774" t="s">
+        <v>203</v>
+      </c>
+      <c r="I1774" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1774">
+        <v>1</v>
+      </c>
+      <c r="K1774">
+        <v>184486500</v>
+      </c>
+      <c r="L1774">
+        <v>184486500</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:12">
+      <c r="A1775">
+        <v>1772</v>
+      </c>
+      <c r="B1775">
+        <v>403829</v>
+      </c>
+      <c r="C1775" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1775" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E1775" t="s">
+        <v>1750</v>
+      </c>
+      <c r="F1775" t="s">
+        <v>1751</v>
+      </c>
+      <c r="G1775" t="s">
+        <v>1752</v>
+      </c>
+      <c r="H1775" t="s">
+        <v>116</v>
+      </c>
+      <c r="I1775" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1775">
+        <v>1</v>
+      </c>
+      <c r="K1775">
+        <v>25076000</v>
+      </c>
+      <c r="L1775">
+        <v>25076000</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:12">
+      <c r="A1776">
+        <v>1773</v>
+      </c>
+      <c r="B1776">
+        <v>403829</v>
+      </c>
+      <c r="C1776" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1776" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E1776" t="s">
+        <v>1753</v>
+      </c>
+      <c r="F1776" t="s">
+        <v>1754</v>
+      </c>
+      <c r="G1776" t="s">
+        <v>1755</v>
+      </c>
+      <c r="H1776" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1776" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1776">
+        <v>1</v>
+      </c>
+      <c r="K1776">
+        <v>6860000</v>
+      </c>
+      <c r="L1776">
+        <v>6860000</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:12">
+      <c r="A1777">
+        <v>1774</v>
+      </c>
+      <c r="B1777">
+        <v>403829</v>
+      </c>
+      <c r="C1777" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1777" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E1777" t="s">
+        <v>1753</v>
+      </c>
+      <c r="F1777" t="s">
+        <v>1754</v>
+      </c>
+      <c r="G1777" t="s">
+        <v>1755</v>
+      </c>
+      <c r="H1777" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1777" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1777">
+        <v>1</v>
+      </c>
+      <c r="K1777">
+        <v>29415000</v>
+      </c>
+      <c r="L1777">
+        <v>29415000</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:12">
+      <c r="A1778">
+        <v>1775</v>
+      </c>
+      <c r="B1778">
+        <v>403829</v>
+      </c>
+      <c r="C1778" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1778" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E1778" t="s">
+        <v>1756</v>
+      </c>
+      <c r="F1778" t="s">
+        <v>1757</v>
+      </c>
+      <c r="G1778" t="s">
+        <v>1758</v>
+      </c>
+      <c r="H1778" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1778" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1778">
+        <v>1</v>
+      </c>
+      <c r="K1778">
+        <v>1400000</v>
+      </c>
+      <c r="L1778">
+        <v>1400000</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:12">
+      <c r="A1779">
+        <v>1776</v>
+      </c>
+      <c r="B1779">
+        <v>403829</v>
+      </c>
+      <c r="C1779" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1779" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E1779" t="s">
+        <v>1756</v>
+      </c>
+      <c r="F1779" t="s">
+        <v>1757</v>
+      </c>
+      <c r="G1779" t="s">
+        <v>1758</v>
+      </c>
+      <c r="H1779" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1779" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1779">
+        <v>1</v>
+      </c>
+      <c r="K1779">
+        <v>44696000</v>
+      </c>
+      <c r="L1779">
+        <v>44696000</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:12">
+      <c r="A1780">
+        <v>1777</v>
+      </c>
+      <c r="B1780">
+        <v>403829</v>
+      </c>
+      <c r="C1780" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1780" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E1780" t="s">
+        <v>1759</v>
+      </c>
+      <c r="F1780" t="s">
+        <v>1760</v>
+      </c>
+      <c r="G1780" t="s">
+        <v>1761</v>
+      </c>
+      <c r="H1780" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1780" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1780">
+        <v>1</v>
+      </c>
+      <c r="K1780">
+        <v>2100000</v>
+      </c>
+      <c r="L1780">
+        <v>2100000</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:12">
+      <c r="A1781">
+        <v>1778</v>
+      </c>
+      <c r="B1781">
+        <v>403829</v>
+      </c>
+      <c r="C1781" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1781" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E1781" t="s">
+        <v>1759</v>
+      </c>
+      <c r="F1781" t="s">
+        <v>1760</v>
+      </c>
+      <c r="G1781" t="s">
+        <v>1761</v>
+      </c>
+      <c r="H1781" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1781" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1781">
+        <v>1</v>
+      </c>
+      <c r="K1781">
+        <v>22829000</v>
+      </c>
+      <c r="L1781">
+        <v>22829000</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:12">
+      <c r="A1782">
+        <v>1779</v>
+      </c>
+      <c r="B1782">
+        <v>403829</v>
+      </c>
+      <c r="C1782" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1782" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E1782" t="s">
+        <v>1762</v>
+      </c>
+      <c r="F1782" t="s">
+        <v>1763</v>
+      </c>
+      <c r="G1782" t="s">
+        <v>1764</v>
+      </c>
+      <c r="H1782" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1782" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1782">
+        <v>1</v>
+      </c>
+      <c r="K1782">
+        <v>2100000</v>
+      </c>
+      <c r="L1782">
+        <v>2100000</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:12">
+      <c r="A1783">
+        <v>1780</v>
+      </c>
+      <c r="B1783">
+        <v>403829</v>
+      </c>
+      <c r="C1783" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1783" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E1783" t="s">
+        <v>1762</v>
+      </c>
+      <c r="F1783" t="s">
+        <v>1763</v>
+      </c>
+      <c r="G1783" t="s">
+        <v>1764</v>
+      </c>
+      <c r="H1783" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1783" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1783">
+        <v>1</v>
+      </c>
+      <c r="K1783">
+        <v>14171000</v>
+      </c>
+      <c r="L1783">
+        <v>14171000</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:12">
+      <c r="A1784">
+        <v>1781</v>
+      </c>
+      <c r="B1784">
+        <v>403829</v>
+      </c>
+      <c r="C1784" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1784" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E1784" t="s">
+        <v>1765</v>
+      </c>
+      <c r="F1784" t="s">
+        <v>1766</v>
+      </c>
+      <c r="G1784" t="s">
+        <v>1767</v>
+      </c>
+      <c r="H1784" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1784" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1784">
+        <v>1</v>
+      </c>
+      <c r="K1784">
+        <v>9800000</v>
+      </c>
+      <c r="L1784">
+        <v>9800000</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:12">
+      <c r="A1785">
+        <v>1782</v>
+      </c>
+      <c r="B1785">
+        <v>403829</v>
+      </c>
+      <c r="C1785" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1785" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E1785" t="s">
+        <v>1765</v>
+      </c>
+      <c r="F1785" t="s">
+        <v>1766</v>
+      </c>
+      <c r="G1785" t="s">
+        <v>1767</v>
+      </c>
+      <c r="H1785" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1785" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1785">
+        <v>1</v>
+      </c>
+      <c r="K1785">
+        <v>111814000</v>
+      </c>
+      <c r="L1785">
+        <v>111814000</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:12">
+      <c r="A1786">
+        <v>1783</v>
+      </c>
+      <c r="B1786">
+        <v>403829</v>
+      </c>
+      <c r="C1786" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1786" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E1786" t="s">
+        <v>1768</v>
+      </c>
+      <c r="F1786" t="s">
+        <v>1769</v>
+      </c>
+      <c r="G1786" t="s">
+        <v>1770</v>
+      </c>
+      <c r="H1786" t="s">
+        <v>1685</v>
+      </c>
+      <c r="I1786" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1786">
+        <v>1</v>
+      </c>
+      <c r="K1786">
+        <v>7700000</v>
+      </c>
+      <c r="L1786">
+        <v>7700000</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:12">
+      <c r="A1787">
+        <v>1784</v>
+      </c>
+      <c r="B1787">
+        <v>403829</v>
+      </c>
+      <c r="C1787" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1787" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E1787" t="s">
+        <v>1768</v>
+      </c>
+      <c r="F1787" t="s">
+        <v>1769</v>
+      </c>
+      <c r="G1787" t="s">
+        <v>1770</v>
+      </c>
+      <c r="H1787" t="s">
+        <v>1686</v>
+      </c>
+      <c r="I1787" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1787">
+        <v>1</v>
+      </c>
+      <c r="K1787">
+        <v>19240000</v>
+      </c>
+      <c r="L1787">
+        <v>19240000</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:12">
+      <c r="A1788">
+        <v>1785</v>
+      </c>
+      <c r="B1788">
+        <v>403829</v>
+      </c>
+      <c r="C1788" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1788" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E1788" t="s">
+        <v>1771</v>
+      </c>
+      <c r="F1788" t="s">
+        <v>1772</v>
+      </c>
+      <c r="G1788" t="s">
+        <v>1773</v>
+      </c>
+      <c r="H1788" t="s">
+        <v>241</v>
+      </c>
+      <c r="I1788" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1788">
+        <v>1</v>
+      </c>
+      <c r="K1788">
+        <v>1400000</v>
+      </c>
+      <c r="L1788">
+        <v>1400000</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:12">
+      <c r="A1789">
+        <v>1786</v>
+      </c>
+      <c r="B1789">
+        <v>403829</v>
+      </c>
+      <c r="C1789" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1789" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E1789" t="s">
+        <v>1771</v>
+      </c>
+      <c r="F1789" t="s">
+        <v>1772</v>
+      </c>
+      <c r="G1789" t="s">
+        <v>1773</v>
+      </c>
+      <c r="H1789" t="s">
+        <v>149</v>
+      </c>
+      <c r="I1789" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1789">
+        <v>1</v>
+      </c>
+      <c r="K1789">
+        <v>21460000</v>
+      </c>
+      <c r="L1789">
+        <v>21460000</v>
+      </c>
+    </row>
+    <row r="1790" spans="1:12">
+      <c r="A1790">
+        <v>1787</v>
+      </c>
+      <c r="B1790">
+        <v>403829</v>
+      </c>
+      <c r="C1790" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1790" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E1790" t="s">
+        <v>1771</v>
+      </c>
+      <c r="F1790" t="s">
+        <v>1772</v>
+      </c>
+      <c r="G1790" t="s">
+        <v>1773</v>
+      </c>
+      <c r="H1790" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1790" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1790">
+        <v>1</v>
+      </c>
+      <c r="K1790">
+        <v>1640000</v>
+      </c>
+      <c r="L1790">
+        <v>1640000</v>
+      </c>
+    </row>
+    <row r="1791" spans="1:12">
+      <c r="A1791">
+        <v>1788</v>
+      </c>
+      <c r="B1791">
+        <v>403829</v>
+      </c>
+      <c r="C1791" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1791" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E1791" t="s">
+        <v>1774</v>
+      </c>
+      <c r="F1791" t="s">
+        <v>1775</v>
+      </c>
+      <c r="G1791" t="s">
+        <v>1776</v>
+      </c>
+      <c r="H1791" t="s">
+        <v>266</v>
+      </c>
+      <c r="I1791" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1791">
+        <v>1</v>
+      </c>
+      <c r="K1791">
+        <v>10395000</v>
+      </c>
+      <c r="L1791">
+        <v>10395000</v>
+      </c>
+    </row>
+    <row r="1792" spans="1:12">
+      <c r="A1792">
+        <v>1789</v>
+      </c>
+      <c r="B1792">
+        <v>403829</v>
+      </c>
+      <c r="C1792" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1792" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E1792" t="s">
+        <v>1774</v>
+      </c>
+      <c r="F1792" t="s">
+        <v>1775</v>
+      </c>
+      <c r="G1792" t="s">
+        <v>1776</v>
+      </c>
+      <c r="H1792" t="s">
+        <v>267</v>
+      </c>
+      <c r="I1792" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1792">
+        <v>1</v>
+      </c>
+      <c r="K1792">
+        <v>95164000</v>
+      </c>
+      <c r="L1792">
+        <v>95164000</v>
+      </c>
+    </row>
+    <row r="1793" spans="1:12">
+      <c r="A1793">
+        <v>1790</v>
+      </c>
+      <c r="B1793">
+        <v>403829</v>
+      </c>
+      <c r="C1793" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1793" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E1793" t="s">
+        <v>1774</v>
+      </c>
+      <c r="F1793" t="s">
+        <v>1775</v>
+      </c>
+      <c r="G1793" t="s">
+        <v>1776</v>
+      </c>
+      <c r="H1793" t="s">
+        <v>268</v>
+      </c>
+      <c r="I1793" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1793">
+        <v>1</v>
+      </c>
+      <c r="K1793">
+        <v>17466000</v>
+      </c>
+      <c r="L1793">
+        <v>17466000</v>
+      </c>
+    </row>
+    <row r="1794" spans="1:12">
+      <c r="A1794">
+        <v>1791</v>
+      </c>
+      <c r="B1794">
+        <v>403829</v>
+      </c>
+      <c r="C1794" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1794" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E1794" t="s">
+        <v>1777</v>
+      </c>
+      <c r="F1794" t="s">
+        <v>1778</v>
+      </c>
+      <c r="G1794" t="s">
+        <v>1779</v>
+      </c>
+      <c r="H1794" t="s">
+        <v>149</v>
+      </c>
+      <c r="I1794" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1794">
+        <v>1</v>
+      </c>
+      <c r="K1794">
+        <v>2183000</v>
+      </c>
+      <c r="L1794">
+        <v>2183000</v>
+      </c>
+    </row>
+    <row r="1795" spans="1:12">
+      <c r="A1795">
+        <v>1792</v>
+      </c>
+      <c r="B1795">
+        <v>403829</v>
+      </c>
+      <c r="C1795" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1795" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E1795" t="s">
+        <v>1777</v>
+      </c>
+      <c r="F1795" t="s">
+        <v>1778</v>
+      </c>
+      <c r="G1795" t="s">
+        <v>1779</v>
+      </c>
+      <c r="H1795" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1795" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1795">
+        <v>1</v>
+      </c>
+      <c r="K1795">
+        <v>1640000</v>
+      </c>
+      <c r="L1795">
+        <v>1640000</v>
+      </c>
+    </row>
+    <row r="1796" spans="1:12">
+      <c r="A1796">
+        <v>1793</v>
+      </c>
+      <c r="B1796">
+        <v>403829</v>
+      </c>
+      <c r="C1796" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1796" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E1796" t="s">
+        <v>1780</v>
+      </c>
+      <c r="F1796" t="s">
+        <v>1781</v>
+      </c>
+      <c r="G1796" t="s">
+        <v>1782</v>
+      </c>
+      <c r="H1796" t="s">
+        <v>266</v>
+      </c>
+      <c r="I1796" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1796">
+        <v>1</v>
+      </c>
+      <c r="K1796">
+        <v>20172000</v>
+      </c>
+      <c r="L1796">
+        <v>20172000</v>
+      </c>
+    </row>
+    <row r="1797" spans="1:12">
+      <c r="A1797">
+        <v>1794</v>
+      </c>
+      <c r="B1797">
+        <v>403829</v>
+      </c>
+      <c r="C1797" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1797" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E1797" t="s">
+        <v>1780</v>
+      </c>
+      <c r="F1797" t="s">
+        <v>1781</v>
+      </c>
+      <c r="G1797" t="s">
+        <v>1782</v>
+      </c>
+      <c r="H1797" t="s">
+        <v>267</v>
+      </c>
+      <c r="I1797" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1797">
+        <v>1</v>
+      </c>
+      <c r="K1797">
+        <v>64195000</v>
+      </c>
+      <c r="L1797">
+        <v>64195000</v>
+      </c>
+    </row>
+    <row r="1798" spans="1:12">
+      <c r="A1798">
+        <v>1795</v>
+      </c>
+      <c r="B1798">
+        <v>403829</v>
+      </c>
+      <c r="C1798" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1798" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E1798" t="s">
+        <v>1780</v>
+      </c>
+      <c r="F1798" t="s">
+        <v>1781</v>
+      </c>
+      <c r="G1798" t="s">
+        <v>1782</v>
+      </c>
+      <c r="H1798" t="s">
+        <v>268</v>
+      </c>
+      <c r="I1798" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1798">
+        <v>1</v>
+      </c>
+      <c r="K1798">
+        <v>11060000</v>
+      </c>
+      <c r="L1798">
+        <v>11060000</v>
       </c>
     </row>
   </sheetData>

--- a/Database/MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D.xlsx
+++ b/Database/MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1783">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1790">
   <si>
     <t>MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D</t>
   </si>
@@ -5364,6 +5364,27 @@
   </si>
   <si>
     <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Nopember 2025 untuk 129 Pegawai</t>
+  </si>
+  <si>
+    <t>2025-12-05</t>
+  </si>
+  <si>
+    <t>'00523T</t>
+  </si>
+  <si>
+    <t>'259991320741000</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang berupa Tagihan PDAM Bulan Nopember 2025 Idple No. 1249-1046 An Lemb Perikanan Darat</t>
+  </si>
+  <si>
+    <t>'00524T</t>
+  </si>
+  <si>
+    <t>'259991311304509</t>
+  </si>
+  <si>
+    <t>'403829.023.523121.03212WA.2378EBA.A000000001.00000.2.0252.2.000000.000000.994.002.DC.000305</t>
   </si>
 </sst>
 </file>
@@ -5706,7 +5727,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:L1798"/>
+  <dimension ref="A1:L1811"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -73961,6 +73982,500 @@
       </c>
       <c r="L1798">
         <v>11060000</v>
+      </c>
+    </row>
+    <row r="1799" spans="1:12">
+      <c r="A1799">
+        <v>1796</v>
+      </c>
+      <c r="B1799">
+        <v>403829</v>
+      </c>
+      <c r="C1799" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1799" t="s">
+        <v>1783</v>
+      </c>
+      <c r="E1799" t="s">
+        <v>1784</v>
+      </c>
+      <c r="F1799" t="s">
+        <v>1785</v>
+      </c>
+      <c r="G1799" t="s">
+        <v>1786</v>
+      </c>
+      <c r="H1799" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1799" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1799">
+        <v>1</v>
+      </c>
+      <c r="K1799">
+        <v>604300</v>
+      </c>
+      <c r="L1799">
+        <v>604300</v>
+      </c>
+    </row>
+    <row r="1800" spans="1:12">
+      <c r="A1800">
+        <v>1797</v>
+      </c>
+      <c r="B1800">
+        <v>403829</v>
+      </c>
+      <c r="C1800" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1800" t="s">
+        <v>1783</v>
+      </c>
+      <c r="E1800" t="s">
+        <v>1787</v>
+      </c>
+      <c r="F1800" t="s">
+        <v>1788</v>
+      </c>
+      <c r="G1800" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1800" t="s">
+        <v>173</v>
+      </c>
+      <c r="I1800" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1800">
+        <v>1</v>
+      </c>
+      <c r="K1800">
+        <v>3953112</v>
+      </c>
+      <c r="L1800">
+        <v>3953112</v>
+      </c>
+    </row>
+    <row r="1801" spans="1:12">
+      <c r="A1801">
+        <v>1798</v>
+      </c>
+      <c r="B1801">
+        <v>403829</v>
+      </c>
+      <c r="C1801" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1801" t="s">
+        <v>1783</v>
+      </c>
+      <c r="E1801" t="s">
+        <v>1787</v>
+      </c>
+      <c r="F1801" t="s">
+        <v>1788</v>
+      </c>
+      <c r="G1801" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1801" t="s">
+        <v>1584</v>
+      </c>
+      <c r="I1801" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1801">
+        <v>1</v>
+      </c>
+      <c r="K1801">
+        <v>50601600</v>
+      </c>
+      <c r="L1801">
+        <v>50601600</v>
+      </c>
+    </row>
+    <row r="1802" spans="1:12">
+      <c r="A1802">
+        <v>1799</v>
+      </c>
+      <c r="B1802">
+        <v>403829</v>
+      </c>
+      <c r="C1802" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1802" t="s">
+        <v>1783</v>
+      </c>
+      <c r="E1802" t="s">
+        <v>1787</v>
+      </c>
+      <c r="F1802" t="s">
+        <v>1788</v>
+      </c>
+      <c r="G1802" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1802" t="s">
+        <v>386</v>
+      </c>
+      <c r="I1802" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1802">
+        <v>1</v>
+      </c>
+      <c r="K1802">
+        <v>300000</v>
+      </c>
+      <c r="L1802">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="1803" spans="1:12">
+      <c r="A1803">
+        <v>1800</v>
+      </c>
+      <c r="B1803">
+        <v>403829</v>
+      </c>
+      <c r="C1803" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1803" t="s">
+        <v>1783</v>
+      </c>
+      <c r="E1803" t="s">
+        <v>1787</v>
+      </c>
+      <c r="F1803" t="s">
+        <v>1788</v>
+      </c>
+      <c r="G1803" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1803" t="s">
+        <v>159</v>
+      </c>
+      <c r="I1803" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1803">
+        <v>1</v>
+      </c>
+      <c r="K1803">
+        <v>180000</v>
+      </c>
+      <c r="L1803">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="1804" spans="1:12">
+      <c r="A1804">
+        <v>1801</v>
+      </c>
+      <c r="B1804">
+        <v>403829</v>
+      </c>
+      <c r="C1804" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1804" t="s">
+        <v>1783</v>
+      </c>
+      <c r="E1804" t="s">
+        <v>1787</v>
+      </c>
+      <c r="F1804" t="s">
+        <v>1788</v>
+      </c>
+      <c r="G1804" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1804" t="s">
+        <v>174</v>
+      </c>
+      <c r="I1804" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1804">
+        <v>1</v>
+      </c>
+      <c r="K1804">
+        <v>1380500</v>
+      </c>
+      <c r="L1804">
+        <v>1380500</v>
+      </c>
+    </row>
+    <row r="1805" spans="1:12">
+      <c r="A1805">
+        <v>1802</v>
+      </c>
+      <c r="B1805">
+        <v>403829</v>
+      </c>
+      <c r="C1805" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1805" t="s">
+        <v>1783</v>
+      </c>
+      <c r="E1805" t="s">
+        <v>1787</v>
+      </c>
+      <c r="F1805" t="s">
+        <v>1788</v>
+      </c>
+      <c r="G1805" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1805" t="s">
+        <v>178</v>
+      </c>
+      <c r="I1805" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1805">
+        <v>1</v>
+      </c>
+      <c r="K1805">
+        <v>9468528</v>
+      </c>
+      <c r="L1805">
+        <v>9468528</v>
+      </c>
+    </row>
+    <row r="1806" spans="1:12">
+      <c r="A1806">
+        <v>1803</v>
+      </c>
+      <c r="B1806">
+        <v>403829</v>
+      </c>
+      <c r="C1806" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1806" t="s">
+        <v>1783</v>
+      </c>
+      <c r="E1806" t="s">
+        <v>1787</v>
+      </c>
+      <c r="F1806" t="s">
+        <v>1788</v>
+      </c>
+      <c r="G1806" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1806" t="s">
+        <v>1710</v>
+      </c>
+      <c r="I1806" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1806">
+        <v>1</v>
+      </c>
+      <c r="K1806">
+        <v>22953312</v>
+      </c>
+      <c r="L1806">
+        <v>22953312</v>
+      </c>
+    </row>
+    <row r="1807" spans="1:12">
+      <c r="A1807">
+        <v>1804</v>
+      </c>
+      <c r="B1807">
+        <v>403829</v>
+      </c>
+      <c r="C1807" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1807" t="s">
+        <v>1783</v>
+      </c>
+      <c r="E1807" t="s">
+        <v>1787</v>
+      </c>
+      <c r="F1807" t="s">
+        <v>1788</v>
+      </c>
+      <c r="G1807" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1807" t="s">
+        <v>1711</v>
+      </c>
+      <c r="I1807" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1807">
+        <v>1</v>
+      </c>
+      <c r="K1807">
+        <v>4629928</v>
+      </c>
+      <c r="L1807">
+        <v>4629928</v>
+      </c>
+    </row>
+    <row r="1808" spans="1:12">
+      <c r="A1808">
+        <v>1805</v>
+      </c>
+      <c r="B1808">
+        <v>403829</v>
+      </c>
+      <c r="C1808" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1808" t="s">
+        <v>1783</v>
+      </c>
+      <c r="E1808" t="s">
+        <v>1787</v>
+      </c>
+      <c r="F1808" t="s">
+        <v>1788</v>
+      </c>
+      <c r="G1808" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1808" t="s">
+        <v>185</v>
+      </c>
+      <c r="I1808" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1808">
+        <v>1</v>
+      </c>
+      <c r="K1808">
+        <v>2890000</v>
+      </c>
+      <c r="L1808">
+        <v>2890000</v>
+      </c>
+    </row>
+    <row r="1809" spans="1:12">
+      <c r="A1809">
+        <v>1806</v>
+      </c>
+      <c r="B1809">
+        <v>403829</v>
+      </c>
+      <c r="C1809" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1809" t="s">
+        <v>1783</v>
+      </c>
+      <c r="E1809" t="s">
+        <v>1787</v>
+      </c>
+      <c r="F1809" t="s">
+        <v>1788</v>
+      </c>
+      <c r="G1809" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1809" t="s">
+        <v>186</v>
+      </c>
+      <c r="I1809" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1809">
+        <v>1</v>
+      </c>
+      <c r="K1809">
+        <v>1490000</v>
+      </c>
+      <c r="L1809">
+        <v>1490000</v>
+      </c>
+    </row>
+    <row r="1810" spans="1:12">
+      <c r="A1810">
+        <v>1807</v>
+      </c>
+      <c r="B1810">
+        <v>403829</v>
+      </c>
+      <c r="C1810" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1810" t="s">
+        <v>1783</v>
+      </c>
+      <c r="E1810" t="s">
+        <v>1787</v>
+      </c>
+      <c r="F1810" t="s">
+        <v>1788</v>
+      </c>
+      <c r="G1810" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1810" t="s">
+        <v>191</v>
+      </c>
+      <c r="I1810" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1810">
+        <v>1</v>
+      </c>
+      <c r="K1810">
+        <v>1560138</v>
+      </c>
+      <c r="L1810">
+        <v>1560138</v>
+      </c>
+    </row>
+    <row r="1811" spans="1:12">
+      <c r="A1811">
+        <v>1808</v>
+      </c>
+      <c r="B1811">
+        <v>403829</v>
+      </c>
+      <c r="C1811" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1811" t="s">
+        <v>1783</v>
+      </c>
+      <c r="E1811" t="s">
+        <v>1787</v>
+      </c>
+      <c r="F1811" t="s">
+        <v>1788</v>
+      </c>
+      <c r="G1811" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1811" t="s">
+        <v>1789</v>
+      </c>
+      <c r="I1811" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1811">
+        <v>1</v>
+      </c>
+      <c r="K1811">
+        <v>750000</v>
+      </c>
+      <c r="L1811">
+        <v>750000</v>
       </c>
     </row>
   </sheetData>

--- a/Database/MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D.xlsx
+++ b/Database/MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1790">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1816">
   <si>
     <t>MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D</t>
   </si>
@@ -5385,6 +5385,84 @@
   </si>
   <si>
     <t>'403829.023.523121.03212WA.2378EBA.A000000001.00000.2.0252.2.000000.000000.994.002.DC.000305</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>'00527T</t>
+  </si>
+  <si>
+    <t>'259991320775229</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang berupa Tagihan Internet Bulan November 2025 idpel No.GO18A106 An Balai Riset Perikanan Budidaya Air Tawar dan Penyuluhan Perikanan</t>
+  </si>
+  <si>
+    <t>2025-12-09</t>
+  </si>
+  <si>
+    <t>'00528T</t>
+  </si>
+  <si>
+    <t>'259991311359950</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Nopember tahun 2025 untuk 130 Pegawai</t>
+  </si>
+  <si>
+    <t>'00529T</t>
+  </si>
+  <si>
+    <t>'259991330479138</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja  bulan Nopember tahun 2025 untuk 167 Pegawai</t>
+  </si>
+  <si>
+    <t>2025-12-11</t>
+  </si>
+  <si>
+    <t>'00531T</t>
+  </si>
+  <si>
+    <t>'259991311381905</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Nopember tahun 2025 untuk 50 Pegawai</t>
+  </si>
+  <si>
+    <t>'00534T</t>
+  </si>
+  <si>
+    <t>'259991311381906</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Nopember tahun 2025 untuk 35 Pegawai</t>
+  </si>
+  <si>
+    <t>'00536T</t>
+  </si>
+  <si>
+    <t>'259991311381903</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Desember tahun 2025 untuk 129 Pegawai</t>
+  </si>
+  <si>
+    <t>'00538T</t>
+  </si>
+  <si>
+    <t>'259991311381904</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Desember tahun 2025 untuk 50 Pegawai</t>
+  </si>
+  <si>
+    <t>'00540T</t>
+  </si>
+  <si>
+    <t>'259991311381907</t>
   </si>
 </sst>
 </file>
@@ -5727,7 +5805,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:L1811"/>
+  <dimension ref="A1:L1819"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -74476,6 +74554,310 @@
       </c>
       <c r="L1811">
         <v>750000</v>
+      </c>
+    </row>
+    <row r="1812" spans="1:12">
+      <c r="A1812">
+        <v>1809</v>
+      </c>
+      <c r="B1812">
+        <v>403829</v>
+      </c>
+      <c r="C1812" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1812" t="s">
+        <v>1790</v>
+      </c>
+      <c r="E1812" t="s">
+        <v>1791</v>
+      </c>
+      <c r="F1812" t="s">
+        <v>1792</v>
+      </c>
+      <c r="G1812" t="s">
+        <v>1793</v>
+      </c>
+      <c r="H1812" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1812" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1812">
+        <v>1</v>
+      </c>
+      <c r="K1812">
+        <v>6670000</v>
+      </c>
+      <c r="L1812">
+        <v>6670000</v>
+      </c>
+    </row>
+    <row r="1813" spans="1:12">
+      <c r="A1813">
+        <v>1810</v>
+      </c>
+      <c r="B1813">
+        <v>403829</v>
+      </c>
+      <c r="C1813" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1813" t="s">
+        <v>1794</v>
+      </c>
+      <c r="E1813" t="s">
+        <v>1795</v>
+      </c>
+      <c r="F1813" t="s">
+        <v>1796</v>
+      </c>
+      <c r="G1813" t="s">
+        <v>1797</v>
+      </c>
+      <c r="H1813" t="s">
+        <v>272</v>
+      </c>
+      <c r="I1813" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1813">
+        <v>1</v>
+      </c>
+      <c r="K1813">
+        <v>782621737</v>
+      </c>
+      <c r="L1813">
+        <v>782621737</v>
+      </c>
+    </row>
+    <row r="1814" spans="1:12">
+      <c r="A1814">
+        <v>1811</v>
+      </c>
+      <c r="B1814">
+        <v>403829</v>
+      </c>
+      <c r="C1814" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1814" t="s">
+        <v>1794</v>
+      </c>
+      <c r="E1814" t="s">
+        <v>1798</v>
+      </c>
+      <c r="F1814" t="s">
+        <v>1799</v>
+      </c>
+      <c r="G1814" t="s">
+        <v>1800</v>
+      </c>
+      <c r="H1814" t="s">
+        <v>272</v>
+      </c>
+      <c r="I1814" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1814">
+        <v>1</v>
+      </c>
+      <c r="K1814">
+        <v>980114708</v>
+      </c>
+      <c r="L1814">
+        <v>980114708</v>
+      </c>
+    </row>
+    <row r="1815" spans="1:12">
+      <c r="A1815">
+        <v>1812</v>
+      </c>
+      <c r="B1815">
+        <v>403829</v>
+      </c>
+      <c r="C1815" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1815" t="s">
+        <v>1801</v>
+      </c>
+      <c r="E1815" t="s">
+        <v>1802</v>
+      </c>
+      <c r="F1815" t="s">
+        <v>1803</v>
+      </c>
+      <c r="G1815" t="s">
+        <v>1804</v>
+      </c>
+      <c r="H1815" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1815" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1815">
+        <v>1</v>
+      </c>
+      <c r="K1815">
+        <v>247818118</v>
+      </c>
+      <c r="L1815">
+        <v>247818118</v>
+      </c>
+    </row>
+    <row r="1816" spans="1:12">
+      <c r="A1816">
+        <v>1813</v>
+      </c>
+      <c r="B1816">
+        <v>403829</v>
+      </c>
+      <c r="C1816" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1816" t="s">
+        <v>1801</v>
+      </c>
+      <c r="E1816" t="s">
+        <v>1805</v>
+      </c>
+      <c r="F1816" t="s">
+        <v>1806</v>
+      </c>
+      <c r="G1816" t="s">
+        <v>1807</v>
+      </c>
+      <c r="H1816" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1816" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1816">
+        <v>1</v>
+      </c>
+      <c r="K1816">
+        <v>179638737</v>
+      </c>
+      <c r="L1816">
+        <v>179638737</v>
+      </c>
+    </row>
+    <row r="1817" spans="1:12">
+      <c r="A1817">
+        <v>1814</v>
+      </c>
+      <c r="B1817">
+        <v>403829</v>
+      </c>
+      <c r="C1817" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1817" t="s">
+        <v>1801</v>
+      </c>
+      <c r="E1817" t="s">
+        <v>1808</v>
+      </c>
+      <c r="F1817" t="s">
+        <v>1809</v>
+      </c>
+      <c r="G1817" t="s">
+        <v>1810</v>
+      </c>
+      <c r="H1817" t="s">
+        <v>272</v>
+      </c>
+      <c r="I1817" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1817">
+        <v>1</v>
+      </c>
+      <c r="K1817">
+        <v>788886921</v>
+      </c>
+      <c r="L1817">
+        <v>788886921</v>
+      </c>
+    </row>
+    <row r="1818" spans="1:12">
+      <c r="A1818">
+        <v>1815</v>
+      </c>
+      <c r="B1818">
+        <v>403829</v>
+      </c>
+      <c r="C1818" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1818" t="s">
+        <v>1801</v>
+      </c>
+      <c r="E1818" t="s">
+        <v>1811</v>
+      </c>
+      <c r="F1818" t="s">
+        <v>1812</v>
+      </c>
+      <c r="G1818" t="s">
+        <v>1813</v>
+      </c>
+      <c r="H1818" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1818" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1818">
+        <v>1</v>
+      </c>
+      <c r="K1818">
+        <v>221451850</v>
+      </c>
+      <c r="L1818">
+        <v>221451850</v>
+      </c>
+    </row>
+    <row r="1819" spans="1:12">
+      <c r="A1819">
+        <v>1816</v>
+      </c>
+      <c r="B1819">
+        <v>403829</v>
+      </c>
+      <c r="C1819" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1819" t="s">
+        <v>1801</v>
+      </c>
+      <c r="E1819" t="s">
+        <v>1814</v>
+      </c>
+      <c r="F1819" t="s">
+        <v>1815</v>
+      </c>
+      <c r="G1819" t="s">
+        <v>1736</v>
+      </c>
+      <c r="H1819" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1819" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1819">
+        <v>1</v>
+      </c>
+      <c r="K1819">
+        <v>158055800</v>
+      </c>
+      <c r="L1819">
+        <v>158055800</v>
       </c>
     </row>
   </sheetData>

--- a/Database/MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D.xlsx
+++ b/Database/MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1816">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1891">
   <si>
     <t>MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D</t>
   </si>
@@ -5387,6 +5387,27 @@
     <t>'403829.023.523121.03212WA.2378EBA.A000000001.00000.2.0252.2.000000.000000.994.002.DC.000305</t>
   </si>
   <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>'00525T</t>
+  </si>
+  <si>
+    <t>'259991311337999</t>
+  </si>
+  <si>
+    <t>Pembayaran belanja barang berupa tagihan telepon bulan Desember 2025 untuk 12 invoice</t>
+  </si>
+  <si>
+    <t>'00526T</t>
+  </si>
+  <si>
+    <t>'259991320771827</t>
+  </si>
+  <si>
+    <t>Pembayaran belanja barang berupa tagihan listrik bulan Desember 2025 untuk 6 invoice</t>
+  </si>
+  <si>
     <t>2025-12-10</t>
   </si>
   <si>
@@ -5423,6 +5444,15 @@
     <t>2025-12-11</t>
   </si>
   <si>
+    <t>'00530T</t>
+  </si>
+  <si>
+    <t>'259991305287917</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Nopember  tahun 2025 untuk 167 Pegawai</t>
+  </si>
+  <si>
     <t>'00531T</t>
   </si>
   <si>
@@ -5432,6 +5462,24 @@
     <t>Pembayaran tunjangan kinerja bulan Nopember tahun 2025 untuk 50 Pegawai</t>
   </si>
   <si>
+    <t>'00532T</t>
+  </si>
+  <si>
+    <t>'259991305287918</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Nopember tahun 2025 untuk 38 Pegawai</t>
+  </si>
+  <si>
+    <t>'00533T</t>
+  </si>
+  <si>
+    <t>'259991330489028</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Nopember tahun 2025 untuk 63 Pegawai</t>
+  </si>
+  <si>
     <t>'00534T</t>
   </si>
   <si>
@@ -5441,6 +5489,15 @@
     <t>Pembayaran tunjangan kinerja bulan Nopember tahun 2025 untuk 35 Pegawai</t>
   </si>
   <si>
+    <t>'00535T</t>
+  </si>
+  <si>
+    <t>'259991330489031</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Nopember tahun 2025 untuk 23 Pegawai</t>
+  </si>
+  <si>
     <t>'00536T</t>
   </si>
   <si>
@@ -5450,6 +5507,15 @@
     <t>Pembayaran tunjangan kinerja bulan Desember tahun 2025 untuk 129 Pegawai</t>
   </si>
   <si>
+    <t>'00537T</t>
+  </si>
+  <si>
+    <t>'259991330489027</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Desember tahun 2025 untuk 165 Pegawai</t>
+  </si>
+  <si>
     <t>'00538T</t>
   </si>
   <si>
@@ -5459,10 +5525,169 @@
     <t>Pembayaran tunjangan kinerja bulan Desember tahun 2025 untuk 50 Pegawai</t>
   </si>
   <si>
+    <t>'00539T</t>
+  </si>
+  <si>
+    <t>'259991330489029</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Desember tahun 2025 untuk 63 Pegawai</t>
+  </si>
+  <si>
     <t>'00540T</t>
   </si>
   <si>
     <t>'259991311381907</t>
+  </si>
+  <si>
+    <t>'00541T</t>
+  </si>
+  <si>
+    <t>'259991305287915</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Desember tahun 2025 untuk 38 Pegawai</t>
+  </si>
+  <si>
+    <t>'00542T</t>
+  </si>
+  <si>
+    <t>'259991305287916</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Desember 2026 tahun 2025 untuk 167 Pegawai</t>
+  </si>
+  <si>
+    <t>'00543T</t>
+  </si>
+  <si>
+    <t>'259991330489030</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Desember tahun 2025 untuk 23 Pegawai</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>'00544T</t>
+  </si>
+  <si>
+    <t>'259991311395759</t>
+  </si>
+  <si>
+    <t>2025-12-17</t>
+  </si>
+  <si>
+    <t>'00545T</t>
+  </si>
+  <si>
+    <t>'259991311422954</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang sesuai SPD No. 0061-0069/BRPBATPP/KO.440/X/2025 Tanggal 20 Oktober 2025 sd 23 Oktober 2025</t>
+  </si>
+  <si>
+    <t>'00546T</t>
+  </si>
+  <si>
+    <t>'259991320835039</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang Sesuai Kwitansi NO. 170/GSR-KW/XII/2025 Tanggal 9 Desember 2025 berupa pekerjaan galian,perbaikan pondasi dan saluran</t>
+  </si>
+  <si>
+    <t>'00547T</t>
+  </si>
+  <si>
+    <t>'259991320834999</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang sesuai Kwitansi No 030/KUI-KPRA/XII/2025 Tanggal 8 Desember 2025 berupa Pekerjaan Perbaikan Kolam</t>
+  </si>
+  <si>
+    <t>2025-12-22</t>
+  </si>
+  <si>
+    <t>'00548T</t>
+  </si>
+  <si>
+    <t>'259990302015136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pengisian RPATA atas Kontrak Nomor 2/BRPBATPP/PPK/PL.400/I/2025 untuk Pekerjaan Pengadaan Jasa Outsourcing Satpam </t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>'00549T</t>
+  </si>
+  <si>
+    <t>'259991330522534</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Gaji Susulan Bulan Desember 2025 untuk 1 Pegawai/1 Jiwa</t>
+  </si>
+  <si>
+    <t>'00550T</t>
+  </si>
+  <si>
+    <t>'259991330522537</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Pegawai berupa Uang Makan Bulan Nopember 2025 untuk 1 Pegawai</t>
+  </si>
+  <si>
+    <t>'00551T</t>
+  </si>
+  <si>
+    <t>'259991330522536</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja susulan bulan November tahun 2025 untuk 1 Pegawai</t>
+  </si>
+  <si>
+    <t>'00552T</t>
+  </si>
+  <si>
+    <t>'259991330522535</t>
+  </si>
+  <si>
+    <t>Pembayaran tunjangan kinerja bulan Desember tahun 2025 untuk 1 Pegawai</t>
+  </si>
+  <si>
+    <t>'00553T</t>
+  </si>
+  <si>
+    <t>'259991320856513</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang sesuai Kwitansi No. 051/KUITANSI-DA/XII/2025 Tanggal 16 Desember 2025 berupa pekerjaan Perbaikan Bak Sampah</t>
+  </si>
+  <si>
+    <t>'403829.023.523111.03212WA.2378EBA.A000000001.00000.2.0252.2.000000.000000.994.002.DC.000298</t>
+  </si>
+  <si>
+    <t>'00554T</t>
+  </si>
+  <si>
+    <t>'259991320856511</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang sesuai kwitansi No. 042/KUITANSI-MER/XII/2025 Tanggal 16 Desember 2025 berupa Pekerjaan Pembangunan Saluran Air/Drainase cijeruk</t>
+  </si>
+  <si>
+    <t>'00555T</t>
+  </si>
+  <si>
+    <t>'259991320856512</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang Sesuai Kwitansi No. 052/KUITANSI-DA/XII/2025 tanggal 17 Desember 2025 beupa Pekerjaan  Perbaikan Lantai gedung serbaguna cijeurk</t>
+  </si>
+  <si>
+    <t>'403829.023.523111.03212WA.2378EBA.A000000001.00000.2.0252.2.000000.000000.994.002.DC.000280</t>
   </si>
 </sst>
 </file>
@@ -5805,7 +6030,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:L1819"/>
+  <dimension ref="A1:L1853"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -74579,7 +74804,7 @@
         <v>1793</v>
       </c>
       <c r="H1812" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I1812" t="s">
         <v>19</v>
@@ -74588,10 +74813,10 @@
         <v>1</v>
       </c>
       <c r="K1812">
-        <v>6670000</v>
+        <v>263514</v>
       </c>
       <c r="L1812">
-        <v>6670000</v>
+        <v>263514</v>
       </c>
     </row>
     <row r="1813" spans="1:12">
@@ -74605,19 +74830,19 @@
         <v>13</v>
       </c>
       <c r="D1813" t="s">
-        <v>1794</v>
+        <v>1790</v>
       </c>
       <c r="E1813" t="s">
-        <v>1795</v>
+        <v>1791</v>
       </c>
       <c r="F1813" t="s">
-        <v>1796</v>
+        <v>1792</v>
       </c>
       <c r="G1813" t="s">
-        <v>1797</v>
+        <v>1793</v>
       </c>
       <c r="H1813" t="s">
-        <v>272</v>
+        <v>84</v>
       </c>
       <c r="I1813" t="s">
         <v>19</v>
@@ -74626,10 +74851,10 @@
         <v>1</v>
       </c>
       <c r="K1813">
-        <v>782621737</v>
+        <v>2580750</v>
       </c>
       <c r="L1813">
-        <v>782621737</v>
+        <v>2580750</v>
       </c>
     </row>
     <row r="1814" spans="1:12">
@@ -74643,19 +74868,19 @@
         <v>13</v>
       </c>
       <c r="D1814" t="s">
+        <v>1790</v>
+      </c>
+      <c r="E1814" t="s">
         <v>1794</v>
       </c>
-      <c r="E1814" t="s">
-        <v>1798</v>
-      </c>
       <c r="F1814" t="s">
-        <v>1799</v>
+        <v>1795</v>
       </c>
       <c r="G1814" t="s">
-        <v>1800</v>
+        <v>1796</v>
       </c>
       <c r="H1814" t="s">
-        <v>272</v>
+        <v>79</v>
       </c>
       <c r="I1814" t="s">
         <v>19</v>
@@ -74664,10 +74889,10 @@
         <v>1</v>
       </c>
       <c r="K1814">
-        <v>980114708</v>
+        <v>38886478</v>
       </c>
       <c r="L1814">
-        <v>980114708</v>
+        <v>38886478</v>
       </c>
     </row>
     <row r="1815" spans="1:12">
@@ -74681,19 +74906,19 @@
         <v>13</v>
       </c>
       <c r="D1815" t="s">
-        <v>1801</v>
+        <v>1797</v>
       </c>
       <c r="E1815" t="s">
-        <v>1802</v>
+        <v>1798</v>
       </c>
       <c r="F1815" t="s">
-        <v>1803</v>
+        <v>1799</v>
       </c>
       <c r="G1815" t="s">
-        <v>1804</v>
+        <v>1800</v>
       </c>
       <c r="H1815" t="s">
-        <v>276</v>
+        <v>84</v>
       </c>
       <c r="I1815" t="s">
         <v>19</v>
@@ -74702,10 +74927,10 @@
         <v>1</v>
       </c>
       <c r="K1815">
-        <v>247818118</v>
+        <v>6670000</v>
       </c>
       <c r="L1815">
-        <v>247818118</v>
+        <v>6670000</v>
       </c>
     </row>
     <row r="1816" spans="1:12">
@@ -74722,16 +74947,16 @@
         <v>1801</v>
       </c>
       <c r="E1816" t="s">
-        <v>1805</v>
+        <v>1802</v>
       </c>
       <c r="F1816" t="s">
-        <v>1806</v>
+        <v>1803</v>
       </c>
       <c r="G1816" t="s">
-        <v>1807</v>
+        <v>1804</v>
       </c>
       <c r="H1816" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="I1816" t="s">
         <v>19</v>
@@ -74740,10 +74965,10 @@
         <v>1</v>
       </c>
       <c r="K1816">
-        <v>179638737</v>
+        <v>782621737</v>
       </c>
       <c r="L1816">
-        <v>179638737</v>
+        <v>782621737</v>
       </c>
     </row>
     <row r="1817" spans="1:12">
@@ -74760,13 +74985,13 @@
         <v>1801</v>
       </c>
       <c r="E1817" t="s">
-        <v>1808</v>
+        <v>1805</v>
       </c>
       <c r="F1817" t="s">
-        <v>1809</v>
+        <v>1806</v>
       </c>
       <c r="G1817" t="s">
-        <v>1810</v>
+        <v>1807</v>
       </c>
       <c r="H1817" t="s">
         <v>272</v>
@@ -74778,10 +75003,10 @@
         <v>1</v>
       </c>
       <c r="K1817">
-        <v>788886921</v>
+        <v>980114708</v>
       </c>
       <c r="L1817">
-        <v>788886921</v>
+        <v>980114708</v>
       </c>
     </row>
     <row r="1818" spans="1:12">
@@ -74795,16 +75020,16 @@
         <v>13</v>
       </c>
       <c r="D1818" t="s">
-        <v>1801</v>
+        <v>1808</v>
       </c>
       <c r="E1818" t="s">
+        <v>1809</v>
+      </c>
+      <c r="F1818" t="s">
+        <v>1810</v>
+      </c>
+      <c r="G1818" t="s">
         <v>1811</v>
-      </c>
-      <c r="F1818" t="s">
-        <v>1812</v>
-      </c>
-      <c r="G1818" t="s">
-        <v>1813</v>
       </c>
       <c r="H1818" t="s">
         <v>276</v>
@@ -74816,10 +75041,10 @@
         <v>1</v>
       </c>
       <c r="K1818">
-        <v>221451850</v>
+        <v>751855489</v>
       </c>
       <c r="L1818">
-        <v>221451850</v>
+        <v>751855489</v>
       </c>
     </row>
     <row r="1819" spans="1:12">
@@ -74833,16 +75058,16 @@
         <v>13</v>
       </c>
       <c r="D1819" t="s">
-        <v>1801</v>
+        <v>1808</v>
       </c>
       <c r="E1819" t="s">
+        <v>1812</v>
+      </c>
+      <c r="F1819" t="s">
+        <v>1813</v>
+      </c>
+      <c r="G1819" t="s">
         <v>1814</v>
-      </c>
-      <c r="F1819" t="s">
-        <v>1815</v>
-      </c>
-      <c r="G1819" t="s">
-        <v>1736</v>
       </c>
       <c r="H1819" t="s">
         <v>276</v>
@@ -74854,10 +75079,1302 @@
         <v>1</v>
       </c>
       <c r="K1819">
+        <v>247818118</v>
+      </c>
+      <c r="L1819">
+        <v>247818118</v>
+      </c>
+    </row>
+    <row r="1820" spans="1:12">
+      <c r="A1820">
+        <v>1817</v>
+      </c>
+      <c r="B1820">
+        <v>403829</v>
+      </c>
+      <c r="C1820" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1820" t="s">
+        <v>1808</v>
+      </c>
+      <c r="E1820" t="s">
+        <v>1815</v>
+      </c>
+      <c r="F1820" t="s">
+        <v>1816</v>
+      </c>
+      <c r="G1820" t="s">
+        <v>1817</v>
+      </c>
+      <c r="H1820" t="s">
+        <v>1702</v>
+      </c>
+      <c r="I1820" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1820">
+        <v>1</v>
+      </c>
+      <c r="K1820">
+        <v>141369312</v>
+      </c>
+      <c r="L1820">
+        <v>141369312</v>
+      </c>
+    </row>
+    <row r="1821" spans="1:12">
+      <c r="A1821">
+        <v>1818</v>
+      </c>
+      <c r="B1821">
+        <v>403829</v>
+      </c>
+      <c r="C1821" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1821" t="s">
+        <v>1808</v>
+      </c>
+      <c r="E1821" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F1821" t="s">
+        <v>1819</v>
+      </c>
+      <c r="G1821" t="s">
+        <v>1820</v>
+      </c>
+      <c r="H1821" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1821" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1821">
+        <v>1</v>
+      </c>
+      <c r="K1821">
+        <v>325557641</v>
+      </c>
+      <c r="L1821">
+        <v>325557641</v>
+      </c>
+    </row>
+    <row r="1822" spans="1:12">
+      <c r="A1822">
+        <v>1819</v>
+      </c>
+      <c r="B1822">
+        <v>403829</v>
+      </c>
+      <c r="C1822" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1822" t="s">
+        <v>1808</v>
+      </c>
+      <c r="E1822" t="s">
+        <v>1821</v>
+      </c>
+      <c r="F1822" t="s">
+        <v>1822</v>
+      </c>
+      <c r="G1822" t="s">
+        <v>1823</v>
+      </c>
+      <c r="H1822" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1822" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1822">
+        <v>1</v>
+      </c>
+      <c r="K1822">
+        <v>179638737</v>
+      </c>
+      <c r="L1822">
+        <v>179638737</v>
+      </c>
+    </row>
+    <row r="1823" spans="1:12">
+      <c r="A1823">
+        <v>1820</v>
+      </c>
+      <c r="B1823">
+        <v>403829</v>
+      </c>
+      <c r="C1823" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1823" t="s">
+        <v>1808</v>
+      </c>
+      <c r="E1823" t="s">
+        <v>1824</v>
+      </c>
+      <c r="F1823" t="s">
+        <v>1825</v>
+      </c>
+      <c r="G1823" t="s">
+        <v>1826</v>
+      </c>
+      <c r="H1823" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1823" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1823">
+        <v>1</v>
+      </c>
+      <c r="K1823">
+        <v>116041279</v>
+      </c>
+      <c r="L1823">
+        <v>116041279</v>
+      </c>
+    </row>
+    <row r="1824" spans="1:12">
+      <c r="A1824">
+        <v>1821</v>
+      </c>
+      <c r="B1824">
+        <v>403829</v>
+      </c>
+      <c r="C1824" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1824" t="s">
+        <v>1808</v>
+      </c>
+      <c r="E1824" t="s">
+        <v>1827</v>
+      </c>
+      <c r="F1824" t="s">
+        <v>1828</v>
+      </c>
+      <c r="G1824" t="s">
+        <v>1829</v>
+      </c>
+      <c r="H1824" t="s">
+        <v>272</v>
+      </c>
+      <c r="I1824" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1824">
+        <v>1</v>
+      </c>
+      <c r="K1824">
+        <v>788886921</v>
+      </c>
+      <c r="L1824">
+        <v>788886921</v>
+      </c>
+    </row>
+    <row r="1825" spans="1:12">
+      <c r="A1825">
+        <v>1822</v>
+      </c>
+      <c r="B1825">
+        <v>403829</v>
+      </c>
+      <c r="C1825" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1825" t="s">
+        <v>1808</v>
+      </c>
+      <c r="E1825" t="s">
+        <v>1830</v>
+      </c>
+      <c r="F1825" t="s">
+        <v>1831</v>
+      </c>
+      <c r="G1825" t="s">
+        <v>1832</v>
+      </c>
+      <c r="H1825" t="s">
+        <v>272</v>
+      </c>
+      <c r="I1825" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1825">
+        <v>1</v>
+      </c>
+      <c r="K1825">
+        <v>975224550</v>
+      </c>
+      <c r="L1825">
+        <v>975224550</v>
+      </c>
+    </row>
+    <row r="1826" spans="1:12">
+      <c r="A1826">
+        <v>1823</v>
+      </c>
+      <c r="B1826">
+        <v>403829</v>
+      </c>
+      <c r="C1826" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1826" t="s">
+        <v>1808</v>
+      </c>
+      <c r="E1826" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F1826" t="s">
+        <v>1834</v>
+      </c>
+      <c r="G1826" t="s">
+        <v>1835</v>
+      </c>
+      <c r="H1826" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1826" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1826">
+        <v>1</v>
+      </c>
+      <c r="K1826">
+        <v>221451850</v>
+      </c>
+      <c r="L1826">
+        <v>221451850</v>
+      </c>
+    </row>
+    <row r="1827" spans="1:12">
+      <c r="A1827">
+        <v>1824</v>
+      </c>
+      <c r="B1827">
+        <v>403829</v>
+      </c>
+      <c r="C1827" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1827" t="s">
+        <v>1808</v>
+      </c>
+      <c r="E1827" t="s">
+        <v>1836</v>
+      </c>
+      <c r="F1827" t="s">
+        <v>1837</v>
+      </c>
+      <c r="G1827" t="s">
+        <v>1838</v>
+      </c>
+      <c r="H1827" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1827" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1827">
+        <v>1</v>
+      </c>
+      <c r="K1827">
+        <v>297193400</v>
+      </c>
+      <c r="L1827">
+        <v>297193400</v>
+      </c>
+    </row>
+    <row r="1828" spans="1:12">
+      <c r="A1828">
+        <v>1825</v>
+      </c>
+      <c r="B1828">
+        <v>403829</v>
+      </c>
+      <c r="C1828" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1828" t="s">
+        <v>1808</v>
+      </c>
+      <c r="E1828" t="s">
+        <v>1839</v>
+      </c>
+      <c r="F1828" t="s">
+        <v>1840</v>
+      </c>
+      <c r="G1828" t="s">
+        <v>1736</v>
+      </c>
+      <c r="H1828" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1828" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1828">
+        <v>1</v>
+      </c>
+      <c r="K1828">
         <v>158055800</v>
       </c>
-      <c r="L1819">
+      <c r="L1828">
         <v>158055800</v>
+      </c>
+    </row>
+    <row r="1829" spans="1:12">
+      <c r="A1829">
+        <v>1826</v>
+      </c>
+      <c r="B1829">
+        <v>403829</v>
+      </c>
+      <c r="C1829" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1829" t="s">
+        <v>1808</v>
+      </c>
+      <c r="E1829" t="s">
+        <v>1841</v>
+      </c>
+      <c r="F1829" t="s">
+        <v>1842</v>
+      </c>
+      <c r="G1829" t="s">
+        <v>1843</v>
+      </c>
+      <c r="H1829" t="s">
+        <v>1702</v>
+      </c>
+      <c r="I1829" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1829">
+        <v>1</v>
+      </c>
+      <c r="K1829">
+        <v>142394450</v>
+      </c>
+      <c r="L1829">
+        <v>142394450</v>
+      </c>
+    </row>
+    <row r="1830" spans="1:12">
+      <c r="A1830">
+        <v>1827</v>
+      </c>
+      <c r="B1830">
+        <v>403829</v>
+      </c>
+      <c r="C1830" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1830" t="s">
+        <v>1808</v>
+      </c>
+      <c r="E1830" t="s">
+        <v>1844</v>
+      </c>
+      <c r="F1830" t="s">
+        <v>1845</v>
+      </c>
+      <c r="G1830" t="s">
+        <v>1846</v>
+      </c>
+      <c r="H1830" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1830" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1830">
+        <v>1</v>
+      </c>
+      <c r="K1830">
+        <v>752203550</v>
+      </c>
+      <c r="L1830">
+        <v>752203550</v>
+      </c>
+    </row>
+    <row r="1831" spans="1:12">
+      <c r="A1831">
+        <v>1828</v>
+      </c>
+      <c r="B1831">
+        <v>403829</v>
+      </c>
+      <c r="C1831" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1831" t="s">
+        <v>1808</v>
+      </c>
+      <c r="E1831" t="s">
+        <v>1847</v>
+      </c>
+      <c r="F1831" t="s">
+        <v>1848</v>
+      </c>
+      <c r="G1831" t="s">
+        <v>1849</v>
+      </c>
+      <c r="H1831" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1831" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1831">
+        <v>1</v>
+      </c>
+      <c r="K1831">
+        <v>102562200</v>
+      </c>
+      <c r="L1831">
+        <v>102562200</v>
+      </c>
+    </row>
+    <row r="1832" spans="1:12">
+      <c r="A1832">
+        <v>1829</v>
+      </c>
+      <c r="B1832">
+        <v>403829</v>
+      </c>
+      <c r="C1832" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1832" t="s">
+        <v>1850</v>
+      </c>
+      <c r="E1832" t="s">
+        <v>1851</v>
+      </c>
+      <c r="F1832" t="s">
+        <v>1852</v>
+      </c>
+      <c r="G1832" t="s">
+        <v>206</v>
+      </c>
+      <c r="H1832" t="s">
+        <v>173</v>
+      </c>
+      <c r="I1832" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1832">
+        <v>1</v>
+      </c>
+      <c r="K1832">
+        <v>26837269</v>
+      </c>
+      <c r="L1832">
+        <v>26837269</v>
+      </c>
+    </row>
+    <row r="1833" spans="1:12">
+      <c r="A1833">
+        <v>1830</v>
+      </c>
+      <c r="B1833">
+        <v>403829</v>
+      </c>
+      <c r="C1833" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1833" t="s">
+        <v>1850</v>
+      </c>
+      <c r="E1833" t="s">
+        <v>1851</v>
+      </c>
+      <c r="F1833" t="s">
+        <v>1852</v>
+      </c>
+      <c r="G1833" t="s">
+        <v>206</v>
+      </c>
+      <c r="H1833" t="s">
+        <v>175</v>
+      </c>
+      <c r="I1833" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1833">
+        <v>1</v>
+      </c>
+      <c r="K1833">
+        <v>5388100</v>
+      </c>
+      <c r="L1833">
+        <v>5388100</v>
+      </c>
+    </row>
+    <row r="1834" spans="1:12">
+      <c r="A1834">
+        <v>1831</v>
+      </c>
+      <c r="B1834">
+        <v>403829</v>
+      </c>
+      <c r="C1834" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1834" t="s">
+        <v>1850</v>
+      </c>
+      <c r="E1834" t="s">
+        <v>1851</v>
+      </c>
+      <c r="F1834" t="s">
+        <v>1852</v>
+      </c>
+      <c r="G1834" t="s">
+        <v>206</v>
+      </c>
+      <c r="H1834" t="s">
+        <v>207</v>
+      </c>
+      <c r="I1834" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1834">
+        <v>1</v>
+      </c>
+      <c r="K1834">
+        <v>769000</v>
+      </c>
+      <c r="L1834">
+        <v>769000</v>
+      </c>
+    </row>
+    <row r="1835" spans="1:12">
+      <c r="A1835">
+        <v>1832</v>
+      </c>
+      <c r="B1835">
+        <v>403829</v>
+      </c>
+      <c r="C1835" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1835" t="s">
+        <v>1850</v>
+      </c>
+      <c r="E1835" t="s">
+        <v>1851</v>
+      </c>
+      <c r="F1835" t="s">
+        <v>1852</v>
+      </c>
+      <c r="G1835" t="s">
+        <v>206</v>
+      </c>
+      <c r="H1835" t="s">
+        <v>208</v>
+      </c>
+      <c r="I1835" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1835">
+        <v>1</v>
+      </c>
+      <c r="K1835">
+        <v>1968050</v>
+      </c>
+      <c r="L1835">
+        <v>1968050</v>
+      </c>
+    </row>
+    <row r="1836" spans="1:12">
+      <c r="A1836">
+        <v>1833</v>
+      </c>
+      <c r="B1836">
+        <v>403829</v>
+      </c>
+      <c r="C1836" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1836" t="s">
+        <v>1850</v>
+      </c>
+      <c r="E1836" t="s">
+        <v>1851</v>
+      </c>
+      <c r="F1836" t="s">
+        <v>1852</v>
+      </c>
+      <c r="G1836" t="s">
+        <v>206</v>
+      </c>
+      <c r="H1836" t="s">
+        <v>186</v>
+      </c>
+      <c r="I1836" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1836">
+        <v>1</v>
+      </c>
+      <c r="K1836">
+        <v>39116668</v>
+      </c>
+      <c r="L1836">
+        <v>39116668</v>
+      </c>
+    </row>
+    <row r="1837" spans="1:12">
+      <c r="A1837">
+        <v>1834</v>
+      </c>
+      <c r="B1837">
+        <v>403829</v>
+      </c>
+      <c r="C1837" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1837" t="s">
+        <v>1850</v>
+      </c>
+      <c r="E1837" t="s">
+        <v>1851</v>
+      </c>
+      <c r="F1837" t="s">
+        <v>1852</v>
+      </c>
+      <c r="G1837" t="s">
+        <v>206</v>
+      </c>
+      <c r="H1837" t="s">
+        <v>189</v>
+      </c>
+      <c r="I1837" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1837">
+        <v>1</v>
+      </c>
+      <c r="K1837">
+        <v>488000</v>
+      </c>
+      <c r="L1837">
+        <v>488000</v>
+      </c>
+    </row>
+    <row r="1838" spans="1:12">
+      <c r="A1838">
+        <v>1835</v>
+      </c>
+      <c r="B1838">
+        <v>403829</v>
+      </c>
+      <c r="C1838" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1838" t="s">
+        <v>1850</v>
+      </c>
+      <c r="E1838" t="s">
+        <v>1851</v>
+      </c>
+      <c r="F1838" t="s">
+        <v>1852</v>
+      </c>
+      <c r="G1838" t="s">
+        <v>206</v>
+      </c>
+      <c r="H1838" t="s">
+        <v>191</v>
+      </c>
+      <c r="I1838" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1838">
+        <v>1</v>
+      </c>
+      <c r="K1838">
+        <v>953390</v>
+      </c>
+      <c r="L1838">
+        <v>953390</v>
+      </c>
+    </row>
+    <row r="1839" spans="1:12">
+      <c r="A1839">
+        <v>1836</v>
+      </c>
+      <c r="B1839">
+        <v>403829</v>
+      </c>
+      <c r="C1839" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1839" t="s">
+        <v>1850</v>
+      </c>
+      <c r="E1839" t="s">
+        <v>1851</v>
+      </c>
+      <c r="F1839" t="s">
+        <v>1852</v>
+      </c>
+      <c r="G1839" t="s">
+        <v>206</v>
+      </c>
+      <c r="H1839" t="s">
+        <v>1712</v>
+      </c>
+      <c r="I1839" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1839">
+        <v>1</v>
+      </c>
+      <c r="K1839">
+        <v>581410</v>
+      </c>
+      <c r="L1839">
+        <v>581410</v>
+      </c>
+    </row>
+    <row r="1840" spans="1:12">
+      <c r="A1840">
+        <v>1837</v>
+      </c>
+      <c r="B1840">
+        <v>403829</v>
+      </c>
+      <c r="C1840" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1840" t="s">
+        <v>1853</v>
+      </c>
+      <c r="E1840" t="s">
+        <v>1854</v>
+      </c>
+      <c r="F1840" t="s">
+        <v>1855</v>
+      </c>
+      <c r="G1840" t="s">
+        <v>1856</v>
+      </c>
+      <c r="H1840" t="s">
+        <v>797</v>
+      </c>
+      <c r="I1840" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1840">
+        <v>1</v>
+      </c>
+      <c r="K1840">
+        <v>800000</v>
+      </c>
+      <c r="L1840">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="1841" spans="1:12">
+      <c r="A1841">
+        <v>1838</v>
+      </c>
+      <c r="B1841">
+        <v>403829</v>
+      </c>
+      <c r="C1841" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1841" t="s">
+        <v>1853</v>
+      </c>
+      <c r="E1841" t="s">
+        <v>1857</v>
+      </c>
+      <c r="F1841" t="s">
+        <v>1858</v>
+      </c>
+      <c r="G1841" t="s">
+        <v>1859</v>
+      </c>
+      <c r="H1841" t="s">
+        <v>228</v>
+      </c>
+      <c r="I1841" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1841">
+        <v>1</v>
+      </c>
+      <c r="K1841">
+        <v>21185000</v>
+      </c>
+      <c r="L1841">
+        <v>21185000</v>
+      </c>
+    </row>
+    <row r="1842" spans="1:12">
+      <c r="A1842">
+        <v>1839</v>
+      </c>
+      <c r="B1842">
+        <v>403829</v>
+      </c>
+      <c r="C1842" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1842" t="s">
+        <v>1853</v>
+      </c>
+      <c r="E1842" t="s">
+        <v>1860</v>
+      </c>
+      <c r="F1842" t="s">
+        <v>1861</v>
+      </c>
+      <c r="G1842" t="s">
+        <v>1862</v>
+      </c>
+      <c r="H1842" t="s">
+        <v>768</v>
+      </c>
+      <c r="I1842" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1842">
+        <v>1</v>
+      </c>
+      <c r="K1842">
+        <v>21170500</v>
+      </c>
+      <c r="L1842">
+        <v>21170500</v>
+      </c>
+    </row>
+    <row r="1843" spans="1:12">
+      <c r="A1843">
+        <v>1840</v>
+      </c>
+      <c r="B1843">
+        <v>403829</v>
+      </c>
+      <c r="C1843" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1843" t="s">
+        <v>1863</v>
+      </c>
+      <c r="E1843" t="s">
+        <v>1864</v>
+      </c>
+      <c r="F1843" t="s">
+        <v>1865</v>
+      </c>
+      <c r="G1843" t="s">
+        <v>1866</v>
+      </c>
+      <c r="H1843" t="s">
+        <v>203</v>
+      </c>
+      <c r="I1843" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1843">
+        <v>1</v>
+      </c>
+      <c r="K1843">
+        <v>184486500</v>
+      </c>
+      <c r="L1843">
+        <v>184486500</v>
+      </c>
+    </row>
+    <row r="1844" spans="1:12">
+      <c r="A1844">
+        <v>1841</v>
+      </c>
+      <c r="B1844">
+        <v>403829</v>
+      </c>
+      <c r="C1844" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1844" t="s">
+        <v>1867</v>
+      </c>
+      <c r="E1844" t="s">
+        <v>1868</v>
+      </c>
+      <c r="F1844" t="s">
+        <v>1869</v>
+      </c>
+      <c r="G1844" t="s">
+        <v>1870</v>
+      </c>
+      <c r="H1844" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1844" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1844">
+        <v>1</v>
+      </c>
+      <c r="K1844">
+        <v>3390500</v>
+      </c>
+      <c r="L1844">
+        <v>3390500</v>
+      </c>
+    </row>
+    <row r="1845" spans="1:12">
+      <c r="A1845">
+        <v>1842</v>
+      </c>
+      <c r="B1845">
+        <v>403829</v>
+      </c>
+      <c r="C1845" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1845" t="s">
+        <v>1867</v>
+      </c>
+      <c r="E1845" t="s">
+        <v>1868</v>
+      </c>
+      <c r="F1845" t="s">
+        <v>1869</v>
+      </c>
+      <c r="G1845" t="s">
+        <v>1870</v>
+      </c>
+      <c r="H1845" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1845" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1845">
+        <v>1</v>
+      </c>
+      <c r="K1845">
+        <v>76</v>
+      </c>
+      <c r="L1845">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="1846" spans="1:12">
+      <c r="A1846">
+        <v>1843</v>
+      </c>
+      <c r="B1846">
+        <v>403829</v>
+      </c>
+      <c r="C1846" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1846" t="s">
+        <v>1867</v>
+      </c>
+      <c r="E1846" t="s">
+        <v>1868</v>
+      </c>
+      <c r="F1846" t="s">
+        <v>1869</v>
+      </c>
+      <c r="G1846" t="s">
+        <v>1870</v>
+      </c>
+      <c r="H1846" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1846" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1846">
+        <v>1</v>
+      </c>
+      <c r="K1846">
+        <v>540000</v>
+      </c>
+      <c r="L1846">
+        <v>540000</v>
+      </c>
+    </row>
+    <row r="1847" spans="1:12">
+      <c r="A1847">
+        <v>1844</v>
+      </c>
+      <c r="B1847">
+        <v>403829</v>
+      </c>
+      <c r="C1847" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1847" t="s">
+        <v>1867</v>
+      </c>
+      <c r="E1847" t="s">
+        <v>1868</v>
+      </c>
+      <c r="F1847" t="s">
+        <v>1869</v>
+      </c>
+      <c r="G1847" t="s">
+        <v>1870</v>
+      </c>
+      <c r="H1847" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1847" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1847">
+        <v>1</v>
+      </c>
+      <c r="K1847">
+        <v>72420</v>
+      </c>
+      <c r="L1847">
+        <v>72420</v>
+      </c>
+    </row>
+    <row r="1848" spans="1:12">
+      <c r="A1848">
+        <v>1845</v>
+      </c>
+      <c r="B1848">
+        <v>403829</v>
+      </c>
+      <c r="C1848" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1848" t="s">
+        <v>1867</v>
+      </c>
+      <c r="E1848" t="s">
+        <v>1871</v>
+      </c>
+      <c r="F1848" t="s">
+        <v>1872</v>
+      </c>
+      <c r="G1848" t="s">
+        <v>1873</v>
+      </c>
+      <c r="H1848" t="s">
+        <v>267</v>
+      </c>
+      <c r="I1848" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1848">
+        <v>1</v>
+      </c>
+      <c r="K1848">
+        <v>740000</v>
+      </c>
+      <c r="L1848">
+        <v>740000</v>
+      </c>
+    </row>
+    <row r="1849" spans="1:12">
+      <c r="A1849">
+        <v>1846</v>
+      </c>
+      <c r="B1849">
+        <v>403829</v>
+      </c>
+      <c r="C1849" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1849" t="s">
+        <v>1867</v>
+      </c>
+      <c r="E1849" t="s">
+        <v>1874</v>
+      </c>
+      <c r="F1849" t="s">
+        <v>1875</v>
+      </c>
+      <c r="G1849" t="s">
+        <v>1876</v>
+      </c>
+      <c r="H1849" t="s">
+        <v>272</v>
+      </c>
+      <c r="I1849" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1849">
+        <v>1</v>
+      </c>
+      <c r="K1849">
+        <v>4595150</v>
+      </c>
+      <c r="L1849">
+        <v>4595150</v>
+      </c>
+    </row>
+    <row r="1850" spans="1:12">
+      <c r="A1850">
+        <v>1847</v>
+      </c>
+      <c r="B1850">
+        <v>403829</v>
+      </c>
+      <c r="C1850" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1850" t="s">
+        <v>1867</v>
+      </c>
+      <c r="E1850" t="s">
+        <v>1877</v>
+      </c>
+      <c r="F1850" t="s">
+        <v>1878</v>
+      </c>
+      <c r="G1850" t="s">
+        <v>1879</v>
+      </c>
+      <c r="H1850" t="s">
+        <v>272</v>
+      </c>
+      <c r="I1850" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1850">
+        <v>1</v>
+      </c>
+      <c r="K1850">
+        <v>4595150</v>
+      </c>
+      <c r="L1850">
+        <v>4595150</v>
+      </c>
+    </row>
+    <row r="1851" spans="1:12">
+      <c r="A1851">
+        <v>1848</v>
+      </c>
+      <c r="B1851">
+        <v>403829</v>
+      </c>
+      <c r="C1851" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1851" t="s">
+        <v>1863</v>
+      </c>
+      <c r="E1851" t="s">
+        <v>1880</v>
+      </c>
+      <c r="F1851" t="s">
+        <v>1881</v>
+      </c>
+      <c r="G1851" t="s">
+        <v>1882</v>
+      </c>
+      <c r="H1851" t="s">
+        <v>1883</v>
+      </c>
+      <c r="I1851" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1851">
+        <v>1</v>
+      </c>
+      <c r="K1851">
+        <v>4300000</v>
+      </c>
+      <c r="L1851">
+        <v>4300000</v>
+      </c>
+    </row>
+    <row r="1852" spans="1:12">
+      <c r="A1852">
+        <v>1849</v>
+      </c>
+      <c r="B1852">
+        <v>403829</v>
+      </c>
+      <c r="C1852" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1852" t="s">
+        <v>1863</v>
+      </c>
+      <c r="E1852" t="s">
+        <v>1884</v>
+      </c>
+      <c r="F1852" t="s">
+        <v>1885</v>
+      </c>
+      <c r="G1852" t="s">
+        <v>1886</v>
+      </c>
+      <c r="H1852" t="s">
+        <v>992</v>
+      </c>
+      <c r="I1852" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1852">
+        <v>1</v>
+      </c>
+      <c r="K1852">
+        <v>48790000</v>
+      </c>
+      <c r="L1852">
+        <v>48790000</v>
+      </c>
+    </row>
+    <row r="1853" spans="1:12">
+      <c r="A1853">
+        <v>1850</v>
+      </c>
+      <c r="B1853">
+        <v>403829</v>
+      </c>
+      <c r="C1853" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1853" t="s">
+        <v>1863</v>
+      </c>
+      <c r="E1853" t="s">
+        <v>1887</v>
+      </c>
+      <c r="F1853" t="s">
+        <v>1888</v>
+      </c>
+      <c r="G1853" t="s">
+        <v>1889</v>
+      </c>
+      <c r="H1853" t="s">
+        <v>1890</v>
+      </c>
+      <c r="I1853" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1853">
+        <v>1</v>
+      </c>
+      <c r="K1853">
+        <v>30407000</v>
+      </c>
+      <c r="L1853">
+        <v>30407000</v>
       </c>
     </row>
   </sheetData>

--- a/Database/MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D.xlsx
+++ b/Database/MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1891">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1920">
   <si>
     <t>MONITORING DETAIL TRANSAKSI FA 16 SEGMEN VERSI SP2D</t>
   </si>
@@ -5688,6 +5688,93 @@
   </si>
   <si>
     <t>'403829.023.523111.03212WA.2378EBA.A000000001.00000.2.0252.2.000000.000000.994.002.DC.000280</t>
+  </si>
+  <si>
+    <t>2025-12-23</t>
+  </si>
+  <si>
+    <t>'00556T</t>
+  </si>
+  <si>
+    <t>'259991311455416</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang sesuai Kwitansi No. 61/SPH/TM/xII/2025 Tanggal 8 Desember 2025 berupa Jasa Kepengurusan Turun Daya Listrik dan Perbaikan Panel Listrik Utama Depok</t>
+  </si>
+  <si>
+    <t>2025-12-24</t>
+  </si>
+  <si>
+    <t>'00558T</t>
+  </si>
+  <si>
+    <t>'259991320872105</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang sesuai Kwitansi No 294 Tanggal 19 Desember 2025 berupa belanja Pakaian Lapangan</t>
+  </si>
+  <si>
+    <t>'403829.023.521119.03212WA.2378EBA.A000000001.00000.2.0252.2.000000.000000.994.002.DD.000309</t>
+  </si>
+  <si>
+    <t>'00559T</t>
+  </si>
+  <si>
+    <t>'259991702104495</t>
+  </si>
+  <si>
+    <t>'403829.023.521211.03212WA.2378EBA.A000000001.00000.2.0252.2.000000.000000.994.002.DA.000306</t>
+  </si>
+  <si>
+    <t>'403829.023.523111.03212WA.2378EBA.A000000001.00000.2.0252.2.000000.000000.994.002.DC.000310</t>
+  </si>
+  <si>
+    <t>'403829.023.523121.03212WA.2378EBA.A000000001.00000.2.0252.2.000000.000000.994.002.DC.000307</t>
+  </si>
+  <si>
+    <t>'403829.023.523121.03212WA.2378EBA.A000000001.00000.2.0252.2.000000.000000.994.002.DC.000308</t>
+  </si>
+  <si>
+    <t>'00560T</t>
+  </si>
+  <si>
+    <t>'259991320872993</t>
+  </si>
+  <si>
+    <t>Pembayaran Belanja Barang Sesuai Kwitansi No. 04/SAJ/KW/XII/2025 Tanggal 19 Desember 2025 berupa Pekerjaan Rehabilitasi Ruang Kantor sempur</t>
+  </si>
+  <si>
+    <t>2025-12-30</t>
+  </si>
+  <si>
+    <t>'00561T</t>
+  </si>
+  <si>
+    <t>'259991702134149</t>
+  </si>
+  <si>
+    <t>Pertanggungjawaban Tambahan Uang Persediaan untuk keperluan belanja barang</t>
+  </si>
+  <si>
+    <t>'403829.023.523111.03212WA.2378EBA.A000000001.00000.2.0252.2.000000.000000.994.002.DC.000302</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>'00562T</t>
+  </si>
+  <si>
+    <t>'259991702139947</t>
+  </si>
+  <si>
+    <t>Pertanggungjawaban Tambahan Uang Persediaan untuk keperluan belanja pegawai</t>
+  </si>
+  <si>
+    <t>'00563T</t>
+  </si>
+  <si>
+    <t>'259991702139946</t>
   </si>
 </sst>
 </file>
@@ -6030,7 +6117,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:L1853"/>
+  <dimension ref="A1:L1918"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -76375,6 +76462,2476 @@
       </c>
       <c r="L1853">
         <v>30407000</v>
+      </c>
+    </row>
+    <row r="1854" spans="1:12">
+      <c r="A1854">
+        <v>1851</v>
+      </c>
+      <c r="B1854">
+        <v>403829</v>
+      </c>
+      <c r="C1854" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1854" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E1854" t="s">
+        <v>1892</v>
+      </c>
+      <c r="F1854" t="s">
+        <v>1893</v>
+      </c>
+      <c r="G1854" t="s">
+        <v>1894</v>
+      </c>
+      <c r="H1854" t="s">
+        <v>208</v>
+      </c>
+      <c r="I1854" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1854">
+        <v>1</v>
+      </c>
+      <c r="K1854">
+        <v>10830000</v>
+      </c>
+      <c r="L1854">
+        <v>10830000</v>
+      </c>
+    </row>
+    <row r="1855" spans="1:12">
+      <c r="A1855">
+        <v>1852</v>
+      </c>
+      <c r="B1855">
+        <v>403829</v>
+      </c>
+      <c r="C1855" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1855" t="s">
+        <v>1895</v>
+      </c>
+      <c r="E1855" t="s">
+        <v>1896</v>
+      </c>
+      <c r="F1855" t="s">
+        <v>1897</v>
+      </c>
+      <c r="G1855" t="s">
+        <v>1898</v>
+      </c>
+      <c r="H1855" t="s">
+        <v>1899</v>
+      </c>
+      <c r="I1855" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1855">
+        <v>1</v>
+      </c>
+      <c r="K1855">
+        <v>19800000</v>
+      </c>
+      <c r="L1855">
+        <v>19800000</v>
+      </c>
+    </row>
+    <row r="1856" spans="1:12">
+      <c r="A1856">
+        <v>1853</v>
+      </c>
+      <c r="B1856">
+        <v>403829</v>
+      </c>
+      <c r="C1856" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1856" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E1856" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F1856" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G1856" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1856" t="s">
+        <v>173</v>
+      </c>
+      <c r="I1856" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1856">
+        <v>1</v>
+      </c>
+      <c r="K1856">
+        <v>2629333</v>
+      </c>
+      <c r="L1856">
+        <v>2629333</v>
+      </c>
+    </row>
+    <row r="1857" spans="1:12">
+      <c r="A1857">
+        <v>1854</v>
+      </c>
+      <c r="B1857">
+        <v>403829</v>
+      </c>
+      <c r="C1857" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1857" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E1857" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F1857" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G1857" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1857" t="s">
+        <v>386</v>
+      </c>
+      <c r="I1857" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1857">
+        <v>1</v>
+      </c>
+      <c r="K1857">
+        <v>600000</v>
+      </c>
+      <c r="L1857">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="1858" spans="1:12">
+      <c r="A1858">
+        <v>1855</v>
+      </c>
+      <c r="B1858">
+        <v>403829</v>
+      </c>
+      <c r="C1858" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1858" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E1858" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F1858" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G1858" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1858" t="s">
+        <v>159</v>
+      </c>
+      <c r="I1858" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1858">
+        <v>1</v>
+      </c>
+      <c r="K1858">
+        <v>360000</v>
+      </c>
+      <c r="L1858">
+        <v>360000</v>
+      </c>
+    </row>
+    <row r="1859" spans="1:12">
+      <c r="A1859">
+        <v>1856</v>
+      </c>
+      <c r="B1859">
+        <v>403829</v>
+      </c>
+      <c r="C1859" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1859" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E1859" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F1859" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G1859" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1859" t="s">
+        <v>174</v>
+      </c>
+      <c r="I1859" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1859">
+        <v>1</v>
+      </c>
+      <c r="K1859">
+        <v>1026500</v>
+      </c>
+      <c r="L1859">
+        <v>1026500</v>
+      </c>
+    </row>
+    <row r="1860" spans="1:12">
+      <c r="A1860">
+        <v>1857</v>
+      </c>
+      <c r="B1860">
+        <v>403829</v>
+      </c>
+      <c r="C1860" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1860" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E1860" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F1860" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G1860" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1860" t="s">
+        <v>252</v>
+      </c>
+      <c r="I1860" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1860">
+        <v>1</v>
+      </c>
+      <c r="K1860">
+        <v>808000</v>
+      </c>
+      <c r="L1860">
+        <v>808000</v>
+      </c>
+    </row>
+    <row r="1861" spans="1:12">
+      <c r="A1861">
+        <v>1858</v>
+      </c>
+      <c r="B1861">
+        <v>403829</v>
+      </c>
+      <c r="C1861" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1861" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E1861" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F1861" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G1861" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1861" t="s">
+        <v>175</v>
+      </c>
+      <c r="I1861" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1861">
+        <v>1</v>
+      </c>
+      <c r="K1861">
+        <v>4228000</v>
+      </c>
+      <c r="L1861">
+        <v>4228000</v>
+      </c>
+    </row>
+    <row r="1862" spans="1:12">
+      <c r="A1862">
+        <v>1859</v>
+      </c>
+      <c r="B1862">
+        <v>403829</v>
+      </c>
+      <c r="C1862" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1862" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E1862" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F1862" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G1862" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1862" t="s">
+        <v>1902</v>
+      </c>
+      <c r="I1862" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1862">
+        <v>1</v>
+      </c>
+      <c r="K1862">
+        <v>2750000</v>
+      </c>
+      <c r="L1862">
+        <v>2750000</v>
+      </c>
+    </row>
+    <row r="1863" spans="1:12">
+      <c r="A1863">
+        <v>1860</v>
+      </c>
+      <c r="B1863">
+        <v>403829</v>
+      </c>
+      <c r="C1863" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1863" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E1863" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F1863" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G1863" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1863" t="s">
+        <v>176</v>
+      </c>
+      <c r="I1863" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1863">
+        <v>1</v>
+      </c>
+      <c r="K1863">
+        <v>12065000</v>
+      </c>
+      <c r="L1863">
+        <v>12065000</v>
+      </c>
+    </row>
+    <row r="1864" spans="1:12">
+      <c r="A1864">
+        <v>1861</v>
+      </c>
+      <c r="B1864">
+        <v>403829</v>
+      </c>
+      <c r="C1864" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1864" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E1864" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F1864" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G1864" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1864" t="s">
+        <v>1040</v>
+      </c>
+      <c r="I1864" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1864">
+        <v>1</v>
+      </c>
+      <c r="K1864">
+        <v>10000000</v>
+      </c>
+      <c r="L1864">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="1865" spans="1:12">
+      <c r="A1865">
+        <v>1862</v>
+      </c>
+      <c r="B1865">
+        <v>403829</v>
+      </c>
+      <c r="C1865" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1865" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E1865" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F1865" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G1865" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1865" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1865" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1865">
+        <v>1</v>
+      </c>
+      <c r="K1865">
+        <v>1034800</v>
+      </c>
+      <c r="L1865">
+        <v>1034800</v>
+      </c>
+    </row>
+    <row r="1866" spans="1:12">
+      <c r="A1866">
+        <v>1863</v>
+      </c>
+      <c r="B1866">
+        <v>403829</v>
+      </c>
+      <c r="C1866" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1866" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E1866" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F1866" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G1866" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1866" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1866" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1866">
+        <v>1</v>
+      </c>
+      <c r="K1866">
+        <v>1047400</v>
+      </c>
+      <c r="L1866">
+        <v>1047400</v>
+      </c>
+    </row>
+    <row r="1867" spans="1:12">
+      <c r="A1867">
+        <v>1864</v>
+      </c>
+      <c r="B1867">
+        <v>403829</v>
+      </c>
+      <c r="C1867" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1867" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E1867" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F1867" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G1867" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1867" t="s">
+        <v>207</v>
+      </c>
+      <c r="I1867" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1867">
+        <v>1</v>
+      </c>
+      <c r="K1867">
+        <v>170065</v>
+      </c>
+      <c r="L1867">
+        <v>170065</v>
+      </c>
+    </row>
+    <row r="1868" spans="1:12">
+      <c r="A1868">
+        <v>1865</v>
+      </c>
+      <c r="B1868">
+        <v>403829</v>
+      </c>
+      <c r="C1868" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1868" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E1868" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F1868" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G1868" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1868" t="s">
+        <v>178</v>
+      </c>
+      <c r="I1868" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1868">
+        <v>1</v>
+      </c>
+      <c r="K1868">
+        <v>9468528</v>
+      </c>
+      <c r="L1868">
+        <v>9468528</v>
+      </c>
+    </row>
+    <row r="1869" spans="1:12">
+      <c r="A1869">
+        <v>1866</v>
+      </c>
+      <c r="B1869">
+        <v>403829</v>
+      </c>
+      <c r="C1869" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1869" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E1869" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F1869" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G1869" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1869" t="s">
+        <v>1710</v>
+      </c>
+      <c r="I1869" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1869">
+        <v>1</v>
+      </c>
+      <c r="K1869">
+        <v>22953312</v>
+      </c>
+      <c r="L1869">
+        <v>22953312</v>
+      </c>
+    </row>
+    <row r="1870" spans="1:12">
+      <c r="A1870">
+        <v>1867</v>
+      </c>
+      <c r="B1870">
+        <v>403829</v>
+      </c>
+      <c r="C1870" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1870" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E1870" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F1870" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G1870" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1870" t="s">
+        <v>1711</v>
+      </c>
+      <c r="I1870" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1870">
+        <v>1</v>
+      </c>
+      <c r="K1870">
+        <v>4629928</v>
+      </c>
+      <c r="L1870">
+        <v>4629928</v>
+      </c>
+    </row>
+    <row r="1871" spans="1:12">
+      <c r="A1871">
+        <v>1868</v>
+      </c>
+      <c r="B1871">
+        <v>403829</v>
+      </c>
+      <c r="C1871" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1871" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E1871" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F1871" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G1871" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1871" t="s">
+        <v>181</v>
+      </c>
+      <c r="I1871" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1871">
+        <v>1</v>
+      </c>
+      <c r="K1871">
+        <v>14735500</v>
+      </c>
+      <c r="L1871">
+        <v>14735500</v>
+      </c>
+    </row>
+    <row r="1872" spans="1:12">
+      <c r="A1872">
+        <v>1869</v>
+      </c>
+      <c r="B1872">
+        <v>403829</v>
+      </c>
+      <c r="C1872" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1872" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E1872" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F1872" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G1872" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1872" t="s">
+        <v>182</v>
+      </c>
+      <c r="I1872" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1872">
+        <v>1</v>
+      </c>
+      <c r="K1872">
+        <v>375000</v>
+      </c>
+      <c r="L1872">
+        <v>375000</v>
+      </c>
+    </row>
+    <row r="1873" spans="1:12">
+      <c r="A1873">
+        <v>1870</v>
+      </c>
+      <c r="B1873">
+        <v>403829</v>
+      </c>
+      <c r="C1873" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1873" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E1873" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F1873" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G1873" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1873" t="s">
+        <v>184</v>
+      </c>
+      <c r="I1873" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1873">
+        <v>1</v>
+      </c>
+      <c r="K1873">
+        <v>1800000</v>
+      </c>
+      <c r="L1873">
+        <v>1800000</v>
+      </c>
+    </row>
+    <row r="1874" spans="1:12">
+      <c r="A1874">
+        <v>1871</v>
+      </c>
+      <c r="B1874">
+        <v>403829</v>
+      </c>
+      <c r="C1874" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1874" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E1874" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F1874" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G1874" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1874" t="s">
+        <v>1903</v>
+      </c>
+      <c r="I1874" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1874">
+        <v>1</v>
+      </c>
+      <c r="K1874">
+        <v>3332500</v>
+      </c>
+      <c r="L1874">
+        <v>3332500</v>
+      </c>
+    </row>
+    <row r="1875" spans="1:12">
+      <c r="A1875">
+        <v>1872</v>
+      </c>
+      <c r="B1875">
+        <v>403829</v>
+      </c>
+      <c r="C1875" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1875" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E1875" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F1875" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G1875" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1875" t="s">
+        <v>185</v>
+      </c>
+      <c r="I1875" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1875">
+        <v>1</v>
+      </c>
+      <c r="K1875">
+        <v>2330000</v>
+      </c>
+      <c r="L1875">
+        <v>2330000</v>
+      </c>
+    </row>
+    <row r="1876" spans="1:12">
+      <c r="A1876">
+        <v>1873</v>
+      </c>
+      <c r="B1876">
+        <v>403829</v>
+      </c>
+      <c r="C1876" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1876" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E1876" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F1876" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G1876" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1876" t="s">
+        <v>1378</v>
+      </c>
+      <c r="I1876" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1876">
+        <v>1</v>
+      </c>
+      <c r="K1876">
+        <v>2500000</v>
+      </c>
+      <c r="L1876">
+        <v>2500000</v>
+      </c>
+    </row>
+    <row r="1877" spans="1:12">
+      <c r="A1877">
+        <v>1874</v>
+      </c>
+      <c r="B1877">
+        <v>403829</v>
+      </c>
+      <c r="C1877" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1877" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E1877" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F1877" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G1877" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1877" t="s">
+        <v>186</v>
+      </c>
+      <c r="I1877" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1877">
+        <v>1</v>
+      </c>
+      <c r="K1877">
+        <v>6936853</v>
+      </c>
+      <c r="L1877">
+        <v>6936853</v>
+      </c>
+    </row>
+    <row r="1878" spans="1:12">
+      <c r="A1878">
+        <v>1875</v>
+      </c>
+      <c r="B1878">
+        <v>403829</v>
+      </c>
+      <c r="C1878" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1878" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E1878" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F1878" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G1878" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1878" t="s">
+        <v>187</v>
+      </c>
+      <c r="I1878" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1878">
+        <v>1</v>
+      </c>
+      <c r="K1878">
+        <v>90000</v>
+      </c>
+      <c r="L1878">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="1879" spans="1:12">
+      <c r="A1879">
+        <v>1876</v>
+      </c>
+      <c r="B1879">
+        <v>403829</v>
+      </c>
+      <c r="C1879" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1879" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E1879" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F1879" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G1879" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1879" t="s">
+        <v>189</v>
+      </c>
+      <c r="I1879" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1879">
+        <v>1</v>
+      </c>
+      <c r="K1879">
+        <v>1897941</v>
+      </c>
+      <c r="L1879">
+        <v>1897941</v>
+      </c>
+    </row>
+    <row r="1880" spans="1:12">
+      <c r="A1880">
+        <v>1877</v>
+      </c>
+      <c r="B1880">
+        <v>403829</v>
+      </c>
+      <c r="C1880" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1880" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E1880" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F1880" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G1880" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1880" t="s">
+        <v>191</v>
+      </c>
+      <c r="I1880" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1880">
+        <v>1</v>
+      </c>
+      <c r="K1880">
+        <v>7088340</v>
+      </c>
+      <c r="L1880">
+        <v>7088340</v>
+      </c>
+    </row>
+    <row r="1881" spans="1:12">
+      <c r="A1881">
+        <v>1878</v>
+      </c>
+      <c r="B1881">
+        <v>403829</v>
+      </c>
+      <c r="C1881" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1881" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E1881" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F1881" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G1881" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1881" t="s">
+        <v>1789</v>
+      </c>
+      <c r="I1881" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1881">
+        <v>1</v>
+      </c>
+      <c r="K1881">
+        <v>700000</v>
+      </c>
+      <c r="L1881">
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="1882" spans="1:12">
+      <c r="A1882">
+        <v>1879</v>
+      </c>
+      <c r="B1882">
+        <v>403829</v>
+      </c>
+      <c r="C1882" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1882" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E1882" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F1882" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G1882" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1882" t="s">
+        <v>1904</v>
+      </c>
+      <c r="I1882" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1882">
+        <v>1</v>
+      </c>
+      <c r="K1882">
+        <v>3955000</v>
+      </c>
+      <c r="L1882">
+        <v>3955000</v>
+      </c>
+    </row>
+    <row r="1883" spans="1:12">
+      <c r="A1883">
+        <v>1880</v>
+      </c>
+      <c r="B1883">
+        <v>403829</v>
+      </c>
+      <c r="C1883" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1883" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E1883" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F1883" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G1883" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1883" t="s">
+        <v>1905</v>
+      </c>
+      <c r="I1883" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1883">
+        <v>1</v>
+      </c>
+      <c r="K1883">
+        <v>488000</v>
+      </c>
+      <c r="L1883">
+        <v>488000</v>
+      </c>
+    </row>
+    <row r="1884" spans="1:12">
+      <c r="A1884">
+        <v>1881</v>
+      </c>
+      <c r="B1884">
+        <v>403829</v>
+      </c>
+      <c r="C1884" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1884" t="s">
+        <v>1895</v>
+      </c>
+      <c r="E1884" t="s">
+        <v>1906</v>
+      </c>
+      <c r="F1884" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G1884" t="s">
+        <v>1908</v>
+      </c>
+      <c r="H1884" t="s">
+        <v>116</v>
+      </c>
+      <c r="I1884" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1884">
+        <v>1</v>
+      </c>
+      <c r="K1884">
+        <v>49648000</v>
+      </c>
+      <c r="L1884">
+        <v>49648000</v>
+      </c>
+    </row>
+    <row r="1885" spans="1:12">
+      <c r="A1885">
+        <v>1882</v>
+      </c>
+      <c r="B1885">
+        <v>403829</v>
+      </c>
+      <c r="C1885" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1885" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E1885" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F1885" t="s">
+        <v>1911</v>
+      </c>
+      <c r="G1885" t="s">
+        <v>1912</v>
+      </c>
+      <c r="H1885" t="s">
+        <v>173</v>
+      </c>
+      <c r="I1885" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1885">
+        <v>1</v>
+      </c>
+      <c r="K1885">
+        <v>7166612</v>
+      </c>
+      <c r="L1885">
+        <v>7166612</v>
+      </c>
+    </row>
+    <row r="1886" spans="1:12">
+      <c r="A1886">
+        <v>1883</v>
+      </c>
+      <c r="B1886">
+        <v>403829</v>
+      </c>
+      <c r="C1886" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1886" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E1886" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F1886" t="s">
+        <v>1911</v>
+      </c>
+      <c r="G1886" t="s">
+        <v>1912</v>
+      </c>
+      <c r="H1886" t="s">
+        <v>174</v>
+      </c>
+      <c r="I1886" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1886">
+        <v>1</v>
+      </c>
+      <c r="K1886">
+        <v>940500</v>
+      </c>
+      <c r="L1886">
+        <v>940500</v>
+      </c>
+    </row>
+    <row r="1887" spans="1:12">
+      <c r="A1887">
+        <v>1884</v>
+      </c>
+      <c r="B1887">
+        <v>403829</v>
+      </c>
+      <c r="C1887" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1887" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E1887" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F1887" t="s">
+        <v>1911</v>
+      </c>
+      <c r="G1887" t="s">
+        <v>1912</v>
+      </c>
+      <c r="H1887" t="s">
+        <v>175</v>
+      </c>
+      <c r="I1887" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1887">
+        <v>1</v>
+      </c>
+      <c r="K1887">
+        <v>6150000</v>
+      </c>
+      <c r="L1887">
+        <v>6150000</v>
+      </c>
+    </row>
+    <row r="1888" spans="1:12">
+      <c r="A1888">
+        <v>1885</v>
+      </c>
+      <c r="B1888">
+        <v>403829</v>
+      </c>
+      <c r="C1888" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1888" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E1888" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F1888" t="s">
+        <v>1911</v>
+      </c>
+      <c r="G1888" t="s">
+        <v>1912</v>
+      </c>
+      <c r="H1888" t="s">
+        <v>1902</v>
+      </c>
+      <c r="I1888" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1888">
+        <v>1</v>
+      </c>
+      <c r="K1888">
+        <v>3025000</v>
+      </c>
+      <c r="L1888">
+        <v>3025000</v>
+      </c>
+    </row>
+    <row r="1889" spans="1:12">
+      <c r="A1889">
+        <v>1886</v>
+      </c>
+      <c r="B1889">
+        <v>403829</v>
+      </c>
+      <c r="C1889" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1889" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E1889" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F1889" t="s">
+        <v>1911</v>
+      </c>
+      <c r="G1889" t="s">
+        <v>1912</v>
+      </c>
+      <c r="H1889" t="s">
+        <v>254</v>
+      </c>
+      <c r="I1889" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1889">
+        <v>1</v>
+      </c>
+      <c r="K1889">
+        <v>5035000</v>
+      </c>
+      <c r="L1889">
+        <v>5035000</v>
+      </c>
+    </row>
+    <row r="1890" spans="1:12">
+      <c r="A1890">
+        <v>1887</v>
+      </c>
+      <c r="B1890">
+        <v>403829</v>
+      </c>
+      <c r="C1890" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1890" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E1890" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F1890" t="s">
+        <v>1911</v>
+      </c>
+      <c r="G1890" t="s">
+        <v>1912</v>
+      </c>
+      <c r="H1890" t="s">
+        <v>1526</v>
+      </c>
+      <c r="I1890" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1890">
+        <v>1</v>
+      </c>
+      <c r="K1890">
+        <v>1689500</v>
+      </c>
+      <c r="L1890">
+        <v>1689500</v>
+      </c>
+    </row>
+    <row r="1891" spans="1:12">
+      <c r="A1891">
+        <v>1888</v>
+      </c>
+      <c r="B1891">
+        <v>403829</v>
+      </c>
+      <c r="C1891" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1891" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E1891" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F1891" t="s">
+        <v>1911</v>
+      </c>
+      <c r="G1891" t="s">
+        <v>1912</v>
+      </c>
+      <c r="H1891" t="s">
+        <v>181</v>
+      </c>
+      <c r="I1891" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1891">
+        <v>1</v>
+      </c>
+      <c r="K1891">
+        <v>1040000</v>
+      </c>
+      <c r="L1891">
+        <v>1040000</v>
+      </c>
+    </row>
+    <row r="1892" spans="1:12">
+      <c r="A1892">
+        <v>1889</v>
+      </c>
+      <c r="B1892">
+        <v>403829</v>
+      </c>
+      <c r="C1892" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1892" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E1892" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F1892" t="s">
+        <v>1911</v>
+      </c>
+      <c r="G1892" t="s">
+        <v>1912</v>
+      </c>
+      <c r="H1892" t="s">
+        <v>182</v>
+      </c>
+      <c r="I1892" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1892">
+        <v>1</v>
+      </c>
+      <c r="K1892">
+        <v>220920</v>
+      </c>
+      <c r="L1892">
+        <v>220920</v>
+      </c>
+    </row>
+    <row r="1893" spans="1:12">
+      <c r="A1893">
+        <v>1890</v>
+      </c>
+      <c r="B1893">
+        <v>403829</v>
+      </c>
+      <c r="C1893" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1893" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E1893" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F1893" t="s">
+        <v>1911</v>
+      </c>
+      <c r="G1893" t="s">
+        <v>1912</v>
+      </c>
+      <c r="H1893" t="s">
+        <v>116</v>
+      </c>
+      <c r="I1893" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1893">
+        <v>1</v>
+      </c>
+      <c r="K1893">
+        <v>44000000</v>
+      </c>
+      <c r="L1893">
+        <v>44000000</v>
+      </c>
+    </row>
+    <row r="1894" spans="1:12">
+      <c r="A1894">
+        <v>1891</v>
+      </c>
+      <c r="B1894">
+        <v>403829</v>
+      </c>
+      <c r="C1894" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1894" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E1894" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F1894" t="s">
+        <v>1911</v>
+      </c>
+      <c r="G1894" t="s">
+        <v>1912</v>
+      </c>
+      <c r="H1894" t="s">
+        <v>128</v>
+      </c>
+      <c r="I1894" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1894">
+        <v>1</v>
+      </c>
+      <c r="K1894">
+        <v>4395000</v>
+      </c>
+      <c r="L1894">
+        <v>4395000</v>
+      </c>
+    </row>
+    <row r="1895" spans="1:12">
+      <c r="A1895">
+        <v>1892</v>
+      </c>
+      <c r="B1895">
+        <v>403829</v>
+      </c>
+      <c r="C1895" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1895" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E1895" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F1895" t="s">
+        <v>1911</v>
+      </c>
+      <c r="G1895" t="s">
+        <v>1912</v>
+      </c>
+      <c r="H1895" t="s">
+        <v>184</v>
+      </c>
+      <c r="I1895" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1895">
+        <v>1</v>
+      </c>
+      <c r="K1895">
+        <v>600000</v>
+      </c>
+      <c r="L1895">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="1896" spans="1:12">
+      <c r="A1896">
+        <v>1893</v>
+      </c>
+      <c r="B1896">
+        <v>403829</v>
+      </c>
+      <c r="C1896" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1896" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E1896" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F1896" t="s">
+        <v>1911</v>
+      </c>
+      <c r="G1896" t="s">
+        <v>1912</v>
+      </c>
+      <c r="H1896" t="s">
+        <v>1913</v>
+      </c>
+      <c r="I1896" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1896">
+        <v>1</v>
+      </c>
+      <c r="K1896">
+        <v>5695000</v>
+      </c>
+      <c r="L1896">
+        <v>5695000</v>
+      </c>
+    </row>
+    <row r="1897" spans="1:12">
+      <c r="A1897">
+        <v>1894</v>
+      </c>
+      <c r="B1897">
+        <v>403829</v>
+      </c>
+      <c r="C1897" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1897" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E1897" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F1897" t="s">
+        <v>1911</v>
+      </c>
+      <c r="G1897" t="s">
+        <v>1912</v>
+      </c>
+      <c r="H1897" t="s">
+        <v>1726</v>
+      </c>
+      <c r="I1897" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1897">
+        <v>1</v>
+      </c>
+      <c r="K1897">
+        <v>4000000</v>
+      </c>
+      <c r="L1897">
+        <v>4000000</v>
+      </c>
+    </row>
+    <row r="1898" spans="1:12">
+      <c r="A1898">
+        <v>1895</v>
+      </c>
+      <c r="B1898">
+        <v>403829</v>
+      </c>
+      <c r="C1898" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1898" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E1898" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F1898" t="s">
+        <v>1911</v>
+      </c>
+      <c r="G1898" t="s">
+        <v>1912</v>
+      </c>
+      <c r="H1898" t="s">
+        <v>185</v>
+      </c>
+      <c r="I1898" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1898">
+        <v>1</v>
+      </c>
+      <c r="K1898">
+        <v>3220000</v>
+      </c>
+      <c r="L1898">
+        <v>3220000</v>
+      </c>
+    </row>
+    <row r="1899" spans="1:12">
+      <c r="A1899">
+        <v>1896</v>
+      </c>
+      <c r="B1899">
+        <v>403829</v>
+      </c>
+      <c r="C1899" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1899" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E1899" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F1899" t="s">
+        <v>1911</v>
+      </c>
+      <c r="G1899" t="s">
+        <v>1912</v>
+      </c>
+      <c r="H1899" t="s">
+        <v>208</v>
+      </c>
+      <c r="I1899" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1899">
+        <v>1</v>
+      </c>
+      <c r="K1899">
+        <v>2310000</v>
+      </c>
+      <c r="L1899">
+        <v>2310000</v>
+      </c>
+    </row>
+    <row r="1900" spans="1:12">
+      <c r="A1900">
+        <v>1897</v>
+      </c>
+      <c r="B1900">
+        <v>403829</v>
+      </c>
+      <c r="C1900" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1900" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E1900" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F1900" t="s">
+        <v>1911</v>
+      </c>
+      <c r="G1900" t="s">
+        <v>1912</v>
+      </c>
+      <c r="H1900" t="s">
+        <v>186</v>
+      </c>
+      <c r="I1900" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1900">
+        <v>1</v>
+      </c>
+      <c r="K1900">
+        <v>4273102</v>
+      </c>
+      <c r="L1900">
+        <v>4273102</v>
+      </c>
+    </row>
+    <row r="1901" spans="1:12">
+      <c r="A1901">
+        <v>1898</v>
+      </c>
+      <c r="B1901">
+        <v>403829</v>
+      </c>
+      <c r="C1901" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1901" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E1901" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F1901" t="s">
+        <v>1911</v>
+      </c>
+      <c r="G1901" t="s">
+        <v>1912</v>
+      </c>
+      <c r="H1901" t="s">
+        <v>187</v>
+      </c>
+      <c r="I1901" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1901">
+        <v>1</v>
+      </c>
+      <c r="K1901">
+        <v>135000</v>
+      </c>
+      <c r="L1901">
+        <v>135000</v>
+      </c>
+    </row>
+    <row r="1902" spans="1:12">
+      <c r="A1902">
+        <v>1899</v>
+      </c>
+      <c r="B1902">
+        <v>403829</v>
+      </c>
+      <c r="C1902" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1902" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E1902" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F1902" t="s">
+        <v>1911</v>
+      </c>
+      <c r="G1902" t="s">
+        <v>1912</v>
+      </c>
+      <c r="H1902" t="s">
+        <v>259</v>
+      </c>
+      <c r="I1902" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1902">
+        <v>1</v>
+      </c>
+      <c r="K1902">
+        <v>7986000</v>
+      </c>
+      <c r="L1902">
+        <v>7986000</v>
+      </c>
+    </row>
+    <row r="1903" spans="1:12">
+      <c r="A1903">
+        <v>1900</v>
+      </c>
+      <c r="B1903">
+        <v>403829</v>
+      </c>
+      <c r="C1903" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1903" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E1903" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F1903" t="s">
+        <v>1911</v>
+      </c>
+      <c r="G1903" t="s">
+        <v>1912</v>
+      </c>
+      <c r="H1903" t="s">
+        <v>188</v>
+      </c>
+      <c r="I1903" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1903">
+        <v>1</v>
+      </c>
+      <c r="K1903">
+        <v>1000000</v>
+      </c>
+      <c r="L1903">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="1904" spans="1:12">
+      <c r="A1904">
+        <v>1901</v>
+      </c>
+      <c r="B1904">
+        <v>403829</v>
+      </c>
+      <c r="C1904" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1904" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E1904" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F1904" t="s">
+        <v>1911</v>
+      </c>
+      <c r="G1904" t="s">
+        <v>1912</v>
+      </c>
+      <c r="H1904" t="s">
+        <v>189</v>
+      </c>
+      <c r="I1904" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1904">
+        <v>1</v>
+      </c>
+      <c r="K1904">
+        <v>980000</v>
+      </c>
+      <c r="L1904">
+        <v>980000</v>
+      </c>
+    </row>
+    <row r="1905" spans="1:12">
+      <c r="A1905">
+        <v>1902</v>
+      </c>
+      <c r="B1905">
+        <v>403829</v>
+      </c>
+      <c r="C1905" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1905" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E1905" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F1905" t="s">
+        <v>1911</v>
+      </c>
+      <c r="G1905" t="s">
+        <v>1912</v>
+      </c>
+      <c r="H1905" t="s">
+        <v>190</v>
+      </c>
+      <c r="I1905" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1905">
+        <v>1</v>
+      </c>
+      <c r="K1905">
+        <v>500000</v>
+      </c>
+      <c r="L1905">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="1906" spans="1:12">
+      <c r="A1906">
+        <v>1903</v>
+      </c>
+      <c r="B1906">
+        <v>403829</v>
+      </c>
+      <c r="C1906" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1906" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E1906" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F1906" t="s">
+        <v>1911</v>
+      </c>
+      <c r="G1906" t="s">
+        <v>1912</v>
+      </c>
+      <c r="H1906" t="s">
+        <v>191</v>
+      </c>
+      <c r="I1906" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1906">
+        <v>1</v>
+      </c>
+      <c r="K1906">
+        <v>2170726</v>
+      </c>
+      <c r="L1906">
+        <v>2170726</v>
+      </c>
+    </row>
+    <row r="1907" spans="1:12">
+      <c r="A1907">
+        <v>1904</v>
+      </c>
+      <c r="B1907">
+        <v>403829</v>
+      </c>
+      <c r="C1907" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1907" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E1907" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F1907" t="s">
+        <v>1911</v>
+      </c>
+      <c r="G1907" t="s">
+        <v>1912</v>
+      </c>
+      <c r="H1907" t="s">
+        <v>1712</v>
+      </c>
+      <c r="I1907" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1907">
+        <v>1</v>
+      </c>
+      <c r="K1907">
+        <v>85000</v>
+      </c>
+      <c r="L1907">
+        <v>85000</v>
+      </c>
+    </row>
+    <row r="1908" spans="1:12">
+      <c r="A1908">
+        <v>1905</v>
+      </c>
+      <c r="B1908">
+        <v>403829</v>
+      </c>
+      <c r="C1908" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1908" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E1908" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F1908" t="s">
+        <v>1911</v>
+      </c>
+      <c r="G1908" t="s">
+        <v>1912</v>
+      </c>
+      <c r="H1908" t="s">
+        <v>1905</v>
+      </c>
+      <c r="I1908" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1908">
+        <v>1</v>
+      </c>
+      <c r="K1908">
+        <v>510000</v>
+      </c>
+      <c r="L1908">
+        <v>510000</v>
+      </c>
+    </row>
+    <row r="1909" spans="1:12">
+      <c r="A1909">
+        <v>1906</v>
+      </c>
+      <c r="B1909">
+        <v>403829</v>
+      </c>
+      <c r="C1909" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1909" t="s">
+        <v>1914</v>
+      </c>
+      <c r="E1909" t="s">
+        <v>1915</v>
+      </c>
+      <c r="F1909" t="s">
+        <v>1916</v>
+      </c>
+      <c r="G1909" t="s">
+        <v>1917</v>
+      </c>
+      <c r="H1909" t="s">
+        <v>1685</v>
+      </c>
+      <c r="I1909" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1909">
+        <v>1</v>
+      </c>
+      <c r="K1909">
+        <v>8085000</v>
+      </c>
+      <c r="L1909">
+        <v>8085000</v>
+      </c>
+    </row>
+    <row r="1910" spans="1:12">
+      <c r="A1910">
+        <v>1907</v>
+      </c>
+      <c r="B1910">
+        <v>403829</v>
+      </c>
+      <c r="C1910" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1910" t="s">
+        <v>1914</v>
+      </c>
+      <c r="E1910" t="s">
+        <v>1915</v>
+      </c>
+      <c r="F1910" t="s">
+        <v>1916</v>
+      </c>
+      <c r="G1910" t="s">
+        <v>1917</v>
+      </c>
+      <c r="H1910" t="s">
+        <v>1686</v>
+      </c>
+      <c r="I1910" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1910">
+        <v>1</v>
+      </c>
+      <c r="K1910">
+        <v>20831000</v>
+      </c>
+      <c r="L1910">
+        <v>20831000</v>
+      </c>
+    </row>
+    <row r="1911" spans="1:12">
+      <c r="A1911">
+        <v>1908</v>
+      </c>
+      <c r="B1911">
+        <v>403829</v>
+      </c>
+      <c r="C1911" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1911" t="s">
+        <v>1914</v>
+      </c>
+      <c r="E1911" t="s">
+        <v>1915</v>
+      </c>
+      <c r="F1911" t="s">
+        <v>1916</v>
+      </c>
+      <c r="G1911" t="s">
+        <v>1917</v>
+      </c>
+      <c r="H1911" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1911" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1911">
+        <v>1</v>
+      </c>
+      <c r="K1911">
+        <v>23310000</v>
+      </c>
+      <c r="L1911">
+        <v>23310000</v>
+      </c>
+    </row>
+    <row r="1912" spans="1:12">
+      <c r="A1912">
+        <v>1909</v>
+      </c>
+      <c r="B1912">
+        <v>403829</v>
+      </c>
+      <c r="C1912" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1912" t="s">
+        <v>1914</v>
+      </c>
+      <c r="E1912" t="s">
+        <v>1915</v>
+      </c>
+      <c r="F1912" t="s">
+        <v>1916</v>
+      </c>
+      <c r="G1912" t="s">
+        <v>1917</v>
+      </c>
+      <c r="H1912" t="s">
+        <v>234</v>
+      </c>
+      <c r="I1912" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1912">
+        <v>1</v>
+      </c>
+      <c r="K1912">
+        <v>232471000</v>
+      </c>
+      <c r="L1912">
+        <v>232471000</v>
+      </c>
+    </row>
+    <row r="1913" spans="1:12">
+      <c r="A1913">
+        <v>1910</v>
+      </c>
+      <c r="B1913">
+        <v>403829</v>
+      </c>
+      <c r="C1913" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1913" t="s">
+        <v>1914</v>
+      </c>
+      <c r="E1913" t="s">
+        <v>1918</v>
+      </c>
+      <c r="F1913" t="s">
+        <v>1919</v>
+      </c>
+      <c r="G1913" t="s">
+        <v>1917</v>
+      </c>
+      <c r="H1913" t="s">
+        <v>241</v>
+      </c>
+      <c r="I1913" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1913">
+        <v>1</v>
+      </c>
+      <c r="K1913">
+        <v>1470000</v>
+      </c>
+      <c r="L1913">
+        <v>1470000</v>
+      </c>
+    </row>
+    <row r="1914" spans="1:12">
+      <c r="A1914">
+        <v>1911</v>
+      </c>
+      <c r="B1914">
+        <v>403829</v>
+      </c>
+      <c r="C1914" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1914" t="s">
+        <v>1914</v>
+      </c>
+      <c r="E1914" t="s">
+        <v>1918</v>
+      </c>
+      <c r="F1914" t="s">
+        <v>1919</v>
+      </c>
+      <c r="G1914" t="s">
+        <v>1917</v>
+      </c>
+      <c r="H1914" t="s">
+        <v>149</v>
+      </c>
+      <c r="I1914" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1914">
+        <v>1</v>
+      </c>
+      <c r="K1914">
+        <v>22126000</v>
+      </c>
+      <c r="L1914">
+        <v>22126000</v>
+      </c>
+    </row>
+    <row r="1915" spans="1:12">
+      <c r="A1915">
+        <v>1912</v>
+      </c>
+      <c r="B1915">
+        <v>403829</v>
+      </c>
+      <c r="C1915" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1915" t="s">
+        <v>1914</v>
+      </c>
+      <c r="E1915" t="s">
+        <v>1918</v>
+      </c>
+      <c r="F1915" t="s">
+        <v>1919</v>
+      </c>
+      <c r="G1915" t="s">
+        <v>1917</v>
+      </c>
+      <c r="H1915" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1915" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1915">
+        <v>1</v>
+      </c>
+      <c r="K1915">
+        <v>1435000</v>
+      </c>
+      <c r="L1915">
+        <v>1435000</v>
+      </c>
+    </row>
+    <row r="1916" spans="1:12">
+      <c r="A1916">
+        <v>1913</v>
+      </c>
+      <c r="B1916">
+        <v>403829</v>
+      </c>
+      <c r="C1916" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1916" t="s">
+        <v>1914</v>
+      </c>
+      <c r="E1916" t="s">
+        <v>1918</v>
+      </c>
+      <c r="F1916" t="s">
+        <v>1919</v>
+      </c>
+      <c r="G1916" t="s">
+        <v>1917</v>
+      </c>
+      <c r="H1916" t="s">
+        <v>266</v>
+      </c>
+      <c r="I1916" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1916">
+        <v>1</v>
+      </c>
+      <c r="K1916">
+        <v>21385000</v>
+      </c>
+      <c r="L1916">
+        <v>21385000</v>
+      </c>
+    </row>
+    <row r="1917" spans="1:12">
+      <c r="A1917">
+        <v>1914</v>
+      </c>
+      <c r="B1917">
+        <v>403829</v>
+      </c>
+      <c r="C1917" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1917" t="s">
+        <v>1914</v>
+      </c>
+      <c r="E1917" t="s">
+        <v>1918</v>
+      </c>
+      <c r="F1917" t="s">
+        <v>1919</v>
+      </c>
+      <c r="G1917" t="s">
+        <v>1917</v>
+      </c>
+      <c r="H1917" t="s">
+        <v>267</v>
+      </c>
+      <c r="I1917" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1917">
+        <v>1</v>
+      </c>
+      <c r="K1917">
+        <v>169164000</v>
+      </c>
+      <c r="L1917">
+        <v>169164000</v>
+      </c>
+    </row>
+    <row r="1918" spans="1:12">
+      <c r="A1918">
+        <v>1915</v>
+      </c>
+      <c r="B1918">
+        <v>403829</v>
+      </c>
+      <c r="C1918" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1918" t="s">
+        <v>1914</v>
+      </c>
+      <c r="E1918" t="s">
+        <v>1918</v>
+      </c>
+      <c r="F1918" t="s">
+        <v>1919</v>
+      </c>
+      <c r="G1918" t="s">
+        <v>1917</v>
+      </c>
+      <c r="H1918" t="s">
+        <v>268</v>
+      </c>
+      <c r="I1918" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1918">
+        <v>1</v>
+      </c>
+      <c r="K1918">
+        <v>38745000</v>
+      </c>
+      <c r="L1918">
+        <v>38745000</v>
       </c>
     </row>
   </sheetData>
